--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8017" uniqueCount="3985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8021" uniqueCount="3987">
   <si>
     <t>연번</t>
   </si>
@@ -3662,12 +3662,12 @@
     <t>조선백호</t>
   </si>
   <si>
+    <t>인천광역시 중구 개항로96번길 11(1,2층 경동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 개항로96번길 11(1층 경동)</t>
   </si>
   <si>
-    <t>인천광역시 중구 개항로96번길 11(1,2층 경동)</t>
-  </si>
-  <si>
     <t>주윤 상차림</t>
   </si>
   <si>
@@ -3809,12 +3809,12 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
-    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
     <t>꿈꾸는카페-혜윰도그파크점</t>
   </si>
   <si>
@@ -4007,12 +4007,12 @@
     <t>송경솥밥</t>
   </si>
   <si>
+    <t>광주광역시 동구 동명로14번길 19-8(2층 동명동)</t>
+  </si>
+  <si>
     <t>광주광역시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
   </si>
   <si>
-    <t>광주광역시 동구 동명로14번길 19-8(2층 동명동)</t>
-  </si>
-  <si>
     <t>쉘터커피로스터스</t>
   </si>
   <si>
@@ -9600,6 +9600,12 @@
   </si>
   <si>
     <t>경상남도 거제시 장목면 거제북로 1073(1층)</t>
+  </si>
+  <si>
+    <t>워크오프(work off)</t>
+  </si>
+  <si>
+    <t>경상남도 양산시 물금읍 화합3길 16(101호)</t>
   </si>
   <si>
     <t>이시마표고버섯식당농원</t>
@@ -39544,7 +39550,7 @@
         <v>1616.0</v>
       </c>
       <c r="B1617" t="s" s="3">
-        <v>892</v>
+        <v>3212</v>
       </c>
       <c r="C1617" t="s" s="2">
         <v>6</v>
@@ -39553,7 +39559,7 @@
         <v>3044</v>
       </c>
       <c r="E1617" t="s" s="3">
-        <v>3212</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="1618" ht="36.0" customHeight="true">
@@ -39561,7 +39567,7 @@
         <v>1617.0</v>
       </c>
       <c r="B1618" t="s" s="3">
-        <v>3213</v>
+        <v>892</v>
       </c>
       <c r="C1618" t="s" s="2">
         <v>6</v>
@@ -40193,7 +40199,7 @@
         <v>3287</v>
       </c>
       <c r="C1655" t="s" s="2">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="D1655" t="s" s="2">
         <v>3044</v>
@@ -40675,7 +40681,7 @@
         <v>3044</v>
       </c>
       <c r="E1683" t="s" s="3">
-        <v>3228</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="1684" ht="36.0" customHeight="true">
@@ -40683,7 +40689,7 @@
         <v>1683.0</v>
       </c>
       <c r="B1684" t="s" s="3">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="C1684" t="s" s="2">
         <v>580</v>
@@ -40692,7 +40698,7 @@
         <v>3044</v>
       </c>
       <c r="E1684" t="s" s="3">
-        <v>3345</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="1685" ht="36.0" customHeight="true">
@@ -41281,7 +41287,7 @@
         <v>3414</v>
       </c>
       <c r="C1719" t="s" s="2">
-        <v>751</v>
+        <v>580</v>
       </c>
       <c r="D1719" t="s" s="2">
         <v>3044</v>
@@ -41366,13 +41372,13 @@
         <v>3424</v>
       </c>
       <c r="C1724" t="s" s="2">
-        <v>6</v>
+        <v>751</v>
       </c>
       <c r="D1724" t="s" s="2">
+        <v>3044</v>
+      </c>
+      <c r="E1724" t="s" s="3">
         <v>3425</v>
-      </c>
-      <c r="E1724" t="s" s="3">
-        <v>3426</v>
       </c>
     </row>
     <row r="1725" ht="36.0" customHeight="true">
@@ -41380,13 +41386,13 @@
         <v>1724.0</v>
       </c>
       <c r="B1725" t="s" s="3">
+        <v>3426</v>
+      </c>
+      <c r="C1725" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1725" t="s" s="2">
         <v>3427</v>
-      </c>
-      <c r="C1725" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1725" t="s" s="2">
-        <v>3425</v>
       </c>
       <c r="E1725" t="s" s="3">
         <v>3428</v>
@@ -41403,7 +41409,7 @@
         <v>6</v>
       </c>
       <c r="D1726" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1726" t="s" s="3">
         <v>3430</v>
@@ -41420,7 +41426,7 @@
         <v>6</v>
       </c>
       <c r="D1727" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1727" t="s" s="3">
         <v>3432</v>
@@ -41437,7 +41443,7 @@
         <v>6</v>
       </c>
       <c r="D1728" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1728" t="s" s="3">
         <v>3434</v>
@@ -41454,7 +41460,7 @@
         <v>6</v>
       </c>
       <c r="D1729" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1729" t="s" s="3">
         <v>3436</v>
@@ -41471,7 +41477,7 @@
         <v>6</v>
       </c>
       <c r="D1730" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1730" t="s" s="3">
         <v>3438</v>
@@ -41488,7 +41494,7 @@
         <v>6</v>
       </c>
       <c r="D1731" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1731" t="s" s="3">
         <v>3440</v>
@@ -41505,7 +41511,7 @@
         <v>6</v>
       </c>
       <c r="D1732" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1732" t="s" s="3">
         <v>3442</v>
@@ -41522,7 +41528,7 @@
         <v>6</v>
       </c>
       <c r="D1733" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1733" t="s" s="3">
         <v>3444</v>
@@ -41539,7 +41545,7 @@
         <v>6</v>
       </c>
       <c r="D1734" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1734" t="s" s="3">
         <v>3446</v>
@@ -41556,7 +41562,7 @@
         <v>6</v>
       </c>
       <c r="D1735" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1735" t="s" s="3">
         <v>3448</v>
@@ -41573,7 +41579,7 @@
         <v>6</v>
       </c>
       <c r="D1736" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1736" t="s" s="3">
         <v>3450</v>
@@ -41590,7 +41596,7 @@
         <v>6</v>
       </c>
       <c r="D1737" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1737" t="s" s="3">
         <v>3452</v>
@@ -41607,7 +41613,7 @@
         <v>6</v>
       </c>
       <c r="D1738" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1738" t="s" s="3">
         <v>3454</v>
@@ -41624,7 +41630,7 @@
         <v>6</v>
       </c>
       <c r="D1739" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1739" t="s" s="3">
         <v>3456</v>
@@ -41641,7 +41647,7 @@
         <v>6</v>
       </c>
       <c r="D1740" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1740" t="s" s="3">
         <v>3458</v>
@@ -41658,7 +41664,7 @@
         <v>6</v>
       </c>
       <c r="D1741" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1741" t="s" s="3">
         <v>3460</v>
@@ -41675,7 +41681,7 @@
         <v>6</v>
       </c>
       <c r="D1742" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1742" t="s" s="3">
         <v>3462</v>
@@ -41692,7 +41698,7 @@
         <v>6</v>
       </c>
       <c r="D1743" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1743" t="s" s="3">
         <v>3464</v>
@@ -41709,7 +41715,7 @@
         <v>6</v>
       </c>
       <c r="D1744" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1744" t="s" s="3">
         <v>3466</v>
@@ -41726,7 +41732,7 @@
         <v>6</v>
       </c>
       <c r="D1745" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1745" t="s" s="3">
         <v>3468</v>
@@ -41743,7 +41749,7 @@
         <v>6</v>
       </c>
       <c r="D1746" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1746" t="s" s="3">
         <v>3470</v>
@@ -41760,7 +41766,7 @@
         <v>6</v>
       </c>
       <c r="D1747" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1747" t="s" s="3">
         <v>3472</v>
@@ -41777,7 +41783,7 @@
         <v>6</v>
       </c>
       <c r="D1748" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1748" t="s" s="3">
         <v>3474</v>
@@ -41794,7 +41800,7 @@
         <v>6</v>
       </c>
       <c r="D1749" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1749" t="s" s="3">
         <v>3476</v>
@@ -41811,7 +41817,7 @@
         <v>6</v>
       </c>
       <c r="D1750" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1750" t="s" s="3">
         <v>3478</v>
@@ -41828,7 +41834,7 @@
         <v>6</v>
       </c>
       <c r="D1751" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1751" t="s" s="3">
         <v>3480</v>
@@ -41845,7 +41851,7 @@
         <v>6</v>
       </c>
       <c r="D1752" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1752" t="s" s="3">
         <v>3482</v>
@@ -41862,7 +41868,7 @@
         <v>6</v>
       </c>
       <c r="D1753" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1753" t="s" s="3">
         <v>3484</v>
@@ -41879,7 +41885,7 @@
         <v>6</v>
       </c>
       <c r="D1754" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1754" t="s" s="3">
         <v>3486</v>
@@ -41896,7 +41902,7 @@
         <v>6</v>
       </c>
       <c r="D1755" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1755" t="s" s="3">
         <v>3488</v>
@@ -41913,7 +41919,7 @@
         <v>6</v>
       </c>
       <c r="D1756" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1756" t="s" s="3">
         <v>3490</v>
@@ -41930,7 +41936,7 @@
         <v>6</v>
       </c>
       <c r="D1757" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1757" t="s" s="3">
         <v>3492</v>
@@ -41947,7 +41953,7 @@
         <v>6</v>
       </c>
       <c r="D1758" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1758" t="s" s="3">
         <v>3494</v>
@@ -41964,7 +41970,7 @@
         <v>6</v>
       </c>
       <c r="D1759" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1759" t="s" s="3">
         <v>3496</v>
@@ -41981,7 +41987,7 @@
         <v>6</v>
       </c>
       <c r="D1760" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1760" t="s" s="3">
         <v>3498</v>
@@ -41998,7 +42004,7 @@
         <v>6</v>
       </c>
       <c r="D1761" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1761" t="s" s="3">
         <v>3500</v>
@@ -42015,7 +42021,7 @@
         <v>6</v>
       </c>
       <c r="D1762" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1762" t="s" s="3">
         <v>3502</v>
@@ -42032,7 +42038,7 @@
         <v>6</v>
       </c>
       <c r="D1763" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1763" t="s" s="3">
         <v>3504</v>
@@ -42049,7 +42055,7 @@
         <v>6</v>
       </c>
       <c r="D1764" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1764" t="s" s="3">
         <v>3506</v>
@@ -42066,7 +42072,7 @@
         <v>6</v>
       </c>
       <c r="D1765" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1765" t="s" s="3">
         <v>3508</v>
@@ -42083,7 +42089,7 @@
         <v>6</v>
       </c>
       <c r="D1766" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1766" t="s" s="3">
         <v>3510</v>
@@ -42100,7 +42106,7 @@
         <v>6</v>
       </c>
       <c r="D1767" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1767" t="s" s="3">
         <v>3512</v>
@@ -42117,7 +42123,7 @@
         <v>6</v>
       </c>
       <c r="D1768" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1768" t="s" s="3">
         <v>3514</v>
@@ -42134,7 +42140,7 @@
         <v>6</v>
       </c>
       <c r="D1769" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1769" t="s" s="3">
         <v>3516</v>
@@ -42151,7 +42157,7 @@
         <v>6</v>
       </c>
       <c r="D1770" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1770" t="s" s="3">
         <v>3518</v>
@@ -42165,10 +42171,10 @@
         <v>3519</v>
       </c>
       <c r="C1771" t="s" s="2">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="D1771" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1771" t="s" s="3">
         <v>3520</v>
@@ -42185,7 +42191,7 @@
         <v>580</v>
       </c>
       <c r="D1772" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1772" t="s" s="3">
         <v>3522</v>
@@ -42202,7 +42208,7 @@
         <v>580</v>
       </c>
       <c r="D1773" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1773" t="s" s="3">
         <v>3524</v>
@@ -42219,7 +42225,7 @@
         <v>580</v>
       </c>
       <c r="D1774" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1774" t="s" s="3">
         <v>3526</v>
@@ -42236,7 +42242,7 @@
         <v>580</v>
       </c>
       <c r="D1775" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1775" t="s" s="3">
         <v>3528</v>
@@ -42253,7 +42259,7 @@
         <v>580</v>
       </c>
       <c r="D1776" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1776" t="s" s="3">
         <v>3530</v>
@@ -42270,7 +42276,7 @@
         <v>580</v>
       </c>
       <c r="D1777" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1777" t="s" s="3">
         <v>3532</v>
@@ -42287,7 +42293,7 @@
         <v>580</v>
       </c>
       <c r="D1778" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1778" t="s" s="3">
         <v>3534</v>
@@ -42304,7 +42310,7 @@
         <v>580</v>
       </c>
       <c r="D1779" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1779" t="s" s="3">
         <v>3536</v>
@@ -42321,7 +42327,7 @@
         <v>580</v>
       </c>
       <c r="D1780" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1780" t="s" s="3">
         <v>3538</v>
@@ -42338,7 +42344,7 @@
         <v>580</v>
       </c>
       <c r="D1781" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1781" t="s" s="3">
         <v>3540</v>
@@ -42355,7 +42361,7 @@
         <v>580</v>
       </c>
       <c r="D1782" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1782" t="s" s="3">
         <v>3542</v>
@@ -42372,7 +42378,7 @@
         <v>580</v>
       </c>
       <c r="D1783" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1783" t="s" s="3">
         <v>3544</v>
@@ -42389,7 +42395,7 @@
         <v>580</v>
       </c>
       <c r="D1784" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1784" t="s" s="3">
         <v>3546</v>
@@ -42406,7 +42412,7 @@
         <v>580</v>
       </c>
       <c r="D1785" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1785" t="s" s="3">
         <v>3548</v>
@@ -42423,7 +42429,7 @@
         <v>580</v>
       </c>
       <c r="D1786" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1786" t="s" s="3">
         <v>3550</v>
@@ -42440,7 +42446,7 @@
         <v>580</v>
       </c>
       <c r="D1787" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1787" t="s" s="3">
         <v>3552</v>
@@ -42457,7 +42463,7 @@
         <v>580</v>
       </c>
       <c r="D1788" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1788" t="s" s="3">
         <v>3554</v>
@@ -42474,7 +42480,7 @@
         <v>580</v>
       </c>
       <c r="D1789" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1789" t="s" s="3">
         <v>3556</v>
@@ -42491,7 +42497,7 @@
         <v>580</v>
       </c>
       <c r="D1790" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1790" t="s" s="3">
         <v>3558</v>
@@ -42508,7 +42514,7 @@
         <v>580</v>
       </c>
       <c r="D1791" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1791" t="s" s="3">
         <v>3560</v>
@@ -42525,7 +42531,7 @@
         <v>580</v>
       </c>
       <c r="D1792" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1792" t="s" s="3">
         <v>3562</v>
@@ -42542,7 +42548,7 @@
         <v>580</v>
       </c>
       <c r="D1793" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1793" t="s" s="3">
         <v>3564</v>
@@ -42559,7 +42565,7 @@
         <v>580</v>
       </c>
       <c r="D1794" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1794" t="s" s="3">
         <v>3566</v>
@@ -42576,7 +42582,7 @@
         <v>580</v>
       </c>
       <c r="D1795" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1795" t="s" s="3">
         <v>3568</v>
@@ -42593,7 +42599,7 @@
         <v>580</v>
       </c>
       <c r="D1796" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1796" t="s" s="3">
         <v>3570</v>
@@ -42610,7 +42616,7 @@
         <v>580</v>
       </c>
       <c r="D1797" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1797" t="s" s="3">
         <v>3572</v>
@@ -42627,7 +42633,7 @@
         <v>580</v>
       </c>
       <c r="D1798" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1798" t="s" s="3">
         <v>3574</v>
@@ -42644,7 +42650,7 @@
         <v>580</v>
       </c>
       <c r="D1799" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1799" t="s" s="3">
         <v>3576</v>
@@ -42661,7 +42667,7 @@
         <v>580</v>
       </c>
       <c r="D1800" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1800" t="s" s="3">
         <v>3578</v>
@@ -42678,7 +42684,7 @@
         <v>580</v>
       </c>
       <c r="D1801" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1801" t="s" s="3">
         <v>3580</v>
@@ -42695,7 +42701,7 @@
         <v>580</v>
       </c>
       <c r="D1802" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1802" t="s" s="3">
         <v>3582</v>
@@ -42712,7 +42718,7 @@
         <v>580</v>
       </c>
       <c r="D1803" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1803" t="s" s="3">
         <v>3584</v>
@@ -42729,7 +42735,7 @@
         <v>580</v>
       </c>
       <c r="D1804" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1804" t="s" s="3">
         <v>3586</v>
@@ -42743,10 +42749,10 @@
         <v>3587</v>
       </c>
       <c r="C1805" t="s" s="2">
-        <v>751</v>
+        <v>580</v>
       </c>
       <c r="D1805" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1805" t="s" s="3">
         <v>3588</v>
@@ -42763,7 +42769,7 @@
         <v>751</v>
       </c>
       <c r="D1806" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1806" t="s" s="3">
         <v>3590</v>
@@ -42780,7 +42786,7 @@
         <v>751</v>
       </c>
       <c r="D1807" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1807" t="s" s="3">
         <v>3592</v>
@@ -42797,7 +42803,7 @@
         <v>751</v>
       </c>
       <c r="D1808" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1808" t="s" s="3">
         <v>3594</v>
@@ -42814,7 +42820,7 @@
         <v>751</v>
       </c>
       <c r="D1809" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1809" t="s" s="3">
         <v>3596</v>
@@ -42831,7 +42837,7 @@
         <v>751</v>
       </c>
       <c r="D1810" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1810" t="s" s="3">
         <v>3598</v>
@@ -42848,7 +42854,7 @@
         <v>751</v>
       </c>
       <c r="D1811" t="s" s="2">
-        <v>3425</v>
+        <v>3427</v>
       </c>
       <c r="E1811" t="s" s="3">
         <v>3600</v>
@@ -42862,13 +42868,13 @@
         <v>3601</v>
       </c>
       <c r="C1812" t="s" s="2">
-        <v>6</v>
+        <v>751</v>
       </c>
       <c r="D1812" t="s" s="2">
+        <v>3427</v>
+      </c>
+      <c r="E1812" t="s" s="3">
         <v>3602</v>
-      </c>
-      <c r="E1812" t="s" s="3">
-        <v>3603</v>
       </c>
     </row>
     <row r="1813" ht="36.0" customHeight="true">
@@ -42876,13 +42882,13 @@
         <v>1812.0</v>
       </c>
       <c r="B1813" t="s" s="3">
+        <v>3603</v>
+      </c>
+      <c r="C1813" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1813" t="s" s="2">
         <v>3604</v>
-      </c>
-      <c r="C1813" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1813" t="s" s="2">
-        <v>3602</v>
       </c>
       <c r="E1813" t="s" s="3">
         <v>3605</v>
@@ -42899,7 +42905,7 @@
         <v>6</v>
       </c>
       <c r="D1814" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1814" t="s" s="3">
         <v>3607</v>
@@ -42916,7 +42922,7 @@
         <v>6</v>
       </c>
       <c r="D1815" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1815" t="s" s="3">
         <v>3609</v>
@@ -42933,7 +42939,7 @@
         <v>6</v>
       </c>
       <c r="D1816" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1816" t="s" s="3">
         <v>3611</v>
@@ -42950,7 +42956,7 @@
         <v>6</v>
       </c>
       <c r="D1817" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1817" t="s" s="3">
         <v>3613</v>
@@ -42967,7 +42973,7 @@
         <v>6</v>
       </c>
       <c r="D1818" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1818" t="s" s="3">
         <v>3615</v>
@@ -42984,7 +42990,7 @@
         <v>6</v>
       </c>
       <c r="D1819" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1819" t="s" s="3">
         <v>3617</v>
@@ -43001,7 +43007,7 @@
         <v>6</v>
       </c>
       <c r="D1820" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1820" t="s" s="3">
         <v>3619</v>
@@ -43018,7 +43024,7 @@
         <v>6</v>
       </c>
       <c r="D1821" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1821" t="s" s="3">
         <v>3621</v>
@@ -43035,7 +43041,7 @@
         <v>6</v>
       </c>
       <c r="D1822" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1822" t="s" s="3">
         <v>3623</v>
@@ -43052,7 +43058,7 @@
         <v>6</v>
       </c>
       <c r="D1823" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1823" t="s" s="3">
         <v>3625</v>
@@ -43069,7 +43075,7 @@
         <v>6</v>
       </c>
       <c r="D1824" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1824" t="s" s="3">
         <v>3627</v>
@@ -43086,7 +43092,7 @@
         <v>6</v>
       </c>
       <c r="D1825" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1825" t="s" s="3">
         <v>3629</v>
@@ -43103,7 +43109,7 @@
         <v>6</v>
       </c>
       <c r="D1826" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1826" t="s" s="3">
         <v>3631</v>
@@ -43120,7 +43126,7 @@
         <v>6</v>
       </c>
       <c r="D1827" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1827" t="s" s="3">
         <v>3633</v>
@@ -43137,7 +43143,7 @@
         <v>6</v>
       </c>
       <c r="D1828" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1828" t="s" s="3">
         <v>3635</v>
@@ -43154,7 +43160,7 @@
         <v>6</v>
       </c>
       <c r="D1829" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1829" t="s" s="3">
         <v>3637</v>
@@ -43171,7 +43177,7 @@
         <v>6</v>
       </c>
       <c r="D1830" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1830" t="s" s="3">
         <v>3639</v>
@@ -43188,7 +43194,7 @@
         <v>6</v>
       </c>
       <c r="D1831" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1831" t="s" s="3">
         <v>3641</v>
@@ -43205,7 +43211,7 @@
         <v>6</v>
       </c>
       <c r="D1832" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1832" t="s" s="3">
         <v>3643</v>
@@ -43222,7 +43228,7 @@
         <v>6</v>
       </c>
       <c r="D1833" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1833" t="s" s="3">
         <v>3645</v>
@@ -43239,7 +43245,7 @@
         <v>6</v>
       </c>
       <c r="D1834" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1834" t="s" s="3">
         <v>3647</v>
@@ -43256,7 +43262,7 @@
         <v>6</v>
       </c>
       <c r="D1835" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1835" t="s" s="3">
         <v>3649</v>
@@ -43273,7 +43279,7 @@
         <v>6</v>
       </c>
       <c r="D1836" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1836" t="s" s="3">
         <v>3651</v>
@@ -43290,7 +43296,7 @@
         <v>6</v>
       </c>
       <c r="D1837" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1837" t="s" s="3">
         <v>3653</v>
@@ -43307,7 +43313,7 @@
         <v>6</v>
       </c>
       <c r="D1838" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1838" t="s" s="3">
         <v>3655</v>
@@ -43324,7 +43330,7 @@
         <v>6</v>
       </c>
       <c r="D1839" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1839" t="s" s="3">
         <v>3657</v>
@@ -43341,7 +43347,7 @@
         <v>6</v>
       </c>
       <c r="D1840" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1840" t="s" s="3">
         <v>3659</v>
@@ -43358,7 +43364,7 @@
         <v>6</v>
       </c>
       <c r="D1841" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1841" t="s" s="3">
         <v>3661</v>
@@ -43375,7 +43381,7 @@
         <v>6</v>
       </c>
       <c r="D1842" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1842" t="s" s="3">
         <v>3663</v>
@@ -43392,7 +43398,7 @@
         <v>6</v>
       </c>
       <c r="D1843" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1843" t="s" s="3">
         <v>3665</v>
@@ -43409,7 +43415,7 @@
         <v>6</v>
       </c>
       <c r="D1844" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1844" t="s" s="3">
         <v>3667</v>
@@ -43426,7 +43432,7 @@
         <v>6</v>
       </c>
       <c r="D1845" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1845" t="s" s="3">
         <v>3669</v>
@@ -43443,7 +43449,7 @@
         <v>6</v>
       </c>
       <c r="D1846" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1846" t="s" s="3">
         <v>3671</v>
@@ -43460,7 +43466,7 @@
         <v>6</v>
       </c>
       <c r="D1847" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1847" t="s" s="3">
         <v>3673</v>
@@ -43477,7 +43483,7 @@
         <v>6</v>
       </c>
       <c r="D1848" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1848" t="s" s="3">
         <v>3675</v>
@@ -43494,7 +43500,7 @@
         <v>6</v>
       </c>
       <c r="D1849" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1849" t="s" s="3">
         <v>3677</v>
@@ -43511,7 +43517,7 @@
         <v>6</v>
       </c>
       <c r="D1850" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1850" t="s" s="3">
         <v>3679</v>
@@ -43528,7 +43534,7 @@
         <v>6</v>
       </c>
       <c r="D1851" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1851" t="s" s="3">
         <v>3681</v>
@@ -43545,7 +43551,7 @@
         <v>6</v>
       </c>
       <c r="D1852" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1852" t="s" s="3">
         <v>3683</v>
@@ -43562,7 +43568,7 @@
         <v>6</v>
       </c>
       <c r="D1853" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1853" t="s" s="3">
         <v>3685</v>
@@ -43579,7 +43585,7 @@
         <v>6</v>
       </c>
       <c r="D1854" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1854" t="s" s="3">
         <v>3687</v>
@@ -43596,7 +43602,7 @@
         <v>6</v>
       </c>
       <c r="D1855" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1855" t="s" s="3">
         <v>3689</v>
@@ -43613,7 +43619,7 @@
         <v>6</v>
       </c>
       <c r="D1856" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1856" t="s" s="3">
         <v>3691</v>
@@ -43630,7 +43636,7 @@
         <v>6</v>
       </c>
       <c r="D1857" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1857" t="s" s="3">
         <v>3693</v>
@@ -43647,7 +43653,7 @@
         <v>6</v>
       </c>
       <c r="D1858" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1858" t="s" s="3">
         <v>3695</v>
@@ -43664,7 +43670,7 @@
         <v>6</v>
       </c>
       <c r="D1859" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1859" t="s" s="3">
         <v>3697</v>
@@ -43681,7 +43687,7 @@
         <v>6</v>
       </c>
       <c r="D1860" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1860" t="s" s="3">
         <v>3699</v>
@@ -43698,7 +43704,7 @@
         <v>6</v>
       </c>
       <c r="D1861" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1861" t="s" s="3">
         <v>3701</v>
@@ -43715,7 +43721,7 @@
         <v>6</v>
       </c>
       <c r="D1862" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1862" t="s" s="3">
         <v>3703</v>
@@ -43732,7 +43738,7 @@
         <v>6</v>
       </c>
       <c r="D1863" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1863" t="s" s="3">
         <v>3705</v>
@@ -43749,7 +43755,7 @@
         <v>6</v>
       </c>
       <c r="D1864" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1864" t="s" s="3">
         <v>3707</v>
@@ -43766,7 +43772,7 @@
         <v>6</v>
       </c>
       <c r="D1865" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1865" t="s" s="3">
         <v>3709</v>
@@ -43783,7 +43789,7 @@
         <v>6</v>
       </c>
       <c r="D1866" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1866" t="s" s="3">
         <v>3711</v>
@@ -43800,7 +43806,7 @@
         <v>6</v>
       </c>
       <c r="D1867" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1867" t="s" s="3">
         <v>3713</v>
@@ -43817,7 +43823,7 @@
         <v>6</v>
       </c>
       <c r="D1868" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1868" t="s" s="3">
         <v>3715</v>
@@ -43834,7 +43840,7 @@
         <v>6</v>
       </c>
       <c r="D1869" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1869" t="s" s="3">
         <v>3717</v>
@@ -43851,7 +43857,7 @@
         <v>6</v>
       </c>
       <c r="D1870" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1870" t="s" s="3">
         <v>3719</v>
@@ -43868,7 +43874,7 @@
         <v>6</v>
       </c>
       <c r="D1871" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1871" t="s" s="3">
         <v>3721</v>
@@ -43885,7 +43891,7 @@
         <v>6</v>
       </c>
       <c r="D1872" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1872" t="s" s="3">
         <v>3723</v>
@@ -43902,7 +43908,7 @@
         <v>6</v>
       </c>
       <c r="D1873" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1873" t="s" s="3">
         <v>3725</v>
@@ -43919,7 +43925,7 @@
         <v>6</v>
       </c>
       <c r="D1874" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1874" t="s" s="3">
         <v>3727</v>
@@ -43936,7 +43942,7 @@
         <v>6</v>
       </c>
       <c r="D1875" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1875" t="s" s="3">
         <v>3729</v>
@@ -43953,7 +43959,7 @@
         <v>6</v>
       </c>
       <c r="D1876" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1876" t="s" s="3">
         <v>3731</v>
@@ -43970,7 +43976,7 @@
         <v>6</v>
       </c>
       <c r="D1877" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1877" t="s" s="3">
         <v>3733</v>
@@ -43987,7 +43993,7 @@
         <v>6</v>
       </c>
       <c r="D1878" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1878" t="s" s="3">
         <v>3735</v>
@@ -44004,7 +44010,7 @@
         <v>6</v>
       </c>
       <c r="D1879" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1879" t="s" s="3">
         <v>3737</v>
@@ -44021,7 +44027,7 @@
         <v>6</v>
       </c>
       <c r="D1880" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1880" t="s" s="3">
         <v>3739</v>
@@ -44038,7 +44044,7 @@
         <v>6</v>
       </c>
       <c r="D1881" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1881" t="s" s="3">
         <v>3741</v>
@@ -44055,7 +44061,7 @@
         <v>6</v>
       </c>
       <c r="D1882" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1882" t="s" s="3">
         <v>3743</v>
@@ -44072,7 +44078,7 @@
         <v>6</v>
       </c>
       <c r="D1883" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1883" t="s" s="3">
         <v>3745</v>
@@ -44089,7 +44095,7 @@
         <v>6</v>
       </c>
       <c r="D1884" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1884" t="s" s="3">
         <v>3747</v>
@@ -44106,7 +44112,7 @@
         <v>6</v>
       </c>
       <c r="D1885" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1885" t="s" s="3">
         <v>3749</v>
@@ -44123,7 +44129,7 @@
         <v>6</v>
       </c>
       <c r="D1886" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1886" t="s" s="3">
         <v>3751</v>
@@ -44140,7 +44146,7 @@
         <v>6</v>
       </c>
       <c r="D1887" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1887" t="s" s="3">
         <v>3753</v>
@@ -44157,7 +44163,7 @@
         <v>6</v>
       </c>
       <c r="D1888" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1888" t="s" s="3">
         <v>3755</v>
@@ -44174,7 +44180,7 @@
         <v>6</v>
       </c>
       <c r="D1889" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1889" t="s" s="3">
         <v>3757</v>
@@ -44191,7 +44197,7 @@
         <v>6</v>
       </c>
       <c r="D1890" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1890" t="s" s="3">
         <v>3759</v>
@@ -44208,7 +44214,7 @@
         <v>6</v>
       </c>
       <c r="D1891" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1891" t="s" s="3">
         <v>3761</v>
@@ -44225,7 +44231,7 @@
         <v>6</v>
       </c>
       <c r="D1892" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1892" t="s" s="3">
         <v>3763</v>
@@ -44242,7 +44248,7 @@
         <v>6</v>
       </c>
       <c r="D1893" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1893" t="s" s="3">
         <v>3765</v>
@@ -44259,7 +44265,7 @@
         <v>6</v>
       </c>
       <c r="D1894" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1894" t="s" s="3">
         <v>3767</v>
@@ -44276,7 +44282,7 @@
         <v>6</v>
       </c>
       <c r="D1895" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1895" t="s" s="3">
         <v>3769</v>
@@ -44293,7 +44299,7 @@
         <v>6</v>
       </c>
       <c r="D1896" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1896" t="s" s="3">
         <v>3771</v>
@@ -44310,7 +44316,7 @@
         <v>6</v>
       </c>
       <c r="D1897" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1897" t="s" s="3">
         <v>3773</v>
@@ -44327,7 +44333,7 @@
         <v>6</v>
       </c>
       <c r="D1898" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1898" t="s" s="3">
         <v>3775</v>
@@ -44344,7 +44350,7 @@
         <v>6</v>
       </c>
       <c r="D1899" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1899" t="s" s="3">
         <v>3777</v>
@@ -44361,7 +44367,7 @@
         <v>6</v>
       </c>
       <c r="D1900" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1900" t="s" s="3">
         <v>3779</v>
@@ -44378,7 +44384,7 @@
         <v>6</v>
       </c>
       <c r="D1901" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1901" t="s" s="3">
         <v>3781</v>
@@ -44395,7 +44401,7 @@
         <v>6</v>
       </c>
       <c r="D1902" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1902" t="s" s="3">
         <v>3783</v>
@@ -44412,7 +44418,7 @@
         <v>6</v>
       </c>
       <c r="D1903" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1903" t="s" s="3">
         <v>3785</v>
@@ -44429,7 +44435,7 @@
         <v>6</v>
       </c>
       <c r="D1904" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1904" t="s" s="3">
         <v>3787</v>
@@ -44446,7 +44452,7 @@
         <v>6</v>
       </c>
       <c r="D1905" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1905" t="s" s="3">
         <v>3789</v>
@@ -44463,7 +44469,7 @@
         <v>6</v>
       </c>
       <c r="D1906" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1906" t="s" s="3">
         <v>3791</v>
@@ -44480,7 +44486,7 @@
         <v>6</v>
       </c>
       <c r="D1907" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1907" t="s" s="3">
         <v>3793</v>
@@ -44497,7 +44503,7 @@
         <v>6</v>
       </c>
       <c r="D1908" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1908" t="s" s="3">
         <v>3795</v>
@@ -44514,7 +44520,7 @@
         <v>6</v>
       </c>
       <c r="D1909" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1909" t="s" s="3">
         <v>3797</v>
@@ -44531,7 +44537,7 @@
         <v>6</v>
       </c>
       <c r="D1910" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1910" t="s" s="3">
         <v>3799</v>
@@ -44548,7 +44554,7 @@
         <v>6</v>
       </c>
       <c r="D1911" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1911" t="s" s="3">
         <v>3801</v>
@@ -44559,16 +44565,16 @@
         <v>1911.0</v>
       </c>
       <c r="B1912" t="s" s="3">
-        <v>2275</v>
+        <v>3802</v>
       </c>
       <c r="C1912" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1912" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1912" t="s" s="3">
-        <v>3802</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="1913" ht="36.0" customHeight="true">
@@ -44576,13 +44582,13 @@
         <v>1912.0</v>
       </c>
       <c r="B1913" t="s" s="3">
-        <v>3803</v>
+        <v>2275</v>
       </c>
       <c r="C1913" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1913" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1913" t="s" s="3">
         <v>3804</v>
@@ -44599,7 +44605,7 @@
         <v>6</v>
       </c>
       <c r="D1914" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1914" t="s" s="3">
         <v>3806</v>
@@ -44616,7 +44622,7 @@
         <v>6</v>
       </c>
       <c r="D1915" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1915" t="s" s="3">
         <v>3808</v>
@@ -44633,7 +44639,7 @@
         <v>6</v>
       </c>
       <c r="D1916" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1916" t="s" s="3">
         <v>3810</v>
@@ -44650,7 +44656,7 @@
         <v>6</v>
       </c>
       <c r="D1917" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1917" t="s" s="3">
         <v>3812</v>
@@ -44667,7 +44673,7 @@
         <v>6</v>
       </c>
       <c r="D1918" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1918" t="s" s="3">
         <v>3814</v>
@@ -44684,7 +44690,7 @@
         <v>6</v>
       </c>
       <c r="D1919" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1919" t="s" s="3">
         <v>3816</v>
@@ -44701,7 +44707,7 @@
         <v>6</v>
       </c>
       <c r="D1920" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1920" t="s" s="3">
         <v>3818</v>
@@ -44715,10 +44721,10 @@
         <v>3819</v>
       </c>
       <c r="C1921" t="s" s="2">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="D1921" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1921" t="s" s="3">
         <v>3820</v>
@@ -44735,7 +44741,7 @@
         <v>580</v>
       </c>
       <c r="D1922" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1922" t="s" s="3">
         <v>3822</v>
@@ -44752,7 +44758,7 @@
         <v>580</v>
       </c>
       <c r="D1923" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1923" t="s" s="3">
         <v>3824</v>
@@ -44769,7 +44775,7 @@
         <v>580</v>
       </c>
       <c r="D1924" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1924" t="s" s="3">
         <v>3826</v>
@@ -44786,7 +44792,7 @@
         <v>580</v>
       </c>
       <c r="D1925" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1925" t="s" s="3">
         <v>3828</v>
@@ -44803,7 +44809,7 @@
         <v>580</v>
       </c>
       <c r="D1926" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1926" t="s" s="3">
         <v>3830</v>
@@ -44820,7 +44826,7 @@
         <v>580</v>
       </c>
       <c r="D1927" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1927" t="s" s="3">
         <v>3832</v>
@@ -44837,7 +44843,7 @@
         <v>580</v>
       </c>
       <c r="D1928" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1928" t="s" s="3">
         <v>3834</v>
@@ -44854,7 +44860,7 @@
         <v>580</v>
       </c>
       <c r="D1929" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1929" t="s" s="3">
         <v>3836</v>
@@ -44871,7 +44877,7 @@
         <v>580</v>
       </c>
       <c r="D1930" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1930" t="s" s="3">
         <v>3838</v>
@@ -44888,7 +44894,7 @@
         <v>580</v>
       </c>
       <c r="D1931" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1931" t="s" s="3">
         <v>3840</v>
@@ -44905,7 +44911,7 @@
         <v>580</v>
       </c>
       <c r="D1932" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1932" t="s" s="3">
         <v>3842</v>
@@ -44922,7 +44928,7 @@
         <v>580</v>
       </c>
       <c r="D1933" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1933" t="s" s="3">
         <v>3844</v>
@@ -44939,7 +44945,7 @@
         <v>580</v>
       </c>
       <c r="D1934" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1934" t="s" s="3">
         <v>3846</v>
@@ -44956,7 +44962,7 @@
         <v>580</v>
       </c>
       <c r="D1935" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1935" t="s" s="3">
         <v>3848</v>
@@ -44973,7 +44979,7 @@
         <v>580</v>
       </c>
       <c r="D1936" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1936" t="s" s="3">
         <v>3850</v>
@@ -44990,7 +44996,7 @@
         <v>580</v>
       </c>
       <c r="D1937" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1937" t="s" s="3">
         <v>3852</v>
@@ -45007,7 +45013,7 @@
         <v>580</v>
       </c>
       <c r="D1938" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1938" t="s" s="3">
         <v>3854</v>
@@ -45024,7 +45030,7 @@
         <v>580</v>
       </c>
       <c r="D1939" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1939" t="s" s="3">
         <v>3856</v>
@@ -45041,7 +45047,7 @@
         <v>580</v>
       </c>
       <c r="D1940" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1940" t="s" s="3">
         <v>3858</v>
@@ -45058,7 +45064,7 @@
         <v>580</v>
       </c>
       <c r="D1941" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1941" t="s" s="3">
         <v>3860</v>
@@ -45075,7 +45081,7 @@
         <v>580</v>
       </c>
       <c r="D1942" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1942" t="s" s="3">
         <v>3862</v>
@@ -45092,7 +45098,7 @@
         <v>580</v>
       </c>
       <c r="D1943" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1943" t="s" s="3">
         <v>3864</v>
@@ -45109,7 +45115,7 @@
         <v>580</v>
       </c>
       <c r="D1944" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1944" t="s" s="3">
         <v>3866</v>
@@ -45126,7 +45132,7 @@
         <v>580</v>
       </c>
       <c r="D1945" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1945" t="s" s="3">
         <v>3868</v>
@@ -45143,7 +45149,7 @@
         <v>580</v>
       </c>
       <c r="D1946" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1946" t="s" s="3">
         <v>3870</v>
@@ -45160,7 +45166,7 @@
         <v>580</v>
       </c>
       <c r="D1947" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1947" t="s" s="3">
         <v>3872</v>
@@ -45177,7 +45183,7 @@
         <v>580</v>
       </c>
       <c r="D1948" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1948" t="s" s="3">
         <v>3874</v>
@@ -45194,7 +45200,7 @@
         <v>580</v>
       </c>
       <c r="D1949" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1949" t="s" s="3">
         <v>3876</v>
@@ -45211,7 +45217,7 @@
         <v>580</v>
       </c>
       <c r="D1950" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1950" t="s" s="3">
         <v>3878</v>
@@ -45228,7 +45234,7 @@
         <v>580</v>
       </c>
       <c r="D1951" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1951" t="s" s="3">
         <v>3880</v>
@@ -45245,7 +45251,7 @@
         <v>580</v>
       </c>
       <c r="D1952" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1952" t="s" s="3">
         <v>3882</v>
@@ -45262,7 +45268,7 @@
         <v>580</v>
       </c>
       <c r="D1953" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1953" t="s" s="3">
         <v>3884</v>
@@ -45279,10 +45285,10 @@
         <v>580</v>
       </c>
       <c r="D1954" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1954" t="s" s="3">
-        <v>3649</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="1955" ht="36.0" customHeight="true">
@@ -45290,16 +45296,16 @@
         <v>1954.0</v>
       </c>
       <c r="B1955" t="s" s="3">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="C1955" t="s" s="2">
         <v>580</v>
       </c>
       <c r="D1955" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1955" t="s" s="3">
-        <v>3887</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="1956" ht="36.0" customHeight="true">
@@ -45313,7 +45319,7 @@
         <v>580</v>
       </c>
       <c r="D1956" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1956" t="s" s="3">
         <v>3889</v>
@@ -45330,7 +45336,7 @@
         <v>580</v>
       </c>
       <c r="D1957" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1957" t="s" s="3">
         <v>3891</v>
@@ -45347,7 +45353,7 @@
         <v>580</v>
       </c>
       <c r="D1958" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1958" t="s" s="3">
         <v>3893</v>
@@ -45361,10 +45367,10 @@
         <v>3894</v>
       </c>
       <c r="C1959" t="s" s="2">
-        <v>751</v>
+        <v>580</v>
       </c>
       <c r="D1959" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1959" t="s" s="3">
         <v>3895</v>
@@ -45381,7 +45387,7 @@
         <v>751</v>
       </c>
       <c r="D1960" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3897</v>
@@ -45392,16 +45398,16 @@
         <v>1960.0</v>
       </c>
       <c r="B1961" t="s" s="3">
-        <v>3881</v>
+        <v>3898</v>
       </c>
       <c r="C1961" t="s" s="2">
         <v>751</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3602</v>
+        <v>3604</v>
       </c>
       <c r="E1961" t="s" s="3">
-        <v>3898</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="1962" ht="36.0" customHeight="true">
@@ -45409,16 +45415,16 @@
         <v>1961.0</v>
       </c>
       <c r="B1962" t="s" s="3">
-        <v>3899</v>
+        <v>3883</v>
       </c>
       <c r="C1962" t="s" s="2">
-        <v>6</v>
+        <v>751</v>
       </c>
       <c r="D1962" t="s" s="2">
+        <v>3604</v>
+      </c>
+      <c r="E1962" t="s" s="3">
         <v>3900</v>
-      </c>
-      <c r="E1962" t="s" s="3">
-        <v>3901</v>
       </c>
     </row>
     <row r="1963" ht="36.0" customHeight="true">
@@ -45426,13 +45432,13 @@
         <v>1962.0</v>
       </c>
       <c r="B1963" t="s" s="3">
+        <v>3901</v>
+      </c>
+      <c r="C1963" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1963" t="s" s="2">
         <v>3902</v>
-      </c>
-      <c r="C1963" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1963" t="s" s="2">
-        <v>3900</v>
       </c>
       <c r="E1963" t="s" s="3">
         <v>3903</v>
@@ -45449,7 +45455,7 @@
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1964" t="s" s="3">
         <v>3905</v>
@@ -45466,7 +45472,7 @@
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3907</v>
@@ -45483,7 +45489,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3909</v>
@@ -45500,7 +45506,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3911</v>
@@ -45517,7 +45523,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3913</v>
@@ -45534,7 +45540,7 @@
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1969" t="s" s="3">
         <v>3915</v>
@@ -45551,7 +45557,7 @@
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1970" t="s" s="3">
         <v>3917</v>
@@ -45568,7 +45574,7 @@
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3919</v>
@@ -45585,7 +45591,7 @@
         <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3921</v>
@@ -45602,7 +45608,7 @@
         <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3923</v>
@@ -45619,7 +45625,7 @@
         <v>6</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3925</v>
@@ -45636,7 +45642,7 @@
         <v>6</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3927</v>
@@ -45653,7 +45659,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3929</v>
@@ -45670,7 +45676,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3931</v>
@@ -45687,7 +45693,7 @@
         <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3933</v>
@@ -45704,7 +45710,7 @@
         <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3935</v>
@@ -45721,7 +45727,7 @@
         <v>6</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3937</v>
@@ -45738,7 +45744,7 @@
         <v>6</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3939</v>
@@ -45755,7 +45761,7 @@
         <v>6</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3941</v>
@@ -45772,7 +45778,7 @@
         <v>6</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3943</v>
@@ -45789,7 +45795,7 @@
         <v>6</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3945</v>
@@ -45806,7 +45812,7 @@
         <v>6</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3947</v>
@@ -45823,7 +45829,7 @@
         <v>6</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3949</v>
@@ -45840,7 +45846,7 @@
         <v>6</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3951</v>
@@ -45857,7 +45863,7 @@
         <v>6</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3953</v>
@@ -45871,13 +45877,13 @@
         <v>3954</v>
       </c>
       <c r="C1989" t="s" s="2">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1989" t="s" s="3">
-        <v>3935</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="1990" ht="36.0" customHeight="true">
@@ -45885,16 +45891,16 @@
         <v>1989.0</v>
       </c>
       <c r="B1990" t="s" s="3">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="C1990" t="s" s="2">
         <v>580</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1990" t="s" s="3">
-        <v>3956</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="1991" ht="36.0" customHeight="true">
@@ -45908,7 +45914,7 @@
         <v>580</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3958</v>
@@ -45925,7 +45931,7 @@
         <v>580</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3960</v>
@@ -45942,7 +45948,7 @@
         <v>580</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3962</v>
@@ -45959,7 +45965,7 @@
         <v>580</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3964</v>
@@ -45976,7 +45982,7 @@
         <v>580</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3966</v>
@@ -45993,7 +45999,7 @@
         <v>580</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3968</v>
@@ -46010,7 +46016,7 @@
         <v>580</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3970</v>
@@ -46027,7 +46033,7 @@
         <v>580</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3972</v>
@@ -46044,7 +46050,7 @@
         <v>580</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3974</v>
@@ -46061,7 +46067,7 @@
         <v>580</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3976</v>
@@ -46078,7 +46084,7 @@
         <v>580</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3978</v>
@@ -46095,7 +46101,7 @@
         <v>580</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3980</v>
@@ -46112,7 +46118,7 @@
         <v>580</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3982</v>
@@ -46129,10 +46135,27 @@
         <v>580</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3984</v>
+      </c>
+    </row>
+    <row r="2005" ht="36.0" customHeight="true">
+      <c r="A2005" t="n" s="2">
+        <v>2004.0</v>
+      </c>
+      <c r="B2005" t="s" s="3">
+        <v>3985</v>
+      </c>
+      <c r="C2005" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="D2005" t="s" s="2">
+        <v>3902</v>
+      </c>
+      <c r="E2005" t="s" s="3">
+        <v>3986</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3734,12 +3734,12 @@
     <t>조선백호</t>
   </si>
   <si>
+    <t>인천광역시 중구 개항로96번길 11(1층 경동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 개항로96번길 11(1,2층 경동)</t>
   </si>
   <si>
-    <t>인천광역시 중구 개항로96번길 11(1층 경동)</t>
-  </si>
-  <si>
     <t>주윤 상차림</t>
   </si>
   <si>
@@ -3881,10 +3881,10 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 백운로 510(2동 1,2층 운북동)</t>
-  </si>
-  <si>
-    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
   </si>
   <si>
     <t>꿈꾸는카페-혜윰도그파크점</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8229" uniqueCount="4089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8241" uniqueCount="4096">
   <si>
     <t>연번</t>
   </si>
@@ -827,6 +827,12 @@
     <t>서울특별시 송파구 삼학사로 35(1층 삼전동)</t>
   </si>
   <si>
+    <t>사랑은 초록</t>
+  </si>
+  <si>
+    <t>서울특별시 서초구 강남대로2길 70(GP빌딩 1층 양재동)</t>
+  </si>
+  <si>
     <t>사루</t>
   </si>
   <si>
@@ -1085,12 +1091,6 @@
     <t>서울특별시 구로구 개봉로12길 9-40(1층 개봉동)</t>
   </si>
   <si>
-    <t>어느새봄</t>
-  </si>
-  <si>
-    <t>서울특별시 서초구 강남대로2길 70(GP빌딩 1층 양재동)</t>
-  </si>
-  <si>
     <t>어딕티브</t>
   </si>
   <si>
@@ -3758,12 +3758,12 @@
     <t>조선백호</t>
   </si>
   <si>
+    <t>인천광역시 중구 개항로96번길 11(1,2층 경동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 개항로96번길 11(1층 경동)</t>
   </si>
   <si>
-    <t>인천광역시 중구 개항로96번길 11(1,2층 경동)</t>
-  </si>
-  <si>
     <t>주윤 상차림</t>
   </si>
   <si>
@@ -3911,12 +3911,12 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
-    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
     <t>꿈꾸는카페-혜윰도그파크점</t>
   </si>
   <si>
@@ -7400,6 +7400,12 @@
     <t>경기도 양주시 청담로243번길 60(사동 1층 전체 고암동)</t>
   </si>
   <si>
+    <t>라운지365(LOUNGE365)</t>
+  </si>
+  <si>
+    <t>경기도 용인시 수지구 용구대로2801번길 10-6(1층 103호 죽전동)</t>
+  </si>
+  <si>
     <t>로아</t>
   </si>
   <si>
@@ -8198,6 +8204,12 @@
     <t>충청북도 영동군 영동읍 성안길 25</t>
   </si>
   <si>
+    <t>디앤디케이크(DND CAKE)</t>
+  </si>
+  <si>
+    <t>충청북도 충주시 천변로 309-1(1층 교현동)</t>
+  </si>
+  <si>
     <t>모도리</t>
   </si>
   <si>
@@ -12279,6 +12291,15 @@
   </si>
   <si>
     <t>전북특별자치도 남원시 시청북로 17(주1동 2층 도통동)</t>
+  </si>
+  <si>
+    <t>산예</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>서울특별시 마포구 동교로46길 28(1층 연남동)</t>
   </si>
 </sst>
 </file>
@@ -18921,7 +18942,7 @@
         <v>7</v>
       </c>
       <c r="E385" t="s" s="3">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="386" ht="36.0" customHeight="true">
@@ -33464,7 +33485,7 @@
         <v>1240.0</v>
       </c>
       <c r="B1241" t="s" s="3">
-        <v>1802</v>
+        <v>2464</v>
       </c>
       <c r="C1241" t="s" s="2">
         <v>600</v>
@@ -33473,7 +33494,7 @@
         <v>1606</v>
       </c>
       <c r="E1241" t="s" s="3">
-        <v>1803</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="1242" ht="36.0" customHeight="true">
@@ -33481,7 +33502,7 @@
         <v>1241.0</v>
       </c>
       <c r="B1242" t="s" s="3">
-        <v>2464</v>
+        <v>1802</v>
       </c>
       <c r="C1242" t="s" s="2">
         <v>600</v>
@@ -33490,7 +33511,7 @@
         <v>1606</v>
       </c>
       <c r="E1242" t="s" s="3">
-        <v>2465</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1243" ht="36.0" customHeight="true">
@@ -35020,7 +35041,7 @@
         <v>1606</v>
       </c>
       <c r="E1332" t="s" s="3">
-        <v>2170</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="1333" ht="36.0" customHeight="true">
@@ -35028,7 +35049,7 @@
         <v>1332.0</v>
       </c>
       <c r="B1333" t="s" s="3">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C1333" t="s" s="2">
         <v>600</v>
@@ -35037,7 +35058,7 @@
         <v>1606</v>
       </c>
       <c r="E1333" t="s" s="3">
-        <v>2646</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1334" ht="36.0" customHeight="true">
@@ -35300,7 +35321,7 @@
         <v>1348.0</v>
       </c>
       <c r="B1349" t="s" s="3">
-        <v>2351</v>
+        <v>2677</v>
       </c>
       <c r="C1349" t="s" s="2">
         <v>600</v>
@@ -35309,7 +35330,7 @@
         <v>1606</v>
       </c>
       <c r="E1349" t="s" s="3">
-        <v>2352</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="1350" ht="36.0" customHeight="true">
@@ -35317,7 +35338,7 @@
         <v>1349.0</v>
       </c>
       <c r="B1350" t="s" s="3">
-        <v>2677</v>
+        <v>2351</v>
       </c>
       <c r="C1350" t="s" s="2">
         <v>600</v>
@@ -35326,7 +35347,7 @@
         <v>1606</v>
       </c>
       <c r="E1350" t="s" s="3">
-        <v>2678</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1351" ht="36.0" customHeight="true">
@@ -35507,7 +35528,7 @@
         <v>2699</v>
       </c>
       <c r="C1361" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1361" t="s" s="2">
         <v>1606</v>
@@ -35626,13 +35647,13 @@
         <v>2713</v>
       </c>
       <c r="C1368" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1368" t="s" s="2">
+        <v>1606</v>
+      </c>
+      <c r="E1368" t="s" s="3">
         <v>2714</v>
-      </c>
-      <c r="E1368" t="s" s="3">
-        <v>2715</v>
       </c>
     </row>
     <row r="1369" ht="36.0" customHeight="true">
@@ -35640,13 +35661,13 @@
         <v>1368.0</v>
       </c>
       <c r="B1369" t="s" s="3">
+        <v>2715</v>
+      </c>
+      <c r="C1369" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1369" t="s" s="2">
         <v>2716</v>
-      </c>
-      <c r="C1369" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1369" t="s" s="2">
-        <v>2714</v>
       </c>
       <c r="E1369" t="s" s="3">
         <v>2717</v>
@@ -35663,7 +35684,7 @@
         <v>6</v>
       </c>
       <c r="D1370" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1370" t="s" s="3">
         <v>2719</v>
@@ -35680,7 +35701,7 @@
         <v>6</v>
       </c>
       <c r="D1371" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1371" t="s" s="3">
         <v>2721</v>
@@ -35697,7 +35718,7 @@
         <v>6</v>
       </c>
       <c r="D1372" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1372" t="s" s="3">
         <v>2723</v>
@@ -35714,7 +35735,7 @@
         <v>6</v>
       </c>
       <c r="D1373" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1373" t="s" s="3">
         <v>2725</v>
@@ -35731,7 +35752,7 @@
         <v>6</v>
       </c>
       <c r="D1374" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1374" t="s" s="3">
         <v>2727</v>
@@ -35748,7 +35769,7 @@
         <v>6</v>
       </c>
       <c r="D1375" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1375" t="s" s="3">
         <v>2729</v>
@@ -35765,7 +35786,7 @@
         <v>6</v>
       </c>
       <c r="D1376" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1376" t="s" s="3">
         <v>2731</v>
@@ -35782,7 +35803,7 @@
         <v>6</v>
       </c>
       <c r="D1377" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1377" t="s" s="3">
         <v>2733</v>
@@ -35799,7 +35820,7 @@
         <v>6</v>
       </c>
       <c r="D1378" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1378" t="s" s="3">
         <v>2735</v>
@@ -35816,7 +35837,7 @@
         <v>6</v>
       </c>
       <c r="D1379" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1379" t="s" s="3">
         <v>2737</v>
@@ -35833,7 +35854,7 @@
         <v>6</v>
       </c>
       <c r="D1380" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1380" t="s" s="3">
         <v>2739</v>
@@ -35850,7 +35871,7 @@
         <v>6</v>
       </c>
       <c r="D1381" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1381" t="s" s="3">
         <v>2741</v>
@@ -35867,7 +35888,7 @@
         <v>6</v>
       </c>
       <c r="D1382" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1382" t="s" s="3">
         <v>2743</v>
@@ -35884,7 +35905,7 @@
         <v>6</v>
       </c>
       <c r="D1383" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1383" t="s" s="3">
         <v>2745</v>
@@ -35901,7 +35922,7 @@
         <v>6</v>
       </c>
       <c r="D1384" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1384" t="s" s="3">
         <v>2747</v>
@@ -35918,7 +35939,7 @@
         <v>6</v>
       </c>
       <c r="D1385" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1385" t="s" s="3">
         <v>2749</v>
@@ -35935,7 +35956,7 @@
         <v>6</v>
       </c>
       <c r="D1386" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1386" t="s" s="3">
         <v>2751</v>
@@ -35952,7 +35973,7 @@
         <v>6</v>
       </c>
       <c r="D1387" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1387" t="s" s="3">
         <v>2753</v>
@@ -35969,7 +35990,7 @@
         <v>6</v>
       </c>
       <c r="D1388" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1388" t="s" s="3">
         <v>2755</v>
@@ -35986,7 +36007,7 @@
         <v>6</v>
       </c>
       <c r="D1389" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1389" t="s" s="3">
         <v>2757</v>
@@ -36003,7 +36024,7 @@
         <v>6</v>
       </c>
       <c r="D1390" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1390" t="s" s="3">
         <v>2759</v>
@@ -36020,7 +36041,7 @@
         <v>6</v>
       </c>
       <c r="D1391" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1391" t="s" s="3">
         <v>2761</v>
@@ -36037,7 +36058,7 @@
         <v>6</v>
       </c>
       <c r="D1392" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1392" t="s" s="3">
         <v>2763</v>
@@ -36054,7 +36075,7 @@
         <v>6</v>
       </c>
       <c r="D1393" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1393" t="s" s="3">
         <v>2765</v>
@@ -36071,7 +36092,7 @@
         <v>6</v>
       </c>
       <c r="D1394" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1394" t="s" s="3">
         <v>2767</v>
@@ -36088,7 +36109,7 @@
         <v>6</v>
       </c>
       <c r="D1395" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1395" t="s" s="3">
         <v>2769</v>
@@ -36105,7 +36126,7 @@
         <v>6</v>
       </c>
       <c r="D1396" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1396" t="s" s="3">
         <v>2771</v>
@@ -36122,7 +36143,7 @@
         <v>6</v>
       </c>
       <c r="D1397" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1397" t="s" s="3">
         <v>2773</v>
@@ -36139,7 +36160,7 @@
         <v>6</v>
       </c>
       <c r="D1398" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1398" t="s" s="3">
         <v>2775</v>
@@ -36156,7 +36177,7 @@
         <v>6</v>
       </c>
       <c r="D1399" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1399" t="s" s="3">
         <v>2777</v>
@@ -36173,7 +36194,7 @@
         <v>6</v>
       </c>
       <c r="D1400" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1400" t="s" s="3">
         <v>2779</v>
@@ -36190,7 +36211,7 @@
         <v>6</v>
       </c>
       <c r="D1401" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1401" t="s" s="3">
         <v>2781</v>
@@ -36207,7 +36228,7 @@
         <v>6</v>
       </c>
       <c r="D1402" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1402" t="s" s="3">
         <v>2783</v>
@@ -36224,7 +36245,7 @@
         <v>6</v>
       </c>
       <c r="D1403" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1403" t="s" s="3">
         <v>2785</v>
@@ -36241,7 +36262,7 @@
         <v>6</v>
       </c>
       <c r="D1404" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1404" t="s" s="3">
         <v>2787</v>
@@ -36258,7 +36279,7 @@
         <v>6</v>
       </c>
       <c r="D1405" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1405" t="s" s="3">
         <v>2789</v>
@@ -36275,7 +36296,7 @@
         <v>6</v>
       </c>
       <c r="D1406" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1406" t="s" s="3">
         <v>2791</v>
@@ -36289,10 +36310,10 @@
         <v>2792</v>
       </c>
       <c r="C1407" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1407" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1407" t="s" s="3">
         <v>2793</v>
@@ -36306,10 +36327,10 @@
         <v>2794</v>
       </c>
       <c r="C1408" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1408" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1408" t="s" s="3">
         <v>2795</v>
@@ -36326,7 +36347,7 @@
         <v>600</v>
       </c>
       <c r="D1409" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1409" t="s" s="3">
         <v>2797</v>
@@ -36343,7 +36364,7 @@
         <v>600</v>
       </c>
       <c r="D1410" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1410" t="s" s="3">
         <v>2799</v>
@@ -36360,7 +36381,7 @@
         <v>600</v>
       </c>
       <c r="D1411" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1411" t="s" s="3">
         <v>2801</v>
@@ -36377,7 +36398,7 @@
         <v>600</v>
       </c>
       <c r="D1412" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1412" t="s" s="3">
         <v>2803</v>
@@ -36394,7 +36415,7 @@
         <v>600</v>
       </c>
       <c r="D1413" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1413" t="s" s="3">
         <v>2805</v>
@@ -36411,7 +36432,7 @@
         <v>600</v>
       </c>
       <c r="D1414" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1414" t="s" s="3">
         <v>2807</v>
@@ -36428,7 +36449,7 @@
         <v>600</v>
       </c>
       <c r="D1415" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1415" t="s" s="3">
         <v>2809</v>
@@ -36442,10 +36463,10 @@
         <v>2810</v>
       </c>
       <c r="C1416" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1416" t="s" s="2">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1416" t="s" s="3">
         <v>2811</v>
@@ -36459,13 +36480,13 @@
         <v>2812</v>
       </c>
       <c r="C1417" t="s" s="2">
-        <v>6</v>
+        <v>600</v>
       </c>
       <c r="D1417" t="s" s="2">
+        <v>2716</v>
+      </c>
+      <c r="E1417" t="s" s="3">
         <v>2813</v>
-      </c>
-      <c r="E1417" t="s" s="3">
-        <v>2814</v>
       </c>
     </row>
     <row r="1418" ht="36.0" customHeight="true">
@@ -36473,16 +36494,16 @@
         <v>1417.0</v>
       </c>
       <c r="B1418" t="s" s="3">
+        <v>2814</v>
+      </c>
+      <c r="C1418" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1418" t="s" s="2">
+        <v>2716</v>
+      </c>
+      <c r="E1418" t="s" s="3">
         <v>2815</v>
-      </c>
-      <c r="C1418" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1418" t="s" s="2">
-        <v>2813</v>
-      </c>
-      <c r="E1418" t="s" s="3">
-        <v>2816</v>
       </c>
     </row>
     <row r="1419" ht="36.0" customHeight="true">
@@ -36490,13 +36511,13 @@
         <v>1418.0</v>
       </c>
       <c r="B1419" t="s" s="3">
+        <v>2816</v>
+      </c>
+      <c r="C1419" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1419" t="s" s="2">
         <v>2817</v>
-      </c>
-      <c r="C1419" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1419" t="s" s="2">
-        <v>2813</v>
       </c>
       <c r="E1419" t="s" s="3">
         <v>2818</v>
@@ -36513,7 +36534,7 @@
         <v>6</v>
       </c>
       <c r="D1420" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1420" t="s" s="3">
         <v>2820</v>
@@ -36530,7 +36551,7 @@
         <v>6</v>
       </c>
       <c r="D1421" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1421" t="s" s="3">
         <v>2822</v>
@@ -36547,7 +36568,7 @@
         <v>6</v>
       </c>
       <c r="D1422" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1422" t="s" s="3">
         <v>2824</v>
@@ -36564,7 +36585,7 @@
         <v>6</v>
       </c>
       <c r="D1423" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1423" t="s" s="3">
         <v>2826</v>
@@ -36581,7 +36602,7 @@
         <v>6</v>
       </c>
       <c r="D1424" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1424" t="s" s="3">
         <v>2828</v>
@@ -36598,7 +36619,7 @@
         <v>6</v>
       </c>
       <c r="D1425" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1425" t="s" s="3">
         <v>2830</v>
@@ -36615,7 +36636,7 @@
         <v>6</v>
       </c>
       <c r="D1426" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1426" t="s" s="3">
         <v>2832</v>
@@ -36632,7 +36653,7 @@
         <v>6</v>
       </c>
       <c r="D1427" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1427" t="s" s="3">
         <v>2834</v>
@@ -36649,7 +36670,7 @@
         <v>6</v>
       </c>
       <c r="D1428" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1428" t="s" s="3">
         <v>2836</v>
@@ -36666,7 +36687,7 @@
         <v>6</v>
       </c>
       <c r="D1429" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1429" t="s" s="3">
         <v>2838</v>
@@ -36683,7 +36704,7 @@
         <v>6</v>
       </c>
       <c r="D1430" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1430" t="s" s="3">
         <v>2840</v>
@@ -36700,7 +36721,7 @@
         <v>6</v>
       </c>
       <c r="D1431" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1431" t="s" s="3">
         <v>2842</v>
@@ -36717,7 +36738,7 @@
         <v>6</v>
       </c>
       <c r="D1432" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1432" t="s" s="3">
         <v>2844</v>
@@ -36734,7 +36755,7 @@
         <v>6</v>
       </c>
       <c r="D1433" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1433" t="s" s="3">
         <v>2846</v>
@@ -36751,7 +36772,7 @@
         <v>6</v>
       </c>
       <c r="D1434" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1434" t="s" s="3">
         <v>2848</v>
@@ -36768,7 +36789,7 @@
         <v>6</v>
       </c>
       <c r="D1435" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1435" t="s" s="3">
         <v>2850</v>
@@ -36785,7 +36806,7 @@
         <v>6</v>
       </c>
       <c r="D1436" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1436" t="s" s="3">
         <v>2852</v>
@@ -36802,7 +36823,7 @@
         <v>6</v>
       </c>
       <c r="D1437" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1437" t="s" s="3">
         <v>2854</v>
@@ -36819,7 +36840,7 @@
         <v>6</v>
       </c>
       <c r="D1438" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1438" t="s" s="3">
         <v>2856</v>
@@ -36836,7 +36857,7 @@
         <v>6</v>
       </c>
       <c r="D1439" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1439" t="s" s="3">
         <v>2858</v>
@@ -36853,7 +36874,7 @@
         <v>6</v>
       </c>
       <c r="D1440" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1440" t="s" s="3">
         <v>2860</v>
@@ -36870,7 +36891,7 @@
         <v>6</v>
       </c>
       <c r="D1441" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1441" t="s" s="3">
         <v>2862</v>
@@ -36887,7 +36908,7 @@
         <v>6</v>
       </c>
       <c r="D1442" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1442" t="s" s="3">
         <v>2864</v>
@@ -36904,7 +36925,7 @@
         <v>6</v>
       </c>
       <c r="D1443" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1443" t="s" s="3">
         <v>2866</v>
@@ -36921,7 +36942,7 @@
         <v>6</v>
       </c>
       <c r="D1444" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1444" t="s" s="3">
         <v>2868</v>
@@ -36938,7 +36959,7 @@
         <v>6</v>
       </c>
       <c r="D1445" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1445" t="s" s="3">
         <v>2870</v>
@@ -36955,7 +36976,7 @@
         <v>6</v>
       </c>
       <c r="D1446" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1446" t="s" s="3">
         <v>2872</v>
@@ -36972,7 +36993,7 @@
         <v>6</v>
       </c>
       <c r="D1447" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1447" t="s" s="3">
         <v>2874</v>
@@ -36989,7 +37010,7 @@
         <v>6</v>
       </c>
       <c r="D1448" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1448" t="s" s="3">
         <v>2876</v>
@@ -37006,7 +37027,7 @@
         <v>6</v>
       </c>
       <c r="D1449" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1449" t="s" s="3">
         <v>2878</v>
@@ -37023,7 +37044,7 @@
         <v>6</v>
       </c>
       <c r="D1450" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1450" t="s" s="3">
         <v>2880</v>
@@ -37040,7 +37061,7 @@
         <v>6</v>
       </c>
       <c r="D1451" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1451" t="s" s="3">
         <v>2882</v>
@@ -37057,7 +37078,7 @@
         <v>6</v>
       </c>
       <c r="D1452" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1452" t="s" s="3">
         <v>2884</v>
@@ -37074,7 +37095,7 @@
         <v>6</v>
       </c>
       <c r="D1453" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1453" t="s" s="3">
         <v>2886</v>
@@ -37091,7 +37112,7 @@
         <v>6</v>
       </c>
       <c r="D1454" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1454" t="s" s="3">
         <v>2888</v>
@@ -37108,7 +37129,7 @@
         <v>6</v>
       </c>
       <c r="D1455" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1455" t="s" s="3">
         <v>2890</v>
@@ -37122,10 +37143,10 @@
         <v>2891</v>
       </c>
       <c r="C1456" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1456" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1456" t="s" s="3">
         <v>2892</v>
@@ -37139,10 +37160,10 @@
         <v>2893</v>
       </c>
       <c r="C1457" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1457" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1457" t="s" s="3">
         <v>2894</v>
@@ -37159,7 +37180,7 @@
         <v>600</v>
       </c>
       <c r="D1458" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1458" t="s" s="3">
         <v>2896</v>
@@ -37176,7 +37197,7 @@
         <v>600</v>
       </c>
       <c r="D1459" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1459" t="s" s="3">
         <v>2898</v>
@@ -37193,7 +37214,7 @@
         <v>600</v>
       </c>
       <c r="D1460" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1460" t="s" s="3">
         <v>2900</v>
@@ -37210,7 +37231,7 @@
         <v>600</v>
       </c>
       <c r="D1461" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1461" t="s" s="3">
         <v>2902</v>
@@ -37227,7 +37248,7 @@
         <v>600</v>
       </c>
       <c r="D1462" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1462" t="s" s="3">
         <v>2904</v>
@@ -37244,7 +37265,7 @@
         <v>600</v>
       </c>
       <c r="D1463" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1463" t="s" s="3">
         <v>2906</v>
@@ -37261,7 +37282,7 @@
         <v>600</v>
       </c>
       <c r="D1464" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1464" t="s" s="3">
         <v>2908</v>
@@ -37278,7 +37299,7 @@
         <v>600</v>
       </c>
       <c r="D1465" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1465" t="s" s="3">
         <v>2910</v>
@@ -37295,7 +37316,7 @@
         <v>600</v>
       </c>
       <c r="D1466" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1466" t="s" s="3">
         <v>2912</v>
@@ -37312,7 +37333,7 @@
         <v>600</v>
       </c>
       <c r="D1467" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1467" t="s" s="3">
         <v>2914</v>
@@ -37329,7 +37350,7 @@
         <v>600</v>
       </c>
       <c r="D1468" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1468" t="s" s="3">
         <v>2916</v>
@@ -37346,7 +37367,7 @@
         <v>600</v>
       </c>
       <c r="D1469" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1469" t="s" s="3">
         <v>2918</v>
@@ -37363,7 +37384,7 @@
         <v>600</v>
       </c>
       <c r="D1470" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1470" t="s" s="3">
         <v>2920</v>
@@ -37380,7 +37401,7 @@
         <v>600</v>
       </c>
       <c r="D1471" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1471" t="s" s="3">
         <v>2922</v>
@@ -37397,7 +37418,7 @@
         <v>600</v>
       </c>
       <c r="D1472" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1472" t="s" s="3">
         <v>2924</v>
@@ -37414,7 +37435,7 @@
         <v>600</v>
       </c>
       <c r="D1473" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1473" t="s" s="3">
         <v>2926</v>
@@ -37431,7 +37452,7 @@
         <v>600</v>
       </c>
       <c r="D1474" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1474" t="s" s="3">
         <v>2928</v>
@@ -37448,7 +37469,7 @@
         <v>600</v>
       </c>
       <c r="D1475" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1475" t="s" s="3">
         <v>2930</v>
@@ -37462,10 +37483,10 @@
         <v>2931</v>
       </c>
       <c r="C1476" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1476" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1476" t="s" s="3">
         <v>2932</v>
@@ -37479,10 +37500,10 @@
         <v>2933</v>
       </c>
       <c r="C1477" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1477" t="s" s="2">
-        <v>2813</v>
+        <v>2817</v>
       </c>
       <c r="E1477" t="s" s="3">
         <v>2934</v>
@@ -37496,13 +37517,13 @@
         <v>2935</v>
       </c>
       <c r="C1478" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1478" t="s" s="2">
+        <v>2817</v>
+      </c>
+      <c r="E1478" t="s" s="3">
         <v>2936</v>
-      </c>
-      <c r="E1478" t="s" s="3">
-        <v>2937</v>
       </c>
     </row>
     <row r="1479" ht="36.0" customHeight="true">
@@ -37510,16 +37531,16 @@
         <v>1478.0</v>
       </c>
       <c r="B1479" t="s" s="3">
+        <v>2937</v>
+      </c>
+      <c r="C1479" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1479" t="s" s="2">
+        <v>2817</v>
+      </c>
+      <c r="E1479" t="s" s="3">
         <v>2938</v>
-      </c>
-      <c r="C1479" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1479" t="s" s="2">
-        <v>2936</v>
-      </c>
-      <c r="E1479" t="s" s="3">
-        <v>2939</v>
       </c>
     </row>
     <row r="1480" ht="36.0" customHeight="true">
@@ -37527,13 +37548,13 @@
         <v>1479.0</v>
       </c>
       <c r="B1480" t="s" s="3">
+        <v>2939</v>
+      </c>
+      <c r="C1480" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1480" t="s" s="2">
         <v>2940</v>
-      </c>
-      <c r="C1480" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1480" t="s" s="2">
-        <v>2936</v>
       </c>
       <c r="E1480" t="s" s="3">
         <v>2941</v>
@@ -37550,7 +37571,7 @@
         <v>6</v>
       </c>
       <c r="D1481" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1481" t="s" s="3">
         <v>2943</v>
@@ -37567,7 +37588,7 @@
         <v>6</v>
       </c>
       <c r="D1482" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1482" t="s" s="3">
         <v>2945</v>
@@ -37584,7 +37605,7 @@
         <v>6</v>
       </c>
       <c r="D1483" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1483" t="s" s="3">
         <v>2947</v>
@@ -37601,7 +37622,7 @@
         <v>6</v>
       </c>
       <c r="D1484" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1484" t="s" s="3">
         <v>2949</v>
@@ -37618,7 +37639,7 @@
         <v>6</v>
       </c>
       <c r="D1485" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1485" t="s" s="3">
         <v>2951</v>
@@ -37635,7 +37656,7 @@
         <v>6</v>
       </c>
       <c r="D1486" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1486" t="s" s="3">
         <v>2953</v>
@@ -37652,7 +37673,7 @@
         <v>6</v>
       </c>
       <c r="D1487" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1487" t="s" s="3">
         <v>2955</v>
@@ -37669,7 +37690,7 @@
         <v>6</v>
       </c>
       <c r="D1488" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1488" t="s" s="3">
         <v>2957</v>
@@ -37686,7 +37707,7 @@
         <v>6</v>
       </c>
       <c r="D1489" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1489" t="s" s="3">
         <v>2959</v>
@@ -37703,7 +37724,7 @@
         <v>6</v>
       </c>
       <c r="D1490" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1490" t="s" s="3">
         <v>2961</v>
@@ -37720,7 +37741,7 @@
         <v>6</v>
       </c>
       <c r="D1491" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1491" t="s" s="3">
         <v>2963</v>
@@ -37737,7 +37758,7 @@
         <v>6</v>
       </c>
       <c r="D1492" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1492" t="s" s="3">
         <v>2965</v>
@@ -37754,7 +37775,7 @@
         <v>6</v>
       </c>
       <c r="D1493" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1493" t="s" s="3">
         <v>2967</v>
@@ -37771,7 +37792,7 @@
         <v>6</v>
       </c>
       <c r="D1494" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1494" t="s" s="3">
         <v>2969</v>
@@ -37788,7 +37809,7 @@
         <v>6</v>
       </c>
       <c r="D1495" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1495" t="s" s="3">
         <v>2971</v>
@@ -37805,7 +37826,7 @@
         <v>6</v>
       </c>
       <c r="D1496" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1496" t="s" s="3">
         <v>2973</v>
@@ -37822,7 +37843,7 @@
         <v>6</v>
       </c>
       <c r="D1497" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1497" t="s" s="3">
         <v>2975</v>
@@ -37839,7 +37860,7 @@
         <v>6</v>
       </c>
       <c r="D1498" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1498" t="s" s="3">
         <v>2977</v>
@@ -37856,7 +37877,7 @@
         <v>6</v>
       </c>
       <c r="D1499" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1499" t="s" s="3">
         <v>2979</v>
@@ -37873,7 +37894,7 @@
         <v>6</v>
       </c>
       <c r="D1500" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1500" t="s" s="3">
         <v>2981</v>
@@ -37890,7 +37911,7 @@
         <v>6</v>
       </c>
       <c r="D1501" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1501" t="s" s="3">
         <v>2983</v>
@@ -37907,7 +37928,7 @@
         <v>6</v>
       </c>
       <c r="D1502" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1502" t="s" s="3">
         <v>2985</v>
@@ -37924,7 +37945,7 @@
         <v>6</v>
       </c>
       <c r="D1503" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1503" t="s" s="3">
         <v>2987</v>
@@ -37941,7 +37962,7 @@
         <v>6</v>
       </c>
       <c r="D1504" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1504" t="s" s="3">
         <v>2989</v>
@@ -37955,10 +37976,10 @@
         <v>2990</v>
       </c>
       <c r="C1505" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1505" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1505" t="s" s="3">
         <v>2991</v>
@@ -37972,10 +37993,10 @@
         <v>2992</v>
       </c>
       <c r="C1506" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1506" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1506" t="s" s="3">
         <v>2993</v>
@@ -37992,7 +38013,7 @@
         <v>600</v>
       </c>
       <c r="D1507" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1507" t="s" s="3">
         <v>2995</v>
@@ -38009,7 +38030,7 @@
         <v>600</v>
       </c>
       <c r="D1508" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1508" t="s" s="3">
         <v>2997</v>
@@ -38026,7 +38047,7 @@
         <v>600</v>
       </c>
       <c r="D1509" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1509" t="s" s="3">
         <v>2999</v>
@@ -38043,7 +38064,7 @@
         <v>600</v>
       </c>
       <c r="D1510" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1510" t="s" s="3">
         <v>3001</v>
@@ -38060,7 +38081,7 @@
         <v>600</v>
       </c>
       <c r="D1511" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1511" t="s" s="3">
         <v>3003</v>
@@ -38077,7 +38098,7 @@
         <v>600</v>
       </c>
       <c r="D1512" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1512" t="s" s="3">
         <v>3005</v>
@@ -38094,7 +38115,7 @@
         <v>600</v>
       </c>
       <c r="D1513" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1513" t="s" s="3">
         <v>3007</v>
@@ -38111,7 +38132,7 @@
         <v>600</v>
       </c>
       <c r="D1514" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1514" t="s" s="3">
         <v>3009</v>
@@ -38128,7 +38149,7 @@
         <v>600</v>
       </c>
       <c r="D1515" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1515" t="s" s="3">
         <v>3011</v>
@@ -38145,7 +38166,7 @@
         <v>600</v>
       </c>
       <c r="D1516" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1516" t="s" s="3">
         <v>3013</v>
@@ -38162,7 +38183,7 @@
         <v>600</v>
       </c>
       <c r="D1517" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1517" t="s" s="3">
         <v>3015</v>
@@ -38176,10 +38197,10 @@
         <v>3016</v>
       </c>
       <c r="C1518" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1518" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1518" t="s" s="3">
         <v>3017</v>
@@ -38193,10 +38214,10 @@
         <v>3018</v>
       </c>
       <c r="C1519" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1519" t="s" s="2">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="E1519" t="s" s="3">
         <v>3019</v>
@@ -38210,13 +38231,13 @@
         <v>3020</v>
       </c>
       <c r="C1520" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1520" t="s" s="2">
+        <v>2940</v>
+      </c>
+      <c r="E1520" t="s" s="3">
         <v>3021</v>
-      </c>
-      <c r="E1520" t="s" s="3">
-        <v>3022</v>
       </c>
     </row>
     <row r="1521" ht="36.0" customHeight="true">
@@ -38224,16 +38245,16 @@
         <v>1520.0</v>
       </c>
       <c r="B1521" t="s" s="3">
+        <v>3022</v>
+      </c>
+      <c r="C1521" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1521" t="s" s="2">
+        <v>2940</v>
+      </c>
+      <c r="E1521" t="s" s="3">
         <v>3023</v>
-      </c>
-      <c r="C1521" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1521" t="s" s="2">
-        <v>3021</v>
-      </c>
-      <c r="E1521" t="s" s="3">
-        <v>3024</v>
       </c>
     </row>
     <row r="1522" ht="36.0" customHeight="true">
@@ -38241,13 +38262,13 @@
         <v>1521.0</v>
       </c>
       <c r="B1522" t="s" s="3">
+        <v>3024</v>
+      </c>
+      <c r="C1522" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1522" t="s" s="2">
         <v>3025</v>
-      </c>
-      <c r="C1522" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1522" t="s" s="2">
-        <v>3021</v>
       </c>
       <c r="E1522" t="s" s="3">
         <v>3026</v>
@@ -38264,7 +38285,7 @@
         <v>6</v>
       </c>
       <c r="D1523" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1523" t="s" s="3">
         <v>3028</v>
@@ -38281,7 +38302,7 @@
         <v>6</v>
       </c>
       <c r="D1524" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1524" t="s" s="3">
         <v>3030</v>
@@ -38298,7 +38319,7 @@
         <v>6</v>
       </c>
       <c r="D1525" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1525" t="s" s="3">
         <v>3032</v>
@@ -38315,7 +38336,7 @@
         <v>6</v>
       </c>
       <c r="D1526" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1526" t="s" s="3">
         <v>3034</v>
@@ -38332,7 +38353,7 @@
         <v>6</v>
       </c>
       <c r="D1527" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1527" t="s" s="3">
         <v>3036</v>
@@ -38349,7 +38370,7 @@
         <v>6</v>
       </c>
       <c r="D1528" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1528" t="s" s="3">
         <v>3038</v>
@@ -38366,7 +38387,7 @@
         <v>6</v>
       </c>
       <c r="D1529" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1529" t="s" s="3">
         <v>3040</v>
@@ -38383,7 +38404,7 @@
         <v>6</v>
       </c>
       <c r="D1530" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1530" t="s" s="3">
         <v>3042</v>
@@ -38400,7 +38421,7 @@
         <v>6</v>
       </c>
       <c r="D1531" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1531" t="s" s="3">
         <v>3044</v>
@@ -38417,7 +38438,7 @@
         <v>6</v>
       </c>
       <c r="D1532" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1532" t="s" s="3">
         <v>3046</v>
@@ -38434,7 +38455,7 @@
         <v>6</v>
       </c>
       <c r="D1533" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1533" t="s" s="3">
         <v>3048</v>
@@ -38451,7 +38472,7 @@
         <v>6</v>
       </c>
       <c r="D1534" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1534" t="s" s="3">
         <v>3050</v>
@@ -38468,7 +38489,7 @@
         <v>6</v>
       </c>
       <c r="D1535" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1535" t="s" s="3">
         <v>3052</v>
@@ -38485,7 +38506,7 @@
         <v>6</v>
       </c>
       <c r="D1536" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1536" t="s" s="3">
         <v>3054</v>
@@ -38502,7 +38523,7 @@
         <v>6</v>
       </c>
       <c r="D1537" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1537" t="s" s="3">
         <v>3056</v>
@@ -38519,7 +38540,7 @@
         <v>6</v>
       </c>
       <c r="D1538" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1538" t="s" s="3">
         <v>3058</v>
@@ -38536,7 +38557,7 @@
         <v>6</v>
       </c>
       <c r="D1539" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1539" t="s" s="3">
         <v>3060</v>
@@ -38553,7 +38574,7 @@
         <v>6</v>
       </c>
       <c r="D1540" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1540" t="s" s="3">
         <v>3062</v>
@@ -38570,7 +38591,7 @@
         <v>6</v>
       </c>
       <c r="D1541" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1541" t="s" s="3">
         <v>3064</v>
@@ -38587,7 +38608,7 @@
         <v>6</v>
       </c>
       <c r="D1542" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1542" t="s" s="3">
         <v>3066</v>
@@ -38604,7 +38625,7 @@
         <v>6</v>
       </c>
       <c r="D1543" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1543" t="s" s="3">
         <v>3068</v>
@@ -38621,7 +38642,7 @@
         <v>6</v>
       </c>
       <c r="D1544" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1544" t="s" s="3">
         <v>3070</v>
@@ -38638,7 +38659,7 @@
         <v>6</v>
       </c>
       <c r="D1545" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1545" t="s" s="3">
         <v>3072</v>
@@ -38655,7 +38676,7 @@
         <v>6</v>
       </c>
       <c r="D1546" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1546" t="s" s="3">
         <v>3074</v>
@@ -38672,7 +38693,7 @@
         <v>6</v>
       </c>
       <c r="D1547" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1547" t="s" s="3">
         <v>3076</v>
@@ -38689,7 +38710,7 @@
         <v>6</v>
       </c>
       <c r="D1548" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1548" t="s" s="3">
         <v>3078</v>
@@ -38706,10 +38727,10 @@
         <v>6</v>
       </c>
       <c r="D1549" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1549" t="s" s="3">
-        <v>3062</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="1550" ht="36.0" customHeight="true">
@@ -38717,16 +38738,16 @@
         <v>1549.0</v>
       </c>
       <c r="B1550" t="s" s="3">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C1550" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1550" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1550" t="s" s="3">
-        <v>3081</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="1551" ht="36.0" customHeight="true">
@@ -38734,16 +38755,16 @@
         <v>1550.0</v>
       </c>
       <c r="B1551" t="s" s="3">
-        <v>2628</v>
+        <v>3083</v>
       </c>
       <c r="C1551" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1551" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1551" t="s" s="3">
-        <v>3082</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1552" ht="36.0" customHeight="true">
@@ -38751,16 +38772,16 @@
         <v>1551.0</v>
       </c>
       <c r="B1552" t="s" s="3">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="C1552" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1552" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1552" t="s" s="3">
-        <v>3084</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="1553" ht="36.0" customHeight="true">
@@ -38768,13 +38789,13 @@
         <v>1552.0</v>
       </c>
       <c r="B1553" t="s" s="3">
-        <v>3085</v>
+        <v>2630</v>
       </c>
       <c r="C1553" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1553" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1553" t="s" s="3">
         <v>3086</v>
@@ -38791,7 +38812,7 @@
         <v>6</v>
       </c>
       <c r="D1554" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1554" t="s" s="3">
         <v>3088</v>
@@ -38808,7 +38829,7 @@
         <v>6</v>
       </c>
       <c r="D1555" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1555" t="s" s="3">
         <v>3090</v>
@@ -38825,7 +38846,7 @@
         <v>6</v>
       </c>
       <c r="D1556" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1556" t="s" s="3">
         <v>3092</v>
@@ -38842,7 +38863,7 @@
         <v>6</v>
       </c>
       <c r="D1557" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1557" t="s" s="3">
         <v>3094</v>
@@ -38856,10 +38877,10 @@
         <v>3095</v>
       </c>
       <c r="C1558" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1558" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1558" t="s" s="3">
         <v>3096</v>
@@ -38873,10 +38894,10 @@
         <v>3097</v>
       </c>
       <c r="C1559" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1559" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1559" t="s" s="3">
         <v>3098</v>
@@ -38893,7 +38914,7 @@
         <v>600</v>
       </c>
       <c r="D1560" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1560" t="s" s="3">
         <v>3100</v>
@@ -38910,7 +38931,7 @@
         <v>600</v>
       </c>
       <c r="D1561" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1561" t="s" s="3">
         <v>3102</v>
@@ -38927,7 +38948,7 @@
         <v>600</v>
       </c>
       <c r="D1562" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1562" t="s" s="3">
         <v>3104</v>
@@ -38944,7 +38965,7 @@
         <v>600</v>
       </c>
       <c r="D1563" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1563" t="s" s="3">
         <v>3106</v>
@@ -38961,7 +38982,7 @@
         <v>600</v>
       </c>
       <c r="D1564" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1564" t="s" s="3">
         <v>3108</v>
@@ -38978,7 +38999,7 @@
         <v>600</v>
       </c>
       <c r="D1565" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1565" t="s" s="3">
         <v>3110</v>
@@ -38995,7 +39016,7 @@
         <v>600</v>
       </c>
       <c r="D1566" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1566" t="s" s="3">
         <v>3112</v>
@@ -39012,7 +39033,7 @@
         <v>600</v>
       </c>
       <c r="D1567" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1567" t="s" s="3">
         <v>3114</v>
@@ -39029,7 +39050,7 @@
         <v>600</v>
       </c>
       <c r="D1568" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1568" t="s" s="3">
         <v>3116</v>
@@ -39046,7 +39067,7 @@
         <v>600</v>
       </c>
       <c r="D1569" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1569" t="s" s="3">
         <v>3118</v>
@@ -39063,7 +39084,7 @@
         <v>600</v>
       </c>
       <c r="D1570" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1570" t="s" s="3">
         <v>3120</v>
@@ -39080,7 +39101,7 @@
         <v>600</v>
       </c>
       <c r="D1571" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1571" t="s" s="3">
         <v>3122</v>
@@ -39097,7 +39118,7 @@
         <v>600</v>
       </c>
       <c r="D1572" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1572" t="s" s="3">
         <v>3124</v>
@@ -39114,7 +39135,7 @@
         <v>600</v>
       </c>
       <c r="D1573" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1573" t="s" s="3">
         <v>3126</v>
@@ -39131,7 +39152,7 @@
         <v>600</v>
       </c>
       <c r="D1574" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1574" t="s" s="3">
         <v>3128</v>
@@ -39148,7 +39169,7 @@
         <v>600</v>
       </c>
       <c r="D1575" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1575" t="s" s="3">
         <v>3130</v>
@@ -39162,10 +39183,10 @@
         <v>3131</v>
       </c>
       <c r="C1576" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1576" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1576" t="s" s="3">
         <v>3132</v>
@@ -39179,10 +39200,10 @@
         <v>3133</v>
       </c>
       <c r="C1577" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1577" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1577" t="s" s="3">
         <v>3134</v>
@@ -39193,16 +39214,16 @@
         <v>1577.0</v>
       </c>
       <c r="B1578" t="s" s="3">
-        <v>3080</v>
+        <v>3135</v>
       </c>
       <c r="C1578" t="s" s="2">
         <v>773</v>
       </c>
       <c r="D1578" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1578" t="s" s="3">
-        <v>3081</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="1579" ht="36.0" customHeight="true">
@@ -39210,16 +39231,16 @@
         <v>1578.0</v>
       </c>
       <c r="B1579" t="s" s="3">
-        <v>3135</v>
+        <v>3137</v>
       </c>
       <c r="C1579" t="s" s="2">
         <v>773</v>
       </c>
       <c r="D1579" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1579" t="s" s="3">
-        <v>3136</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="1580" ht="36.0" customHeight="true">
@@ -39227,16 +39248,16 @@
         <v>1579.0</v>
       </c>
       <c r="B1580" t="s" s="3">
-        <v>3137</v>
+        <v>3084</v>
       </c>
       <c r="C1580" t="s" s="2">
         <v>773</v>
       </c>
       <c r="D1580" t="s" s="2">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="E1580" t="s" s="3">
-        <v>3138</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="1581" ht="36.0" customHeight="true">
@@ -39247,13 +39268,13 @@
         <v>3139</v>
       </c>
       <c r="C1581" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1581" t="s" s="2">
+        <v>3025</v>
+      </c>
+      <c r="E1581" t="s" s="3">
         <v>3140</v>
-      </c>
-      <c r="E1581" t="s" s="3">
-        <v>3141</v>
       </c>
     </row>
     <row r="1582" ht="36.0" customHeight="true">
@@ -39261,16 +39282,16 @@
         <v>1581.0</v>
       </c>
       <c r="B1582" t="s" s="3">
+        <v>3141</v>
+      </c>
+      <c r="C1582" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1582" t="s" s="2">
+        <v>3025</v>
+      </c>
+      <c r="E1582" t="s" s="3">
         <v>3142</v>
-      </c>
-      <c r="C1582" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1582" t="s" s="2">
-        <v>3140</v>
-      </c>
-      <c r="E1582" t="s" s="3">
-        <v>3143</v>
       </c>
     </row>
     <row r="1583" ht="36.0" customHeight="true">
@@ -39278,13 +39299,13 @@
         <v>1582.0</v>
       </c>
       <c r="B1583" t="s" s="3">
+        <v>3143</v>
+      </c>
+      <c r="C1583" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1583" t="s" s="2">
         <v>3144</v>
-      </c>
-      <c r="C1583" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1583" t="s" s="2">
-        <v>3140</v>
       </c>
       <c r="E1583" t="s" s="3">
         <v>3145</v>
@@ -39301,7 +39322,7 @@
         <v>6</v>
       </c>
       <c r="D1584" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1584" t="s" s="3">
         <v>3147</v>
@@ -39318,7 +39339,7 @@
         <v>6</v>
       </c>
       <c r="D1585" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1585" t="s" s="3">
         <v>3149</v>
@@ -39335,7 +39356,7 @@
         <v>6</v>
       </c>
       <c r="D1586" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1586" t="s" s="3">
         <v>3151</v>
@@ -39352,7 +39373,7 @@
         <v>6</v>
       </c>
       <c r="D1587" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1587" t="s" s="3">
         <v>3153</v>
@@ -39369,7 +39390,7 @@
         <v>6</v>
       </c>
       <c r="D1588" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1588" t="s" s="3">
         <v>3155</v>
@@ -39386,7 +39407,7 @@
         <v>6</v>
       </c>
       <c r="D1589" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1589" t="s" s="3">
         <v>3157</v>
@@ -39403,7 +39424,7 @@
         <v>6</v>
       </c>
       <c r="D1590" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1590" t="s" s="3">
         <v>3159</v>
@@ -39420,7 +39441,7 @@
         <v>6</v>
       </c>
       <c r="D1591" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1591" t="s" s="3">
         <v>3161</v>
@@ -39437,7 +39458,7 @@
         <v>6</v>
       </c>
       <c r="D1592" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1592" t="s" s="3">
         <v>3163</v>
@@ -39454,7 +39475,7 @@
         <v>6</v>
       </c>
       <c r="D1593" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1593" t="s" s="3">
         <v>3165</v>
@@ -39471,7 +39492,7 @@
         <v>6</v>
       </c>
       <c r="D1594" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1594" t="s" s="3">
         <v>3167</v>
@@ -39488,7 +39509,7 @@
         <v>6</v>
       </c>
       <c r="D1595" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1595" t="s" s="3">
         <v>3169</v>
@@ -39505,7 +39526,7 @@
         <v>6</v>
       </c>
       <c r="D1596" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1596" t="s" s="3">
         <v>3171</v>
@@ -39522,7 +39543,7 @@
         <v>6</v>
       </c>
       <c r="D1597" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1597" t="s" s="3">
         <v>3173</v>
@@ -39539,7 +39560,7 @@
         <v>6</v>
       </c>
       <c r="D1598" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1598" t="s" s="3">
         <v>3175</v>
@@ -39556,7 +39577,7 @@
         <v>6</v>
       </c>
       <c r="D1599" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1599" t="s" s="3">
         <v>3177</v>
@@ -39573,7 +39594,7 @@
         <v>6</v>
       </c>
       <c r="D1600" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1600" t="s" s="3">
         <v>3179</v>
@@ -39590,7 +39611,7 @@
         <v>6</v>
       </c>
       <c r="D1601" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1601" t="s" s="3">
         <v>3181</v>
@@ -39607,7 +39628,7 @@
         <v>6</v>
       </c>
       <c r="D1602" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1602" t="s" s="3">
         <v>3183</v>
@@ -39624,7 +39645,7 @@
         <v>6</v>
       </c>
       <c r="D1603" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1603" t="s" s="3">
         <v>3185</v>
@@ -39641,7 +39662,7 @@
         <v>6</v>
       </c>
       <c r="D1604" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1604" t="s" s="3">
         <v>3187</v>
@@ -39658,7 +39679,7 @@
         <v>6</v>
       </c>
       <c r="D1605" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1605" t="s" s="3">
         <v>3189</v>
@@ -39675,7 +39696,7 @@
         <v>6</v>
       </c>
       <c r="D1606" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1606" t="s" s="3">
         <v>3191</v>
@@ -39692,7 +39713,7 @@
         <v>6</v>
       </c>
       <c r="D1607" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1607" t="s" s="3">
         <v>3193</v>
@@ -39709,7 +39730,7 @@
         <v>6</v>
       </c>
       <c r="D1608" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1608" t="s" s="3">
         <v>3195</v>
@@ -39726,7 +39747,7 @@
         <v>6</v>
       </c>
       <c r="D1609" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1609" t="s" s="3">
         <v>3197</v>
@@ -39743,7 +39764,7 @@
         <v>6</v>
       </c>
       <c r="D1610" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1610" t="s" s="3">
         <v>3199</v>
@@ -39760,7 +39781,7 @@
         <v>6</v>
       </c>
       <c r="D1611" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1611" t="s" s="3">
         <v>3201</v>
@@ -39777,7 +39798,7 @@
         <v>6</v>
       </c>
       <c r="D1612" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1612" t="s" s="3">
         <v>3203</v>
@@ -39794,7 +39815,7 @@
         <v>6</v>
       </c>
       <c r="D1613" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1613" t="s" s="3">
         <v>3205</v>
@@ -39811,7 +39832,7 @@
         <v>6</v>
       </c>
       <c r="D1614" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1614" t="s" s="3">
         <v>3207</v>
@@ -39828,7 +39849,7 @@
         <v>6</v>
       </c>
       <c r="D1615" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1615" t="s" s="3">
         <v>3209</v>
@@ -39845,7 +39866,7 @@
         <v>6</v>
       </c>
       <c r="D1616" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1616" t="s" s="3">
         <v>3211</v>
@@ -39862,7 +39883,7 @@
         <v>6</v>
       </c>
       <c r="D1617" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1617" t="s" s="3">
         <v>3213</v>
@@ -39879,7 +39900,7 @@
         <v>6</v>
       </c>
       <c r="D1618" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1618" t="s" s="3">
         <v>3215</v>
@@ -39896,7 +39917,7 @@
         <v>6</v>
       </c>
       <c r="D1619" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1619" t="s" s="3">
         <v>3217</v>
@@ -39913,7 +39934,7 @@
         <v>6</v>
       </c>
       <c r="D1620" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1620" t="s" s="3">
         <v>3219</v>
@@ -39930,7 +39951,7 @@
         <v>6</v>
       </c>
       <c r="D1621" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1621" t="s" s="3">
         <v>3221</v>
@@ -39947,7 +39968,7 @@
         <v>6</v>
       </c>
       <c r="D1622" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1622" t="s" s="3">
         <v>3223</v>
@@ -39964,7 +39985,7 @@
         <v>6</v>
       </c>
       <c r="D1623" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1623" t="s" s="3">
         <v>3225</v>
@@ -39981,7 +40002,7 @@
         <v>6</v>
       </c>
       <c r="D1624" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1624" t="s" s="3">
         <v>3227</v>
@@ -39998,7 +40019,7 @@
         <v>6</v>
       </c>
       <c r="D1625" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1625" t="s" s="3">
         <v>3229</v>
@@ -40015,7 +40036,7 @@
         <v>6</v>
       </c>
       <c r="D1626" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1626" t="s" s="3">
         <v>3231</v>
@@ -40032,7 +40053,7 @@
         <v>6</v>
       </c>
       <c r="D1627" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1627" t="s" s="3">
         <v>3233</v>
@@ -40049,7 +40070,7 @@
         <v>6</v>
       </c>
       <c r="D1628" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1628" t="s" s="3">
         <v>3235</v>
@@ -40066,7 +40087,7 @@
         <v>6</v>
       </c>
       <c r="D1629" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1629" t="s" s="3">
         <v>3237</v>
@@ -40083,7 +40104,7 @@
         <v>6</v>
       </c>
       <c r="D1630" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1630" t="s" s="3">
         <v>3239</v>
@@ -40100,7 +40121,7 @@
         <v>6</v>
       </c>
       <c r="D1631" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1631" t="s" s="3">
         <v>3241</v>
@@ -40117,7 +40138,7 @@
         <v>6</v>
       </c>
       <c r="D1632" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1632" t="s" s="3">
         <v>3243</v>
@@ -40134,7 +40155,7 @@
         <v>6</v>
       </c>
       <c r="D1633" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1633" t="s" s="3">
         <v>3245</v>
@@ -40151,7 +40172,7 @@
         <v>6</v>
       </c>
       <c r="D1634" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1634" t="s" s="3">
         <v>3247</v>
@@ -40168,7 +40189,7 @@
         <v>6</v>
       </c>
       <c r="D1635" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1635" t="s" s="3">
         <v>3249</v>
@@ -40185,7 +40206,7 @@
         <v>6</v>
       </c>
       <c r="D1636" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1636" t="s" s="3">
         <v>3251</v>
@@ -40202,7 +40223,7 @@
         <v>6</v>
       </c>
       <c r="D1637" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1637" t="s" s="3">
         <v>3253</v>
@@ -40219,7 +40240,7 @@
         <v>6</v>
       </c>
       <c r="D1638" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1638" t="s" s="3">
         <v>3255</v>
@@ -40236,7 +40257,7 @@
         <v>6</v>
       </c>
       <c r="D1639" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1639" t="s" s="3">
         <v>3257</v>
@@ -40253,7 +40274,7 @@
         <v>6</v>
       </c>
       <c r="D1640" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1640" t="s" s="3">
         <v>3259</v>
@@ -40270,7 +40291,7 @@
         <v>6</v>
       </c>
       <c r="D1641" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1641" t="s" s="3">
         <v>3261</v>
@@ -40287,7 +40308,7 @@
         <v>6</v>
       </c>
       <c r="D1642" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1642" t="s" s="3">
         <v>3263</v>
@@ -40304,7 +40325,7 @@
         <v>6</v>
       </c>
       <c r="D1643" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1643" t="s" s="3">
         <v>3265</v>
@@ -40321,7 +40342,7 @@
         <v>6</v>
       </c>
       <c r="D1644" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1644" t="s" s="3">
         <v>3267</v>
@@ -40338,7 +40359,7 @@
         <v>6</v>
       </c>
       <c r="D1645" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1645" t="s" s="3">
         <v>3269</v>
@@ -40355,7 +40376,7 @@
         <v>6</v>
       </c>
       <c r="D1646" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1646" t="s" s="3">
         <v>3271</v>
@@ -40372,7 +40393,7 @@
         <v>6</v>
       </c>
       <c r="D1647" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1647" t="s" s="3">
         <v>3273</v>
@@ -40389,7 +40410,7 @@
         <v>6</v>
       </c>
       <c r="D1648" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1648" t="s" s="3">
         <v>3275</v>
@@ -40406,7 +40427,7 @@
         <v>6</v>
       </c>
       <c r="D1649" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1649" t="s" s="3">
         <v>3277</v>
@@ -40423,7 +40444,7 @@
         <v>6</v>
       </c>
       <c r="D1650" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1650" t="s" s="3">
         <v>3279</v>
@@ -40440,7 +40461,7 @@
         <v>6</v>
       </c>
       <c r="D1651" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1651" t="s" s="3">
         <v>3281</v>
@@ -40457,7 +40478,7 @@
         <v>6</v>
       </c>
       <c r="D1652" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1652" t="s" s="3">
         <v>3283</v>
@@ -40474,7 +40495,7 @@
         <v>6</v>
       </c>
       <c r="D1653" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1653" t="s" s="3">
         <v>3285</v>
@@ -40491,7 +40512,7 @@
         <v>6</v>
       </c>
       <c r="D1654" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1654" t="s" s="3">
         <v>3287</v>
@@ -40508,7 +40529,7 @@
         <v>6</v>
       </c>
       <c r="D1655" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1655" t="s" s="3">
         <v>3289</v>
@@ -40525,7 +40546,7 @@
         <v>6</v>
       </c>
       <c r="D1656" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1656" t="s" s="3">
         <v>3291</v>
@@ -40542,7 +40563,7 @@
         <v>6</v>
       </c>
       <c r="D1657" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1657" t="s" s="3">
         <v>3293</v>
@@ -40559,7 +40580,7 @@
         <v>6</v>
       </c>
       <c r="D1658" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1658" t="s" s="3">
         <v>3295</v>
@@ -40576,7 +40597,7 @@
         <v>6</v>
       </c>
       <c r="D1659" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1659" t="s" s="3">
         <v>3297</v>
@@ -40593,7 +40614,7 @@
         <v>6</v>
       </c>
       <c r="D1660" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1660" t="s" s="3">
         <v>3299</v>
@@ -40610,7 +40631,7 @@
         <v>6</v>
       </c>
       <c r="D1661" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1661" t="s" s="3">
         <v>3301</v>
@@ -40627,7 +40648,7 @@
         <v>6</v>
       </c>
       <c r="D1662" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1662" t="s" s="3">
         <v>3303</v>
@@ -40644,7 +40665,7 @@
         <v>6</v>
       </c>
       <c r="D1663" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1663" t="s" s="3">
         <v>3305</v>
@@ -40661,7 +40682,7 @@
         <v>6</v>
       </c>
       <c r="D1664" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1664" t="s" s="3">
         <v>3307</v>
@@ -40678,7 +40699,7 @@
         <v>6</v>
       </c>
       <c r="D1665" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1665" t="s" s="3">
         <v>3309</v>
@@ -40695,7 +40716,7 @@
         <v>6</v>
       </c>
       <c r="D1666" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1666" t="s" s="3">
         <v>3311</v>
@@ -40706,16 +40727,16 @@
         <v>1666.0</v>
       </c>
       <c r="B1667" t="s" s="3">
-        <v>920</v>
+        <v>3312</v>
       </c>
       <c r="C1667" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1667" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1667" t="s" s="3">
-        <v>3312</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="1668" ht="36.0" customHeight="true">
@@ -40723,16 +40744,16 @@
         <v>1667.0</v>
       </c>
       <c r="B1668" t="s" s="3">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="C1668" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1668" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1668" t="s" s="3">
-        <v>3314</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="1669" ht="36.0" customHeight="true">
@@ -40740,13 +40761,13 @@
         <v>1668.0</v>
       </c>
       <c r="B1669" t="s" s="3">
-        <v>3315</v>
+        <v>920</v>
       </c>
       <c r="C1669" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1669" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1669" t="s" s="3">
         <v>3316</v>
@@ -40763,7 +40784,7 @@
         <v>6</v>
       </c>
       <c r="D1670" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1670" t="s" s="3">
         <v>3318</v>
@@ -40780,7 +40801,7 @@
         <v>6</v>
       </c>
       <c r="D1671" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1671" t="s" s="3">
         <v>3320</v>
@@ -40797,7 +40818,7 @@
         <v>6</v>
       </c>
       <c r="D1672" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1672" t="s" s="3">
         <v>3322</v>
@@ -40814,7 +40835,7 @@
         <v>6</v>
       </c>
       <c r="D1673" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1673" t="s" s="3">
         <v>3324</v>
@@ -40831,7 +40852,7 @@
         <v>6</v>
       </c>
       <c r="D1674" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1674" t="s" s="3">
         <v>3326</v>
@@ -40848,7 +40869,7 @@
         <v>6</v>
       </c>
       <c r="D1675" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1675" t="s" s="3">
         <v>3328</v>
@@ -40865,7 +40886,7 @@
         <v>6</v>
       </c>
       <c r="D1676" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1676" t="s" s="3">
         <v>3330</v>
@@ -40882,7 +40903,7 @@
         <v>6</v>
       </c>
       <c r="D1677" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1677" t="s" s="3">
         <v>3332</v>
@@ -40899,7 +40920,7 @@
         <v>6</v>
       </c>
       <c r="D1678" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1678" t="s" s="3">
         <v>3334</v>
@@ -40916,7 +40937,7 @@
         <v>6</v>
       </c>
       <c r="D1679" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1679" t="s" s="3">
         <v>3336</v>
@@ -40933,7 +40954,7 @@
         <v>6</v>
       </c>
       <c r="D1680" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1680" t="s" s="3">
         <v>3338</v>
@@ -40950,7 +40971,7 @@
         <v>6</v>
       </c>
       <c r="D1681" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1681" t="s" s="3">
         <v>3340</v>
@@ -40967,7 +40988,7 @@
         <v>6</v>
       </c>
       <c r="D1682" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1682" t="s" s="3">
         <v>3342</v>
@@ -40984,7 +41005,7 @@
         <v>6</v>
       </c>
       <c r="D1683" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1683" t="s" s="3">
         <v>3344</v>
@@ -41001,7 +41022,7 @@
         <v>6</v>
       </c>
       <c r="D1684" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1684" t="s" s="3">
         <v>3346</v>
@@ -41018,7 +41039,7 @@
         <v>6</v>
       </c>
       <c r="D1685" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1685" t="s" s="3">
         <v>3348</v>
@@ -41035,7 +41056,7 @@
         <v>6</v>
       </c>
       <c r="D1686" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1686" t="s" s="3">
         <v>3350</v>
@@ -41052,7 +41073,7 @@
         <v>6</v>
       </c>
       <c r="D1687" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1687" t="s" s="3">
         <v>3352</v>
@@ -41069,7 +41090,7 @@
         <v>6</v>
       </c>
       <c r="D1688" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1688" t="s" s="3">
         <v>3354</v>
@@ -41086,7 +41107,7 @@
         <v>6</v>
       </c>
       <c r="D1689" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1689" t="s" s="3">
         <v>3356</v>
@@ -41103,7 +41124,7 @@
         <v>6</v>
       </c>
       <c r="D1690" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1690" t="s" s="3">
         <v>3358</v>
@@ -41120,7 +41141,7 @@
         <v>6</v>
       </c>
       <c r="D1691" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1691" t="s" s="3">
         <v>3360</v>
@@ -41137,7 +41158,7 @@
         <v>6</v>
       </c>
       <c r="D1692" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1692" t="s" s="3">
         <v>3362</v>
@@ -41154,7 +41175,7 @@
         <v>6</v>
       </c>
       <c r="D1693" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1693" t="s" s="3">
         <v>3364</v>
@@ -41171,7 +41192,7 @@
         <v>6</v>
       </c>
       <c r="D1694" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1694" t="s" s="3">
         <v>3366</v>
@@ -41188,7 +41209,7 @@
         <v>6</v>
       </c>
       <c r="D1695" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1695" t="s" s="3">
         <v>3368</v>
@@ -41205,7 +41226,7 @@
         <v>6</v>
       </c>
       <c r="D1696" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1696" t="s" s="3">
         <v>3370</v>
@@ -41222,7 +41243,7 @@
         <v>6</v>
       </c>
       <c r="D1697" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1697" t="s" s="3">
         <v>3372</v>
@@ -41239,7 +41260,7 @@
         <v>6</v>
       </c>
       <c r="D1698" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1698" t="s" s="3">
         <v>3374</v>
@@ -41256,7 +41277,7 @@
         <v>6</v>
       </c>
       <c r="D1699" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1699" t="s" s="3">
         <v>3376</v>
@@ -41273,7 +41294,7 @@
         <v>6</v>
       </c>
       <c r="D1700" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1700" t="s" s="3">
         <v>3378</v>
@@ -41290,7 +41311,7 @@
         <v>6</v>
       </c>
       <c r="D1701" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1701" t="s" s="3">
         <v>3380</v>
@@ -41307,7 +41328,7 @@
         <v>6</v>
       </c>
       <c r="D1702" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1702" t="s" s="3">
         <v>3382</v>
@@ -41324,7 +41345,7 @@
         <v>6</v>
       </c>
       <c r="D1703" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1703" t="s" s="3">
         <v>3384</v>
@@ -41341,7 +41362,7 @@
         <v>6</v>
       </c>
       <c r="D1704" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1704" t="s" s="3">
         <v>3386</v>
@@ -41355,10 +41376,10 @@
         <v>3387</v>
       </c>
       <c r="C1705" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1705" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1705" t="s" s="3">
         <v>3388</v>
@@ -41372,10 +41393,10 @@
         <v>3389</v>
       </c>
       <c r="C1706" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1706" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1706" t="s" s="3">
         <v>3390</v>
@@ -41392,7 +41413,7 @@
         <v>600</v>
       </c>
       <c r="D1707" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1707" t="s" s="3">
         <v>3392</v>
@@ -41409,7 +41430,7 @@
         <v>600</v>
       </c>
       <c r="D1708" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1708" t="s" s="3">
         <v>3394</v>
@@ -41426,7 +41447,7 @@
         <v>600</v>
       </c>
       <c r="D1709" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1709" t="s" s="3">
         <v>3396</v>
@@ -41443,7 +41464,7 @@
         <v>600</v>
       </c>
       <c r="D1710" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1710" t="s" s="3">
         <v>3398</v>
@@ -41460,7 +41481,7 @@
         <v>600</v>
       </c>
       <c r="D1711" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1711" t="s" s="3">
         <v>3400</v>
@@ -41477,7 +41498,7 @@
         <v>600</v>
       </c>
       <c r="D1712" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1712" t="s" s="3">
         <v>3402</v>
@@ -41494,7 +41515,7 @@
         <v>600</v>
       </c>
       <c r="D1713" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1713" t="s" s="3">
         <v>3404</v>
@@ -41511,7 +41532,7 @@
         <v>600</v>
       </c>
       <c r="D1714" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1714" t="s" s="3">
         <v>3406</v>
@@ -41528,7 +41549,7 @@
         <v>600</v>
       </c>
       <c r="D1715" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1715" t="s" s="3">
         <v>3408</v>
@@ -41545,7 +41566,7 @@
         <v>600</v>
       </c>
       <c r="D1716" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1716" t="s" s="3">
         <v>3410</v>
@@ -41562,7 +41583,7 @@
         <v>600</v>
       </c>
       <c r="D1717" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1717" t="s" s="3">
         <v>3412</v>
@@ -41579,7 +41600,7 @@
         <v>600</v>
       </c>
       <c r="D1718" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1718" t="s" s="3">
         <v>3414</v>
@@ -41596,7 +41617,7 @@
         <v>600</v>
       </c>
       <c r="D1719" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1719" t="s" s="3">
         <v>3416</v>
@@ -41613,7 +41634,7 @@
         <v>600</v>
       </c>
       <c r="D1720" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1720" t="s" s="3">
         <v>3418</v>
@@ -41630,7 +41651,7 @@
         <v>600</v>
       </c>
       <c r="D1721" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1721" t="s" s="3">
         <v>3420</v>
@@ -41647,7 +41668,7 @@
         <v>600</v>
       </c>
       <c r="D1722" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1722" t="s" s="3">
         <v>3422</v>
@@ -41664,7 +41685,7 @@
         <v>600</v>
       </c>
       <c r="D1723" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1723" t="s" s="3">
         <v>3424</v>
@@ -41681,7 +41702,7 @@
         <v>600</v>
       </c>
       <c r="D1724" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1724" t="s" s="3">
         <v>3426</v>
@@ -41698,7 +41719,7 @@
         <v>600</v>
       </c>
       <c r="D1725" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1725" t="s" s="3">
         <v>3428</v>
@@ -41715,7 +41736,7 @@
         <v>600</v>
       </c>
       <c r="D1726" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1726" t="s" s="3">
         <v>3430</v>
@@ -41732,7 +41753,7 @@
         <v>600</v>
       </c>
       <c r="D1727" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1727" t="s" s="3">
         <v>3432</v>
@@ -41749,7 +41770,7 @@
         <v>600</v>
       </c>
       <c r="D1728" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1728" t="s" s="3">
         <v>3434</v>
@@ -41766,7 +41787,7 @@
         <v>600</v>
       </c>
       <c r="D1729" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1729" t="s" s="3">
         <v>3436</v>
@@ -41783,7 +41804,7 @@
         <v>600</v>
       </c>
       <c r="D1730" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1730" t="s" s="3">
         <v>3438</v>
@@ -41800,7 +41821,7 @@
         <v>600</v>
       </c>
       <c r="D1731" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1731" t="s" s="3">
         <v>3440</v>
@@ -41817,7 +41838,7 @@
         <v>600</v>
       </c>
       <c r="D1732" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1732" t="s" s="3">
         <v>3442</v>
@@ -41834,10 +41855,10 @@
         <v>600</v>
       </c>
       <c r="D1733" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1733" t="s" s="3">
-        <v>3328</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="1734" ht="36.0" customHeight="true">
@@ -41845,16 +41866,16 @@
         <v>1733.0</v>
       </c>
       <c r="B1734" t="s" s="3">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="C1734" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D1734" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1734" t="s" s="3">
-        <v>3445</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="1735" ht="36.0" customHeight="true">
@@ -41862,16 +41883,16 @@
         <v>1734.0</v>
       </c>
       <c r="B1735" t="s" s="3">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="C1735" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D1735" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1735" t="s" s="3">
-        <v>3447</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="1736" ht="36.0" customHeight="true">
@@ -41885,7 +41906,7 @@
         <v>600</v>
       </c>
       <c r="D1736" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1736" t="s" s="3">
         <v>3449</v>
@@ -41902,7 +41923,7 @@
         <v>600</v>
       </c>
       <c r="D1737" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1737" t="s" s="3">
         <v>3451</v>
@@ -41919,7 +41940,7 @@
         <v>600</v>
       </c>
       <c r="D1738" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1738" t="s" s="3">
         <v>3453</v>
@@ -41936,7 +41957,7 @@
         <v>600</v>
       </c>
       <c r="D1739" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1739" t="s" s="3">
         <v>3455</v>
@@ -41953,7 +41974,7 @@
         <v>600</v>
       </c>
       <c r="D1740" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1740" t="s" s="3">
         <v>3457</v>
@@ -41970,7 +41991,7 @@
         <v>600</v>
       </c>
       <c r="D1741" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1741" t="s" s="3">
         <v>3459</v>
@@ -41987,7 +42008,7 @@
         <v>600</v>
       </c>
       <c r="D1742" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1742" t="s" s="3">
         <v>3461</v>
@@ -42004,7 +42025,7 @@
         <v>600</v>
       </c>
       <c r="D1743" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1743" t="s" s="3">
         <v>3463</v>
@@ -42021,7 +42042,7 @@
         <v>600</v>
       </c>
       <c r="D1744" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1744" t="s" s="3">
         <v>3465</v>
@@ -42038,7 +42059,7 @@
         <v>600</v>
       </c>
       <c r="D1745" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1745" t="s" s="3">
         <v>3467</v>
@@ -42055,7 +42076,7 @@
         <v>600</v>
       </c>
       <c r="D1746" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1746" t="s" s="3">
         <v>3469</v>
@@ -42072,7 +42093,7 @@
         <v>600</v>
       </c>
       <c r="D1747" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1747" t="s" s="3">
         <v>3471</v>
@@ -42089,7 +42110,7 @@
         <v>600</v>
       </c>
       <c r="D1748" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1748" t="s" s="3">
         <v>3473</v>
@@ -42106,7 +42127,7 @@
         <v>600</v>
       </c>
       <c r="D1749" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1749" t="s" s="3">
         <v>3475</v>
@@ -42123,7 +42144,7 @@
         <v>600</v>
       </c>
       <c r="D1750" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1750" t="s" s="3">
         <v>3477</v>
@@ -42140,7 +42161,7 @@
         <v>600</v>
       </c>
       <c r="D1751" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1751" t="s" s="3">
         <v>3479</v>
@@ -42157,7 +42178,7 @@
         <v>600</v>
       </c>
       <c r="D1752" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1752" t="s" s="3">
         <v>3481</v>
@@ -42174,7 +42195,7 @@
         <v>600</v>
       </c>
       <c r="D1753" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1753" t="s" s="3">
         <v>3483</v>
@@ -42191,7 +42212,7 @@
         <v>600</v>
       </c>
       <c r="D1754" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1754" t="s" s="3">
         <v>3485</v>
@@ -42208,7 +42229,7 @@
         <v>600</v>
       </c>
       <c r="D1755" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1755" t="s" s="3">
         <v>3487</v>
@@ -42225,7 +42246,7 @@
         <v>600</v>
       </c>
       <c r="D1756" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1756" t="s" s="3">
         <v>3489</v>
@@ -42242,7 +42263,7 @@
         <v>600</v>
       </c>
       <c r="D1757" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1757" t="s" s="3">
         <v>3491</v>
@@ -42259,7 +42280,7 @@
         <v>600</v>
       </c>
       <c r="D1758" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1758" t="s" s="3">
         <v>3493</v>
@@ -42276,7 +42297,7 @@
         <v>600</v>
       </c>
       <c r="D1759" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1759" t="s" s="3">
         <v>3495</v>
@@ -42293,7 +42314,7 @@
         <v>600</v>
       </c>
       <c r="D1760" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1760" t="s" s="3">
         <v>3497</v>
@@ -42310,7 +42331,7 @@
         <v>600</v>
       </c>
       <c r="D1761" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1761" t="s" s="3">
         <v>3499</v>
@@ -42327,7 +42348,7 @@
         <v>600</v>
       </c>
       <c r="D1762" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1762" t="s" s="3">
         <v>3501</v>
@@ -42344,7 +42365,7 @@
         <v>600</v>
       </c>
       <c r="D1763" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1763" t="s" s="3">
         <v>3503</v>
@@ -42361,7 +42382,7 @@
         <v>600</v>
       </c>
       <c r="D1764" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1764" t="s" s="3">
         <v>3505</v>
@@ -42378,7 +42399,7 @@
         <v>600</v>
       </c>
       <c r="D1765" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1765" t="s" s="3">
         <v>3507</v>
@@ -42395,7 +42416,7 @@
         <v>600</v>
       </c>
       <c r="D1766" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1766" t="s" s="3">
         <v>3509</v>
@@ -42412,7 +42433,7 @@
         <v>600</v>
       </c>
       <c r="D1767" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1767" t="s" s="3">
         <v>3511</v>
@@ -42429,7 +42450,7 @@
         <v>600</v>
       </c>
       <c r="D1768" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1768" t="s" s="3">
         <v>3513</v>
@@ -42443,10 +42464,10 @@
         <v>3514</v>
       </c>
       <c r="C1769" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1769" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1769" t="s" s="3">
         <v>3515</v>
@@ -42460,10 +42481,10 @@
         <v>3516</v>
       </c>
       <c r="C1770" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1770" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1770" t="s" s="3">
         <v>3517</v>
@@ -42480,7 +42501,7 @@
         <v>773</v>
       </c>
       <c r="D1771" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1771" t="s" s="3">
         <v>3519</v>
@@ -42497,7 +42518,7 @@
         <v>773</v>
       </c>
       <c r="D1772" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1772" t="s" s="3">
         <v>3521</v>
@@ -42514,7 +42535,7 @@
         <v>773</v>
       </c>
       <c r="D1773" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="E1773" t="s" s="3">
         <v>3523</v>
@@ -42528,13 +42549,13 @@
         <v>3524</v>
       </c>
       <c r="C1774" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1774" t="s" s="2">
+        <v>3144</v>
+      </c>
+      <c r="E1774" t="s" s="3">
         <v>3525</v>
-      </c>
-      <c r="E1774" t="s" s="3">
-        <v>3526</v>
       </c>
     </row>
     <row r="1775" ht="36.0" customHeight="true">
@@ -42542,16 +42563,16 @@
         <v>1774.0</v>
       </c>
       <c r="B1775" t="s" s="3">
+        <v>3526</v>
+      </c>
+      <c r="C1775" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1775" t="s" s="2">
+        <v>3144</v>
+      </c>
+      <c r="E1775" t="s" s="3">
         <v>3527</v>
-      </c>
-      <c r="C1775" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1775" t="s" s="2">
-        <v>3525</v>
-      </c>
-      <c r="E1775" t="s" s="3">
-        <v>3528</v>
       </c>
     </row>
     <row r="1776" ht="36.0" customHeight="true">
@@ -42559,13 +42580,13 @@
         <v>1775.0</v>
       </c>
       <c r="B1776" t="s" s="3">
+        <v>3528</v>
+      </c>
+      <c r="C1776" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1776" t="s" s="2">
         <v>3529</v>
-      </c>
-      <c r="C1776" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1776" t="s" s="2">
-        <v>3525</v>
       </c>
       <c r="E1776" t="s" s="3">
         <v>3530</v>
@@ -42582,7 +42603,7 @@
         <v>6</v>
       </c>
       <c r="D1777" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1777" t="s" s="3">
         <v>3532</v>
@@ -42599,7 +42620,7 @@
         <v>6</v>
       </c>
       <c r="D1778" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1778" t="s" s="3">
         <v>3534</v>
@@ -42616,7 +42637,7 @@
         <v>6</v>
       </c>
       <c r="D1779" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1779" t="s" s="3">
         <v>3536</v>
@@ -42633,7 +42654,7 @@
         <v>6</v>
       </c>
       <c r="D1780" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1780" t="s" s="3">
         <v>3538</v>
@@ -42650,7 +42671,7 @@
         <v>6</v>
       </c>
       <c r="D1781" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1781" t="s" s="3">
         <v>3540</v>
@@ -42667,7 +42688,7 @@
         <v>6</v>
       </c>
       <c r="D1782" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1782" t="s" s="3">
         <v>3542</v>
@@ -42684,7 +42705,7 @@
         <v>6</v>
       </c>
       <c r="D1783" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1783" t="s" s="3">
         <v>3544</v>
@@ -42701,7 +42722,7 @@
         <v>6</v>
       </c>
       <c r="D1784" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1784" t="s" s="3">
         <v>3546</v>
@@ -42718,7 +42739,7 @@
         <v>6</v>
       </c>
       <c r="D1785" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1785" t="s" s="3">
         <v>3548</v>
@@ -42735,7 +42756,7 @@
         <v>6</v>
       </c>
       <c r="D1786" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1786" t="s" s="3">
         <v>3550</v>
@@ -42752,7 +42773,7 @@
         <v>6</v>
       </c>
       <c r="D1787" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1787" t="s" s="3">
         <v>3552</v>
@@ -42769,7 +42790,7 @@
         <v>6</v>
       </c>
       <c r="D1788" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1788" t="s" s="3">
         <v>3554</v>
@@ -42786,7 +42807,7 @@
         <v>6</v>
       </c>
       <c r="D1789" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1789" t="s" s="3">
         <v>3556</v>
@@ -42803,7 +42824,7 @@
         <v>6</v>
       </c>
       <c r="D1790" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1790" t="s" s="3">
         <v>3558</v>
@@ -42820,7 +42841,7 @@
         <v>6</v>
       </c>
       <c r="D1791" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1791" t="s" s="3">
         <v>3560</v>
@@ -42837,7 +42858,7 @@
         <v>6</v>
       </c>
       <c r="D1792" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1792" t="s" s="3">
         <v>3562</v>
@@ -42854,7 +42875,7 @@
         <v>6</v>
       </c>
       <c r="D1793" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1793" t="s" s="3">
         <v>3564</v>
@@ -42871,7 +42892,7 @@
         <v>6</v>
       </c>
       <c r="D1794" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1794" t="s" s="3">
         <v>3566</v>
@@ -42888,7 +42909,7 @@
         <v>6</v>
       </c>
       <c r="D1795" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1795" t="s" s="3">
         <v>3568</v>
@@ -42905,7 +42926,7 @@
         <v>6</v>
       </c>
       <c r="D1796" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1796" t="s" s="3">
         <v>3570</v>
@@ -42922,7 +42943,7 @@
         <v>6</v>
       </c>
       <c r="D1797" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1797" t="s" s="3">
         <v>3572</v>
@@ -42939,7 +42960,7 @@
         <v>6</v>
       </c>
       <c r="D1798" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1798" t="s" s="3">
         <v>3574</v>
@@ -42956,7 +42977,7 @@
         <v>6</v>
       </c>
       <c r="D1799" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1799" t="s" s="3">
         <v>3576</v>
@@ -42973,7 +42994,7 @@
         <v>6</v>
       </c>
       <c r="D1800" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1800" t="s" s="3">
         <v>3578</v>
@@ -42990,7 +43011,7 @@
         <v>6</v>
       </c>
       <c r="D1801" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1801" t="s" s="3">
         <v>3580</v>
@@ -43007,7 +43028,7 @@
         <v>6</v>
       </c>
       <c r="D1802" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1802" t="s" s="3">
         <v>3582</v>
@@ -43024,7 +43045,7 @@
         <v>6</v>
       </c>
       <c r="D1803" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1803" t="s" s="3">
         <v>3584</v>
@@ -43041,7 +43062,7 @@
         <v>6</v>
       </c>
       <c r="D1804" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1804" t="s" s="3">
         <v>3586</v>
@@ -43058,7 +43079,7 @@
         <v>6</v>
       </c>
       <c r="D1805" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1805" t="s" s="3">
         <v>3588</v>
@@ -43075,7 +43096,7 @@
         <v>6</v>
       </c>
       <c r="D1806" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1806" t="s" s="3">
         <v>3590</v>
@@ -43092,7 +43113,7 @@
         <v>6</v>
       </c>
       <c r="D1807" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1807" t="s" s="3">
         <v>3592</v>
@@ -43109,7 +43130,7 @@
         <v>6</v>
       </c>
       <c r="D1808" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1808" t="s" s="3">
         <v>3594</v>
@@ -43126,7 +43147,7 @@
         <v>6</v>
       </c>
       <c r="D1809" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1809" t="s" s="3">
         <v>3596</v>
@@ -43143,7 +43164,7 @@
         <v>6</v>
       </c>
       <c r="D1810" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1810" t="s" s="3">
         <v>3598</v>
@@ -43160,7 +43181,7 @@
         <v>6</v>
       </c>
       <c r="D1811" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1811" t="s" s="3">
         <v>3600</v>
@@ -43177,7 +43198,7 @@
         <v>6</v>
       </c>
       <c r="D1812" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1812" t="s" s="3">
         <v>3602</v>
@@ -43194,7 +43215,7 @@
         <v>6</v>
       </c>
       <c r="D1813" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1813" t="s" s="3">
         <v>3604</v>
@@ -43211,7 +43232,7 @@
         <v>6</v>
       </c>
       <c r="D1814" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1814" t="s" s="3">
         <v>3606</v>
@@ -43228,7 +43249,7 @@
         <v>6</v>
       </c>
       <c r="D1815" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1815" t="s" s="3">
         <v>3608</v>
@@ -43245,7 +43266,7 @@
         <v>6</v>
       </c>
       <c r="D1816" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1816" t="s" s="3">
         <v>3610</v>
@@ -43262,7 +43283,7 @@
         <v>6</v>
       </c>
       <c r="D1817" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1817" t="s" s="3">
         <v>3612</v>
@@ -43279,7 +43300,7 @@
         <v>6</v>
       </c>
       <c r="D1818" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1818" t="s" s="3">
         <v>3614</v>
@@ -43296,7 +43317,7 @@
         <v>6</v>
       </c>
       <c r="D1819" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1819" t="s" s="3">
         <v>3616</v>
@@ -43313,7 +43334,7 @@
         <v>6</v>
       </c>
       <c r="D1820" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1820" t="s" s="3">
         <v>3618</v>
@@ -43327,10 +43348,10 @@
         <v>3619</v>
       </c>
       <c r="C1821" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1821" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1821" t="s" s="3">
         <v>3620</v>
@@ -43344,10 +43365,10 @@
         <v>3621</v>
       </c>
       <c r="C1822" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1822" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1822" t="s" s="3">
         <v>3622</v>
@@ -43364,7 +43385,7 @@
         <v>600</v>
       </c>
       <c r="D1823" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1823" t="s" s="3">
         <v>3624</v>
@@ -43381,7 +43402,7 @@
         <v>600</v>
       </c>
       <c r="D1824" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1824" t="s" s="3">
         <v>3626</v>
@@ -43398,7 +43419,7 @@
         <v>600</v>
       </c>
       <c r="D1825" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1825" t="s" s="3">
         <v>3628</v>
@@ -43415,7 +43436,7 @@
         <v>600</v>
       </c>
       <c r="D1826" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1826" t="s" s="3">
         <v>3630</v>
@@ -43432,7 +43453,7 @@
         <v>600</v>
       </c>
       <c r="D1827" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1827" t="s" s="3">
         <v>3632</v>
@@ -43449,7 +43470,7 @@
         <v>600</v>
       </c>
       <c r="D1828" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1828" t="s" s="3">
         <v>3634</v>
@@ -43466,7 +43487,7 @@
         <v>600</v>
       </c>
       <c r="D1829" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1829" t="s" s="3">
         <v>3636</v>
@@ -43483,7 +43504,7 @@
         <v>600</v>
       </c>
       <c r="D1830" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1830" t="s" s="3">
         <v>3638</v>
@@ -43500,7 +43521,7 @@
         <v>600</v>
       </c>
       <c r="D1831" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1831" t="s" s="3">
         <v>3640</v>
@@ -43517,7 +43538,7 @@
         <v>600</v>
       </c>
       <c r="D1832" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1832" t="s" s="3">
         <v>3642</v>
@@ -43534,7 +43555,7 @@
         <v>600</v>
       </c>
       <c r="D1833" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1833" t="s" s="3">
         <v>3644</v>
@@ -43551,7 +43572,7 @@
         <v>600</v>
       </c>
       <c r="D1834" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1834" t="s" s="3">
         <v>3646</v>
@@ -43568,7 +43589,7 @@
         <v>600</v>
       </c>
       <c r="D1835" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1835" t="s" s="3">
         <v>3648</v>
@@ -43585,7 +43606,7 @@
         <v>600</v>
       </c>
       <c r="D1836" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1836" t="s" s="3">
         <v>3650</v>
@@ -43602,7 +43623,7 @@
         <v>600</v>
       </c>
       <c r="D1837" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1837" t="s" s="3">
         <v>3652</v>
@@ -43619,7 +43640,7 @@
         <v>600</v>
       </c>
       <c r="D1838" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1838" t="s" s="3">
         <v>3654</v>
@@ -43636,7 +43657,7 @@
         <v>600</v>
       </c>
       <c r="D1839" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1839" t="s" s="3">
         <v>3656</v>
@@ -43653,7 +43674,7 @@
         <v>600</v>
       </c>
       <c r="D1840" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1840" t="s" s="3">
         <v>3658</v>
@@ -43670,7 +43691,7 @@
         <v>600</v>
       </c>
       <c r="D1841" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1841" t="s" s="3">
         <v>3660</v>
@@ -43687,7 +43708,7 @@
         <v>600</v>
       </c>
       <c r="D1842" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1842" t="s" s="3">
         <v>3662</v>
@@ -43704,7 +43725,7 @@
         <v>600</v>
       </c>
       <c r="D1843" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1843" t="s" s="3">
         <v>3664</v>
@@ -43721,7 +43742,7 @@
         <v>600</v>
       </c>
       <c r="D1844" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1844" t="s" s="3">
         <v>3666</v>
@@ -43738,7 +43759,7 @@
         <v>600</v>
       </c>
       <c r="D1845" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1845" t="s" s="3">
         <v>3668</v>
@@ -43755,7 +43776,7 @@
         <v>600</v>
       </c>
       <c r="D1846" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1846" t="s" s="3">
         <v>3670</v>
@@ -43772,7 +43793,7 @@
         <v>600</v>
       </c>
       <c r="D1847" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1847" t="s" s="3">
         <v>3672</v>
@@ -43789,7 +43810,7 @@
         <v>600</v>
       </c>
       <c r="D1848" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1848" t="s" s="3">
         <v>3674</v>
@@ -43806,7 +43827,7 @@
         <v>600</v>
       </c>
       <c r="D1849" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1849" t="s" s="3">
         <v>3676</v>
@@ -43823,7 +43844,7 @@
         <v>600</v>
       </c>
       <c r="D1850" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1850" t="s" s="3">
         <v>3678</v>
@@ -43840,7 +43861,7 @@
         <v>600</v>
       </c>
       <c r="D1851" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1851" t="s" s="3">
         <v>3680</v>
@@ -43857,7 +43878,7 @@
         <v>600</v>
       </c>
       <c r="D1852" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1852" t="s" s="3">
         <v>3682</v>
@@ -43874,7 +43895,7 @@
         <v>600</v>
       </c>
       <c r="D1853" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1853" t="s" s="3">
         <v>3684</v>
@@ -43891,7 +43912,7 @@
         <v>600</v>
       </c>
       <c r="D1854" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1854" t="s" s="3">
         <v>3686</v>
@@ -43905,10 +43926,10 @@
         <v>3687</v>
       </c>
       <c r="C1855" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1855" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1855" t="s" s="3">
         <v>3688</v>
@@ -43922,10 +43943,10 @@
         <v>3689</v>
       </c>
       <c r="C1856" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D1856" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1856" t="s" s="3">
         <v>3690</v>
@@ -43942,7 +43963,7 @@
         <v>773</v>
       </c>
       <c r="D1857" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1857" t="s" s="3">
         <v>3692</v>
@@ -43959,7 +43980,7 @@
         <v>773</v>
       </c>
       <c r="D1858" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1858" t="s" s="3">
         <v>3694</v>
@@ -43976,7 +43997,7 @@
         <v>773</v>
       </c>
       <c r="D1859" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1859" t="s" s="3">
         <v>3696</v>
@@ -43993,7 +44014,7 @@
         <v>773</v>
       </c>
       <c r="D1860" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1860" t="s" s="3">
         <v>3698</v>
@@ -44010,7 +44031,7 @@
         <v>773</v>
       </c>
       <c r="D1861" t="s" s="2">
-        <v>3525</v>
+        <v>3529</v>
       </c>
       <c r="E1861" t="s" s="3">
         <v>3700</v>
@@ -44024,13 +44045,13 @@
         <v>3701</v>
       </c>
       <c r="C1862" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D1862" t="s" s="2">
+        <v>3529</v>
+      </c>
+      <c r="E1862" t="s" s="3">
         <v>3702</v>
-      </c>
-      <c r="E1862" t="s" s="3">
-        <v>3703</v>
       </c>
     </row>
     <row r="1863" ht="36.0" customHeight="true">
@@ -44038,16 +44059,16 @@
         <v>1862.0</v>
       </c>
       <c r="B1863" t="s" s="3">
+        <v>3703</v>
+      </c>
+      <c r="C1863" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D1863" t="s" s="2">
+        <v>3529</v>
+      </c>
+      <c r="E1863" t="s" s="3">
         <v>3704</v>
-      </c>
-      <c r="C1863" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1863" t="s" s="2">
-        <v>3702</v>
-      </c>
-      <c r="E1863" t="s" s="3">
-        <v>3705</v>
       </c>
     </row>
     <row r="1864" ht="36.0" customHeight="true">
@@ -44055,13 +44076,13 @@
         <v>1863.0</v>
       </c>
       <c r="B1864" t="s" s="3">
+        <v>3705</v>
+      </c>
+      <c r="C1864" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1864" t="s" s="2">
         <v>3706</v>
-      </c>
-      <c r="C1864" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1864" t="s" s="2">
-        <v>3702</v>
       </c>
       <c r="E1864" t="s" s="3">
         <v>3707</v>
@@ -44078,7 +44099,7 @@
         <v>6</v>
       </c>
       <c r="D1865" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1865" t="s" s="3">
         <v>3709</v>
@@ -44095,7 +44116,7 @@
         <v>6</v>
       </c>
       <c r="D1866" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1866" t="s" s="3">
         <v>3711</v>
@@ -44112,7 +44133,7 @@
         <v>6</v>
       </c>
       <c r="D1867" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1867" t="s" s="3">
         <v>3713</v>
@@ -44129,7 +44150,7 @@
         <v>6</v>
       </c>
       <c r="D1868" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1868" t="s" s="3">
         <v>3715</v>
@@ -44146,7 +44167,7 @@
         <v>6</v>
       </c>
       <c r="D1869" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1869" t="s" s="3">
         <v>3717</v>
@@ -44163,7 +44184,7 @@
         <v>6</v>
       </c>
       <c r="D1870" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1870" t="s" s="3">
         <v>3719</v>
@@ -44180,7 +44201,7 @@
         <v>6</v>
       </c>
       <c r="D1871" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1871" t="s" s="3">
         <v>3721</v>
@@ -44197,7 +44218,7 @@
         <v>6</v>
       </c>
       <c r="D1872" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1872" t="s" s="3">
         <v>3723</v>
@@ -44214,7 +44235,7 @@
         <v>6</v>
       </c>
       <c r="D1873" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1873" t="s" s="3">
         <v>3725</v>
@@ -44231,7 +44252,7 @@
         <v>6</v>
       </c>
       <c r="D1874" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1874" t="s" s="3">
         <v>3727</v>
@@ -44248,7 +44269,7 @@
         <v>6</v>
       </c>
       <c r="D1875" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1875" t="s" s="3">
         <v>3729</v>
@@ -44265,7 +44286,7 @@
         <v>6</v>
       </c>
       <c r="D1876" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1876" t="s" s="3">
         <v>3731</v>
@@ -44282,7 +44303,7 @@
         <v>6</v>
       </c>
       <c r="D1877" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1877" t="s" s="3">
         <v>3733</v>
@@ -44299,7 +44320,7 @@
         <v>6</v>
       </c>
       <c r="D1878" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1878" t="s" s="3">
         <v>3735</v>
@@ -44316,7 +44337,7 @@
         <v>6</v>
       </c>
       <c r="D1879" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1879" t="s" s="3">
         <v>3737</v>
@@ -44333,7 +44354,7 @@
         <v>6</v>
       </c>
       <c r="D1880" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1880" t="s" s="3">
         <v>3739</v>
@@ -44350,7 +44371,7 @@
         <v>6</v>
       </c>
       <c r="D1881" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1881" t="s" s="3">
         <v>3741</v>
@@ -44367,7 +44388,7 @@
         <v>6</v>
       </c>
       <c r="D1882" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1882" t="s" s="3">
         <v>3743</v>
@@ -44384,7 +44405,7 @@
         <v>6</v>
       </c>
       <c r="D1883" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1883" t="s" s="3">
         <v>3745</v>
@@ -44401,7 +44422,7 @@
         <v>6</v>
       </c>
       <c r="D1884" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1884" t="s" s="3">
         <v>3747</v>
@@ -44418,7 +44439,7 @@
         <v>6</v>
       </c>
       <c r="D1885" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1885" t="s" s="3">
         <v>3749</v>
@@ -44435,7 +44456,7 @@
         <v>6</v>
       </c>
       <c r="D1886" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1886" t="s" s="3">
         <v>3751</v>
@@ -44452,7 +44473,7 @@
         <v>6</v>
       </c>
       <c r="D1887" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1887" t="s" s="3">
         <v>3753</v>
@@ -44469,7 +44490,7 @@
         <v>6</v>
       </c>
       <c r="D1888" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1888" t="s" s="3">
         <v>3755</v>
@@ -44486,7 +44507,7 @@
         <v>6</v>
       </c>
       <c r="D1889" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1889" t="s" s="3">
         <v>3757</v>
@@ -44503,7 +44524,7 @@
         <v>6</v>
       </c>
       <c r="D1890" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1890" t="s" s="3">
         <v>3759</v>
@@ -44520,7 +44541,7 @@
         <v>6</v>
       </c>
       <c r="D1891" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1891" t="s" s="3">
         <v>3761</v>
@@ -44537,7 +44558,7 @@
         <v>6</v>
       </c>
       <c r="D1892" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1892" t="s" s="3">
         <v>3763</v>
@@ -44554,7 +44575,7 @@
         <v>6</v>
       </c>
       <c r="D1893" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1893" t="s" s="3">
         <v>3765</v>
@@ -44571,7 +44592,7 @@
         <v>6</v>
       </c>
       <c r="D1894" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1894" t="s" s="3">
         <v>3767</v>
@@ -44588,7 +44609,7 @@
         <v>6</v>
       </c>
       <c r="D1895" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1895" t="s" s="3">
         <v>3769</v>
@@ -44605,7 +44626,7 @@
         <v>6</v>
       </c>
       <c r="D1896" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1896" t="s" s="3">
         <v>3771</v>
@@ -44622,7 +44643,7 @@
         <v>6</v>
       </c>
       <c r="D1897" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1897" t="s" s="3">
         <v>3773</v>
@@ -44639,7 +44660,7 @@
         <v>6</v>
       </c>
       <c r="D1898" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1898" t="s" s="3">
         <v>3775</v>
@@ -44656,7 +44677,7 @@
         <v>6</v>
       </c>
       <c r="D1899" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1899" t="s" s="3">
         <v>3777</v>
@@ -44673,7 +44694,7 @@
         <v>6</v>
       </c>
       <c r="D1900" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1900" t="s" s="3">
         <v>3779</v>
@@ -44690,7 +44711,7 @@
         <v>6</v>
       </c>
       <c r="D1901" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1901" t="s" s="3">
         <v>3781</v>
@@ -44707,7 +44728,7 @@
         <v>6</v>
       </c>
       <c r="D1902" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1902" t="s" s="3">
         <v>3783</v>
@@ -44724,7 +44745,7 @@
         <v>6</v>
       </c>
       <c r="D1903" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1903" t="s" s="3">
         <v>3785</v>
@@ -44741,7 +44762,7 @@
         <v>6</v>
       </c>
       <c r="D1904" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1904" t="s" s="3">
         <v>3787</v>
@@ -44758,7 +44779,7 @@
         <v>6</v>
       </c>
       <c r="D1905" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1905" t="s" s="3">
         <v>3789</v>
@@ -44775,7 +44796,7 @@
         <v>6</v>
       </c>
       <c r="D1906" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1906" t="s" s="3">
         <v>3791</v>
@@ -44792,7 +44813,7 @@
         <v>6</v>
       </c>
       <c r="D1907" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1907" t="s" s="3">
         <v>3793</v>
@@ -44809,7 +44830,7 @@
         <v>6</v>
       </c>
       <c r="D1908" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1908" t="s" s="3">
         <v>3795</v>
@@ -44826,7 +44847,7 @@
         <v>6</v>
       </c>
       <c r="D1909" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1909" t="s" s="3">
         <v>3797</v>
@@ -44843,7 +44864,7 @@
         <v>6</v>
       </c>
       <c r="D1910" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1910" t="s" s="3">
         <v>3799</v>
@@ -44860,7 +44881,7 @@
         <v>6</v>
       </c>
       <c r="D1911" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1911" t="s" s="3">
         <v>3801</v>
@@ -44877,7 +44898,7 @@
         <v>6</v>
       </c>
       <c r="D1912" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1912" t="s" s="3">
         <v>3803</v>
@@ -44894,7 +44915,7 @@
         <v>6</v>
       </c>
       <c r="D1913" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1913" t="s" s="3">
         <v>3805</v>
@@ -44911,7 +44932,7 @@
         <v>6</v>
       </c>
       <c r="D1914" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1914" t="s" s="3">
         <v>3807</v>
@@ -44928,7 +44949,7 @@
         <v>6</v>
       </c>
       <c r="D1915" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1915" t="s" s="3">
         <v>3809</v>
@@ -44945,7 +44966,7 @@
         <v>6</v>
       </c>
       <c r="D1916" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1916" t="s" s="3">
         <v>3811</v>
@@ -44962,7 +44983,7 @@
         <v>6</v>
       </c>
       <c r="D1917" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1917" t="s" s="3">
         <v>3813</v>
@@ -44979,7 +45000,7 @@
         <v>6</v>
       </c>
       <c r="D1918" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1918" t="s" s="3">
         <v>3815</v>
@@ -44996,7 +45017,7 @@
         <v>6</v>
       </c>
       <c r="D1919" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1919" t="s" s="3">
         <v>3817</v>
@@ -45013,7 +45034,7 @@
         <v>6</v>
       </c>
       <c r="D1920" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1920" t="s" s="3">
         <v>3819</v>
@@ -45030,7 +45051,7 @@
         <v>6</v>
       </c>
       <c r="D1921" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1921" t="s" s="3">
         <v>3821</v>
@@ -45047,7 +45068,7 @@
         <v>6</v>
       </c>
       <c r="D1922" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1922" t="s" s="3">
         <v>3823</v>
@@ -45058,16 +45079,16 @@
         <v>1922.0</v>
       </c>
       <c r="B1923" t="s" s="3">
-        <v>2911</v>
+        <v>3824</v>
       </c>
       <c r="C1923" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1923" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1923" t="s" s="3">
-        <v>3824</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="1924" ht="36.0" customHeight="true">
@@ -45075,16 +45096,16 @@
         <v>1923.0</v>
       </c>
       <c r="B1924" t="s" s="3">
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="C1924" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1924" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1924" t="s" s="3">
-        <v>3826</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="1925" ht="36.0" customHeight="true">
@@ -45092,13 +45113,13 @@
         <v>1924.0</v>
       </c>
       <c r="B1925" t="s" s="3">
-        <v>3827</v>
+        <v>2915</v>
       </c>
       <c r="C1925" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1925" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1925" t="s" s="3">
         <v>3828</v>
@@ -45115,7 +45136,7 @@
         <v>6</v>
       </c>
       <c r="D1926" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1926" t="s" s="3">
         <v>3830</v>
@@ -45132,7 +45153,7 @@
         <v>6</v>
       </c>
       <c r="D1927" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1927" t="s" s="3">
         <v>3832</v>
@@ -45149,7 +45170,7 @@
         <v>6</v>
       </c>
       <c r="D1928" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1928" t="s" s="3">
         <v>3834</v>
@@ -45166,7 +45187,7 @@
         <v>6</v>
       </c>
       <c r="D1929" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1929" t="s" s="3">
         <v>3836</v>
@@ -45183,7 +45204,7 @@
         <v>6</v>
       </c>
       <c r="D1930" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1930" t="s" s="3">
         <v>3838</v>
@@ -45200,7 +45221,7 @@
         <v>6</v>
       </c>
       <c r="D1931" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1931" t="s" s="3">
         <v>3840</v>
@@ -45217,7 +45238,7 @@
         <v>6</v>
       </c>
       <c r="D1932" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1932" t="s" s="3">
         <v>3842</v>
@@ -45234,7 +45255,7 @@
         <v>6</v>
       </c>
       <c r="D1933" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1933" t="s" s="3">
         <v>3844</v>
@@ -45251,7 +45272,7 @@
         <v>6</v>
       </c>
       <c r="D1934" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1934" t="s" s="3">
         <v>3846</v>
@@ -45268,7 +45289,7 @@
         <v>6</v>
       </c>
       <c r="D1935" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1935" t="s" s="3">
         <v>3848</v>
@@ -45285,7 +45306,7 @@
         <v>6</v>
       </c>
       <c r="D1936" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1936" t="s" s="3">
         <v>3850</v>
@@ -45302,7 +45323,7 @@
         <v>6</v>
       </c>
       <c r="D1937" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1937" t="s" s="3">
         <v>3852</v>
@@ -45319,7 +45340,7 @@
         <v>6</v>
       </c>
       <c r="D1938" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1938" t="s" s="3">
         <v>3854</v>
@@ -45336,7 +45357,7 @@
         <v>6</v>
       </c>
       <c r="D1939" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1939" t="s" s="3">
         <v>3856</v>
@@ -45353,7 +45374,7 @@
         <v>6</v>
       </c>
       <c r="D1940" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1940" t="s" s="3">
         <v>3858</v>
@@ -45370,7 +45391,7 @@
         <v>6</v>
       </c>
       <c r="D1941" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1941" t="s" s="3">
         <v>3860</v>
@@ -45387,7 +45408,7 @@
         <v>6</v>
       </c>
       <c r="D1942" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1942" t="s" s="3">
         <v>3862</v>
@@ -45404,7 +45425,7 @@
         <v>6</v>
       </c>
       <c r="D1943" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1943" t="s" s="3">
         <v>3864</v>
@@ -45421,7 +45442,7 @@
         <v>6</v>
       </c>
       <c r="D1944" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1944" t="s" s="3">
         <v>3866</v>
@@ -45438,7 +45459,7 @@
         <v>6</v>
       </c>
       <c r="D1945" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1945" t="s" s="3">
         <v>3868</v>
@@ -45455,7 +45476,7 @@
         <v>6</v>
       </c>
       <c r="D1946" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1946" t="s" s="3">
         <v>3870</v>
@@ -45472,7 +45493,7 @@
         <v>6</v>
       </c>
       <c r="D1947" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1947" t="s" s="3">
         <v>3872</v>
@@ -45489,7 +45510,7 @@
         <v>6</v>
       </c>
       <c r="D1948" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1948" t="s" s="3">
         <v>3874</v>
@@ -45506,7 +45527,7 @@
         <v>6</v>
       </c>
       <c r="D1949" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1949" t="s" s="3">
         <v>3876</v>
@@ -45523,7 +45544,7 @@
         <v>6</v>
       </c>
       <c r="D1950" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1950" t="s" s="3">
         <v>3878</v>
@@ -45540,7 +45561,7 @@
         <v>6</v>
       </c>
       <c r="D1951" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1951" t="s" s="3">
         <v>3880</v>
@@ -45557,7 +45578,7 @@
         <v>6</v>
       </c>
       <c r="D1952" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1952" t="s" s="3">
         <v>3882</v>
@@ -45574,7 +45595,7 @@
         <v>6</v>
       </c>
       <c r="D1953" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1953" t="s" s="3">
         <v>3884</v>
@@ -45591,7 +45612,7 @@
         <v>6</v>
       </c>
       <c r="D1954" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1954" t="s" s="3">
         <v>3886</v>
@@ -45608,7 +45629,7 @@
         <v>6</v>
       </c>
       <c r="D1955" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1955" t="s" s="3">
         <v>3888</v>
@@ -45625,7 +45646,7 @@
         <v>6</v>
       </c>
       <c r="D1956" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1956" t="s" s="3">
         <v>3890</v>
@@ -45642,7 +45663,7 @@
         <v>6</v>
       </c>
       <c r="D1957" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1957" t="s" s="3">
         <v>3892</v>
@@ -45659,7 +45680,7 @@
         <v>6</v>
       </c>
       <c r="D1958" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1958" t="s" s="3">
         <v>3894</v>
@@ -45676,7 +45697,7 @@
         <v>6</v>
       </c>
       <c r="D1959" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1959" t="s" s="3">
         <v>3896</v>
@@ -45693,7 +45714,7 @@
         <v>6</v>
       </c>
       <c r="D1960" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3898</v>
@@ -45710,7 +45731,7 @@
         <v>6</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1961" t="s" s="3">
         <v>3900</v>
@@ -45727,7 +45748,7 @@
         <v>6</v>
       </c>
       <c r="D1962" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1962" t="s" s="3">
         <v>3902</v>
@@ -45738,16 +45759,16 @@
         <v>1962.0</v>
       </c>
       <c r="B1963" t="s" s="3">
-        <v>2347</v>
+        <v>3903</v>
       </c>
       <c r="C1963" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1963" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1963" t="s" s="3">
-        <v>3903</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="1964" ht="36.0" customHeight="true">
@@ -45755,16 +45776,16 @@
         <v>1963.0</v>
       </c>
       <c r="B1964" t="s" s="3">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="C1964" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1964" t="s" s="3">
-        <v>3905</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="1965" ht="36.0" customHeight="true">
@@ -45772,13 +45793,13 @@
         <v>1964.0</v>
       </c>
       <c r="B1965" t="s" s="3">
-        <v>3906</v>
+        <v>2347</v>
       </c>
       <c r="C1965" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3907</v>
@@ -45795,7 +45816,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3909</v>
@@ -45812,7 +45833,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3911</v>
@@ -45829,7 +45850,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3913</v>
@@ -45846,7 +45867,7 @@
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1969" t="s" s="3">
         <v>3915</v>
@@ -45863,7 +45884,7 @@
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1970" t="s" s="3">
         <v>3917</v>
@@ -45880,7 +45901,7 @@
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3919</v>
@@ -45894,10 +45915,10 @@
         <v>3920</v>
       </c>
       <c r="C1972" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3921</v>
@@ -45911,10 +45932,10 @@
         <v>3922</v>
       </c>
       <c r="C1973" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3923</v>
@@ -45931,7 +45952,7 @@
         <v>600</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3925</v>
@@ -45948,7 +45969,7 @@
         <v>600</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3927</v>
@@ -45965,7 +45986,7 @@
         <v>600</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3929</v>
@@ -45982,7 +46003,7 @@
         <v>600</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3931</v>
@@ -45999,7 +46020,7 @@
         <v>600</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3933</v>
@@ -46016,7 +46037,7 @@
         <v>600</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3935</v>
@@ -46033,7 +46054,7 @@
         <v>600</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3937</v>
@@ -46050,7 +46071,7 @@
         <v>600</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3939</v>
@@ -46067,7 +46088,7 @@
         <v>600</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3941</v>
@@ -46084,7 +46105,7 @@
         <v>600</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3943</v>
@@ -46101,7 +46122,7 @@
         <v>600</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3945</v>
@@ -46118,7 +46139,7 @@
         <v>600</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3947</v>
@@ -46135,7 +46156,7 @@
         <v>600</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3949</v>
@@ -46152,7 +46173,7 @@
         <v>600</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3951</v>
@@ -46169,7 +46190,7 @@
         <v>600</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3953</v>
@@ -46186,7 +46207,7 @@
         <v>600</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3955</v>
@@ -46203,7 +46224,7 @@
         <v>600</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3957</v>
@@ -46220,7 +46241,7 @@
         <v>600</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3959</v>
@@ -46237,7 +46258,7 @@
         <v>600</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3961</v>
@@ -46254,7 +46275,7 @@
         <v>600</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3963</v>
@@ -46271,7 +46292,7 @@
         <v>600</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3965</v>
@@ -46288,7 +46309,7 @@
         <v>600</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3967</v>
@@ -46305,7 +46326,7 @@
         <v>600</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3969</v>
@@ -46322,7 +46343,7 @@
         <v>600</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3971</v>
@@ -46339,7 +46360,7 @@
         <v>600</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3973</v>
@@ -46356,7 +46377,7 @@
         <v>600</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3975</v>
@@ -46373,7 +46394,7 @@
         <v>600</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3977</v>
@@ -46390,7 +46411,7 @@
         <v>600</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3979</v>
@@ -46407,7 +46428,7 @@
         <v>600</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3981</v>
@@ -46424,7 +46445,7 @@
         <v>600</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3983</v>
@@ -46441,7 +46462,7 @@
         <v>600</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3985</v>
@@ -46458,7 +46479,7 @@
         <v>600</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3987</v>
@@ -46475,10 +46496,10 @@
         <v>600</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2006" t="s" s="3">
-        <v>3749</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="2007" ht="36.0" customHeight="true">
@@ -46486,16 +46507,16 @@
         <v>2006.0</v>
       </c>
       <c r="B2007" t="s" s="3">
-        <v>3989</v>
+        <v>3990</v>
       </c>
       <c r="C2007" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2007" t="s" s="3">
-        <v>3990</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="2008" ht="36.0" customHeight="true">
@@ -46503,16 +46524,16 @@
         <v>2007.0</v>
       </c>
       <c r="B2008" t="s" s="3">
-        <v>3991</v>
+        <v>3992</v>
       </c>
       <c r="C2008" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2008" t="s" s="3">
-        <v>3992</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="2009" ht="36.0" customHeight="true">
@@ -46526,7 +46547,7 @@
         <v>600</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3994</v>
@@ -46543,7 +46564,7 @@
         <v>600</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3996</v>
@@ -46557,10 +46578,10 @@
         <v>3997</v>
       </c>
       <c r="C2011" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3998</v>
@@ -46574,10 +46595,10 @@
         <v>3999</v>
       </c>
       <c r="C2012" t="s" s="2">
-        <v>773</v>
+        <v>600</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>4000</v>
@@ -46588,16 +46609,16 @@
         <v>2012.0</v>
       </c>
       <c r="B2013" t="s" s="3">
-        <v>3984</v>
+        <v>4001</v>
       </c>
       <c r="C2013" t="s" s="2">
         <v>773</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3702</v>
+        <v>3706</v>
       </c>
       <c r="E2013" t="s" s="3">
-        <v>4001</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="2014" ht="36.0" customHeight="true">
@@ -46605,13 +46626,13 @@
         <v>2013.0</v>
       </c>
       <c r="B2014" t="s" s="3">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="C2014" t="s" s="2">
-        <v>6</v>
+        <v>773</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>4003</v>
+        <v>3706</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>4004</v>
@@ -46622,16 +46643,16 @@
         <v>2014.0</v>
       </c>
       <c r="B2015" t="s" s="3">
+        <v>3988</v>
+      </c>
+      <c r="C2015" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="D2015" t="s" s="2">
+        <v>3706</v>
+      </c>
+      <c r="E2015" t="s" s="3">
         <v>4005</v>
-      </c>
-      <c r="C2015" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2015" t="s" s="2">
-        <v>4003</v>
-      </c>
-      <c r="E2015" t="s" s="3">
-        <v>4006</v>
       </c>
     </row>
     <row r="2016" ht="36.0" customHeight="true">
@@ -46639,13 +46660,13 @@
         <v>2015.0</v>
       </c>
       <c r="B2016" t="s" s="3">
+        <v>4006</v>
+      </c>
+      <c r="C2016" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2016" t="s" s="2">
         <v>4007</v>
-      </c>
-      <c r="C2016" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2016" t="s" s="2">
-        <v>4003</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4008</v>
@@ -46662,7 +46683,7 @@
         <v>6</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4010</v>
@@ -46679,7 +46700,7 @@
         <v>6</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4012</v>
@@ -46696,7 +46717,7 @@
         <v>6</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4014</v>
@@ -46713,7 +46734,7 @@
         <v>6</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4016</v>
@@ -46730,7 +46751,7 @@
         <v>6</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4018</v>
@@ -46747,7 +46768,7 @@
         <v>6</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4020</v>
@@ -46764,7 +46785,7 @@
         <v>6</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4022</v>
@@ -46781,7 +46802,7 @@
         <v>6</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4024</v>
@@ -46798,7 +46819,7 @@
         <v>6</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4026</v>
@@ -46815,7 +46836,7 @@
         <v>6</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4028</v>
@@ -46832,7 +46853,7 @@
         <v>6</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4030</v>
@@ -46849,7 +46870,7 @@
         <v>6</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4032</v>
@@ -46866,7 +46887,7 @@
         <v>6</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4034</v>
@@ -46883,7 +46904,7 @@
         <v>6</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4036</v>
@@ -46900,7 +46921,7 @@
         <v>6</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4038</v>
@@ -46917,7 +46938,7 @@
         <v>6</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4040</v>
@@ -46934,7 +46955,7 @@
         <v>6</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4042</v>
@@ -46951,7 +46972,7 @@
         <v>6</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4044</v>
@@ -46968,7 +46989,7 @@
         <v>6</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2035" t="s" s="3">
         <v>4046</v>
@@ -46985,7 +47006,7 @@
         <v>6</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4048</v>
@@ -47002,7 +47023,7 @@
         <v>6</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2037" t="s" s="3">
         <v>4050</v>
@@ -47019,7 +47040,7 @@
         <v>6</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4052</v>
@@ -47036,7 +47057,7 @@
         <v>6</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2039" t="s" s="3">
         <v>4054</v>
@@ -47053,7 +47074,7 @@
         <v>6</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2040" t="s" s="3">
         <v>4056</v>
@@ -47070,7 +47091,7 @@
         <v>6</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4058</v>
@@ -47084,13 +47105,13 @@
         <v>4059</v>
       </c>
       <c r="C2042" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2042" t="s" s="3">
-        <v>4040</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="2043" ht="36.0" customHeight="true">
@@ -47098,16 +47119,16 @@
         <v>2042.0</v>
       </c>
       <c r="B2043" t="s" s="3">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="C2043" t="s" s="2">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2043" t="s" s="3">
-        <v>4061</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="2044" ht="36.0" customHeight="true">
@@ -47115,16 +47136,16 @@
         <v>2043.0</v>
       </c>
       <c r="B2044" t="s" s="3">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="C2044" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2044" t="s" s="3">
-        <v>4063</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="2045" ht="36.0" customHeight="true">
@@ -47138,7 +47159,7 @@
         <v>600</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4065</v>
@@ -47155,7 +47176,7 @@
         <v>600</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4067</v>
@@ -47172,7 +47193,7 @@
         <v>600</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4069</v>
@@ -47183,16 +47204,16 @@
         <v>2047.0</v>
       </c>
       <c r="B2048" t="s" s="3">
-        <v>4009</v>
+        <v>4070</v>
       </c>
       <c r="C2048" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2048" t="s" s="3">
-        <v>4070</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="2049" ht="36.0" customHeight="true">
@@ -47200,16 +47221,16 @@
         <v>2048.0</v>
       </c>
       <c r="B2049" t="s" s="3">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="C2049" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2049" t="s" s="3">
-        <v>4072</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="2050" ht="36.0" customHeight="true">
@@ -47217,13 +47238,13 @@
         <v>2049.0</v>
       </c>
       <c r="B2050" t="s" s="3">
-        <v>4073</v>
+        <v>4013</v>
       </c>
       <c r="C2050" t="s" s="2">
         <v>600</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4074</v>
@@ -47240,7 +47261,7 @@
         <v>600</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4076</v>
@@ -47257,7 +47278,7 @@
         <v>600</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4078</v>
@@ -47274,7 +47295,7 @@
         <v>600</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4080</v>
@@ -47291,7 +47312,7 @@
         <v>600</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4082</v>
@@ -47308,7 +47329,7 @@
         <v>600</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4084</v>
@@ -47325,7 +47346,7 @@
         <v>600</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4086</v>
@@ -47342,10 +47363,61 @@
         <v>600</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>4003</v>
+        <v>4007</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4088</v>
+      </c>
+    </row>
+    <row r="2058" ht="36.0" customHeight="true">
+      <c r="A2058" t="n" s="2">
+        <v>2057.0</v>
+      </c>
+      <c r="B2058" t="s" s="3">
+        <v>4089</v>
+      </c>
+      <c r="C2058" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D2058" t="s" s="2">
+        <v>4007</v>
+      </c>
+      <c r="E2058" t="s" s="3">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="2059" ht="36.0" customHeight="true">
+      <c r="A2059" t="n" s="2">
+        <v>2058.0</v>
+      </c>
+      <c r="B2059" t="s" s="3">
+        <v>4091</v>
+      </c>
+      <c r="C2059" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D2059" t="s" s="2">
+        <v>4007</v>
+      </c>
+      <c r="E2059" t="s" s="3">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="2060" ht="36.0" customHeight="true">
+      <c r="A2060" t="n" s="2">
+        <v>2059.0</v>
+      </c>
+      <c r="B2060" t="s" s="3">
+        <v>4093</v>
+      </c>
+      <c r="C2060" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D2060" t="s" s="2">
+        <v>4094</v>
+      </c>
+      <c r="E2060" t="s" s="3">
+        <v>4095</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4073,10 +4073,10 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 중구 백운로 510(2동 1,2층 운북동)</t>
-  </si>
-  <si>
-    <t>인천광역시 중구 백운로 510(1동 지1층 운북동)</t>
   </si>
   <si>
     <t>꽁냥이네</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9649" uniqueCount="4789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9653" uniqueCount="4790">
   <si>
     <t>연번</t>
   </si>
@@ -5294,12 +5294,12 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
-    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
     <t>꽁냥이네</t>
   </si>
   <si>
@@ -8954,6 +8954,12 @@
     <t>경기도 여주시 현암로 11-43(1층 102호 현암동)</t>
   </si>
   <si>
+    <t>merci cafe(메르시 카페)</t>
+  </si>
+  <si>
+    <t>경기도 양주시 평화로 1683(1층 일부 회정동)</t>
+  </si>
+  <si>
     <t>ngl(엔지엘)</t>
   </si>
   <si>
@@ -10310,6 +10316,12 @@
     <t>충청남도 태안군 태안읍 그절미길 2-99(1동 1층)</t>
   </si>
   <si>
+    <t>8하치</t>
+  </si>
+  <si>
+    <t>충청남도 아산시 온화로83번길 16-5(1동 101호 온천동)</t>
+  </si>
+  <si>
     <t>ONBREW온브루</t>
   </si>
   <si>
@@ -14370,15 +14382,6 @@
   </si>
   <si>
     <t>전북특별자치도 남원시 시청북로 17(주1동 2층 도통동)</t>
-  </si>
-  <si>
-    <t>8하치</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>충청남도 아산시 온화로83번길 16-5(1동 101호 온천동)</t>
   </si>
 </sst>
 </file>
@@ -40205,7 +40208,7 @@
         <v>1513.0</v>
       </c>
       <c r="B1514" t="s" s="3">
-        <v>2162</v>
+        <v>3008</v>
       </c>
       <c r="C1514" t="s" s="2">
         <v>702</v>
@@ -40214,7 +40217,7 @@
         <v>2026</v>
       </c>
       <c r="E1514" t="s" s="3">
-        <v>3008</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1515" ht="36.0" customHeight="true">
@@ -40222,7 +40225,7 @@
         <v>1514.0</v>
       </c>
       <c r="B1515" t="s" s="3">
-        <v>3009</v>
+        <v>2162</v>
       </c>
       <c r="C1515" t="s" s="2">
         <v>702</v>
@@ -40248,7 +40251,7 @@
         <v>2026</v>
       </c>
       <c r="E1516" t="s" s="3">
-        <v>2268</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="1517" ht="36.0" customHeight="true">
@@ -40256,7 +40259,7 @@
         <v>1516.0</v>
       </c>
       <c r="B1517" t="s" s="3">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="C1517" t="s" s="2">
         <v>702</v>
@@ -40265,7 +40268,7 @@
         <v>2026</v>
       </c>
       <c r="E1517" t="s" s="3">
-        <v>3013</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="1518" ht="36.0" customHeight="true">
@@ -40545,7 +40548,7 @@
         <v>1533.0</v>
       </c>
       <c r="B1534" t="s" s="3">
-        <v>2255</v>
+        <v>3046</v>
       </c>
       <c r="C1534" t="s" s="2">
         <v>702</v>
@@ -40554,7 +40557,7 @@
         <v>2026</v>
       </c>
       <c r="E1534" t="s" s="3">
-        <v>2256</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="1535" ht="36.0" customHeight="true">
@@ -40562,7 +40565,7 @@
         <v>1534.0</v>
       </c>
       <c r="B1535" t="s" s="3">
-        <v>3046</v>
+        <v>2255</v>
       </c>
       <c r="C1535" t="s" s="2">
         <v>702</v>
@@ -40571,7 +40574,7 @@
         <v>2026</v>
       </c>
       <c r="E1535" t="s" s="3">
-        <v>3047</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1536" ht="36.0" customHeight="true">
@@ -42203,7 +42206,7 @@
         <v>2026</v>
       </c>
       <c r="E1631" t="s" s="3">
-        <v>2687</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="1632" ht="36.0" customHeight="true">
@@ -42211,7 +42214,7 @@
         <v>1631.0</v>
       </c>
       <c r="B1632" t="s" s="3">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="C1632" t="s" s="2">
         <v>702</v>
@@ -42220,7 +42223,7 @@
         <v>2026</v>
       </c>
       <c r="E1632" t="s" s="3">
-        <v>3240</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="1633" ht="36.0" customHeight="true">
@@ -42475,7 +42478,7 @@
         <v>2026</v>
       </c>
       <c r="E1647" t="s" s="3">
-        <v>3115</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="1648" ht="36.0" customHeight="true">
@@ -42483,7 +42486,7 @@
         <v>1647.0</v>
       </c>
       <c r="B1648" t="s" s="3">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="C1648" t="s" s="2">
         <v>702</v>
@@ -42492,7 +42495,7 @@
         <v>2026</v>
       </c>
       <c r="E1648" t="s" s="3">
-        <v>3271</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="1649" ht="36.0" customHeight="true">
@@ -42500,7 +42503,7 @@
         <v>1648.0</v>
       </c>
       <c r="B1649" t="s" s="3">
-        <v>2914</v>
+        <v>3272</v>
       </c>
       <c r="C1649" t="s" s="2">
         <v>702</v>
@@ -42509,7 +42512,7 @@
         <v>2026</v>
       </c>
       <c r="E1649" t="s" s="3">
-        <v>2915</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="1650" ht="36.0" customHeight="true">
@@ -42517,7 +42520,7 @@
         <v>1649.0</v>
       </c>
       <c r="B1650" t="s" s="3">
-        <v>3272</v>
+        <v>2914</v>
       </c>
       <c r="C1650" t="s" s="2">
         <v>702</v>
@@ -42526,7 +42529,7 @@
         <v>2026</v>
       </c>
       <c r="E1650" t="s" s="3">
-        <v>3273</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="1651" ht="36.0" customHeight="true">
@@ -42758,7 +42761,7 @@
         <v>3300</v>
       </c>
       <c r="C1664" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1664" t="s" s="2">
         <v>2026</v>
@@ -42874,7 +42877,7 @@
         <v>1670.0</v>
       </c>
       <c r="B1671" t="s" s="3">
-        <v>2642</v>
+        <v>3314</v>
       </c>
       <c r="C1671" t="s" s="2">
         <v>897</v>
@@ -42883,7 +42886,7 @@
         <v>2026</v>
       </c>
       <c r="E1671" t="s" s="3">
-        <v>2643</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="1672" ht="36.0" customHeight="true">
@@ -42891,7 +42894,7 @@
         <v>1671.0</v>
       </c>
       <c r="B1672" t="s" s="3">
-        <v>3314</v>
+        <v>2642</v>
       </c>
       <c r="C1672" t="s" s="2">
         <v>897</v>
@@ -42900,7 +42903,7 @@
         <v>2026</v>
       </c>
       <c r="E1672" t="s" s="3">
-        <v>3315</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="1673" ht="36.0" customHeight="true">
@@ -42945,13 +42948,13 @@
         <v>3320</v>
       </c>
       <c r="C1675" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D1675" t="s" s="2">
+        <v>2026</v>
+      </c>
+      <c r="E1675" t="s" s="3">
         <v>3321</v>
-      </c>
-      <c r="E1675" t="s" s="3">
-        <v>3322</v>
       </c>
     </row>
     <row r="1676" ht="36.0" customHeight="true">
@@ -42959,13 +42962,13 @@
         <v>1675.0</v>
       </c>
       <c r="B1676" t="s" s="3">
+        <v>3322</v>
+      </c>
+      <c r="C1676" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1676" t="s" s="2">
         <v>3323</v>
-      </c>
-      <c r="C1676" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1676" t="s" s="2">
-        <v>3321</v>
       </c>
       <c r="E1676" t="s" s="3">
         <v>3324</v>
@@ -42982,7 +42985,7 @@
         <v>6</v>
       </c>
       <c r="D1677" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1677" t="s" s="3">
         <v>3326</v>
@@ -42999,7 +43002,7 @@
         <v>6</v>
       </c>
       <c r="D1678" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1678" t="s" s="3">
         <v>3328</v>
@@ -43016,7 +43019,7 @@
         <v>6</v>
       </c>
       <c r="D1679" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1679" t="s" s="3">
         <v>3330</v>
@@ -43033,7 +43036,7 @@
         <v>6</v>
       </c>
       <c r="D1680" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1680" t="s" s="3">
         <v>3332</v>
@@ -43050,7 +43053,7 @@
         <v>6</v>
       </c>
       <c r="D1681" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1681" t="s" s="3">
         <v>3334</v>
@@ -43067,7 +43070,7 @@
         <v>6</v>
       </c>
       <c r="D1682" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1682" t="s" s="3">
         <v>3336</v>
@@ -43084,7 +43087,7 @@
         <v>6</v>
       </c>
       <c r="D1683" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1683" t="s" s="3">
         <v>3338</v>
@@ -43101,7 +43104,7 @@
         <v>6</v>
       </c>
       <c r="D1684" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1684" t="s" s="3">
         <v>3340</v>
@@ -43118,7 +43121,7 @@
         <v>6</v>
       </c>
       <c r="D1685" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1685" t="s" s="3">
         <v>3342</v>
@@ -43135,7 +43138,7 @@
         <v>6</v>
       </c>
       <c r="D1686" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1686" t="s" s="3">
         <v>3344</v>
@@ -43152,7 +43155,7 @@
         <v>6</v>
       </c>
       <c r="D1687" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1687" t="s" s="3">
         <v>3346</v>
@@ -43169,7 +43172,7 @@
         <v>6</v>
       </c>
       <c r="D1688" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1688" t="s" s="3">
         <v>3348</v>
@@ -43186,7 +43189,7 @@
         <v>6</v>
       </c>
       <c r="D1689" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1689" t="s" s="3">
         <v>3350</v>
@@ -43203,7 +43206,7 @@
         <v>6</v>
       </c>
       <c r="D1690" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1690" t="s" s="3">
         <v>3352</v>
@@ -43220,7 +43223,7 @@
         <v>6</v>
       </c>
       <c r="D1691" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1691" t="s" s="3">
         <v>3354</v>
@@ -43237,7 +43240,7 @@
         <v>6</v>
       </c>
       <c r="D1692" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1692" t="s" s="3">
         <v>3356</v>
@@ -43254,7 +43257,7 @@
         <v>6</v>
       </c>
       <c r="D1693" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1693" t="s" s="3">
         <v>3358</v>
@@ -43271,7 +43274,7 @@
         <v>6</v>
       </c>
       <c r="D1694" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1694" t="s" s="3">
         <v>3360</v>
@@ -43288,7 +43291,7 @@
         <v>6</v>
       </c>
       <c r="D1695" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1695" t="s" s="3">
         <v>3362</v>
@@ -43305,7 +43308,7 @@
         <v>6</v>
       </c>
       <c r="D1696" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1696" t="s" s="3">
         <v>3364</v>
@@ -43322,7 +43325,7 @@
         <v>6</v>
       </c>
       <c r="D1697" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1697" t="s" s="3">
         <v>3366</v>
@@ -43339,7 +43342,7 @@
         <v>6</v>
       </c>
       <c r="D1698" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1698" t="s" s="3">
         <v>3368</v>
@@ -43356,7 +43359,7 @@
         <v>6</v>
       </c>
       <c r="D1699" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1699" t="s" s="3">
         <v>3370</v>
@@ -43373,7 +43376,7 @@
         <v>6</v>
       </c>
       <c r="D1700" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1700" t="s" s="3">
         <v>3372</v>
@@ -43390,7 +43393,7 @@
         <v>6</v>
       </c>
       <c r="D1701" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1701" t="s" s="3">
         <v>3374</v>
@@ -43407,7 +43410,7 @@
         <v>6</v>
       </c>
       <c r="D1702" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1702" t="s" s="3">
         <v>3376</v>
@@ -43424,7 +43427,7 @@
         <v>6</v>
       </c>
       <c r="D1703" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1703" t="s" s="3">
         <v>3378</v>
@@ -43441,7 +43444,7 @@
         <v>6</v>
       </c>
       <c r="D1704" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1704" t="s" s="3">
         <v>3380</v>
@@ -43458,7 +43461,7 @@
         <v>6</v>
       </c>
       <c r="D1705" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1705" t="s" s="3">
         <v>3382</v>
@@ -43475,7 +43478,7 @@
         <v>6</v>
       </c>
       <c r="D1706" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1706" t="s" s="3">
         <v>3384</v>
@@ -43492,7 +43495,7 @@
         <v>6</v>
       </c>
       <c r="D1707" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1707" t="s" s="3">
         <v>3386</v>
@@ -43509,7 +43512,7 @@
         <v>6</v>
       </c>
       <c r="D1708" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1708" t="s" s="3">
         <v>3388</v>
@@ -43526,7 +43529,7 @@
         <v>6</v>
       </c>
       <c r="D1709" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1709" t="s" s="3">
         <v>3390</v>
@@ -43543,7 +43546,7 @@
         <v>6</v>
       </c>
       <c r="D1710" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1710" t="s" s="3">
         <v>3392</v>
@@ -43560,7 +43563,7 @@
         <v>6</v>
       </c>
       <c r="D1711" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1711" t="s" s="3">
         <v>3394</v>
@@ -43577,7 +43580,7 @@
         <v>6</v>
       </c>
       <c r="D1712" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1712" t="s" s="3">
         <v>3396</v>
@@ -43594,7 +43597,7 @@
         <v>6</v>
       </c>
       <c r="D1713" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1713" t="s" s="3">
         <v>3398</v>
@@ -43611,7 +43614,7 @@
         <v>6</v>
       </c>
       <c r="D1714" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1714" t="s" s="3">
         <v>3400</v>
@@ -43628,7 +43631,7 @@
         <v>6</v>
       </c>
       <c r="D1715" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1715" t="s" s="3">
         <v>3402</v>
@@ -43645,7 +43648,7 @@
         <v>6</v>
       </c>
       <c r="D1716" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1716" t="s" s="3">
         <v>3404</v>
@@ -43659,10 +43662,10 @@
         <v>3405</v>
       </c>
       <c r="C1717" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D1717" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1717" t="s" s="3">
         <v>3406</v>
@@ -43679,7 +43682,7 @@
         <v>702</v>
       </c>
       <c r="D1718" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1718" t="s" s="3">
         <v>3408</v>
@@ -43696,7 +43699,7 @@
         <v>702</v>
       </c>
       <c r="D1719" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1719" t="s" s="3">
         <v>3410</v>
@@ -43713,7 +43716,7 @@
         <v>702</v>
       </c>
       <c r="D1720" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1720" t="s" s="3">
         <v>3412</v>
@@ -43730,7 +43733,7 @@
         <v>702</v>
       </c>
       <c r="D1721" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1721" t="s" s="3">
         <v>3414</v>
@@ -43747,7 +43750,7 @@
         <v>702</v>
       </c>
       <c r="D1722" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1722" t="s" s="3">
         <v>3416</v>
@@ -43764,7 +43767,7 @@
         <v>702</v>
       </c>
       <c r="D1723" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1723" t="s" s="3">
         <v>3418</v>
@@ -43781,7 +43784,7 @@
         <v>702</v>
       </c>
       <c r="D1724" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1724" t="s" s="3">
         <v>3420</v>
@@ -43798,7 +43801,7 @@
         <v>702</v>
       </c>
       <c r="D1725" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1725" t="s" s="3">
         <v>3422</v>
@@ -43815,7 +43818,7 @@
         <v>702</v>
       </c>
       <c r="D1726" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1726" t="s" s="3">
         <v>3424</v>
@@ -43832,7 +43835,7 @@
         <v>702</v>
       </c>
       <c r="D1727" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1727" t="s" s="3">
         <v>3426</v>
@@ -43846,10 +43849,10 @@
         <v>3427</v>
       </c>
       <c r="C1728" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1728" t="s" s="2">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="E1728" t="s" s="3">
         <v>3428</v>
@@ -43863,13 +43866,13 @@
         <v>3429</v>
       </c>
       <c r="C1729" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D1729" t="s" s="2">
+        <v>3323</v>
+      </c>
+      <c r="E1729" t="s" s="3">
         <v>3430</v>
-      </c>
-      <c r="E1729" t="s" s="3">
-        <v>3431</v>
       </c>
     </row>
     <row r="1730" ht="36.0" customHeight="true">
@@ -43877,13 +43880,13 @@
         <v>1729.0</v>
       </c>
       <c r="B1730" t="s" s="3">
+        <v>3431</v>
+      </c>
+      <c r="C1730" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1730" t="s" s="2">
         <v>3432</v>
-      </c>
-      <c r="C1730" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1730" t="s" s="2">
-        <v>3430</v>
       </c>
       <c r="E1730" t="s" s="3">
         <v>3433</v>
@@ -43900,7 +43903,7 @@
         <v>6</v>
       </c>
       <c r="D1731" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1731" t="s" s="3">
         <v>3435</v>
@@ -43917,7 +43920,7 @@
         <v>6</v>
       </c>
       <c r="D1732" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1732" t="s" s="3">
         <v>3437</v>
@@ -43934,7 +43937,7 @@
         <v>6</v>
       </c>
       <c r="D1733" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1733" t="s" s="3">
         <v>3439</v>
@@ -43951,7 +43954,7 @@
         <v>6</v>
       </c>
       <c r="D1734" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1734" t="s" s="3">
         <v>3441</v>
@@ -43968,7 +43971,7 @@
         <v>6</v>
       </c>
       <c r="D1735" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1735" t="s" s="3">
         <v>3443</v>
@@ -43985,7 +43988,7 @@
         <v>6</v>
       </c>
       <c r="D1736" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1736" t="s" s="3">
         <v>3445</v>
@@ -44002,7 +44005,7 @@
         <v>6</v>
       </c>
       <c r="D1737" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1737" t="s" s="3">
         <v>3447</v>
@@ -44019,7 +44022,7 @@
         <v>6</v>
       </c>
       <c r="D1738" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1738" t="s" s="3">
         <v>3449</v>
@@ -44036,7 +44039,7 @@
         <v>6</v>
       </c>
       <c r="D1739" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1739" t="s" s="3">
         <v>3451</v>
@@ -44053,7 +44056,7 @@
         <v>6</v>
       </c>
       <c r="D1740" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1740" t="s" s="3">
         <v>3453</v>
@@ -44070,7 +44073,7 @@
         <v>6</v>
       </c>
       <c r="D1741" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1741" t="s" s="3">
         <v>3455</v>
@@ -44087,7 +44090,7 @@
         <v>6</v>
       </c>
       <c r="D1742" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1742" t="s" s="3">
         <v>3457</v>
@@ -44104,7 +44107,7 @@
         <v>6</v>
       </c>
       <c r="D1743" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1743" t="s" s="3">
         <v>3459</v>
@@ -44121,7 +44124,7 @@
         <v>6</v>
       </c>
       <c r="D1744" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1744" t="s" s="3">
         <v>3461</v>
@@ -44138,7 +44141,7 @@
         <v>6</v>
       </c>
       <c r="D1745" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1745" t="s" s="3">
         <v>3463</v>
@@ -44155,7 +44158,7 @@
         <v>6</v>
       </c>
       <c r="D1746" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1746" t="s" s="3">
         <v>3465</v>
@@ -44172,7 +44175,7 @@
         <v>6</v>
       </c>
       <c r="D1747" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1747" t="s" s="3">
         <v>3467</v>
@@ -44189,7 +44192,7 @@
         <v>6</v>
       </c>
       <c r="D1748" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1748" t="s" s="3">
         <v>3469</v>
@@ -44206,7 +44209,7 @@
         <v>6</v>
       </c>
       <c r="D1749" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1749" t="s" s="3">
         <v>3471</v>
@@ -44223,7 +44226,7 @@
         <v>6</v>
       </c>
       <c r="D1750" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1750" t="s" s="3">
         <v>3473</v>
@@ -44240,7 +44243,7 @@
         <v>6</v>
       </c>
       <c r="D1751" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1751" t="s" s="3">
         <v>3475</v>
@@ -44257,7 +44260,7 @@
         <v>6</v>
       </c>
       <c r="D1752" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1752" t="s" s="3">
         <v>3477</v>
@@ -44274,7 +44277,7 @@
         <v>6</v>
       </c>
       <c r="D1753" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1753" t="s" s="3">
         <v>3479</v>
@@ -44291,7 +44294,7 @@
         <v>6</v>
       </c>
       <c r="D1754" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1754" t="s" s="3">
         <v>3481</v>
@@ -44308,7 +44311,7 @@
         <v>6</v>
       </c>
       <c r="D1755" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1755" t="s" s="3">
         <v>3483</v>
@@ -44325,7 +44328,7 @@
         <v>6</v>
       </c>
       <c r="D1756" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1756" t="s" s="3">
         <v>3485</v>
@@ -44342,7 +44345,7 @@
         <v>6</v>
       </c>
       <c r="D1757" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1757" t="s" s="3">
         <v>3487</v>
@@ -44359,7 +44362,7 @@
         <v>6</v>
       </c>
       <c r="D1758" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1758" t="s" s="3">
         <v>3489</v>
@@ -44376,7 +44379,7 @@
         <v>6</v>
       </c>
       <c r="D1759" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1759" t="s" s="3">
         <v>3491</v>
@@ -44393,7 +44396,7 @@
         <v>6</v>
       </c>
       <c r="D1760" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1760" t="s" s="3">
         <v>3493</v>
@@ -44410,7 +44413,7 @@
         <v>6</v>
       </c>
       <c r="D1761" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1761" t="s" s="3">
         <v>3495</v>
@@ -44427,7 +44430,7 @@
         <v>6</v>
       </c>
       <c r="D1762" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1762" t="s" s="3">
         <v>3497</v>
@@ -44444,7 +44447,7 @@
         <v>6</v>
       </c>
       <c r="D1763" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1763" t="s" s="3">
         <v>3499</v>
@@ -44461,7 +44464,7 @@
         <v>6</v>
       </c>
       <c r="D1764" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1764" t="s" s="3">
         <v>3501</v>
@@ -44478,7 +44481,7 @@
         <v>6</v>
       </c>
       <c r="D1765" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1765" t="s" s="3">
         <v>3503</v>
@@ -44495,7 +44498,7 @@
         <v>6</v>
       </c>
       <c r="D1766" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1766" t="s" s="3">
         <v>3505</v>
@@ -44512,7 +44515,7 @@
         <v>6</v>
       </c>
       <c r="D1767" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1767" t="s" s="3">
         <v>3507</v>
@@ -44529,7 +44532,7 @@
         <v>6</v>
       </c>
       <c r="D1768" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1768" t="s" s="3">
         <v>3509</v>
@@ -44546,7 +44549,7 @@
         <v>6</v>
       </c>
       <c r="D1769" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1769" t="s" s="3">
         <v>3511</v>
@@ -44563,7 +44566,7 @@
         <v>6</v>
       </c>
       <c r="D1770" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1770" t="s" s="3">
         <v>3513</v>
@@ -44580,7 +44583,7 @@
         <v>6</v>
       </c>
       <c r="D1771" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1771" t="s" s="3">
         <v>3515</v>
@@ -44597,7 +44600,7 @@
         <v>6</v>
       </c>
       <c r="D1772" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1772" t="s" s="3">
         <v>3517</v>
@@ -44614,7 +44617,7 @@
         <v>6</v>
       </c>
       <c r="D1773" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1773" t="s" s="3">
         <v>3519</v>
@@ -44631,7 +44634,7 @@
         <v>6</v>
       </c>
       <c r="D1774" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1774" t="s" s="3">
         <v>3521</v>
@@ -44648,7 +44651,7 @@
         <v>6</v>
       </c>
       <c r="D1775" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1775" t="s" s="3">
         <v>3523</v>
@@ -44662,10 +44665,10 @@
         <v>3524</v>
       </c>
       <c r="C1776" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D1776" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1776" t="s" s="3">
         <v>3525</v>
@@ -44679,10 +44682,10 @@
         <v>3526</v>
       </c>
       <c r="C1777" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D1777" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1777" t="s" s="3">
         <v>3527</v>
@@ -44699,7 +44702,7 @@
         <v>702</v>
       </c>
       <c r="D1778" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1778" t="s" s="3">
         <v>3529</v>
@@ -44716,7 +44719,7 @@
         <v>702</v>
       </c>
       <c r="D1779" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1779" t="s" s="3">
         <v>3531</v>
@@ -44733,7 +44736,7 @@
         <v>702</v>
       </c>
       <c r="D1780" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1780" t="s" s="3">
         <v>3533</v>
@@ -44750,7 +44753,7 @@
         <v>702</v>
       </c>
       <c r="D1781" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1781" t="s" s="3">
         <v>3535</v>
@@ -44767,7 +44770,7 @@
         <v>702</v>
       </c>
       <c r="D1782" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1782" t="s" s="3">
         <v>3537</v>
@@ -44784,7 +44787,7 @@
         <v>702</v>
       </c>
       <c r="D1783" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1783" t="s" s="3">
         <v>3539</v>
@@ -44801,7 +44804,7 @@
         <v>702</v>
       </c>
       <c r="D1784" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1784" t="s" s="3">
         <v>3541</v>
@@ -44818,7 +44821,7 @@
         <v>702</v>
       </c>
       <c r="D1785" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1785" t="s" s="3">
         <v>3543</v>
@@ -44835,7 +44838,7 @@
         <v>702</v>
       </c>
       <c r="D1786" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1786" t="s" s="3">
         <v>3545</v>
@@ -44852,7 +44855,7 @@
         <v>702</v>
       </c>
       <c r="D1787" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1787" t="s" s="3">
         <v>3547</v>
@@ -44869,7 +44872,7 @@
         <v>702</v>
       </c>
       <c r="D1788" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1788" t="s" s="3">
         <v>3549</v>
@@ -44886,7 +44889,7 @@
         <v>702</v>
       </c>
       <c r="D1789" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1789" t="s" s="3">
         <v>3551</v>
@@ -44903,7 +44906,7 @@
         <v>702</v>
       </c>
       <c r="D1790" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1790" t="s" s="3">
         <v>3553</v>
@@ -44920,7 +44923,7 @@
         <v>702</v>
       </c>
       <c r="D1791" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1791" t="s" s="3">
         <v>3555</v>
@@ -44937,7 +44940,7 @@
         <v>702</v>
       </c>
       <c r="D1792" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1792" t="s" s="3">
         <v>3557</v>
@@ -44948,16 +44951,16 @@
         <v>1792.0</v>
       </c>
       <c r="B1793" t="s" s="3">
-        <v>3504</v>
+        <v>3558</v>
       </c>
       <c r="C1793" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D1793" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1793" t="s" s="3">
-        <v>3505</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="1794" ht="36.0" customHeight="true">
@@ -44965,16 +44968,16 @@
         <v>1793.0</v>
       </c>
       <c r="B1794" t="s" s="3">
-        <v>3558</v>
+        <v>3560</v>
       </c>
       <c r="C1794" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D1794" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1794" t="s" s="3">
-        <v>3559</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="1795" ht="36.0" customHeight="true">
@@ -44982,16 +44985,16 @@
         <v>1794.0</v>
       </c>
       <c r="B1795" t="s" s="3">
-        <v>3560</v>
+        <v>3508</v>
       </c>
       <c r="C1795" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D1795" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1795" t="s" s="3">
-        <v>3561</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="1796" ht="36.0" customHeight="true">
@@ -45005,7 +45008,7 @@
         <v>702</v>
       </c>
       <c r="D1796" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1796" t="s" s="3">
         <v>3563</v>
@@ -45022,7 +45025,7 @@
         <v>702</v>
       </c>
       <c r="D1797" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1797" t="s" s="3">
         <v>3565</v>
@@ -45039,7 +45042,7 @@
         <v>702</v>
       </c>
       <c r="D1798" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1798" t="s" s="3">
         <v>3567</v>
@@ -45056,7 +45059,7 @@
         <v>702</v>
       </c>
       <c r="D1799" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1799" t="s" s="3">
         <v>3569</v>
@@ -45073,7 +45076,7 @@
         <v>702</v>
       </c>
       <c r="D1800" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1800" t="s" s="3">
         <v>3571</v>
@@ -45090,7 +45093,7 @@
         <v>702</v>
       </c>
       <c r="D1801" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1801" t="s" s="3">
         <v>3573</v>
@@ -45104,10 +45107,10 @@
         <v>3574</v>
       </c>
       <c r="C1802" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1802" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1802" t="s" s="3">
         <v>3575</v>
@@ -45121,10 +45124,10 @@
         <v>3576</v>
       </c>
       <c r="C1803" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1803" t="s" s="2">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="E1803" t="s" s="3">
         <v>3577</v>
@@ -45138,13 +45141,13 @@
         <v>3578</v>
       </c>
       <c r="C1804" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D1804" t="s" s="2">
+        <v>3432</v>
+      </c>
+      <c r="E1804" t="s" s="3">
         <v>3579</v>
-      </c>
-      <c r="E1804" t="s" s="3">
-        <v>3580</v>
       </c>
     </row>
     <row r="1805" ht="36.0" customHeight="true">
@@ -45152,16 +45155,16 @@
         <v>1804.0</v>
       </c>
       <c r="B1805" t="s" s="3">
+        <v>3580</v>
+      </c>
+      <c r="C1805" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="D1805" t="s" s="2">
+        <v>3432</v>
+      </c>
+      <c r="E1805" t="s" s="3">
         <v>3581</v>
-      </c>
-      <c r="C1805" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1805" t="s" s="2">
-        <v>3579</v>
-      </c>
-      <c r="E1805" t="s" s="3">
-        <v>3582</v>
       </c>
     </row>
     <row r="1806" ht="36.0" customHeight="true">
@@ -45169,13 +45172,13 @@
         <v>1805.0</v>
       </c>
       <c r="B1806" t="s" s="3">
+        <v>3582</v>
+      </c>
+      <c r="C1806" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1806" t="s" s="2">
         <v>3583</v>
-      </c>
-      <c r="C1806" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1806" t="s" s="2">
-        <v>3579</v>
       </c>
       <c r="E1806" t="s" s="3">
         <v>3584</v>
@@ -45192,7 +45195,7 @@
         <v>6</v>
       </c>
       <c r="D1807" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1807" t="s" s="3">
         <v>3586</v>
@@ -45209,7 +45212,7 @@
         <v>6</v>
       </c>
       <c r="D1808" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1808" t="s" s="3">
         <v>3588</v>
@@ -45226,7 +45229,7 @@
         <v>6</v>
       </c>
       <c r="D1809" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1809" t="s" s="3">
         <v>3590</v>
@@ -45243,7 +45246,7 @@
         <v>6</v>
       </c>
       <c r="D1810" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1810" t="s" s="3">
         <v>3592</v>
@@ -45260,7 +45263,7 @@
         <v>6</v>
       </c>
       <c r="D1811" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1811" t="s" s="3">
         <v>3594</v>
@@ -45277,7 +45280,7 @@
         <v>6</v>
       </c>
       <c r="D1812" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1812" t="s" s="3">
         <v>3596</v>
@@ -45294,7 +45297,7 @@
         <v>6</v>
       </c>
       <c r="D1813" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1813" t="s" s="3">
         <v>3598</v>
@@ -45311,7 +45314,7 @@
         <v>6</v>
       </c>
       <c r="D1814" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1814" t="s" s="3">
         <v>3600</v>
@@ -45328,7 +45331,7 @@
         <v>6</v>
       </c>
       <c r="D1815" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1815" t="s" s="3">
         <v>3602</v>
@@ -45345,7 +45348,7 @@
         <v>6</v>
       </c>
       <c r="D1816" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1816" t="s" s="3">
         <v>3604</v>
@@ -45362,7 +45365,7 @@
         <v>6</v>
       </c>
       <c r="D1817" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1817" t="s" s="3">
         <v>3606</v>
@@ -45379,7 +45382,7 @@
         <v>6</v>
       </c>
       <c r="D1818" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1818" t="s" s="3">
         <v>3608</v>
@@ -45396,7 +45399,7 @@
         <v>6</v>
       </c>
       <c r="D1819" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1819" t="s" s="3">
         <v>3610</v>
@@ -45413,7 +45416,7 @@
         <v>6</v>
       </c>
       <c r="D1820" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1820" t="s" s="3">
         <v>3612</v>
@@ -45430,7 +45433,7 @@
         <v>6</v>
       </c>
       <c r="D1821" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1821" t="s" s="3">
         <v>3614</v>
@@ -45447,7 +45450,7 @@
         <v>6</v>
       </c>
       <c r="D1822" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1822" t="s" s="3">
         <v>3616</v>
@@ -45464,7 +45467,7 @@
         <v>6</v>
       </c>
       <c r="D1823" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1823" t="s" s="3">
         <v>3618</v>
@@ -45481,7 +45484,7 @@
         <v>6</v>
       </c>
       <c r="D1824" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1824" t="s" s="3">
         <v>3620</v>
@@ -45498,7 +45501,7 @@
         <v>6</v>
       </c>
       <c r="D1825" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1825" t="s" s="3">
         <v>3622</v>
@@ -45515,7 +45518,7 @@
         <v>6</v>
       </c>
       <c r="D1826" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1826" t="s" s="3">
         <v>3624</v>
@@ -45532,7 +45535,7 @@
         <v>6</v>
       </c>
       <c r="D1827" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1827" t="s" s="3">
         <v>3626</v>
@@ -45549,7 +45552,7 @@
         <v>6</v>
       </c>
       <c r="D1828" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1828" t="s" s="3">
         <v>3628</v>
@@ -45566,7 +45569,7 @@
         <v>6</v>
       </c>
       <c r="D1829" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1829" t="s" s="3">
         <v>3630</v>
@@ -45583,7 +45586,7 @@
         <v>6</v>
       </c>
       <c r="D1830" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1830" t="s" s="3">
         <v>3632</v>
@@ -45600,7 +45603,7 @@
         <v>6</v>
       </c>
       <c r="D1831" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1831" t="s" s="3">
         <v>3634</v>
@@ -45617,7 +45620,7 @@
         <v>6</v>
       </c>
       <c r="D1832" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1832" t="s" s="3">
         <v>3636</v>
@@ -45634,7 +45637,7 @@
         <v>6</v>
       </c>
       <c r="D1833" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1833" t="s" s="3">
         <v>3638</v>
@@ -45651,7 +45654,7 @@
         <v>6</v>
       </c>
       <c r="D1834" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1834" t="s" s="3">
         <v>3640</v>
@@ -45668,7 +45671,7 @@
         <v>6</v>
       </c>
       <c r="D1835" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1835" t="s" s="3">
         <v>3642</v>
@@ -45685,7 +45688,7 @@
         <v>6</v>
       </c>
       <c r="D1836" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1836" t="s" s="3">
         <v>3644</v>
@@ -45702,7 +45705,7 @@
         <v>6</v>
       </c>
       <c r="D1837" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1837" t="s" s="3">
         <v>3646</v>
@@ -45719,10 +45722,10 @@
         <v>6</v>
       </c>
       <c r="D1838" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1838" t="s" s="3">
-        <v>3622</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="1839" ht="36.0" customHeight="true">
@@ -45730,16 +45733,16 @@
         <v>1838.0</v>
       </c>
       <c r="B1839" t="s" s="3">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="C1839" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1839" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1839" t="s" s="3">
-        <v>3649</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="1840" ht="36.0" customHeight="true">
@@ -45747,16 +45750,16 @@
         <v>1839.0</v>
       </c>
       <c r="B1840" t="s" s="3">
-        <v>3224</v>
+        <v>3651</v>
       </c>
       <c r="C1840" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1840" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1840" t="s" s="3">
-        <v>3650</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="1841" ht="36.0" customHeight="true">
@@ -45764,16 +45767,16 @@
         <v>1840.0</v>
       </c>
       <c r="B1841" t="s" s="3">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="C1841" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1841" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1841" t="s" s="3">
-        <v>3652</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="1842" ht="36.0" customHeight="true">
@@ -45781,13 +45784,13 @@
         <v>1841.0</v>
       </c>
       <c r="B1842" t="s" s="3">
-        <v>3653</v>
+        <v>3226</v>
       </c>
       <c r="C1842" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1842" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1842" t="s" s="3">
         <v>3654</v>
@@ -45804,7 +45807,7 @@
         <v>6</v>
       </c>
       <c r="D1843" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1843" t="s" s="3">
         <v>3656</v>
@@ -45821,7 +45824,7 @@
         <v>6</v>
       </c>
       <c r="D1844" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1844" t="s" s="3">
         <v>3658</v>
@@ -45838,7 +45841,7 @@
         <v>6</v>
       </c>
       <c r="D1845" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1845" t="s" s="3">
         <v>3660</v>
@@ -45855,7 +45858,7 @@
         <v>6</v>
       </c>
       <c r="D1846" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1846" t="s" s="3">
         <v>3662</v>
@@ -45869,10 +45872,10 @@
         <v>3663</v>
       </c>
       <c r="C1847" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D1847" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1847" t="s" s="3">
         <v>3664</v>
@@ -45886,10 +45889,10 @@
         <v>3665</v>
       </c>
       <c r="C1848" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D1848" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1848" t="s" s="3">
         <v>3666</v>
@@ -45906,7 +45909,7 @@
         <v>702</v>
       </c>
       <c r="D1849" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1849" t="s" s="3">
         <v>3668</v>
@@ -45923,7 +45926,7 @@
         <v>702</v>
       </c>
       <c r="D1850" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1850" t="s" s="3">
         <v>3670</v>
@@ -45940,7 +45943,7 @@
         <v>702</v>
       </c>
       <c r="D1851" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1851" t="s" s="3">
         <v>3672</v>
@@ -45957,7 +45960,7 @@
         <v>702</v>
       </c>
       <c r="D1852" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1852" t="s" s="3">
         <v>3674</v>
@@ -45974,7 +45977,7 @@
         <v>702</v>
       </c>
       <c r="D1853" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1853" t="s" s="3">
         <v>3676</v>
@@ -45991,7 +45994,7 @@
         <v>702</v>
       </c>
       <c r="D1854" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1854" t="s" s="3">
         <v>3678</v>
@@ -46008,7 +46011,7 @@
         <v>702</v>
       </c>
       <c r="D1855" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1855" t="s" s="3">
         <v>3680</v>
@@ -46025,7 +46028,7 @@
         <v>702</v>
       </c>
       <c r="D1856" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1856" t="s" s="3">
         <v>3682</v>
@@ -46042,7 +46045,7 @@
         <v>702</v>
       </c>
       <c r="D1857" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1857" t="s" s="3">
         <v>3684</v>
@@ -46059,7 +46062,7 @@
         <v>702</v>
       </c>
       <c r="D1858" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1858" t="s" s="3">
         <v>3686</v>
@@ -46076,7 +46079,7 @@
         <v>702</v>
       </c>
       <c r="D1859" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1859" t="s" s="3">
         <v>3688</v>
@@ -46093,7 +46096,7 @@
         <v>702</v>
       </c>
       <c r="D1860" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1860" t="s" s="3">
         <v>3690</v>
@@ -46110,7 +46113,7 @@
         <v>702</v>
       </c>
       <c r="D1861" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1861" t="s" s="3">
         <v>3692</v>
@@ -46127,7 +46130,7 @@
         <v>702</v>
       </c>
       <c r="D1862" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1862" t="s" s="3">
         <v>3694</v>
@@ -46144,7 +46147,7 @@
         <v>702</v>
       </c>
       <c r="D1863" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1863" t="s" s="3">
         <v>3696</v>
@@ -46161,7 +46164,7 @@
         <v>702</v>
       </c>
       <c r="D1864" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1864" t="s" s="3">
         <v>3698</v>
@@ -46178,7 +46181,7 @@
         <v>702</v>
       </c>
       <c r="D1865" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1865" t="s" s="3">
         <v>3700</v>
@@ -46195,7 +46198,7 @@
         <v>702</v>
       </c>
       <c r="D1866" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1866" t="s" s="3">
         <v>3702</v>
@@ -46212,7 +46215,7 @@
         <v>702</v>
       </c>
       <c r="D1867" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1867" t="s" s="3">
         <v>3704</v>
@@ -46229,7 +46232,7 @@
         <v>702</v>
       </c>
       <c r="D1868" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1868" t="s" s="3">
         <v>3706</v>
@@ -46246,7 +46249,7 @@
         <v>702</v>
       </c>
       <c r="D1869" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1869" t="s" s="3">
         <v>3708</v>
@@ -46260,10 +46263,10 @@
         <v>3709</v>
       </c>
       <c r="C1870" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1870" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1870" t="s" s="3">
         <v>3710</v>
@@ -46277,10 +46280,10 @@
         <v>3711</v>
       </c>
       <c r="C1871" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D1871" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1871" t="s" s="3">
         <v>3712</v>
@@ -46291,16 +46294,16 @@
         <v>1871.0</v>
       </c>
       <c r="B1872" t="s" s="3">
-        <v>3648</v>
+        <v>3713</v>
       </c>
       <c r="C1872" t="s" s="2">
         <v>897</v>
       </c>
       <c r="D1872" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1872" t="s" s="3">
-        <v>3649</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="1873" ht="36.0" customHeight="true">
@@ -46308,16 +46311,16 @@
         <v>1872.0</v>
       </c>
       <c r="B1873" t="s" s="3">
-        <v>3713</v>
+        <v>3715</v>
       </c>
       <c r="C1873" t="s" s="2">
         <v>897</v>
       </c>
       <c r="D1873" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1873" t="s" s="3">
-        <v>3714</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="1874" ht="36.0" customHeight="true">
@@ -46325,16 +46328,16 @@
         <v>1873.0</v>
       </c>
       <c r="B1874" t="s" s="3">
-        <v>3715</v>
+        <v>3652</v>
       </c>
       <c r="C1874" t="s" s="2">
         <v>897</v>
       </c>
       <c r="D1874" t="s" s="2">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="E1874" t="s" s="3">
-        <v>3716</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="1875" ht="36.0" customHeight="true">
@@ -46345,13 +46348,13 @@
         <v>3717</v>
       </c>
       <c r="C1875" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D1875" t="s" s="2">
+        <v>3583</v>
+      </c>
+      <c r="E1875" t="s" s="3">
         <v>3718</v>
-      </c>
-      <c r="E1875" t="s" s="3">
-        <v>3719</v>
       </c>
     </row>
     <row r="1876" ht="36.0" customHeight="true">
@@ -46359,16 +46362,16 @@
         <v>1875.0</v>
       </c>
       <c r="B1876" t="s" s="3">
+        <v>3719</v>
+      </c>
+      <c r="C1876" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="D1876" t="s" s="2">
+        <v>3583</v>
+      </c>
+      <c r="E1876" t="s" s="3">
         <v>3720</v>
-      </c>
-      <c r="C1876" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1876" t="s" s="2">
-        <v>3718</v>
-      </c>
-      <c r="E1876" t="s" s="3">
-        <v>3721</v>
       </c>
     </row>
     <row r="1877" ht="36.0" customHeight="true">
@@ -46376,13 +46379,13 @@
         <v>1876.0</v>
       </c>
       <c r="B1877" t="s" s="3">
+        <v>3721</v>
+      </c>
+      <c r="C1877" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1877" t="s" s="2">
         <v>3722</v>
-      </c>
-      <c r="C1877" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1877" t="s" s="2">
-        <v>3718</v>
       </c>
       <c r="E1877" t="s" s="3">
         <v>3723</v>
@@ -46399,7 +46402,7 @@
         <v>6</v>
       </c>
       <c r="D1878" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1878" t="s" s="3">
         <v>3725</v>
@@ -46416,7 +46419,7 @@
         <v>6</v>
       </c>
       <c r="D1879" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1879" t="s" s="3">
         <v>3727</v>
@@ -46433,7 +46436,7 @@
         <v>6</v>
       </c>
       <c r="D1880" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1880" t="s" s="3">
         <v>3729</v>
@@ -46450,7 +46453,7 @@
         <v>6</v>
       </c>
       <c r="D1881" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1881" t="s" s="3">
         <v>3731</v>
@@ -46467,7 +46470,7 @@
         <v>6</v>
       </c>
       <c r="D1882" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1882" t="s" s="3">
         <v>3733</v>
@@ -46484,7 +46487,7 @@
         <v>6</v>
       </c>
       <c r="D1883" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1883" t="s" s="3">
         <v>3735</v>
@@ -46501,7 +46504,7 @@
         <v>6</v>
       </c>
       <c r="D1884" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1884" t="s" s="3">
         <v>3737</v>
@@ -46518,7 +46521,7 @@
         <v>6</v>
       </c>
       <c r="D1885" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1885" t="s" s="3">
         <v>3739</v>
@@ -46535,7 +46538,7 @@
         <v>6</v>
       </c>
       <c r="D1886" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1886" t="s" s="3">
         <v>3741</v>
@@ -46552,7 +46555,7 @@
         <v>6</v>
       </c>
       <c r="D1887" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1887" t="s" s="3">
         <v>3743</v>
@@ -46569,7 +46572,7 @@
         <v>6</v>
       </c>
       <c r="D1888" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1888" t="s" s="3">
         <v>3745</v>
@@ -46586,7 +46589,7 @@
         <v>6</v>
       </c>
       <c r="D1889" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1889" t="s" s="3">
         <v>3747</v>
@@ -46603,7 +46606,7 @@
         <v>6</v>
       </c>
       <c r="D1890" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1890" t="s" s="3">
         <v>3749</v>
@@ -46620,7 +46623,7 @@
         <v>6</v>
       </c>
       <c r="D1891" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1891" t="s" s="3">
         <v>3751</v>
@@ -46637,7 +46640,7 @@
         <v>6</v>
       </c>
       <c r="D1892" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1892" t="s" s="3">
         <v>3753</v>
@@ -46654,7 +46657,7 @@
         <v>6</v>
       </c>
       <c r="D1893" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1893" t="s" s="3">
         <v>3755</v>
@@ -46671,7 +46674,7 @@
         <v>6</v>
       </c>
       <c r="D1894" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1894" t="s" s="3">
         <v>3757</v>
@@ -46688,7 +46691,7 @@
         <v>6</v>
       </c>
       <c r="D1895" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1895" t="s" s="3">
         <v>3759</v>
@@ -46705,7 +46708,7 @@
         <v>6</v>
       </c>
       <c r="D1896" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1896" t="s" s="3">
         <v>3761</v>
@@ -46722,7 +46725,7 @@
         <v>6</v>
       </c>
       <c r="D1897" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1897" t="s" s="3">
         <v>3763</v>
@@ -46739,7 +46742,7 @@
         <v>6</v>
       </c>
       <c r="D1898" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1898" t="s" s="3">
         <v>3765</v>
@@ -46756,7 +46759,7 @@
         <v>6</v>
       </c>
       <c r="D1899" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1899" t="s" s="3">
         <v>3767</v>
@@ -46773,7 +46776,7 @@
         <v>6</v>
       </c>
       <c r="D1900" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1900" t="s" s="3">
         <v>3769</v>
@@ -46790,7 +46793,7 @@
         <v>6</v>
       </c>
       <c r="D1901" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1901" t="s" s="3">
         <v>3771</v>
@@ -46807,7 +46810,7 @@
         <v>6</v>
       </c>
       <c r="D1902" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1902" t="s" s="3">
         <v>3773</v>
@@ -46824,7 +46827,7 @@
         <v>6</v>
       </c>
       <c r="D1903" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1903" t="s" s="3">
         <v>3775</v>
@@ -46841,7 +46844,7 @@
         <v>6</v>
       </c>
       <c r="D1904" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1904" t="s" s="3">
         <v>3777</v>
@@ -46858,7 +46861,7 @@
         <v>6</v>
       </c>
       <c r="D1905" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1905" t="s" s="3">
         <v>3779</v>
@@ -46875,7 +46878,7 @@
         <v>6</v>
       </c>
       <c r="D1906" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1906" t="s" s="3">
         <v>3781</v>
@@ -46892,7 +46895,7 @@
         <v>6</v>
       </c>
       <c r="D1907" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1907" t="s" s="3">
         <v>3783</v>
@@ -46909,7 +46912,7 @@
         <v>6</v>
       </c>
       <c r="D1908" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1908" t="s" s="3">
         <v>3785</v>
@@ -46926,7 +46929,7 @@
         <v>6</v>
       </c>
       <c r="D1909" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1909" t="s" s="3">
         <v>3787</v>
@@ -46943,7 +46946,7 @@
         <v>6</v>
       </c>
       <c r="D1910" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1910" t="s" s="3">
         <v>3789</v>
@@ -46960,7 +46963,7 @@
         <v>6</v>
       </c>
       <c r="D1911" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1911" t="s" s="3">
         <v>3791</v>
@@ -46977,7 +46980,7 @@
         <v>6</v>
       </c>
       <c r="D1912" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1912" t="s" s="3">
         <v>3793</v>
@@ -46994,7 +46997,7 @@
         <v>6</v>
       </c>
       <c r="D1913" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1913" t="s" s="3">
         <v>3795</v>
@@ -47011,7 +47014,7 @@
         <v>6</v>
       </c>
       <c r="D1914" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1914" t="s" s="3">
         <v>3797</v>
@@ -47028,7 +47031,7 @@
         <v>6</v>
       </c>
       <c r="D1915" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1915" t="s" s="3">
         <v>3799</v>
@@ -47045,7 +47048,7 @@
         <v>6</v>
       </c>
       <c r="D1916" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1916" t="s" s="3">
         <v>3801</v>
@@ -47062,7 +47065,7 @@
         <v>6</v>
       </c>
       <c r="D1917" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1917" t="s" s="3">
         <v>3803</v>
@@ -47079,7 +47082,7 @@
         <v>6</v>
       </c>
       <c r="D1918" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1918" t="s" s="3">
         <v>3805</v>
@@ -47096,7 +47099,7 @@
         <v>6</v>
       </c>
       <c r="D1919" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1919" t="s" s="3">
         <v>3807</v>
@@ -47113,7 +47116,7 @@
         <v>6</v>
       </c>
       <c r="D1920" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1920" t="s" s="3">
         <v>3809</v>
@@ -47130,7 +47133,7 @@
         <v>6</v>
       </c>
       <c r="D1921" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1921" t="s" s="3">
         <v>3811</v>
@@ -47147,7 +47150,7 @@
         <v>6</v>
       </c>
       <c r="D1922" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1922" t="s" s="3">
         <v>3813</v>
@@ -47164,7 +47167,7 @@
         <v>6</v>
       </c>
       <c r="D1923" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1923" t="s" s="3">
         <v>3815</v>
@@ -47181,7 +47184,7 @@
         <v>6</v>
       </c>
       <c r="D1924" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1924" t="s" s="3">
         <v>3817</v>
@@ -47198,7 +47201,7 @@
         <v>6</v>
       </c>
       <c r="D1925" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1925" t="s" s="3">
         <v>3819</v>
@@ -47215,7 +47218,7 @@
         <v>6</v>
       </c>
       <c r="D1926" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1926" t="s" s="3">
         <v>3821</v>
@@ -47232,7 +47235,7 @@
         <v>6</v>
       </c>
       <c r="D1927" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1927" t="s" s="3">
         <v>3823</v>
@@ -47249,7 +47252,7 @@
         <v>6</v>
       </c>
       <c r="D1928" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1928" t="s" s="3">
         <v>3825</v>
@@ -47266,7 +47269,7 @@
         <v>6</v>
       </c>
       <c r="D1929" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1929" t="s" s="3">
         <v>3827</v>
@@ -47283,7 +47286,7 @@
         <v>6</v>
       </c>
       <c r="D1930" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1930" t="s" s="3">
         <v>3829</v>
@@ -47300,7 +47303,7 @@
         <v>6</v>
       </c>
       <c r="D1931" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1931" t="s" s="3">
         <v>3831</v>
@@ -47317,7 +47320,7 @@
         <v>6</v>
       </c>
       <c r="D1932" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1932" t="s" s="3">
         <v>3833</v>
@@ -47334,7 +47337,7 @@
         <v>6</v>
       </c>
       <c r="D1933" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1933" t="s" s="3">
         <v>3835</v>
@@ -47351,7 +47354,7 @@
         <v>6</v>
       </c>
       <c r="D1934" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1934" t="s" s="3">
         <v>3837</v>
@@ -47368,7 +47371,7 @@
         <v>6</v>
       </c>
       <c r="D1935" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1935" t="s" s="3">
         <v>3839</v>
@@ -47385,7 +47388,7 @@
         <v>6</v>
       </c>
       <c r="D1936" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1936" t="s" s="3">
         <v>3841</v>
@@ -47402,7 +47405,7 @@
         <v>6</v>
       </c>
       <c r="D1937" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1937" t="s" s="3">
         <v>3843</v>
@@ -47419,7 +47422,7 @@
         <v>6</v>
       </c>
       <c r="D1938" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1938" t="s" s="3">
         <v>3845</v>
@@ -47436,7 +47439,7 @@
         <v>6</v>
       </c>
       <c r="D1939" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1939" t="s" s="3">
         <v>3847</v>
@@ -47453,7 +47456,7 @@
         <v>6</v>
       </c>
       <c r="D1940" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1940" t="s" s="3">
         <v>3849</v>
@@ -47470,7 +47473,7 @@
         <v>6</v>
       </c>
       <c r="D1941" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1941" t="s" s="3">
         <v>3851</v>
@@ -47487,7 +47490,7 @@
         <v>6</v>
       </c>
       <c r="D1942" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1942" t="s" s="3">
         <v>3853</v>
@@ -47504,7 +47507,7 @@
         <v>6</v>
       </c>
       <c r="D1943" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1943" t="s" s="3">
         <v>3855</v>
@@ -47521,7 +47524,7 @@
         <v>6</v>
       </c>
       <c r="D1944" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1944" t="s" s="3">
         <v>3857</v>
@@ -47538,7 +47541,7 @@
         <v>6</v>
       </c>
       <c r="D1945" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1945" t="s" s="3">
         <v>3859</v>
@@ -47555,7 +47558,7 @@
         <v>6</v>
       </c>
       <c r="D1946" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1946" t="s" s="3">
         <v>3861</v>
@@ -47572,7 +47575,7 @@
         <v>6</v>
       </c>
       <c r="D1947" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1947" t="s" s="3">
         <v>3863</v>
@@ -47589,7 +47592,7 @@
         <v>6</v>
       </c>
       <c r="D1948" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1948" t="s" s="3">
         <v>3865</v>
@@ -47606,7 +47609,7 @@
         <v>6</v>
       </c>
       <c r="D1949" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1949" t="s" s="3">
         <v>3867</v>
@@ -47623,7 +47626,7 @@
         <v>6</v>
       </c>
       <c r="D1950" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1950" t="s" s="3">
         <v>3869</v>
@@ -47640,7 +47643,7 @@
         <v>6</v>
       </c>
       <c r="D1951" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1951" t="s" s="3">
         <v>3871</v>
@@ -47657,7 +47660,7 @@
         <v>6</v>
       </c>
       <c r="D1952" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1952" t="s" s="3">
         <v>3873</v>
@@ -47674,7 +47677,7 @@
         <v>6</v>
       </c>
       <c r="D1953" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1953" t="s" s="3">
         <v>3875</v>
@@ -47691,7 +47694,7 @@
         <v>6</v>
       </c>
       <c r="D1954" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1954" t="s" s="3">
         <v>3877</v>
@@ -47708,7 +47711,7 @@
         <v>6</v>
       </c>
       <c r="D1955" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1955" t="s" s="3">
         <v>3879</v>
@@ -47725,7 +47728,7 @@
         <v>6</v>
       </c>
       <c r="D1956" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1956" t="s" s="3">
         <v>3881</v>
@@ -47742,7 +47745,7 @@
         <v>6</v>
       </c>
       <c r="D1957" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1957" t="s" s="3">
         <v>3883</v>
@@ -47759,7 +47762,7 @@
         <v>6</v>
       </c>
       <c r="D1958" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1958" t="s" s="3">
         <v>3885</v>
@@ -47776,7 +47779,7 @@
         <v>6</v>
       </c>
       <c r="D1959" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1959" t="s" s="3">
         <v>3887</v>
@@ -47793,7 +47796,7 @@
         <v>6</v>
       </c>
       <c r="D1960" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3889</v>
@@ -47810,7 +47813,7 @@
         <v>6</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1961" t="s" s="3">
         <v>3891</v>
@@ -47827,7 +47830,7 @@
         <v>6</v>
       </c>
       <c r="D1962" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1962" t="s" s="3">
         <v>3893</v>
@@ -47844,7 +47847,7 @@
         <v>6</v>
       </c>
       <c r="D1963" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1963" t="s" s="3">
         <v>3895</v>
@@ -47861,7 +47864,7 @@
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1964" t="s" s="3">
         <v>3897</v>
@@ -47878,7 +47881,7 @@
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3899</v>
@@ -47895,7 +47898,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3901</v>
@@ -47912,7 +47915,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3903</v>
@@ -47929,7 +47932,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3905</v>
@@ -47940,16 +47943,16 @@
         <v>1968.0</v>
       </c>
       <c r="B1969" t="s" s="3">
-        <v>1295</v>
+        <v>3906</v>
       </c>
       <c r="C1969" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1969" t="s" s="3">
-        <v>3906</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="1970" ht="36.0" customHeight="true">
@@ -47957,16 +47960,16 @@
         <v>1969.0</v>
       </c>
       <c r="B1970" t="s" s="3">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="C1970" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1970" t="s" s="3">
-        <v>3908</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="1971" ht="36.0" customHeight="true">
@@ -47974,13 +47977,13 @@
         <v>1970.0</v>
       </c>
       <c r="B1971" t="s" s="3">
-        <v>3909</v>
+        <v>1295</v>
       </c>
       <c r="C1971" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3910</v>
@@ -47997,7 +48000,7 @@
         <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3912</v>
@@ -48014,7 +48017,7 @@
         <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3914</v>
@@ -48031,7 +48034,7 @@
         <v>6</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3916</v>
@@ -48048,7 +48051,7 @@
         <v>6</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3918</v>
@@ -48065,7 +48068,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3920</v>
@@ -48082,7 +48085,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3922</v>
@@ -48099,7 +48102,7 @@
         <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3924</v>
@@ -48116,7 +48119,7 @@
         <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3926</v>
@@ -48133,7 +48136,7 @@
         <v>6</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3928</v>
@@ -48150,7 +48153,7 @@
         <v>6</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3930</v>
@@ -48167,7 +48170,7 @@
         <v>6</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3932</v>
@@ -48184,7 +48187,7 @@
         <v>6</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3934</v>
@@ -48201,7 +48204,7 @@
         <v>6</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3936</v>
@@ -48218,7 +48221,7 @@
         <v>6</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3938</v>
@@ -48235,7 +48238,7 @@
         <v>6</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3940</v>
@@ -48252,7 +48255,7 @@
         <v>6</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3942</v>
@@ -48269,7 +48272,7 @@
         <v>6</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3944</v>
@@ -48286,7 +48289,7 @@
         <v>6</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3946</v>
@@ -48303,7 +48306,7 @@
         <v>6</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3948</v>
@@ -48320,7 +48323,7 @@
         <v>6</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3950</v>
@@ -48337,7 +48340,7 @@
         <v>6</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3952</v>
@@ -48354,7 +48357,7 @@
         <v>6</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3954</v>
@@ -48371,7 +48374,7 @@
         <v>6</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3956</v>
@@ -48388,7 +48391,7 @@
         <v>6</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3958</v>
@@ -48405,7 +48408,7 @@
         <v>6</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3960</v>
@@ -48422,7 +48425,7 @@
         <v>6</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3962</v>
@@ -48439,7 +48442,7 @@
         <v>6</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3964</v>
@@ -48456,7 +48459,7 @@
         <v>6</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3966</v>
@@ -48473,7 +48476,7 @@
         <v>6</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3968</v>
@@ -48490,7 +48493,7 @@
         <v>6</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3970</v>
@@ -48507,7 +48510,7 @@
         <v>6</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3972</v>
@@ -48524,7 +48527,7 @@
         <v>6</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3974</v>
@@ -48541,7 +48544,7 @@
         <v>6</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3976</v>
@@ -48558,7 +48561,7 @@
         <v>6</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3978</v>
@@ -48575,7 +48578,7 @@
         <v>6</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2006" t="s" s="3">
         <v>3980</v>
@@ -48592,7 +48595,7 @@
         <v>6</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2007" t="s" s="3">
         <v>3982</v>
@@ -48609,7 +48612,7 @@
         <v>6</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2008" t="s" s="3">
         <v>3984</v>
@@ -48626,7 +48629,7 @@
         <v>6</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3986</v>
@@ -48640,10 +48643,10 @@
         <v>3987</v>
       </c>
       <c r="C2010" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3988</v>
@@ -48657,10 +48660,10 @@
         <v>3989</v>
       </c>
       <c r="C2011" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3990</v>
@@ -48677,7 +48680,7 @@
         <v>702</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>3992</v>
@@ -48694,7 +48697,7 @@
         <v>702</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2013" t="s" s="3">
         <v>3994</v>
@@ -48711,7 +48714,7 @@
         <v>702</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>3996</v>
@@ -48728,7 +48731,7 @@
         <v>702</v>
       </c>
       <c r="D2015" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>3998</v>
@@ -48745,7 +48748,7 @@
         <v>702</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4000</v>
@@ -48762,7 +48765,7 @@
         <v>702</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4002</v>
@@ -48779,7 +48782,7 @@
         <v>702</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4004</v>
@@ -48796,7 +48799,7 @@
         <v>702</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4006</v>
@@ -48813,7 +48816,7 @@
         <v>702</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4008</v>
@@ -48830,7 +48833,7 @@
         <v>702</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4010</v>
@@ -48847,7 +48850,7 @@
         <v>702</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4012</v>
@@ -48864,7 +48867,7 @@
         <v>702</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4014</v>
@@ -48881,7 +48884,7 @@
         <v>702</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4016</v>
@@ -48898,7 +48901,7 @@
         <v>702</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4018</v>
@@ -48915,7 +48918,7 @@
         <v>702</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4020</v>
@@ -48932,7 +48935,7 @@
         <v>702</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4022</v>
@@ -48949,7 +48952,7 @@
         <v>702</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4024</v>
@@ -48966,7 +48969,7 @@
         <v>702</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4026</v>
@@ -48983,7 +48986,7 @@
         <v>702</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4028</v>
@@ -49000,7 +49003,7 @@
         <v>702</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4030</v>
@@ -49017,7 +49020,7 @@
         <v>702</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4032</v>
@@ -49034,7 +49037,7 @@
         <v>702</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4034</v>
@@ -49051,7 +49054,7 @@
         <v>702</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4036</v>
@@ -49068,7 +49071,7 @@
         <v>702</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2035" t="s" s="3">
         <v>4038</v>
@@ -49085,7 +49088,7 @@
         <v>702</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4040</v>
@@ -49102,7 +49105,7 @@
         <v>702</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2037" t="s" s="3">
         <v>4042</v>
@@ -49119,7 +49122,7 @@
         <v>702</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4044</v>
@@ -49136,10 +49139,10 @@
         <v>702</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2039" t="s" s="3">
-        <v>3926</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="2040" ht="36.0" customHeight="true">
@@ -49147,16 +49150,16 @@
         <v>2039.0</v>
       </c>
       <c r="B2040" t="s" s="3">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C2040" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2040" t="s" s="3">
-        <v>4047</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="2041" ht="36.0" customHeight="true">
@@ -49164,16 +49167,16 @@
         <v>2040.0</v>
       </c>
       <c r="B2041" t="s" s="3">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="C2041" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2041" t="s" s="3">
-        <v>4049</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="2042" ht="36.0" customHeight="true">
@@ -49187,7 +49190,7 @@
         <v>702</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4051</v>
@@ -49204,7 +49207,7 @@
         <v>702</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4053</v>
@@ -49221,7 +49224,7 @@
         <v>702</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4055</v>
@@ -49238,7 +49241,7 @@
         <v>702</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4057</v>
@@ -49255,7 +49258,7 @@
         <v>702</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4059</v>
@@ -49272,7 +49275,7 @@
         <v>702</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4061</v>
@@ -49289,7 +49292,7 @@
         <v>702</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4063</v>
@@ -49306,7 +49309,7 @@
         <v>702</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4065</v>
@@ -49323,7 +49326,7 @@
         <v>702</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4067</v>
@@ -49340,7 +49343,7 @@
         <v>702</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4069</v>
@@ -49357,7 +49360,7 @@
         <v>702</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4071</v>
@@ -49374,7 +49377,7 @@
         <v>702</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4073</v>
@@ -49391,7 +49394,7 @@
         <v>702</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4075</v>
@@ -49408,7 +49411,7 @@
         <v>702</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4077</v>
@@ -49425,7 +49428,7 @@
         <v>702</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4079</v>
@@ -49442,7 +49445,7 @@
         <v>702</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4081</v>
@@ -49459,7 +49462,7 @@
         <v>702</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4083</v>
@@ -49476,7 +49479,7 @@
         <v>702</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4085</v>
@@ -49493,7 +49496,7 @@
         <v>702</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4087</v>
@@ -49510,7 +49513,7 @@
         <v>702</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4089</v>
@@ -49527,7 +49530,7 @@
         <v>702</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4091</v>
@@ -49544,7 +49547,7 @@
         <v>702</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4093</v>
@@ -49561,7 +49564,7 @@
         <v>702</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4095</v>
@@ -49578,7 +49581,7 @@
         <v>702</v>
       </c>
       <c r="D2065" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2065" t="s" s="3">
         <v>4097</v>
@@ -49595,7 +49598,7 @@
         <v>702</v>
       </c>
       <c r="D2066" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4099</v>
@@ -49612,7 +49615,7 @@
         <v>702</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4101</v>
@@ -49629,7 +49632,7 @@
         <v>702</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4103</v>
@@ -49646,7 +49649,7 @@
         <v>702</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4105</v>
@@ -49663,7 +49666,7 @@
         <v>702</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4107</v>
@@ -49680,7 +49683,7 @@
         <v>702</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4109</v>
@@ -49697,7 +49700,7 @@
         <v>702</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2072" t="s" s="3">
         <v>4111</v>
@@ -49714,7 +49717,7 @@
         <v>702</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2073" t="s" s="3">
         <v>4113</v>
@@ -49731,7 +49734,7 @@
         <v>702</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2074" t="s" s="3">
         <v>4115</v>
@@ -49748,7 +49751,7 @@
         <v>702</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2075" t="s" s="3">
         <v>4117</v>
@@ -49765,7 +49768,7 @@
         <v>702</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4119</v>
@@ -49779,10 +49782,10 @@
         <v>4120</v>
       </c>
       <c r="C2077" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4121</v>
@@ -49796,10 +49799,10 @@
         <v>4122</v>
       </c>
       <c r="C2078" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4123</v>
@@ -49816,7 +49819,7 @@
         <v>897</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4125</v>
@@ -49833,7 +49836,7 @@
         <v>897</v>
       </c>
       <c r="D2080" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2080" t="s" s="3">
         <v>4127</v>
@@ -49850,7 +49853,7 @@
         <v>897</v>
       </c>
       <c r="D2081" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4129</v>
@@ -49867,7 +49870,7 @@
         <v>897</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>3718</v>
+        <v>3722</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4131</v>
@@ -49881,13 +49884,13 @@
         <v>4132</v>
       </c>
       <c r="C2083" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D2083" t="s" s="2">
+        <v>3722</v>
+      </c>
+      <c r="E2083" t="s" s="3">
         <v>4133</v>
-      </c>
-      <c r="E2083" t="s" s="3">
-        <v>4134</v>
       </c>
     </row>
     <row r="2084" ht="36.0" customHeight="true">
@@ -49895,16 +49898,16 @@
         <v>2083.0</v>
       </c>
       <c r="B2084" t="s" s="3">
+        <v>4134</v>
+      </c>
+      <c r="C2084" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="D2084" t="s" s="2">
+        <v>3722</v>
+      </c>
+      <c r="E2084" t="s" s="3">
         <v>4135</v>
-      </c>
-      <c r="C2084" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2084" t="s" s="2">
-        <v>4133</v>
-      </c>
-      <c r="E2084" t="s" s="3">
-        <v>4136</v>
       </c>
     </row>
     <row r="2085" ht="36.0" customHeight="true">
@@ -49912,13 +49915,13 @@
         <v>2084.0</v>
       </c>
       <c r="B2085" t="s" s="3">
+        <v>4136</v>
+      </c>
+      <c r="C2085" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2085" t="s" s="2">
         <v>4137</v>
-      </c>
-      <c r="C2085" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2085" t="s" s="2">
-        <v>4133</v>
       </c>
       <c r="E2085" t="s" s="3">
         <v>4138</v>
@@ -49935,7 +49938,7 @@
         <v>6</v>
       </c>
       <c r="D2086" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2086" t="s" s="3">
         <v>4140</v>
@@ -49952,7 +49955,7 @@
         <v>6</v>
       </c>
       <c r="D2087" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4142</v>
@@ -49969,7 +49972,7 @@
         <v>6</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4144</v>
@@ -49986,7 +49989,7 @@
         <v>6</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4146</v>
@@ -50003,7 +50006,7 @@
         <v>6</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2090" t="s" s="3">
         <v>4148</v>
@@ -50020,7 +50023,7 @@
         <v>6</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4150</v>
@@ -50037,7 +50040,7 @@
         <v>6</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4152</v>
@@ -50054,7 +50057,7 @@
         <v>6</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4154</v>
@@ -50071,7 +50074,7 @@
         <v>6</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4156</v>
@@ -50088,7 +50091,7 @@
         <v>6</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4158</v>
@@ -50105,7 +50108,7 @@
         <v>6</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4160</v>
@@ -50122,7 +50125,7 @@
         <v>6</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4162</v>
@@ -50139,7 +50142,7 @@
         <v>6</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4164</v>
@@ -50156,7 +50159,7 @@
         <v>6</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4166</v>
@@ -50173,7 +50176,7 @@
         <v>6</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4168</v>
@@ -50190,7 +50193,7 @@
         <v>6</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2101" t="s" s="3">
         <v>4170</v>
@@ -50207,7 +50210,7 @@
         <v>6</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2102" t="s" s="3">
         <v>4172</v>
@@ -50224,7 +50227,7 @@
         <v>6</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2103" t="s" s="3">
         <v>4174</v>
@@ -50241,7 +50244,7 @@
         <v>6</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2104" t="s" s="3">
         <v>4176</v>
@@ -50258,7 +50261,7 @@
         <v>6</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2105" t="s" s="3">
         <v>4178</v>
@@ -50275,7 +50278,7 @@
         <v>6</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2106" t="s" s="3">
         <v>4180</v>
@@ -50292,7 +50295,7 @@
         <v>6</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2107" t="s" s="3">
         <v>4182</v>
@@ -50309,7 +50312,7 @@
         <v>6</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4184</v>
@@ -50326,7 +50329,7 @@
         <v>6</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2109" t="s" s="3">
         <v>4186</v>
@@ -50343,7 +50346,7 @@
         <v>6</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2110" t="s" s="3">
         <v>4188</v>
@@ -50360,7 +50363,7 @@
         <v>6</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2111" t="s" s="3">
         <v>4190</v>
@@ -50377,7 +50380,7 @@
         <v>6</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4192</v>
@@ -50394,7 +50397,7 @@
         <v>6</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4194</v>
@@ -50411,7 +50414,7 @@
         <v>6</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4196</v>
@@ -50428,7 +50431,7 @@
         <v>6</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4198</v>
@@ -50445,7 +50448,7 @@
         <v>6</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4200</v>
@@ -50462,7 +50465,7 @@
         <v>6</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4202</v>
@@ -50479,7 +50482,7 @@
         <v>6</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4204</v>
@@ -50496,7 +50499,7 @@
         <v>6</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4206</v>
@@ -50513,7 +50516,7 @@
         <v>6</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4208</v>
@@ -50530,7 +50533,7 @@
         <v>6</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4210</v>
@@ -50547,7 +50550,7 @@
         <v>6</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4212</v>
@@ -50564,7 +50567,7 @@
         <v>6</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4214</v>
@@ -50581,7 +50584,7 @@
         <v>6</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2124" t="s" s="3">
         <v>4216</v>
@@ -50598,7 +50601,7 @@
         <v>6</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2125" t="s" s="3">
         <v>4218</v>
@@ -50615,7 +50618,7 @@
         <v>6</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2126" t="s" s="3">
         <v>4220</v>
@@ -50632,7 +50635,7 @@
         <v>6</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2127" t="s" s="3">
         <v>4222</v>
@@ -50649,7 +50652,7 @@
         <v>6</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2128" t="s" s="3">
         <v>4224</v>
@@ -50666,7 +50669,7 @@
         <v>6</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4226</v>
@@ -50683,7 +50686,7 @@
         <v>6</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4228</v>
@@ -50700,7 +50703,7 @@
         <v>6</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4230</v>
@@ -50717,7 +50720,7 @@
         <v>6</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4232</v>
@@ -50734,7 +50737,7 @@
         <v>6</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4234</v>
@@ -50751,7 +50754,7 @@
         <v>6</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4236</v>
@@ -50768,7 +50771,7 @@
         <v>6</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4238</v>
@@ -50785,7 +50788,7 @@
         <v>6</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2136" t="s" s="3">
         <v>4240</v>
@@ -50799,10 +50802,10 @@
         <v>4241</v>
       </c>
       <c r="C2137" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4242</v>
@@ -50816,10 +50819,10 @@
         <v>4243</v>
       </c>
       <c r="C2138" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4244</v>
@@ -50836,7 +50839,7 @@
         <v>702</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4246</v>
@@ -50853,7 +50856,7 @@
         <v>702</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4248</v>
@@ -50870,7 +50873,7 @@
         <v>702</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4250</v>
@@ -50887,7 +50890,7 @@
         <v>702</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4252</v>
@@ -50904,7 +50907,7 @@
         <v>702</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4254</v>
@@ -50921,7 +50924,7 @@
         <v>702</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4256</v>
@@ -50938,7 +50941,7 @@
         <v>702</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2145" t="s" s="3">
         <v>4258</v>
@@ -50955,7 +50958,7 @@
         <v>702</v>
       </c>
       <c r="D2146" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2146" t="s" s="3">
         <v>4260</v>
@@ -50972,7 +50975,7 @@
         <v>702</v>
       </c>
       <c r="D2147" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2147" t="s" s="3">
         <v>4262</v>
@@ -50989,7 +50992,7 @@
         <v>702</v>
       </c>
       <c r="D2148" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2148" t="s" s="3">
         <v>4264</v>
@@ -51006,7 +51009,7 @@
         <v>702</v>
       </c>
       <c r="D2149" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2149" t="s" s="3">
         <v>4266</v>
@@ -51023,7 +51026,7 @@
         <v>702</v>
       </c>
       <c r="D2150" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2150" t="s" s="3">
         <v>4268</v>
@@ -51040,7 +51043,7 @@
         <v>702</v>
       </c>
       <c r="D2151" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2151" t="s" s="3">
         <v>4270</v>
@@ -51057,7 +51060,7 @@
         <v>702</v>
       </c>
       <c r="D2152" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4272</v>
@@ -51074,7 +51077,7 @@
         <v>702</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4274</v>
@@ -51091,7 +51094,7 @@
         <v>702</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4276</v>
@@ -51108,7 +51111,7 @@
         <v>702</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4278</v>
@@ -51125,7 +51128,7 @@
         <v>702</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4280</v>
@@ -51142,7 +51145,7 @@
         <v>702</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4282</v>
@@ -51159,7 +51162,7 @@
         <v>702</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4284</v>
@@ -51176,7 +51179,7 @@
         <v>702</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4286</v>
@@ -51193,7 +51196,7 @@
         <v>702</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4288</v>
@@ -51210,7 +51213,7 @@
         <v>702</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2161" t="s" s="3">
         <v>4290</v>
@@ -51227,7 +51230,7 @@
         <v>702</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2162" t="s" s="3">
         <v>4292</v>
@@ -51244,7 +51247,7 @@
         <v>702</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2163" t="s" s="3">
         <v>4294</v>
@@ -51261,7 +51264,7 @@
         <v>702</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2164" t="s" s="3">
         <v>4296</v>
@@ -51278,7 +51281,7 @@
         <v>702</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2165" t="s" s="3">
         <v>4298</v>
@@ -51295,7 +51298,7 @@
         <v>702</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2166" t="s" s="3">
         <v>4300</v>
@@ -51312,7 +51315,7 @@
         <v>702</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2167" t="s" s="3">
         <v>4302</v>
@@ -51329,7 +51332,7 @@
         <v>702</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2168" t="s" s="3">
         <v>4304</v>
@@ -51346,7 +51349,7 @@
         <v>702</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2169" t="s" s="3">
         <v>4306</v>
@@ -51363,7 +51366,7 @@
         <v>702</v>
       </c>
       <c r="D2170" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2170" t="s" s="3">
         <v>4308</v>
@@ -51380,7 +51383,7 @@
         <v>702</v>
       </c>
       <c r="D2171" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2171" t="s" s="3">
         <v>4310</v>
@@ -51397,7 +51400,7 @@
         <v>702</v>
       </c>
       <c r="D2172" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4312</v>
@@ -51414,7 +51417,7 @@
         <v>702</v>
       </c>
       <c r="D2173" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2173" t="s" s="3">
         <v>4314</v>
@@ -51431,7 +51434,7 @@
         <v>702</v>
       </c>
       <c r="D2174" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2174" t="s" s="3">
         <v>4316</v>
@@ -51445,10 +51448,10 @@
         <v>4317</v>
       </c>
       <c r="C2175" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2175" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4318</v>
@@ -51462,10 +51465,10 @@
         <v>4319</v>
       </c>
       <c r="C2176" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4320</v>
@@ -51482,7 +51485,7 @@
         <v>897</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4322</v>
@@ -51499,7 +51502,7 @@
         <v>897</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4324</v>
@@ -51516,7 +51519,7 @@
         <v>897</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4326</v>
@@ -51533,7 +51536,7 @@
         <v>897</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4328</v>
@@ -51550,7 +51553,7 @@
         <v>897</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4330</v>
@@ -51567,7 +51570,7 @@
         <v>897</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4133</v>
+        <v>4137</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4332</v>
@@ -51581,13 +51584,13 @@
         <v>4333</v>
       </c>
       <c r="C2183" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D2183" t="s" s="2">
+        <v>4137</v>
+      </c>
+      <c r="E2183" t="s" s="3">
         <v>4334</v>
-      </c>
-      <c r="E2183" t="s" s="3">
-        <v>4335</v>
       </c>
     </row>
     <row r="2184" ht="36.0" customHeight="true">
@@ -51595,16 +51598,16 @@
         <v>2183.0</v>
       </c>
       <c r="B2184" t="s" s="3">
+        <v>4335</v>
+      </c>
+      <c r="C2184" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="D2184" t="s" s="2">
+        <v>4137</v>
+      </c>
+      <c r="E2184" t="s" s="3">
         <v>4336</v>
-      </c>
-      <c r="C2184" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2184" t="s" s="2">
-        <v>4334</v>
-      </c>
-      <c r="E2184" t="s" s="3">
-        <v>4337</v>
       </c>
     </row>
     <row r="2185" ht="36.0" customHeight="true">
@@ -51612,13 +51615,13 @@
         <v>2184.0</v>
       </c>
       <c r="B2185" t="s" s="3">
+        <v>4337</v>
+      </c>
+      <c r="C2185" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2185" t="s" s="2">
         <v>4338</v>
-      </c>
-      <c r="C2185" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2185" t="s" s="2">
-        <v>4334</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4339</v>
@@ -51635,7 +51638,7 @@
         <v>6</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4341</v>
@@ -51652,7 +51655,7 @@
         <v>6</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4343</v>
@@ -51669,7 +51672,7 @@
         <v>6</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4345</v>
@@ -51686,7 +51689,7 @@
         <v>6</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4347</v>
@@ -51703,7 +51706,7 @@
         <v>6</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4349</v>
@@ -51720,7 +51723,7 @@
         <v>6</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4351</v>
@@ -51737,7 +51740,7 @@
         <v>6</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4353</v>
@@ -51754,7 +51757,7 @@
         <v>6</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4355</v>
@@ -51771,7 +51774,7 @@
         <v>6</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4357</v>
@@ -51788,7 +51791,7 @@
         <v>6</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2195" t="s" s="3">
         <v>4359</v>
@@ -51805,7 +51808,7 @@
         <v>6</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2196" t="s" s="3">
         <v>4361</v>
@@ -51822,7 +51825,7 @@
         <v>6</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4363</v>
@@ -51839,7 +51842,7 @@
         <v>6</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2198" t="s" s="3">
         <v>4365</v>
@@ -51856,7 +51859,7 @@
         <v>6</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2199" t="s" s="3">
         <v>4367</v>
@@ -51873,7 +51876,7 @@
         <v>6</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4369</v>
@@ -51890,7 +51893,7 @@
         <v>6</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4371</v>
@@ -51907,7 +51910,7 @@
         <v>6</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4373</v>
@@ -51924,7 +51927,7 @@
         <v>6</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4375</v>
@@ -51941,7 +51944,7 @@
         <v>6</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4377</v>
@@ -51958,7 +51961,7 @@
         <v>6</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4379</v>
@@ -51975,7 +51978,7 @@
         <v>6</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4381</v>
@@ -51992,7 +51995,7 @@
         <v>6</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4383</v>
@@ -52009,7 +52012,7 @@
         <v>6</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4385</v>
@@ -52026,7 +52029,7 @@
         <v>6</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4387</v>
@@ -52043,7 +52046,7 @@
         <v>6</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4389</v>
@@ -52060,7 +52063,7 @@
         <v>6</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4391</v>
@@ -52077,7 +52080,7 @@
         <v>6</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2212" t="s" s="3">
         <v>4393</v>
@@ -52094,7 +52097,7 @@
         <v>6</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2213" t="s" s="3">
         <v>4395</v>
@@ -52111,7 +52114,7 @@
         <v>6</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2214" t="s" s="3">
         <v>4397</v>
@@ -52128,7 +52131,7 @@
         <v>6</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2215" t="s" s="3">
         <v>4399</v>
@@ -52145,7 +52148,7 @@
         <v>6</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4401</v>
@@ -52162,7 +52165,7 @@
         <v>6</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4403</v>
@@ -52179,7 +52182,7 @@
         <v>6</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4405</v>
@@ -52196,7 +52199,7 @@
         <v>6</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4407</v>
@@ -52213,7 +52216,7 @@
         <v>6</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4409</v>
@@ -52230,7 +52233,7 @@
         <v>6</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4411</v>
@@ -52247,7 +52250,7 @@
         <v>6</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4413</v>
@@ -52264,7 +52267,7 @@
         <v>6</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4415</v>
@@ -52281,7 +52284,7 @@
         <v>6</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4417</v>
@@ -52298,7 +52301,7 @@
         <v>6</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4419</v>
@@ -52315,7 +52318,7 @@
         <v>6</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4421</v>
@@ -52332,7 +52335,7 @@
         <v>6</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4423</v>
@@ -52349,7 +52352,7 @@
         <v>6</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4425</v>
@@ -52366,7 +52369,7 @@
         <v>6</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4427</v>
@@ -52383,7 +52386,7 @@
         <v>6</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4429</v>
@@ -52400,7 +52403,7 @@
         <v>6</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4431</v>
@@ -52417,7 +52420,7 @@
         <v>6</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4433</v>
@@ -52434,7 +52437,7 @@
         <v>6</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4435</v>
@@ -52451,7 +52454,7 @@
         <v>6</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4437</v>
@@ -52468,7 +52471,7 @@
         <v>6</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4439</v>
@@ -52485,7 +52488,7 @@
         <v>6</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4441</v>
@@ -52502,7 +52505,7 @@
         <v>6</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4443</v>
@@ -52519,7 +52522,7 @@
         <v>6</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4445</v>
@@ -52536,7 +52539,7 @@
         <v>6</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4447</v>
@@ -52553,7 +52556,7 @@
         <v>6</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4449</v>
@@ -52570,7 +52573,7 @@
         <v>6</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4451</v>
@@ -52587,7 +52590,7 @@
         <v>6</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4453</v>
@@ -52604,7 +52607,7 @@
         <v>6</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4455</v>
@@ -52621,7 +52624,7 @@
         <v>6</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4457</v>
@@ -52638,7 +52641,7 @@
         <v>6</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4459</v>
@@ -52655,7 +52658,7 @@
         <v>6</v>
       </c>
       <c r="D2246" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2246" t="s" s="3">
         <v>4461</v>
@@ -52672,7 +52675,7 @@
         <v>6</v>
       </c>
       <c r="D2247" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2247" t="s" s="3">
         <v>4463</v>
@@ -52689,7 +52692,7 @@
         <v>6</v>
       </c>
       <c r="D2248" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2248" t="s" s="3">
         <v>4465</v>
@@ -52706,7 +52709,7 @@
         <v>6</v>
       </c>
       <c r="D2249" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2249" t="s" s="3">
         <v>4467</v>
@@ -52723,7 +52726,7 @@
         <v>6</v>
       </c>
       <c r="D2250" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2250" t="s" s="3">
         <v>4469</v>
@@ -52740,7 +52743,7 @@
         <v>6</v>
       </c>
       <c r="D2251" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2251" t="s" s="3">
         <v>4471</v>
@@ -52751,16 +52754,16 @@
         <v>2251.0</v>
       </c>
       <c r="B2252" t="s" s="3">
-        <v>3546</v>
+        <v>4472</v>
       </c>
       <c r="C2252" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2252" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2252" t="s" s="3">
-        <v>4472</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="2253" ht="36.0" customHeight="true">
@@ -52768,16 +52771,16 @@
         <v>2252.0</v>
       </c>
       <c r="B2253" t="s" s="3">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="C2253" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2253" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2253" t="s" s="3">
-        <v>4474</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="2254" ht="36.0" customHeight="true">
@@ -52785,13 +52788,13 @@
         <v>2253.0</v>
       </c>
       <c r="B2254" t="s" s="3">
-        <v>4475</v>
+        <v>3550</v>
       </c>
       <c r="C2254" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2254" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4476</v>
@@ -52808,7 +52811,7 @@
         <v>6</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4478</v>
@@ -52825,7 +52828,7 @@
         <v>6</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2256" t="s" s="3">
         <v>4480</v>
@@ -52842,7 +52845,7 @@
         <v>6</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2257" t="s" s="3">
         <v>4482</v>
@@ -52859,7 +52862,7 @@
         <v>6</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2258" t="s" s="3">
         <v>4484</v>
@@ -52876,7 +52879,7 @@
         <v>6</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2259" t="s" s="3">
         <v>4486</v>
@@ -52893,7 +52896,7 @@
         <v>6</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2260" t="s" s="3">
         <v>4488</v>
@@ -52910,7 +52913,7 @@
         <v>6</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2261" t="s" s="3">
         <v>4490</v>
@@ -52927,7 +52930,7 @@
         <v>6</v>
       </c>
       <c r="D2262" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2262" t="s" s="3">
         <v>4492</v>
@@ -52944,7 +52947,7 @@
         <v>6</v>
       </c>
       <c r="D2263" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2263" t="s" s="3">
         <v>4494</v>
@@ -52961,7 +52964,7 @@
         <v>6</v>
       </c>
       <c r="D2264" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4496</v>
@@ -52978,7 +52981,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4498</v>
@@ -52995,7 +52998,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4500</v>
@@ -53012,7 +53015,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4502</v>
@@ -53029,7 +53032,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4504</v>
@@ -53046,7 +53049,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4506</v>
@@ -53063,7 +53066,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4508</v>
@@ -53080,7 +53083,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4510</v>
@@ -53097,7 +53100,7 @@
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2272" t="s" s="3">
         <v>4512</v>
@@ -53114,7 +53117,7 @@
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2273" t="s" s="3">
         <v>4514</v>
@@ -53131,7 +53134,7 @@
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2274" t="s" s="3">
         <v>4516</v>
@@ -53148,7 +53151,7 @@
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4518</v>
@@ -53165,7 +53168,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4520</v>
@@ -53182,7 +53185,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4522</v>
@@ -53199,7 +53202,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4524</v>
@@ -53216,7 +53219,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4526</v>
@@ -53233,7 +53236,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4528</v>
@@ -53250,7 +53253,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4530</v>
@@ -53267,7 +53270,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4532</v>
@@ -53284,7 +53287,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4534</v>
@@ -53301,7 +53304,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4536</v>
@@ -53318,7 +53321,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4538</v>
@@ -53335,7 +53338,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4540</v>
@@ -53352,7 +53355,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4542</v>
@@ -53369,7 +53372,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4544</v>
@@ -53386,7 +53389,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4546</v>
@@ -53403,7 +53406,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4548</v>
@@ -53420,7 +53423,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4550</v>
@@ -53437,7 +53440,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4552</v>
@@ -53454,7 +53457,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4554</v>
@@ -53471,7 +53474,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4556</v>
@@ -53488,7 +53491,7 @@
         <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4558</v>
@@ -53505,7 +53508,7 @@
         <v>6</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4560</v>
@@ -53522,7 +53525,7 @@
         <v>6</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4562</v>
@@ -53539,7 +53542,7 @@
         <v>6</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4564</v>
@@ -53556,7 +53559,7 @@
         <v>6</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4566</v>
@@ -53567,16 +53570,16 @@
         <v>2299.0</v>
       </c>
       <c r="B2300" t="s" s="3">
-        <v>2910</v>
+        <v>4567</v>
       </c>
       <c r="C2300" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2300" t="s" s="3">
-        <v>4567</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="2301" ht="36.0" customHeight="true">
@@ -53584,16 +53587,16 @@
         <v>2300.0</v>
       </c>
       <c r="B2301" t="s" s="3">
-        <v>4568</v>
+        <v>4569</v>
       </c>
       <c r="C2301" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2301" t="s" s="3">
-        <v>4569</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="2302" ht="36.0" customHeight="true">
@@ -53601,13 +53604,13 @@
         <v>2301.0</v>
       </c>
       <c r="B2302" t="s" s="3">
-        <v>4570</v>
+        <v>2910</v>
       </c>
       <c r="C2302" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4571</v>
@@ -53624,10 +53627,10 @@
         <v>6</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2303" t="s" s="3">
-        <v>4441</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="2304" ht="36.0" customHeight="true">
@@ -53635,16 +53638,16 @@
         <v>2303.0</v>
       </c>
       <c r="B2304" t="s" s="3">
-        <v>4573</v>
+        <v>4574</v>
       </c>
       <c r="C2304" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2304" t="s" s="3">
-        <v>4574</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="2305" ht="36.0" customHeight="true">
@@ -53652,16 +53655,16 @@
         <v>2304.0</v>
       </c>
       <c r="B2305" t="s" s="3">
-        <v>4575</v>
+        <v>4576</v>
       </c>
       <c r="C2305" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2305" t="s" s="3">
-        <v>4576</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="2306" ht="36.0" customHeight="true">
@@ -53675,7 +53678,7 @@
         <v>6</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4578</v>
@@ -53692,7 +53695,7 @@
         <v>6</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4580</v>
@@ -53709,7 +53712,7 @@
         <v>6</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4582</v>
@@ -53726,7 +53729,7 @@
         <v>6</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4584</v>
@@ -53740,10 +53743,10 @@
         <v>4585</v>
       </c>
       <c r="C2310" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4586</v>
@@ -53757,10 +53760,10 @@
         <v>4587</v>
       </c>
       <c r="C2311" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2311" t="s" s="3">
         <v>4588</v>
@@ -53777,7 +53780,7 @@
         <v>702</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2312" t="s" s="3">
         <v>4590</v>
@@ -53794,7 +53797,7 @@
         <v>702</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2313" t="s" s="3">
         <v>4592</v>
@@ -53811,7 +53814,7 @@
         <v>702</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2314" t="s" s="3">
         <v>4594</v>
@@ -53828,7 +53831,7 @@
         <v>702</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2315" t="s" s="3">
         <v>4596</v>
@@ -53845,7 +53848,7 @@
         <v>702</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2316" t="s" s="3">
         <v>4598</v>
@@ -53862,7 +53865,7 @@
         <v>702</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2317" t="s" s="3">
         <v>4600</v>
@@ -53879,7 +53882,7 @@
         <v>702</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2318" t="s" s="3">
         <v>4602</v>
@@ -53896,7 +53899,7 @@
         <v>702</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2319" t="s" s="3">
         <v>4604</v>
@@ -53913,7 +53916,7 @@
         <v>702</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2320" t="s" s="3">
         <v>4606</v>
@@ -53930,7 +53933,7 @@
         <v>702</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2321" t="s" s="3">
         <v>4608</v>
@@ -53947,7 +53950,7 @@
         <v>702</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2322" t="s" s="3">
         <v>4610</v>
@@ -53964,7 +53967,7 @@
         <v>702</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2323" t="s" s="3">
         <v>4612</v>
@@ -53981,7 +53984,7 @@
         <v>702</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2324" t="s" s="3">
         <v>4614</v>
@@ -53998,7 +54001,7 @@
         <v>702</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2325" t="s" s="3">
         <v>4616</v>
@@ -54015,7 +54018,7 @@
         <v>702</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2326" t="s" s="3">
         <v>4618</v>
@@ -54032,7 +54035,7 @@
         <v>702</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4620</v>
@@ -54049,7 +54052,7 @@
         <v>702</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4622</v>
@@ -54066,7 +54069,7 @@
         <v>702</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4624</v>
@@ -54083,7 +54086,7 @@
         <v>702</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4626</v>
@@ -54100,7 +54103,7 @@
         <v>702</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4628</v>
@@ -54117,7 +54120,7 @@
         <v>702</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4630</v>
@@ -54134,7 +54137,7 @@
         <v>702</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4632</v>
@@ -54151,7 +54154,7 @@
         <v>702</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2334" t="s" s="3">
         <v>4634</v>
@@ -54168,7 +54171,7 @@
         <v>702</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2335" t="s" s="3">
         <v>4636</v>
@@ -54185,7 +54188,7 @@
         <v>702</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2336" t="s" s="3">
         <v>4638</v>
@@ -54202,7 +54205,7 @@
         <v>702</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2337" t="s" s="3">
         <v>4640</v>
@@ -54219,7 +54222,7 @@
         <v>702</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4642</v>
@@ -54236,7 +54239,7 @@
         <v>702</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4644</v>
@@ -54253,7 +54256,7 @@
         <v>702</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4646</v>
@@ -54270,7 +54273,7 @@
         <v>702</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4648</v>
@@ -54287,7 +54290,7 @@
         <v>702</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4650</v>
@@ -54304,7 +54307,7 @@
         <v>702</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4652</v>
@@ -54321,7 +54324,7 @@
         <v>702</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4654</v>
@@ -54338,7 +54341,7 @@
         <v>702</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4656</v>
@@ -54355,7 +54358,7 @@
         <v>702</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4658</v>
@@ -54372,7 +54375,7 @@
         <v>702</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4660</v>
@@ -54389,7 +54392,7 @@
         <v>702</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4662</v>
@@ -54406,10 +54409,10 @@
         <v>702</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2349" t="s" s="3">
-        <v>4383</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="2350" ht="36.0" customHeight="true">
@@ -54417,16 +54420,16 @@
         <v>2349.0</v>
       </c>
       <c r="B2350" t="s" s="3">
-        <v>4664</v>
+        <v>4665</v>
       </c>
       <c r="C2350" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2350" t="s" s="3">
-        <v>4665</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="2351" ht="36.0" customHeight="true">
@@ -54434,16 +54437,16 @@
         <v>2350.0</v>
       </c>
       <c r="B2351" t="s" s="3">
-        <v>4666</v>
+        <v>4667</v>
       </c>
       <c r="C2351" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2351" t="s" s="3">
-        <v>4667</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="2352" ht="36.0" customHeight="true">
@@ -54457,7 +54460,7 @@
         <v>702</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2352" t="s" s="3">
         <v>4669</v>
@@ -54474,7 +54477,7 @@
         <v>702</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4671</v>
@@ -54491,7 +54494,7 @@
         <v>702</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4673</v>
@@ -54508,7 +54511,7 @@
         <v>702</v>
       </c>
       <c r="D2355" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2355" t="s" s="3">
         <v>4675</v>
@@ -54525,7 +54528,7 @@
         <v>702</v>
       </c>
       <c r="D2356" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4677</v>
@@ -54539,10 +54542,10 @@
         <v>4678</v>
       </c>
       <c r="C2357" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4679</v>
@@ -54556,10 +54559,10 @@
         <v>4680</v>
       </c>
       <c r="C2358" t="s" s="2">
-        <v>897</v>
+        <v>702</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4681</v>
@@ -54570,16 +54573,16 @@
         <v>2358.0</v>
       </c>
       <c r="B2359" t="s" s="3">
-        <v>4659</v>
+        <v>4682</v>
       </c>
       <c r="C2359" t="s" s="2">
         <v>897</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4334</v>
+        <v>4338</v>
       </c>
       <c r="E2359" t="s" s="3">
-        <v>4682</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="2360" ht="36.0" customHeight="true">
@@ -54587,13 +54590,13 @@
         <v>2359.0</v>
       </c>
       <c r="B2360" t="s" s="3">
-        <v>4683</v>
+        <v>4684</v>
       </c>
       <c r="C2360" t="s" s="2">
-        <v>6</v>
+        <v>897</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4684</v>
+        <v>4338</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4685</v>
@@ -54604,16 +54607,16 @@
         <v>2360.0</v>
       </c>
       <c r="B2361" t="s" s="3">
+        <v>4663</v>
+      </c>
+      <c r="C2361" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="D2361" t="s" s="2">
+        <v>4338</v>
+      </c>
+      <c r="E2361" t="s" s="3">
         <v>4686</v>
-      </c>
-      <c r="C2361" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2361" t="s" s="2">
-        <v>4684</v>
-      </c>
-      <c r="E2361" t="s" s="3">
-        <v>4687</v>
       </c>
     </row>
     <row r="2362" ht="36.0" customHeight="true">
@@ -54621,13 +54624,13 @@
         <v>2361.0</v>
       </c>
       <c r="B2362" t="s" s="3">
+        <v>4687</v>
+      </c>
+      <c r="C2362" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2362" t="s" s="2">
         <v>4688</v>
-      </c>
-      <c r="C2362" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2362" t="s" s="2">
-        <v>4684</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4689</v>
@@ -54644,7 +54647,7 @@
         <v>6</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4691</v>
@@ -54661,7 +54664,7 @@
         <v>6</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2364" t="s" s="3">
         <v>4693</v>
@@ -54678,7 +54681,7 @@
         <v>6</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2365" t="s" s="3">
         <v>4695</v>
@@ -54695,7 +54698,7 @@
         <v>6</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2366" t="s" s="3">
         <v>4697</v>
@@ -54712,7 +54715,7 @@
         <v>6</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4699</v>
@@ -54729,7 +54732,7 @@
         <v>6</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2368" t="s" s="3">
         <v>4701</v>
@@ -54746,7 +54749,7 @@
         <v>6</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2369" t="s" s="3">
         <v>4703</v>
@@ -54763,7 +54766,7 @@
         <v>6</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2370" t="s" s="3">
         <v>4705</v>
@@ -54780,7 +54783,7 @@
         <v>6</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2371" t="s" s="3">
         <v>4707</v>
@@ -54797,7 +54800,7 @@
         <v>6</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2372" t="s" s="3">
         <v>4709</v>
@@ -54814,7 +54817,7 @@
         <v>6</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2373" t="s" s="3">
         <v>4711</v>
@@ -54831,7 +54834,7 @@
         <v>6</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2374" t="s" s="3">
         <v>4713</v>
@@ -54848,7 +54851,7 @@
         <v>6</v>
       </c>
       <c r="D2375" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2375" t="s" s="3">
         <v>4715</v>
@@ -54865,7 +54868,7 @@
         <v>6</v>
       </c>
       <c r="D2376" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2376" t="s" s="3">
         <v>4717</v>
@@ -54882,7 +54885,7 @@
         <v>6</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2377" t="s" s="3">
         <v>4719</v>
@@ -54899,7 +54902,7 @@
         <v>6</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4721</v>
@@ -54916,7 +54919,7 @@
         <v>6</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4723</v>
@@ -54933,7 +54936,7 @@
         <v>6</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4725</v>
@@ -54950,7 +54953,7 @@
         <v>6</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4727</v>
@@ -54967,7 +54970,7 @@
         <v>6</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4729</v>
@@ -54984,7 +54987,7 @@
         <v>6</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4731</v>
@@ -55001,7 +55004,7 @@
         <v>6</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4733</v>
@@ -55018,7 +55021,7 @@
         <v>6</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4735</v>
@@ -55035,7 +55038,7 @@
         <v>6</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4737</v>
@@ -55052,7 +55055,7 @@
         <v>6</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4739</v>
@@ -55069,7 +55072,7 @@
         <v>6</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4741</v>
@@ -55086,7 +55089,7 @@
         <v>6</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4743</v>
@@ -55103,7 +55106,7 @@
         <v>6</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4745</v>
@@ -55120,7 +55123,7 @@
         <v>6</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4747</v>
@@ -55137,7 +55140,7 @@
         <v>6</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4749</v>
@@ -55151,13 +55154,13 @@
         <v>4750</v>
       </c>
       <c r="C2393" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2393" t="s" s="3">
-        <v>4727</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="2394" ht="36.0" customHeight="true">
@@ -55165,16 +55168,16 @@
         <v>2393.0</v>
       </c>
       <c r="B2394" t="s" s="3">
-        <v>4751</v>
+        <v>4752</v>
       </c>
       <c r="C2394" t="s" s="2">
-        <v>702</v>
+        <v>6</v>
       </c>
       <c r="D2394" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2394" t="s" s="3">
-        <v>4752</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="2395" ht="36.0" customHeight="true">
@@ -55182,16 +55185,16 @@
         <v>2394.0</v>
       </c>
       <c r="B2395" t="s" s="3">
-        <v>4753</v>
+        <v>4754</v>
       </c>
       <c r="C2395" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2395" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2395" t="s" s="3">
-        <v>4754</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="2396" ht="36.0" customHeight="true">
@@ -55205,7 +55208,7 @@
         <v>702</v>
       </c>
       <c r="D2396" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2396" t="s" s="3">
         <v>4756</v>
@@ -55222,7 +55225,7 @@
         <v>702</v>
       </c>
       <c r="D2397" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4758</v>
@@ -55239,7 +55242,7 @@
         <v>702</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4760</v>
@@ -55250,16 +55253,16 @@
         <v>2398.0</v>
       </c>
       <c r="B2399" t="s" s="3">
-        <v>4690</v>
+        <v>4761</v>
       </c>
       <c r="C2399" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2399" t="s" s="3">
-        <v>4761</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="2400" ht="36.0" customHeight="true">
@@ -55267,16 +55270,16 @@
         <v>2399.0</v>
       </c>
       <c r="B2400" t="s" s="3">
-        <v>4762</v>
+        <v>4763</v>
       </c>
       <c r="C2400" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2400" t="s" s="3">
-        <v>4763</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="2401" ht="36.0" customHeight="true">
@@ -55284,13 +55287,13 @@
         <v>2400.0</v>
       </c>
       <c r="B2401" t="s" s="3">
-        <v>4764</v>
+        <v>4694</v>
       </c>
       <c r="C2401" t="s" s="2">
         <v>702</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4765</v>
@@ -55307,7 +55310,7 @@
         <v>702</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4767</v>
@@ -55324,7 +55327,7 @@
         <v>702</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4769</v>
@@ -55341,7 +55344,7 @@
         <v>702</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4771</v>
@@ -55358,7 +55361,7 @@
         <v>702</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4773</v>
@@ -55375,7 +55378,7 @@
         <v>702</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4775</v>
@@ -55392,7 +55395,7 @@
         <v>702</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4777</v>
@@ -55409,7 +55412,7 @@
         <v>702</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4779</v>
@@ -55426,7 +55429,7 @@
         <v>702</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4781</v>
@@ -55443,7 +55446,7 @@
         <v>702</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4783</v>
@@ -55460,7 +55463,7 @@
         <v>702</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4684</v>
+        <v>4688</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4785</v>
@@ -55474,13 +55477,30 @@
         <v>4786</v>
       </c>
       <c r="C2412" t="s" s="2">
-        <v>6</v>
+        <v>702</v>
       </c>
       <c r="D2412" t="s" s="2">
+        <v>4688</v>
+      </c>
+      <c r="E2412" t="s" s="3">
         <v>4787</v>
       </c>
-      <c r="E2412" t="s" s="3">
+    </row>
+    <row r="2413" ht="36.0" customHeight="true">
+      <c r="A2413" t="n" s="2">
+        <v>2412.0</v>
+      </c>
+      <c r="B2413" t="s" s="3">
         <v>4788</v>
+      </c>
+      <c r="C2413" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="D2413" t="s" s="2">
+        <v>4688</v>
+      </c>
+      <c r="E2413" t="s" s="3">
+        <v>4789</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5342,10 +5342,10 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
-  </si>
-  <si>
-    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
   </si>
   <si>
     <t>꽁냥이네</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9949" uniqueCount="4935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9969" uniqueCount="4944">
   <si>
     <t>연번</t>
   </si>
@@ -1412,12 +1412,12 @@
     <t>오르노 합정점</t>
   </si>
   <si>
+    <t>서울특별시 마포구 월드컵로3길 14(지1층 B149,B150,B151, B152,B153,B154호 합정동, 마포 한강 2차 푸르지오)</t>
+  </si>
+  <si>
     <t>서울특별시 마포구 월드컵로3길 14(지1층 B113,114호 합정동, 마포 한강 2차 푸르지오)</t>
   </si>
   <si>
-    <t>서울특별시 마포구 월드컵로3길 14(지1층 B149,B150,B151, B152,B153,B154호 합정동, 마포 한강 2차 푸르지오)</t>
-  </si>
-  <si>
     <t>오베뉴 한남</t>
   </si>
   <si>
@@ -3845,12 +3845,12 @@
     <t>스트럿</t>
   </si>
   <si>
+    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
+  </si>
+  <si>
     <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
   </si>
   <si>
-    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
-  </si>
-  <si>
     <t>시랑</t>
   </si>
   <si>
@@ -5288,12 +5288,12 @@
     <t>조선백호</t>
   </si>
   <si>
+    <t>인천광역시 제물포구 개항로96번길 11(1층 경동)</t>
+  </si>
+  <si>
     <t>인천광역시 제물포구 개항로96번길 11(1,2층 경동)</t>
   </si>
   <si>
-    <t>인천광역시 제물포구 개항로96번길 11(1층 경동)</t>
-  </si>
-  <si>
     <t>주윤 상차림</t>
   </si>
   <si>
@@ -8192,12 +8192,12 @@
     <t>위자네</t>
   </si>
   <si>
+    <t>경기도 화성시 효행구 봉담읍 장등1길 3-10(1층)</t>
+  </si>
+  <si>
     <t>경기도 안양시 만안구 석천로 181(1층 석수동)</t>
   </si>
   <si>
-    <t>경기도 화성시 효행구 봉담읍 장등1길 3-10(1층)</t>
-  </si>
-  <si>
     <t>위클리베이글 평촌점</t>
   </si>
   <si>
@@ -10949,6 +10949,12 @@
     <t>충청남도 태안군 안면읍 백사장1길 37</t>
   </si>
   <si>
+    <t>헬로멍스커뮤니티라운지</t>
+  </si>
+  <si>
+    <t>충청남도 홍성군 홍북읍 청사로174번길 17(청담프라자 II 405호)</t>
+  </si>
+  <si>
     <t>홍산문화살롱</t>
   </si>
   <si>
@@ -11669,6 +11675,12 @@
     <t>경상남도 창원시 의창구 도계로83번길 10-12(1층 103호 도계동, 신우빌라)</t>
   </si>
   <si>
+    <t>남해왼손농장 맛집</t>
+  </si>
+  <si>
+    <t>경상남도 남해군 서면 스포츠로498번길 3(2동)</t>
+  </si>
+  <si>
     <t>노량133</t>
   </si>
   <si>
@@ -11681,12 +11693,24 @@
     <t>경상남도 김해시 가락로 295(2층 구산동)</t>
   </si>
   <si>
+    <t>농가맛집 어부림</t>
+  </si>
+  <si>
+    <t>경상남도 남해군 삼동면 동부대로 1126(1동2층,2동1층)</t>
+  </si>
+  <si>
     <t>누아르(NOIR)</t>
   </si>
   <si>
     <t>경상남도 합천군 초계면 초계2길 12-7</t>
   </si>
   <si>
+    <t>다랭이맛집</t>
+  </si>
+  <si>
+    <t>경상남도 남해군 남면 남면로679번길 31-10</t>
+  </si>
+  <si>
     <t>다소랑정원식당</t>
   </si>
   <si>
@@ -11891,6 +11915,12 @@
     <t>경상남도 거제시 하청면 어온4길 32(1층)</t>
   </si>
   <si>
+    <t>봄여름가을겨울카페</t>
+  </si>
+  <si>
+    <t>경상남도 남해군 창선면 동부대로 2789</t>
+  </si>
+  <si>
     <t>부산식당</t>
   </si>
   <si>
@@ -12089,6 +12119,12 @@
     <t>경상남도 통영시 광도면 죽림해안로 130(동해빌딩 1층)</t>
   </si>
   <si>
+    <t>일출식당</t>
+  </si>
+  <si>
+    <t>경상남도 남해군 미조면 동부대로 581</t>
+  </si>
+  <si>
     <t>일품양평해장국사천곤양IC점</t>
   </si>
   <si>
@@ -14808,15 +14844,6 @@
   </si>
   <si>
     <t>전북특별자치도 남원시 시청북로 17(주1동 2층 도통동)</t>
-  </si>
-  <si>
-    <t>헬로멍스커뮤니티라운지</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>충청남도 홍성군 홍북읍 청사로174번길 17(청담프라자 II 405호)</t>
   </si>
 </sst>
 </file>
@@ -46154,7 +46181,7 @@
         <v>3647</v>
       </c>
       <c r="C1838" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D1838" t="s" s="2">
         <v>3547</v>
@@ -46440,7 +46467,7 @@
         <v>1854.0</v>
       </c>
       <c r="B1855" t="s" s="3">
-        <v>3625</v>
+        <v>3681</v>
       </c>
       <c r="C1855" t="s" s="2">
         <v>719</v>
@@ -46449,7 +46476,7 @@
         <v>3547</v>
       </c>
       <c r="E1855" t="s" s="3">
-        <v>3626</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="1856" ht="36.0" customHeight="true">
@@ -46457,7 +46484,7 @@
         <v>1855.0</v>
       </c>
       <c r="B1856" t="s" s="3">
-        <v>3681</v>
+        <v>3625</v>
       </c>
       <c r="C1856" t="s" s="2">
         <v>719</v>
@@ -46466,7 +46493,7 @@
         <v>3547</v>
       </c>
       <c r="E1856" t="s" s="3">
-        <v>3682</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="1857" ht="36.0" customHeight="true">
@@ -46613,7 +46640,7 @@
         <v>3699</v>
       </c>
       <c r="C1865" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D1865" t="s" s="2">
         <v>3547</v>
@@ -46647,13 +46674,13 @@
         <v>3703</v>
       </c>
       <c r="C1867" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D1867" t="s" s="2">
+        <v>3547</v>
+      </c>
+      <c r="E1867" t="s" s="3">
         <v>3704</v>
-      </c>
-      <c r="E1867" t="s" s="3">
-        <v>3705</v>
       </c>
     </row>
     <row r="1868" ht="36.0" customHeight="true">
@@ -46661,13 +46688,13 @@
         <v>1867.0</v>
       </c>
       <c r="B1868" t="s" s="3">
+        <v>3705</v>
+      </c>
+      <c r="C1868" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1868" t="s" s="2">
         <v>3706</v>
-      </c>
-      <c r="C1868" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1868" t="s" s="2">
-        <v>3704</v>
       </c>
       <c r="E1868" t="s" s="3">
         <v>3707</v>
@@ -46684,7 +46711,7 @@
         <v>6</v>
       </c>
       <c r="D1869" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1869" t="s" s="3">
         <v>3709</v>
@@ -46701,7 +46728,7 @@
         <v>6</v>
       </c>
       <c r="D1870" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1870" t="s" s="3">
         <v>3711</v>
@@ -46718,7 +46745,7 @@
         <v>6</v>
       </c>
       <c r="D1871" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1871" t="s" s="3">
         <v>3713</v>
@@ -46735,7 +46762,7 @@
         <v>6</v>
       </c>
       <c r="D1872" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1872" t="s" s="3">
         <v>3715</v>
@@ -46752,7 +46779,7 @@
         <v>6</v>
       </c>
       <c r="D1873" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1873" t="s" s="3">
         <v>3717</v>
@@ -46769,7 +46796,7 @@
         <v>6</v>
       </c>
       <c r="D1874" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1874" t="s" s="3">
         <v>3719</v>
@@ -46786,7 +46813,7 @@
         <v>6</v>
       </c>
       <c r="D1875" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1875" t="s" s="3">
         <v>3721</v>
@@ -46803,7 +46830,7 @@
         <v>6</v>
       </c>
       <c r="D1876" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1876" t="s" s="3">
         <v>3723</v>
@@ -46820,7 +46847,7 @@
         <v>6</v>
       </c>
       <c r="D1877" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1877" t="s" s="3">
         <v>3725</v>
@@ -46837,7 +46864,7 @@
         <v>6</v>
       </c>
       <c r="D1878" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1878" t="s" s="3">
         <v>3727</v>
@@ -46854,7 +46881,7 @@
         <v>6</v>
       </c>
       <c r="D1879" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1879" t="s" s="3">
         <v>3729</v>
@@ -46871,7 +46898,7 @@
         <v>6</v>
       </c>
       <c r="D1880" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1880" t="s" s="3">
         <v>3731</v>
@@ -46888,7 +46915,7 @@
         <v>6</v>
       </c>
       <c r="D1881" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1881" t="s" s="3">
         <v>3733</v>
@@ -46905,7 +46932,7 @@
         <v>6</v>
       </c>
       <c r="D1882" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1882" t="s" s="3">
         <v>3735</v>
@@ -46922,7 +46949,7 @@
         <v>6</v>
       </c>
       <c r="D1883" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1883" t="s" s="3">
         <v>3737</v>
@@ -46939,7 +46966,7 @@
         <v>6</v>
       </c>
       <c r="D1884" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1884" t="s" s="3">
         <v>3739</v>
@@ -46956,7 +46983,7 @@
         <v>6</v>
       </c>
       <c r="D1885" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1885" t="s" s="3">
         <v>3741</v>
@@ -46973,7 +47000,7 @@
         <v>6</v>
       </c>
       <c r="D1886" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1886" t="s" s="3">
         <v>3743</v>
@@ -46990,7 +47017,7 @@
         <v>6</v>
       </c>
       <c r="D1887" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1887" t="s" s="3">
         <v>3745</v>
@@ -47007,7 +47034,7 @@
         <v>6</v>
       </c>
       <c r="D1888" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1888" t="s" s="3">
         <v>3747</v>
@@ -47024,7 +47051,7 @@
         <v>6</v>
       </c>
       <c r="D1889" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1889" t="s" s="3">
         <v>3749</v>
@@ -47041,7 +47068,7 @@
         <v>6</v>
       </c>
       <c r="D1890" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1890" t="s" s="3">
         <v>3751</v>
@@ -47058,7 +47085,7 @@
         <v>6</v>
       </c>
       <c r="D1891" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1891" t="s" s="3">
         <v>3753</v>
@@ -47075,7 +47102,7 @@
         <v>6</v>
       </c>
       <c r="D1892" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1892" t="s" s="3">
         <v>3755</v>
@@ -47092,7 +47119,7 @@
         <v>6</v>
       </c>
       <c r="D1893" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1893" t="s" s="3">
         <v>3757</v>
@@ -47109,7 +47136,7 @@
         <v>6</v>
       </c>
       <c r="D1894" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1894" t="s" s="3">
         <v>3759</v>
@@ -47126,7 +47153,7 @@
         <v>6</v>
       </c>
       <c r="D1895" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1895" t="s" s="3">
         <v>3761</v>
@@ -47143,7 +47170,7 @@
         <v>6</v>
       </c>
       <c r="D1896" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1896" t="s" s="3">
         <v>3763</v>
@@ -47160,7 +47187,7 @@
         <v>6</v>
       </c>
       <c r="D1897" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1897" t="s" s="3">
         <v>3765</v>
@@ -47177,7 +47204,7 @@
         <v>6</v>
       </c>
       <c r="D1898" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1898" t="s" s="3">
         <v>3767</v>
@@ -47194,7 +47221,7 @@
         <v>6</v>
       </c>
       <c r="D1899" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1899" t="s" s="3">
         <v>3769</v>
@@ -47211,7 +47238,7 @@
         <v>6</v>
       </c>
       <c r="D1900" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1900" t="s" s="3">
         <v>3771</v>
@@ -47228,7 +47255,7 @@
         <v>6</v>
       </c>
       <c r="D1901" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1901" t="s" s="3">
         <v>3773</v>
@@ -47245,7 +47272,7 @@
         <v>6</v>
       </c>
       <c r="D1902" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1902" t="s" s="3">
         <v>3775</v>
@@ -47262,10 +47289,10 @@
         <v>6</v>
       </c>
       <c r="D1903" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1903" t="s" s="3">
-        <v>3751</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="1904" ht="36.0" customHeight="true">
@@ -47273,16 +47300,16 @@
         <v>1903.0</v>
       </c>
       <c r="B1904" t="s" s="3">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="C1904" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1904" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1904" t="s" s="3">
-        <v>3778</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="1905" ht="36.0" customHeight="true">
@@ -47290,16 +47317,16 @@
         <v>1904.0</v>
       </c>
       <c r="B1905" t="s" s="3">
-        <v>3336</v>
+        <v>3779</v>
       </c>
       <c r="C1905" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1905" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1905" t="s" s="3">
-        <v>3779</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="1906" ht="36.0" customHeight="true">
@@ -47307,13 +47334,13 @@
         <v>1905.0</v>
       </c>
       <c r="B1906" t="s" s="3">
-        <v>3780</v>
+        <v>3336</v>
       </c>
       <c r="C1906" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1906" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1906" t="s" s="3">
         <v>3781</v>
@@ -47330,7 +47357,7 @@
         <v>6</v>
       </c>
       <c r="D1907" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1907" t="s" s="3">
         <v>3783</v>
@@ -47347,7 +47374,7 @@
         <v>6</v>
       </c>
       <c r="D1908" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1908" t="s" s="3">
         <v>3785</v>
@@ -47364,7 +47391,7 @@
         <v>6</v>
       </c>
       <c r="D1909" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1909" t="s" s="3">
         <v>3787</v>
@@ -47381,7 +47408,7 @@
         <v>6</v>
       </c>
       <c r="D1910" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1910" t="s" s="3">
         <v>3789</v>
@@ -47398,7 +47425,7 @@
         <v>6</v>
       </c>
       <c r="D1911" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1911" t="s" s="3">
         <v>3791</v>
@@ -47412,10 +47439,10 @@
         <v>3792</v>
       </c>
       <c r="C1912" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D1912" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1912" t="s" s="3">
         <v>3793</v>
@@ -47432,7 +47459,7 @@
         <v>719</v>
       </c>
       <c r="D1913" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1913" t="s" s="3">
         <v>3795</v>
@@ -47449,7 +47476,7 @@
         <v>719</v>
       </c>
       <c r="D1914" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1914" t="s" s="3">
         <v>3797</v>
@@ -47466,7 +47493,7 @@
         <v>719</v>
       </c>
       <c r="D1915" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1915" t="s" s="3">
         <v>3799</v>
@@ -47483,7 +47510,7 @@
         <v>719</v>
       </c>
       <c r="D1916" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1916" t="s" s="3">
         <v>3801</v>
@@ -47500,7 +47527,7 @@
         <v>719</v>
       </c>
       <c r="D1917" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1917" t="s" s="3">
         <v>3803</v>
@@ -47517,7 +47544,7 @@
         <v>719</v>
       </c>
       <c r="D1918" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1918" t="s" s="3">
         <v>3805</v>
@@ -47534,7 +47561,7 @@
         <v>719</v>
       </c>
       <c r="D1919" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1919" t="s" s="3">
         <v>3807</v>
@@ -47551,7 +47578,7 @@
         <v>719</v>
       </c>
       <c r="D1920" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1920" t="s" s="3">
         <v>3809</v>
@@ -47568,7 +47595,7 @@
         <v>719</v>
       </c>
       <c r="D1921" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1921" t="s" s="3">
         <v>3811</v>
@@ -47585,7 +47612,7 @@
         <v>719</v>
       </c>
       <c r="D1922" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1922" t="s" s="3">
         <v>3813</v>
@@ -47602,7 +47629,7 @@
         <v>719</v>
       </c>
       <c r="D1923" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1923" t="s" s="3">
         <v>3815</v>
@@ -47619,7 +47646,7 @@
         <v>719</v>
       </c>
       <c r="D1924" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1924" t="s" s="3">
         <v>3817</v>
@@ -47636,7 +47663,7 @@
         <v>719</v>
       </c>
       <c r="D1925" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1925" t="s" s="3">
         <v>3819</v>
@@ -47653,7 +47680,7 @@
         <v>719</v>
       </c>
       <c r="D1926" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1926" t="s" s="3">
         <v>3821</v>
@@ -47670,7 +47697,7 @@
         <v>719</v>
       </c>
       <c r="D1927" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1927" t="s" s="3">
         <v>3823</v>
@@ -47687,7 +47714,7 @@
         <v>719</v>
       </c>
       <c r="D1928" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1928" t="s" s="3">
         <v>3825</v>
@@ -47704,7 +47731,7 @@
         <v>719</v>
       </c>
       <c r="D1929" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1929" t="s" s="3">
         <v>3827</v>
@@ -47721,7 +47748,7 @@
         <v>719</v>
       </c>
       <c r="D1930" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1930" t="s" s="3">
         <v>3829</v>
@@ -47738,7 +47765,7 @@
         <v>719</v>
       </c>
       <c r="D1931" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1931" t="s" s="3">
         <v>3831</v>
@@ -47755,7 +47782,7 @@
         <v>719</v>
       </c>
       <c r="D1932" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1932" t="s" s="3">
         <v>3833</v>
@@ -47772,7 +47799,7 @@
         <v>719</v>
       </c>
       <c r="D1933" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1933" t="s" s="3">
         <v>3835</v>
@@ -47789,7 +47816,7 @@
         <v>719</v>
       </c>
       <c r="D1934" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1934" t="s" s="3">
         <v>3837</v>
@@ -47806,7 +47833,7 @@
         <v>719</v>
       </c>
       <c r="D1935" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1935" t="s" s="3">
         <v>3839</v>
@@ -47823,7 +47850,7 @@
         <v>719</v>
       </c>
       <c r="D1936" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1936" t="s" s="3">
         <v>3841</v>
@@ -47840,7 +47867,7 @@
         <v>719</v>
       </c>
       <c r="D1937" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1937" t="s" s="3">
         <v>3843</v>
@@ -47857,7 +47884,7 @@
         <v>719</v>
       </c>
       <c r="D1938" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1938" t="s" s="3">
         <v>3845</v>
@@ -47871,10 +47898,10 @@
         <v>3846</v>
       </c>
       <c r="C1939" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D1939" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1939" t="s" s="3">
         <v>3847</v>
@@ -47891,7 +47918,7 @@
         <v>920</v>
       </c>
       <c r="D1940" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1940" t="s" s="3">
         <v>3849</v>
@@ -47902,16 +47929,16 @@
         <v>1940.0</v>
       </c>
       <c r="B1941" t="s" s="3">
-        <v>3777</v>
+        <v>3850</v>
       </c>
       <c r="C1941" t="s" s="2">
         <v>920</v>
       </c>
       <c r="D1941" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1941" t="s" s="3">
-        <v>3778</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="1942" ht="36.0" customHeight="true">
@@ -47919,16 +47946,16 @@
         <v>1941.0</v>
       </c>
       <c r="B1942" t="s" s="3">
-        <v>3850</v>
+        <v>3779</v>
       </c>
       <c r="C1942" t="s" s="2">
         <v>920</v>
       </c>
       <c r="D1942" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1942" t="s" s="3">
-        <v>3851</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="1943" ht="36.0" customHeight="true">
@@ -47942,7 +47969,7 @@
         <v>920</v>
       </c>
       <c r="D1943" t="s" s="2">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="E1943" t="s" s="3">
         <v>3853</v>
@@ -47956,13 +47983,13 @@
         <v>3854</v>
       </c>
       <c r="C1944" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D1944" t="s" s="2">
+        <v>3706</v>
+      </c>
+      <c r="E1944" t="s" s="3">
         <v>3855</v>
-      </c>
-      <c r="E1944" t="s" s="3">
-        <v>3856</v>
       </c>
     </row>
     <row r="1945" ht="36.0" customHeight="true">
@@ -47970,13 +47997,13 @@
         <v>1944.0</v>
       </c>
       <c r="B1945" t="s" s="3">
+        <v>3856</v>
+      </c>
+      <c r="C1945" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1945" t="s" s="2">
         <v>3857</v>
-      </c>
-      <c r="C1945" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1945" t="s" s="2">
-        <v>3855</v>
       </c>
       <c r="E1945" t="s" s="3">
         <v>3858</v>
@@ -47993,7 +48020,7 @@
         <v>6</v>
       </c>
       <c r="D1946" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1946" t="s" s="3">
         <v>3860</v>
@@ -48010,7 +48037,7 @@
         <v>6</v>
       </c>
       <c r="D1947" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1947" t="s" s="3">
         <v>3862</v>
@@ -48027,7 +48054,7 @@
         <v>6</v>
       </c>
       <c r="D1948" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1948" t="s" s="3">
         <v>3864</v>
@@ -48044,7 +48071,7 @@
         <v>6</v>
       </c>
       <c r="D1949" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1949" t="s" s="3">
         <v>3866</v>
@@ -48061,7 +48088,7 @@
         <v>6</v>
       </c>
       <c r="D1950" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1950" t="s" s="3">
         <v>3868</v>
@@ -48078,7 +48105,7 @@
         <v>6</v>
       </c>
       <c r="D1951" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1951" t="s" s="3">
         <v>3870</v>
@@ -48095,7 +48122,7 @@
         <v>6</v>
       </c>
       <c r="D1952" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1952" t="s" s="3">
         <v>3872</v>
@@ -48112,7 +48139,7 @@
         <v>6</v>
       </c>
       <c r="D1953" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1953" t="s" s="3">
         <v>3874</v>
@@ -48129,7 +48156,7 @@
         <v>6</v>
       </c>
       <c r="D1954" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1954" t="s" s="3">
         <v>3876</v>
@@ -48146,7 +48173,7 @@
         <v>6</v>
       </c>
       <c r="D1955" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1955" t="s" s="3">
         <v>3878</v>
@@ -48163,7 +48190,7 @@
         <v>6</v>
       </c>
       <c r="D1956" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1956" t="s" s="3">
         <v>3880</v>
@@ -48180,7 +48207,7 @@
         <v>6</v>
       </c>
       <c r="D1957" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1957" t="s" s="3">
         <v>3882</v>
@@ -48197,7 +48224,7 @@
         <v>6</v>
       </c>
       <c r="D1958" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1958" t="s" s="3">
         <v>3884</v>
@@ -48214,7 +48241,7 @@
         <v>6</v>
       </c>
       <c r="D1959" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1959" t="s" s="3">
         <v>3886</v>
@@ -48231,7 +48258,7 @@
         <v>6</v>
       </c>
       <c r="D1960" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3888</v>
@@ -48248,7 +48275,7 @@
         <v>6</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1961" t="s" s="3">
         <v>3890</v>
@@ -48265,7 +48292,7 @@
         <v>6</v>
       </c>
       <c r="D1962" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1962" t="s" s="3">
         <v>3892</v>
@@ -48282,7 +48309,7 @@
         <v>6</v>
       </c>
       <c r="D1963" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1963" t="s" s="3">
         <v>3894</v>
@@ -48299,7 +48326,7 @@
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1964" t="s" s="3">
         <v>3896</v>
@@ -48316,7 +48343,7 @@
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3898</v>
@@ -48333,7 +48360,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3900</v>
@@ -48350,7 +48377,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3902</v>
@@ -48367,7 +48394,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3904</v>
@@ -48384,7 +48411,7 @@
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1969" t="s" s="3">
         <v>3906</v>
@@ -48401,7 +48428,7 @@
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1970" t="s" s="3">
         <v>3908</v>
@@ -48418,7 +48445,7 @@
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3910</v>
@@ -48435,7 +48462,7 @@
         <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3912</v>
@@ -48452,7 +48479,7 @@
         <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3914</v>
@@ -48469,7 +48496,7 @@
         <v>6</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3916</v>
@@ -48486,7 +48513,7 @@
         <v>6</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3918</v>
@@ -48503,7 +48530,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3920</v>
@@ -48520,7 +48547,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3922</v>
@@ -48537,7 +48564,7 @@
         <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3924</v>
@@ -48554,7 +48581,7 @@
         <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3926</v>
@@ -48571,7 +48598,7 @@
         <v>6</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3928</v>
@@ -48588,7 +48615,7 @@
         <v>6</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3930</v>
@@ -48605,7 +48632,7 @@
         <v>6</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3932</v>
@@ -48622,7 +48649,7 @@
         <v>6</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3934</v>
@@ -48639,7 +48666,7 @@
         <v>6</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3936</v>
@@ -48656,7 +48683,7 @@
         <v>6</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3938</v>
@@ -48673,7 +48700,7 @@
         <v>6</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3940</v>
@@ -48690,7 +48717,7 @@
         <v>6</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3942</v>
@@ -48707,7 +48734,7 @@
         <v>6</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3944</v>
@@ -48724,7 +48751,7 @@
         <v>6</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3946</v>
@@ -48741,7 +48768,7 @@
         <v>6</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3948</v>
@@ -48758,7 +48785,7 @@
         <v>6</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3950</v>
@@ -48775,7 +48802,7 @@
         <v>6</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3952</v>
@@ -48792,7 +48819,7 @@
         <v>6</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3954</v>
@@ -48809,7 +48836,7 @@
         <v>6</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3956</v>
@@ -48826,7 +48853,7 @@
         <v>6</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3958</v>
@@ -48843,7 +48870,7 @@
         <v>6</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1996" t="s" s="3">
         <v>3960</v>
@@ -48860,7 +48887,7 @@
         <v>6</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1997" t="s" s="3">
         <v>3962</v>
@@ -48877,7 +48904,7 @@
         <v>6</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1998" t="s" s="3">
         <v>3964</v>
@@ -48894,7 +48921,7 @@
         <v>6</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3966</v>
@@ -48911,7 +48938,7 @@
         <v>6</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3968</v>
@@ -48928,7 +48955,7 @@
         <v>6</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3970</v>
@@ -48945,7 +48972,7 @@
         <v>6</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3972</v>
@@ -48962,7 +48989,7 @@
         <v>6</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3974</v>
@@ -48979,7 +49006,7 @@
         <v>6</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3976</v>
@@ -48996,7 +49023,7 @@
         <v>6</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3978</v>
@@ -49013,7 +49040,7 @@
         <v>6</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2006" t="s" s="3">
         <v>3980</v>
@@ -49030,7 +49057,7 @@
         <v>6</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2007" t="s" s="3">
         <v>3982</v>
@@ -49047,7 +49074,7 @@
         <v>6</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2008" t="s" s="3">
         <v>3984</v>
@@ -49064,7 +49091,7 @@
         <v>6</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3986</v>
@@ -49081,7 +49108,7 @@
         <v>6</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3988</v>
@@ -49098,7 +49125,7 @@
         <v>6</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3990</v>
@@ -49115,7 +49142,7 @@
         <v>6</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>3992</v>
@@ -49132,7 +49159,7 @@
         <v>6</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2013" t="s" s="3">
         <v>3994</v>
@@ -49149,7 +49176,7 @@
         <v>6</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>3996</v>
@@ -49166,7 +49193,7 @@
         <v>6</v>
       </c>
       <c r="D2015" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>3998</v>
@@ -49183,7 +49210,7 @@
         <v>6</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4000</v>
@@ -49200,7 +49227,7 @@
         <v>6</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4002</v>
@@ -49217,7 +49244,7 @@
         <v>6</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4004</v>
@@ -49234,7 +49261,7 @@
         <v>6</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4006</v>
@@ -49251,7 +49278,7 @@
         <v>6</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4008</v>
@@ -49268,7 +49295,7 @@
         <v>6</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4010</v>
@@ -49285,7 +49312,7 @@
         <v>6</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4012</v>
@@ -49302,7 +49329,7 @@
         <v>6</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4014</v>
@@ -49319,7 +49346,7 @@
         <v>6</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4016</v>
@@ -49336,7 +49363,7 @@
         <v>6</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4018</v>
@@ -49353,7 +49380,7 @@
         <v>6</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4020</v>
@@ -49370,7 +49397,7 @@
         <v>6</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4022</v>
@@ -49387,7 +49414,7 @@
         <v>6</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4024</v>
@@ -49404,7 +49431,7 @@
         <v>6</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4026</v>
@@ -49421,7 +49448,7 @@
         <v>6</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4028</v>
@@ -49438,7 +49465,7 @@
         <v>6</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4030</v>
@@ -49455,7 +49482,7 @@
         <v>6</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4032</v>
@@ -49472,7 +49499,7 @@
         <v>6</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4034</v>
@@ -49489,7 +49516,7 @@
         <v>6</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2034" t="s" s="3">
         <v>4036</v>
@@ -49500,16 +49527,16 @@
         <v>2034.0</v>
       </c>
       <c r="B2035" t="s" s="3">
-        <v>1322</v>
+        <v>4037</v>
       </c>
       <c r="C2035" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2035" t="s" s="3">
-        <v>4037</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="2036" ht="36.0" customHeight="true">
@@ -49517,16 +49544,16 @@
         <v>2035.0</v>
       </c>
       <c r="B2036" t="s" s="3">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="C2036" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2036" t="s" s="3">
-        <v>4039</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="2037" ht="36.0" customHeight="true">
@@ -49534,16 +49561,16 @@
         <v>2036.0</v>
       </c>
       <c r="B2037" t="s" s="3">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="C2037" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2037" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2037" t="s" s="3">
-        <v>4041</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="2038" ht="36.0" customHeight="true">
@@ -49551,16 +49578,16 @@
         <v>2037.0</v>
       </c>
       <c r="B2038" t="s" s="3">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="C2038" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2038" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2038" t="s" s="3">
-        <v>4043</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="2039" ht="36.0" customHeight="true">
@@ -49568,16 +49595,16 @@
         <v>2038.0</v>
       </c>
       <c r="B2039" t="s" s="3">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C2039" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2039" t="s" s="3">
-        <v>4045</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="2040" ht="36.0" customHeight="true">
@@ -49585,16 +49612,16 @@
         <v>2039.0</v>
       </c>
       <c r="B2040" t="s" s="3">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C2040" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2040" t="s" s="3">
-        <v>4047</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="2041" ht="36.0" customHeight="true">
@@ -49602,13 +49629,13 @@
         <v>2040.0</v>
       </c>
       <c r="B2041" t="s" s="3">
-        <v>4048</v>
+        <v>1322</v>
       </c>
       <c r="C2041" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4049</v>
@@ -49625,7 +49652,7 @@
         <v>6</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4051</v>
@@ -49642,7 +49669,7 @@
         <v>6</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4053</v>
@@ -49659,7 +49686,7 @@
         <v>6</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4055</v>
@@ -49676,7 +49703,7 @@
         <v>6</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4057</v>
@@ -49693,7 +49720,7 @@
         <v>6</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4059</v>
@@ -49710,7 +49737,7 @@
         <v>6</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4061</v>
@@ -49727,7 +49754,7 @@
         <v>6</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4063</v>
@@ -49744,7 +49771,7 @@
         <v>6</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4065</v>
@@ -49761,7 +49788,7 @@
         <v>6</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4067</v>
@@ -49778,7 +49805,7 @@
         <v>6</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4069</v>
@@ -49795,7 +49822,7 @@
         <v>6</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4071</v>
@@ -49812,7 +49839,7 @@
         <v>6</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4073</v>
@@ -49829,7 +49856,7 @@
         <v>6</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4075</v>
@@ -49846,7 +49873,7 @@
         <v>6</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4077</v>
@@ -49863,7 +49890,7 @@
         <v>6</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4079</v>
@@ -49880,7 +49907,7 @@
         <v>6</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4081</v>
@@ -49897,7 +49924,7 @@
         <v>6</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4083</v>
@@ -49914,7 +49941,7 @@
         <v>6</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4085</v>
@@ -49931,7 +49958,7 @@
         <v>6</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4087</v>
@@ -49948,7 +49975,7 @@
         <v>6</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4089</v>
@@ -49965,7 +49992,7 @@
         <v>6</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4091</v>
@@ -49982,7 +50009,7 @@
         <v>6</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4093</v>
@@ -49999,7 +50026,7 @@
         <v>6</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4095</v>
@@ -50016,7 +50043,7 @@
         <v>6</v>
       </c>
       <c r="D2065" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2065" t="s" s="3">
         <v>4097</v>
@@ -50033,7 +50060,7 @@
         <v>6</v>
       </c>
       <c r="D2066" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4099</v>
@@ -50050,7 +50077,7 @@
         <v>6</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4101</v>
@@ -50067,7 +50094,7 @@
         <v>6</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4103</v>
@@ -50084,7 +50111,7 @@
         <v>6</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4105</v>
@@ -50101,7 +50128,7 @@
         <v>6</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4107</v>
@@ -50118,7 +50145,7 @@
         <v>6</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4109</v>
@@ -50135,7 +50162,7 @@
         <v>6</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2072" t="s" s="3">
         <v>4111</v>
@@ -50149,10 +50176,10 @@
         <v>4112</v>
       </c>
       <c r="C2073" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2073" t="s" s="3">
         <v>4113</v>
@@ -50166,10 +50193,10 @@
         <v>4114</v>
       </c>
       <c r="C2074" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2074" t="s" s="3">
         <v>4115</v>
@@ -50183,10 +50210,10 @@
         <v>4116</v>
       </c>
       <c r="C2075" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2075" t="s" s="3">
         <v>4117</v>
@@ -50200,10 +50227,10 @@
         <v>4118</v>
       </c>
       <c r="C2076" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4119</v>
@@ -50217,10 +50244,10 @@
         <v>4120</v>
       </c>
       <c r="C2077" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4121</v>
@@ -50234,10 +50261,10 @@
         <v>4122</v>
       </c>
       <c r="C2078" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4123</v>
@@ -50254,7 +50281,7 @@
         <v>719</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4125</v>
@@ -50271,7 +50298,7 @@
         <v>719</v>
       </c>
       <c r="D2080" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2080" t="s" s="3">
         <v>4127</v>
@@ -50288,7 +50315,7 @@
         <v>719</v>
       </c>
       <c r="D2081" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4129</v>
@@ -50305,7 +50332,7 @@
         <v>719</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4131</v>
@@ -50322,7 +50349,7 @@
         <v>719</v>
       </c>
       <c r="D2083" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2083" t="s" s="3">
         <v>4133</v>
@@ -50339,7 +50366,7 @@
         <v>719</v>
       </c>
       <c r="D2084" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2084" t="s" s="3">
         <v>4135</v>
@@ -50356,7 +50383,7 @@
         <v>719</v>
       </c>
       <c r="D2085" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2085" t="s" s="3">
         <v>4137</v>
@@ -50373,7 +50400,7 @@
         <v>719</v>
       </c>
       <c r="D2086" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2086" t="s" s="3">
         <v>4139</v>
@@ -50390,7 +50417,7 @@
         <v>719</v>
       </c>
       <c r="D2087" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4141</v>
@@ -50407,7 +50434,7 @@
         <v>719</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4143</v>
@@ -50424,7 +50451,7 @@
         <v>719</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4145</v>
@@ -50441,7 +50468,7 @@
         <v>719</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2090" t="s" s="3">
         <v>4147</v>
@@ -50458,7 +50485,7 @@
         <v>719</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4149</v>
@@ -50475,7 +50502,7 @@
         <v>719</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4151</v>
@@ -50492,7 +50519,7 @@
         <v>719</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4153</v>
@@ -50509,7 +50536,7 @@
         <v>719</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4155</v>
@@ -50526,7 +50553,7 @@
         <v>719</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4157</v>
@@ -50543,7 +50570,7 @@
         <v>719</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4159</v>
@@ -50560,7 +50587,7 @@
         <v>719</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4161</v>
@@ -50577,7 +50604,7 @@
         <v>719</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4163</v>
@@ -50594,7 +50621,7 @@
         <v>719</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4165</v>
@@ -50611,7 +50638,7 @@
         <v>719</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4167</v>
@@ -50628,10 +50655,10 @@
         <v>719</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2101" t="s" s="3">
-        <v>4053</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="2102" ht="36.0" customHeight="true">
@@ -50639,16 +50666,16 @@
         <v>2101.0</v>
       </c>
       <c r="B2102" t="s" s="3">
-        <v>4169</v>
+        <v>4170</v>
       </c>
       <c r="C2102" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2102" t="s" s="3">
-        <v>4170</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="2103" ht="36.0" customHeight="true">
@@ -50656,16 +50683,16 @@
         <v>2102.0</v>
       </c>
       <c r="B2103" t="s" s="3">
-        <v>4171</v>
+        <v>4172</v>
       </c>
       <c r="C2103" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2103" t="s" s="3">
-        <v>4172</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="2104" ht="36.0" customHeight="true">
@@ -50673,16 +50700,16 @@
         <v>2103.0</v>
       </c>
       <c r="B2104" t="s" s="3">
-        <v>4173</v>
+        <v>4174</v>
       </c>
       <c r="C2104" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2104" t="s" s="3">
-        <v>4174</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="2105" ht="36.0" customHeight="true">
@@ -50690,16 +50717,16 @@
         <v>2104.0</v>
       </c>
       <c r="B2105" t="s" s="3">
-        <v>4175</v>
+        <v>4176</v>
       </c>
       <c r="C2105" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2105" t="s" s="3">
-        <v>4176</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="2106" ht="36.0" customHeight="true">
@@ -50707,16 +50734,16 @@
         <v>2105.0</v>
       </c>
       <c r="B2106" t="s" s="3">
-        <v>4177</v>
+        <v>4178</v>
       </c>
       <c r="C2106" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2106" t="s" s="3">
-        <v>4178</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="2107" ht="36.0" customHeight="true">
@@ -50724,16 +50751,16 @@
         <v>2106.0</v>
       </c>
       <c r="B2107" t="s" s="3">
-        <v>4179</v>
+        <v>4180</v>
       </c>
       <c r="C2107" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2107" t="s" s="3">
-        <v>4180</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="2108" ht="36.0" customHeight="true">
@@ -50747,7 +50774,7 @@
         <v>719</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4182</v>
@@ -50764,7 +50791,7 @@
         <v>719</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2109" t="s" s="3">
         <v>4184</v>
@@ -50781,7 +50808,7 @@
         <v>719</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2110" t="s" s="3">
         <v>4186</v>
@@ -50798,7 +50825,7 @@
         <v>719</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2111" t="s" s="3">
         <v>4188</v>
@@ -50815,7 +50842,7 @@
         <v>719</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4190</v>
@@ -50832,7 +50859,7 @@
         <v>719</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4192</v>
@@ -50849,7 +50876,7 @@
         <v>719</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4194</v>
@@ -50866,7 +50893,7 @@
         <v>719</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4196</v>
@@ -50883,7 +50910,7 @@
         <v>719</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4198</v>
@@ -50900,7 +50927,7 @@
         <v>719</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4200</v>
@@ -50917,7 +50944,7 @@
         <v>719</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4202</v>
@@ -50934,7 +50961,7 @@
         <v>719</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4204</v>
@@ -50951,7 +50978,7 @@
         <v>719</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4206</v>
@@ -50968,7 +50995,7 @@
         <v>719</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4208</v>
@@ -50985,7 +51012,7 @@
         <v>719</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4210</v>
@@ -51002,7 +51029,7 @@
         <v>719</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4212</v>
@@ -51019,7 +51046,7 @@
         <v>719</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2124" t="s" s="3">
         <v>4214</v>
@@ -51036,7 +51063,7 @@
         <v>719</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2125" t="s" s="3">
         <v>4216</v>
@@ -51053,7 +51080,7 @@
         <v>719</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2126" t="s" s="3">
         <v>4218</v>
@@ -51070,7 +51097,7 @@
         <v>719</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2127" t="s" s="3">
         <v>4220</v>
@@ -51087,7 +51114,7 @@
         <v>719</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2128" t="s" s="3">
         <v>4222</v>
@@ -51104,7 +51131,7 @@
         <v>719</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4224</v>
@@ -51121,7 +51148,7 @@
         <v>719</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4226</v>
@@ -51138,7 +51165,7 @@
         <v>719</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4228</v>
@@ -51155,7 +51182,7 @@
         <v>719</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4230</v>
@@ -51172,7 +51199,7 @@
         <v>719</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4232</v>
@@ -51189,7 +51216,7 @@
         <v>719</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4234</v>
@@ -51206,7 +51233,7 @@
         <v>719</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4236</v>
@@ -51223,7 +51250,7 @@
         <v>719</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2136" t="s" s="3">
         <v>4238</v>
@@ -51240,7 +51267,7 @@
         <v>719</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4240</v>
@@ -51257,7 +51284,7 @@
         <v>719</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4242</v>
@@ -51274,7 +51301,7 @@
         <v>719</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4244</v>
@@ -51288,10 +51315,10 @@
         <v>4245</v>
       </c>
       <c r="C2140" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4246</v>
@@ -51305,10 +51332,10 @@
         <v>4247</v>
       </c>
       <c r="C2141" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4248</v>
@@ -51322,10 +51349,10 @@
         <v>4249</v>
       </c>
       <c r="C2142" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4250</v>
@@ -51339,10 +51366,10 @@
         <v>4251</v>
       </c>
       <c r="C2143" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4252</v>
@@ -51356,10 +51383,10 @@
         <v>4253</v>
       </c>
       <c r="C2144" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4254</v>
@@ -51373,10 +51400,10 @@
         <v>4255</v>
       </c>
       <c r="C2145" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="E2145" t="s" s="3">
         <v>4256</v>
@@ -51390,13 +51417,13 @@
         <v>4257</v>
       </c>
       <c r="C2146" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D2146" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2146" t="s" s="3">
         <v>4258</v>
-      </c>
-      <c r="E2146" t="s" s="3">
-        <v>4259</v>
       </c>
     </row>
     <row r="2147" ht="36.0" customHeight="true">
@@ -51404,16 +51431,16 @@
         <v>2146.0</v>
       </c>
       <c r="B2147" t="s" s="3">
+        <v>4259</v>
+      </c>
+      <c r="C2147" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2147" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2147" t="s" s="3">
         <v>4260</v>
-      </c>
-      <c r="C2147" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2147" t="s" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E2147" t="s" s="3">
-        <v>4261</v>
       </c>
     </row>
     <row r="2148" ht="36.0" customHeight="true">
@@ -51421,16 +51448,16 @@
         <v>2147.0</v>
       </c>
       <c r="B2148" t="s" s="3">
+        <v>4261</v>
+      </c>
+      <c r="C2148" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2148" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2148" t="s" s="3">
         <v>4262</v>
-      </c>
-      <c r="C2148" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2148" t="s" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E2148" t="s" s="3">
-        <v>4263</v>
       </c>
     </row>
     <row r="2149" ht="36.0" customHeight="true">
@@ -51438,16 +51465,16 @@
         <v>2148.0</v>
       </c>
       <c r="B2149" t="s" s="3">
+        <v>4263</v>
+      </c>
+      <c r="C2149" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2149" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2149" t="s" s="3">
         <v>4264</v>
-      </c>
-      <c r="C2149" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2149" t="s" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E2149" t="s" s="3">
-        <v>4265</v>
       </c>
     </row>
     <row r="2150" ht="36.0" customHeight="true">
@@ -51455,16 +51482,16 @@
         <v>2149.0</v>
       </c>
       <c r="B2150" t="s" s="3">
+        <v>4265</v>
+      </c>
+      <c r="C2150" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2150" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2150" t="s" s="3">
         <v>4266</v>
-      </c>
-      <c r="C2150" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2150" t="s" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E2150" t="s" s="3">
-        <v>4267</v>
       </c>
     </row>
     <row r="2151" ht="36.0" customHeight="true">
@@ -51472,16 +51499,16 @@
         <v>2150.0</v>
       </c>
       <c r="B2151" t="s" s="3">
+        <v>4267</v>
+      </c>
+      <c r="C2151" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2151" t="s" s="2">
+        <v>3857</v>
+      </c>
+      <c r="E2151" t="s" s="3">
         <v>4268</v>
-      </c>
-      <c r="C2151" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2151" t="s" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E2151" t="s" s="3">
-        <v>4269</v>
       </c>
     </row>
     <row r="2152" ht="36.0" customHeight="true">
@@ -51489,13 +51516,13 @@
         <v>2151.0</v>
       </c>
       <c r="B2152" t="s" s="3">
+        <v>4269</v>
+      </c>
+      <c r="C2152" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2152" t="s" s="2">
         <v>4270</v>
-      </c>
-      <c r="C2152" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2152" t="s" s="2">
-        <v>4258</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4271</v>
@@ -51512,7 +51539,7 @@
         <v>6</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4273</v>
@@ -51529,7 +51556,7 @@
         <v>6</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4275</v>
@@ -51546,7 +51573,7 @@
         <v>6</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4277</v>
@@ -51563,7 +51590,7 @@
         <v>6</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4279</v>
@@ -51580,7 +51607,7 @@
         <v>6</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4281</v>
@@ -51597,7 +51624,7 @@
         <v>6</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4283</v>
@@ -51614,7 +51641,7 @@
         <v>6</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4285</v>
@@ -51631,7 +51658,7 @@
         <v>6</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4287</v>
@@ -51648,7 +51675,7 @@
         <v>6</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2161" t="s" s="3">
         <v>4289</v>
@@ -51665,7 +51692,7 @@
         <v>6</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2162" t="s" s="3">
         <v>4291</v>
@@ -51682,7 +51709,7 @@
         <v>6</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2163" t="s" s="3">
         <v>4293</v>
@@ -51699,7 +51726,7 @@
         <v>6</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2164" t="s" s="3">
         <v>4295</v>
@@ -51716,7 +51743,7 @@
         <v>6</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2165" t="s" s="3">
         <v>4297</v>
@@ -51733,7 +51760,7 @@
         <v>6</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2166" t="s" s="3">
         <v>4299</v>
@@ -51750,7 +51777,7 @@
         <v>6</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2167" t="s" s="3">
         <v>4301</v>
@@ -51767,7 +51794,7 @@
         <v>6</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2168" t="s" s="3">
         <v>4303</v>
@@ -51784,7 +51811,7 @@
         <v>6</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2169" t="s" s="3">
         <v>4305</v>
@@ -51801,7 +51828,7 @@
         <v>6</v>
       </c>
       <c r="D2170" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2170" t="s" s="3">
         <v>4307</v>
@@ -51818,7 +51845,7 @@
         <v>6</v>
       </c>
       <c r="D2171" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2171" t="s" s="3">
         <v>4309</v>
@@ -51835,7 +51862,7 @@
         <v>6</v>
       </c>
       <c r="D2172" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4311</v>
@@ -51852,7 +51879,7 @@
         <v>6</v>
       </c>
       <c r="D2173" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2173" t="s" s="3">
         <v>4313</v>
@@ -51869,7 +51896,7 @@
         <v>6</v>
       </c>
       <c r="D2174" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2174" t="s" s="3">
         <v>4315</v>
@@ -51886,7 +51913,7 @@
         <v>6</v>
       </c>
       <c r="D2175" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4317</v>
@@ -51903,7 +51930,7 @@
         <v>6</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4319</v>
@@ -51920,7 +51947,7 @@
         <v>6</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4321</v>
@@ -51937,7 +51964,7 @@
         <v>6</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4323</v>
@@ -51954,7 +51981,7 @@
         <v>6</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4325</v>
@@ -51971,7 +51998,7 @@
         <v>6</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4327</v>
@@ -51988,7 +52015,7 @@
         <v>6</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4329</v>
@@ -52005,7 +52032,7 @@
         <v>6</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4331</v>
@@ -52022,7 +52049,7 @@
         <v>6</v>
       </c>
       <c r="D2183" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2183" t="s" s="3">
         <v>4333</v>
@@ -52039,7 +52066,7 @@
         <v>6</v>
       </c>
       <c r="D2184" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2184" t="s" s="3">
         <v>4335</v>
@@ -52056,7 +52083,7 @@
         <v>6</v>
       </c>
       <c r="D2185" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4337</v>
@@ -52073,7 +52100,7 @@
         <v>6</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4339</v>
@@ -52090,7 +52117,7 @@
         <v>6</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4341</v>
@@ -52107,7 +52134,7 @@
         <v>6</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4343</v>
@@ -52124,7 +52151,7 @@
         <v>6</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4345</v>
@@ -52141,7 +52168,7 @@
         <v>6</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4347</v>
@@ -52158,7 +52185,7 @@
         <v>6</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4349</v>
@@ -52175,7 +52202,7 @@
         <v>6</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4351</v>
@@ -52192,7 +52219,7 @@
         <v>6</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4353</v>
@@ -52209,7 +52236,7 @@
         <v>6</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4355</v>
@@ -52226,7 +52253,7 @@
         <v>6</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2195" t="s" s="3">
         <v>4357</v>
@@ -52243,7 +52270,7 @@
         <v>6</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2196" t="s" s="3">
         <v>4359</v>
@@ -52260,7 +52287,7 @@
         <v>6</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4361</v>
@@ -52277,7 +52304,7 @@
         <v>6</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2198" t="s" s="3">
         <v>4363</v>
@@ -52294,7 +52321,7 @@
         <v>6</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2199" t="s" s="3">
         <v>4365</v>
@@ -52308,10 +52335,10 @@
         <v>4366</v>
       </c>
       <c r="C2200" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4367</v>
@@ -52325,10 +52352,10 @@
         <v>4368</v>
       </c>
       <c r="C2201" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4369</v>
@@ -52342,10 +52369,10 @@
         <v>4370</v>
       </c>
       <c r="C2202" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4371</v>
@@ -52359,10 +52386,10 @@
         <v>4372</v>
       </c>
       <c r="C2203" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4373</v>
@@ -52376,10 +52403,10 @@
         <v>4374</v>
       </c>
       <c r="C2204" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4375</v>
@@ -52393,10 +52420,10 @@
         <v>4376</v>
       </c>
       <c r="C2205" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4377</v>
@@ -52413,7 +52440,7 @@
         <v>719</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4379</v>
@@ -52430,7 +52457,7 @@
         <v>719</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4381</v>
@@ -52447,7 +52474,7 @@
         <v>719</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4383</v>
@@ -52464,7 +52491,7 @@
         <v>719</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4385</v>
@@ -52481,7 +52508,7 @@
         <v>719</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4387</v>
@@ -52498,7 +52525,7 @@
         <v>719</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4389</v>
@@ -52515,7 +52542,7 @@
         <v>719</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2212" t="s" s="3">
         <v>4391</v>
@@ -52532,7 +52559,7 @@
         <v>719</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2213" t="s" s="3">
         <v>4393</v>
@@ -52549,7 +52576,7 @@
         <v>719</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2214" t="s" s="3">
         <v>4395</v>
@@ -52566,7 +52593,7 @@
         <v>719</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2215" t="s" s="3">
         <v>4397</v>
@@ -52583,7 +52610,7 @@
         <v>719</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4399</v>
@@ -52600,7 +52627,7 @@
         <v>719</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4401</v>
@@ -52617,7 +52644,7 @@
         <v>719</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4403</v>
@@ -52634,7 +52661,7 @@
         <v>719</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4405</v>
@@ -52651,7 +52678,7 @@
         <v>719</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4407</v>
@@ -52668,7 +52695,7 @@
         <v>719</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4409</v>
@@ -52685,7 +52712,7 @@
         <v>719</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4411</v>
@@ -52702,7 +52729,7 @@
         <v>719</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4413</v>
@@ -52719,7 +52746,7 @@
         <v>719</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4415</v>
@@ -52736,7 +52763,7 @@
         <v>719</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4417</v>
@@ -52753,7 +52780,7 @@
         <v>719</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4419</v>
@@ -52770,7 +52797,7 @@
         <v>719</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4421</v>
@@ -52787,7 +52814,7 @@
         <v>719</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4423</v>
@@ -52804,7 +52831,7 @@
         <v>719</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4425</v>
@@ -52821,7 +52848,7 @@
         <v>719</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4427</v>
@@ -52838,7 +52865,7 @@
         <v>719</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4429</v>
@@ -52855,7 +52882,7 @@
         <v>719</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4431</v>
@@ -52872,7 +52899,7 @@
         <v>719</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4433</v>
@@ -52889,7 +52916,7 @@
         <v>719</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4435</v>
@@ -52906,7 +52933,7 @@
         <v>719</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4437</v>
@@ -52923,7 +52950,7 @@
         <v>719</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4439</v>
@@ -52940,7 +52967,7 @@
         <v>719</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4441</v>
@@ -52954,10 +52981,10 @@
         <v>4442</v>
       </c>
       <c r="C2238" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4443</v>
@@ -52971,10 +52998,10 @@
         <v>4444</v>
       </c>
       <c r="C2239" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4445</v>
@@ -52988,10 +53015,10 @@
         <v>4446</v>
       </c>
       <c r="C2240" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4447</v>
@@ -53005,10 +53032,10 @@
         <v>4448</v>
       </c>
       <c r="C2241" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4449</v>
@@ -53022,10 +53049,10 @@
         <v>4450</v>
       </c>
       <c r="C2242" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4451</v>
@@ -53039,10 +53066,10 @@
         <v>4452</v>
       </c>
       <c r="C2243" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4453</v>
@@ -53059,7 +53086,7 @@
         <v>920</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4455</v>
@@ -53076,7 +53103,7 @@
         <v>920</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4258</v>
+        <v>4270</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4457</v>
@@ -53090,13 +53117,13 @@
         <v>4458</v>
       </c>
       <c r="C2246" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D2246" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2246" t="s" s="3">
         <v>4459</v>
-      </c>
-      <c r="E2246" t="s" s="3">
-        <v>4460</v>
       </c>
     </row>
     <row r="2247" ht="36.0" customHeight="true">
@@ -53104,16 +53131,16 @@
         <v>2246.0</v>
       </c>
       <c r="B2247" t="s" s="3">
+        <v>4460</v>
+      </c>
+      <c r="C2247" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2247" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2247" t="s" s="3">
         <v>4461</v>
-      </c>
-      <c r="C2247" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2247" t="s" s="2">
-        <v>4459</v>
-      </c>
-      <c r="E2247" t="s" s="3">
-        <v>4462</v>
       </c>
     </row>
     <row r="2248" ht="36.0" customHeight="true">
@@ -53121,16 +53148,16 @@
         <v>2247.0</v>
       </c>
       <c r="B2248" t="s" s="3">
+        <v>4462</v>
+      </c>
+      <c r="C2248" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2248" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2248" t="s" s="3">
         <v>4463</v>
-      </c>
-      <c r="C2248" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2248" t="s" s="2">
-        <v>4459</v>
-      </c>
-      <c r="E2248" t="s" s="3">
-        <v>4464</v>
       </c>
     </row>
     <row r="2249" ht="36.0" customHeight="true">
@@ -53138,16 +53165,16 @@
         <v>2248.0</v>
       </c>
       <c r="B2249" t="s" s="3">
+        <v>4464</v>
+      </c>
+      <c r="C2249" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2249" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2249" t="s" s="3">
         <v>4465</v>
-      </c>
-      <c r="C2249" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2249" t="s" s="2">
-        <v>4459</v>
-      </c>
-      <c r="E2249" t="s" s="3">
-        <v>4466</v>
       </c>
     </row>
     <row r="2250" ht="36.0" customHeight="true">
@@ -53155,16 +53182,16 @@
         <v>2249.0</v>
       </c>
       <c r="B2250" t="s" s="3">
+        <v>4466</v>
+      </c>
+      <c r="C2250" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2250" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2250" t="s" s="3">
         <v>4467</v>
-      </c>
-      <c r="C2250" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2250" t="s" s="2">
-        <v>4459</v>
-      </c>
-      <c r="E2250" t="s" s="3">
-        <v>4468</v>
       </c>
     </row>
     <row r="2251" ht="36.0" customHeight="true">
@@ -53172,16 +53199,16 @@
         <v>2250.0</v>
       </c>
       <c r="B2251" t="s" s="3">
+        <v>4468</v>
+      </c>
+      <c r="C2251" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2251" t="s" s="2">
+        <v>4270</v>
+      </c>
+      <c r="E2251" t="s" s="3">
         <v>4469</v>
-      </c>
-      <c r="C2251" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2251" t="s" s="2">
-        <v>4459</v>
-      </c>
-      <c r="E2251" t="s" s="3">
-        <v>4470</v>
       </c>
     </row>
     <row r="2252" ht="36.0" customHeight="true">
@@ -53189,13 +53216,13 @@
         <v>2251.0</v>
       </c>
       <c r="B2252" t="s" s="3">
+        <v>4470</v>
+      </c>
+      <c r="C2252" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2252" t="s" s="2">
         <v>4471</v>
-      </c>
-      <c r="C2252" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2252" t="s" s="2">
-        <v>4459</v>
       </c>
       <c r="E2252" t="s" s="3">
         <v>4472</v>
@@ -53212,7 +53239,7 @@
         <v>6</v>
       </c>
       <c r="D2253" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2253" t="s" s="3">
         <v>4474</v>
@@ -53229,7 +53256,7 @@
         <v>6</v>
       </c>
       <c r="D2254" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4476</v>
@@ -53246,7 +53273,7 @@
         <v>6</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4478</v>
@@ -53263,7 +53290,7 @@
         <v>6</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2256" t="s" s="3">
         <v>4480</v>
@@ -53280,7 +53307,7 @@
         <v>6</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2257" t="s" s="3">
         <v>4482</v>
@@ -53297,7 +53324,7 @@
         <v>6</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2258" t="s" s="3">
         <v>4484</v>
@@ -53314,7 +53341,7 @@
         <v>6</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2259" t="s" s="3">
         <v>4486</v>
@@ -53331,7 +53358,7 @@
         <v>6</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2260" t="s" s="3">
         <v>4488</v>
@@ -53348,7 +53375,7 @@
         <v>6</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2261" t="s" s="3">
         <v>4490</v>
@@ -53365,7 +53392,7 @@
         <v>6</v>
       </c>
       <c r="D2262" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2262" t="s" s="3">
         <v>4492</v>
@@ -53382,7 +53409,7 @@
         <v>6</v>
       </c>
       <c r="D2263" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2263" t="s" s="3">
         <v>4494</v>
@@ -53399,7 +53426,7 @@
         <v>6</v>
       </c>
       <c r="D2264" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4496</v>
@@ -53416,7 +53443,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4498</v>
@@ -53433,7 +53460,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4500</v>
@@ -53450,7 +53477,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4502</v>
@@ -53467,7 +53494,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4504</v>
@@ -53484,7 +53511,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4506</v>
@@ -53501,7 +53528,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4508</v>
@@ -53518,7 +53545,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4510</v>
@@ -53535,7 +53562,7 @@
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2272" t="s" s="3">
         <v>4512</v>
@@ -53552,7 +53579,7 @@
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2273" t="s" s="3">
         <v>4514</v>
@@ -53569,7 +53596,7 @@
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2274" t="s" s="3">
         <v>4516</v>
@@ -53586,7 +53613,7 @@
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4518</v>
@@ -53603,7 +53630,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4520</v>
@@ -53620,7 +53647,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4522</v>
@@ -53637,7 +53664,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4524</v>
@@ -53654,7 +53681,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4526</v>
@@ -53671,7 +53698,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4528</v>
@@ -53688,7 +53715,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4530</v>
@@ -53705,7 +53732,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4532</v>
@@ -53722,7 +53749,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4534</v>
@@ -53739,7 +53766,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4536</v>
@@ -53756,7 +53783,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4538</v>
@@ -53773,7 +53800,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4540</v>
@@ -53790,7 +53817,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4542</v>
@@ -53807,7 +53834,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4544</v>
@@ -53824,7 +53851,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4546</v>
@@ -53841,7 +53868,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4548</v>
@@ -53858,7 +53885,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4550</v>
@@ -53875,7 +53902,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4552</v>
@@ -53892,7 +53919,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4554</v>
@@ -53909,7 +53936,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4556</v>
@@ -53926,7 +53953,7 @@
         <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4558</v>
@@ -53943,7 +53970,7 @@
         <v>6</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4560</v>
@@ -53960,7 +53987,7 @@
         <v>6</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4562</v>
@@ -53977,7 +54004,7 @@
         <v>6</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4564</v>
@@ -53994,7 +54021,7 @@
         <v>6</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4566</v>
@@ -54011,7 +54038,7 @@
         <v>6</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2300" t="s" s="3">
         <v>4568</v>
@@ -54028,7 +54055,7 @@
         <v>6</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2301" t="s" s="3">
         <v>4570</v>
@@ -54045,7 +54072,7 @@
         <v>6</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4572</v>
@@ -54062,7 +54089,7 @@
         <v>6</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2303" t="s" s="3">
         <v>4574</v>
@@ -54079,7 +54106,7 @@
         <v>6</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2304" t="s" s="3">
         <v>4576</v>
@@ -54096,7 +54123,7 @@
         <v>6</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2305" t="s" s="3">
         <v>4578</v>
@@ -54113,7 +54140,7 @@
         <v>6</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4580</v>
@@ -54130,7 +54157,7 @@
         <v>6</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4582</v>
@@ -54147,7 +54174,7 @@
         <v>6</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4584</v>
@@ -54164,7 +54191,7 @@
         <v>6</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4586</v>
@@ -54181,7 +54208,7 @@
         <v>6</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4588</v>
@@ -54198,10 +54225,10 @@
         <v>6</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2311" t="s" s="3">
-        <v>4566</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="2312" ht="36.0" customHeight="true">
@@ -54209,16 +54236,16 @@
         <v>2311.0</v>
       </c>
       <c r="B2312" t="s" s="3">
-        <v>4590</v>
+        <v>4591</v>
       </c>
       <c r="C2312" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2312" t="s" s="3">
-        <v>4591</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="2313" ht="36.0" customHeight="true">
@@ -54226,16 +54253,16 @@
         <v>2312.0</v>
       </c>
       <c r="B2313" t="s" s="3">
-        <v>4592</v>
+        <v>4593</v>
       </c>
       <c r="C2313" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2313" t="s" s="3">
-        <v>4593</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="2314" ht="36.0" customHeight="true">
@@ -54243,16 +54270,16 @@
         <v>2313.0</v>
       </c>
       <c r="B2314" t="s" s="3">
-        <v>4594</v>
+        <v>4595</v>
       </c>
       <c r="C2314" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2314" t="s" s="3">
-        <v>4595</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="2315" ht="36.0" customHeight="true">
@@ -54260,16 +54287,16 @@
         <v>2314.0</v>
       </c>
       <c r="B2315" t="s" s="3">
-        <v>4596</v>
+        <v>4597</v>
       </c>
       <c r="C2315" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2315" t="s" s="3">
-        <v>4597</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="2316" ht="36.0" customHeight="true">
@@ -54277,16 +54304,16 @@
         <v>2315.0</v>
       </c>
       <c r="B2316" t="s" s="3">
-        <v>4598</v>
+        <v>4599</v>
       </c>
       <c r="C2316" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2316" t="s" s="3">
-        <v>4599</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="2317" ht="36.0" customHeight="true">
@@ -54294,16 +54321,16 @@
         <v>2316.0</v>
       </c>
       <c r="B2317" t="s" s="3">
-        <v>4600</v>
+        <v>4601</v>
       </c>
       <c r="C2317" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2317" t="s" s="3">
-        <v>4601</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="2318" ht="36.0" customHeight="true">
@@ -54317,10 +54344,10 @@
         <v>6</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2318" t="s" s="3">
-        <v>4528</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="2319" ht="36.0" customHeight="true">
@@ -54328,16 +54355,16 @@
         <v>2318.0</v>
       </c>
       <c r="B2319" t="s" s="3">
-        <v>3669</v>
+        <v>4604</v>
       </c>
       <c r="C2319" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2319" t="s" s="3">
-        <v>4603</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="2320" ht="36.0" customHeight="true">
@@ -54345,16 +54372,16 @@
         <v>2319.0</v>
       </c>
       <c r="B2320" t="s" s="3">
-        <v>4604</v>
+        <v>4606</v>
       </c>
       <c r="C2320" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2320" t="s" s="3">
-        <v>4566</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="2321" ht="36.0" customHeight="true">
@@ -54362,16 +54389,16 @@
         <v>2320.0</v>
       </c>
       <c r="B2321" t="s" s="3">
-        <v>4605</v>
+        <v>4608</v>
       </c>
       <c r="C2321" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2321" t="s" s="3">
-        <v>4606</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="2322" ht="36.0" customHeight="true">
@@ -54379,16 +54406,16 @@
         <v>2321.0</v>
       </c>
       <c r="B2322" t="s" s="3">
-        <v>4607</v>
+        <v>4610</v>
       </c>
       <c r="C2322" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2322" t="s" s="3">
-        <v>4608</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="2323" ht="36.0" customHeight="true">
@@ -54396,16 +54423,16 @@
         <v>2322.0</v>
       </c>
       <c r="B2323" t="s" s="3">
-        <v>4609</v>
+        <v>4612</v>
       </c>
       <c r="C2323" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2323" t="s" s="3">
-        <v>4610</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="2324" ht="36.0" customHeight="true">
@@ -54413,16 +54440,16 @@
         <v>2323.0</v>
       </c>
       <c r="B2324" t="s" s="3">
-        <v>4611</v>
+        <v>4614</v>
       </c>
       <c r="C2324" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2324" t="s" s="3">
-        <v>4612</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="2325" ht="36.0" customHeight="true">
@@ -54430,16 +54457,16 @@
         <v>2324.0</v>
       </c>
       <c r="B2325" t="s" s="3">
-        <v>4613</v>
+        <v>3671</v>
       </c>
       <c r="C2325" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2325" t="s" s="3">
-        <v>4614</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="2326" ht="36.0" customHeight="true">
@@ -54447,16 +54474,16 @@
         <v>2325.0</v>
       </c>
       <c r="B2326" t="s" s="3">
-        <v>4615</v>
+        <v>4616</v>
       </c>
       <c r="C2326" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2326" t="s" s="3">
-        <v>4616</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="2327" ht="36.0" customHeight="true">
@@ -54470,7 +54497,7 @@
         <v>6</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4618</v>
@@ -54487,7 +54514,7 @@
         <v>6</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4620</v>
@@ -54504,7 +54531,7 @@
         <v>6</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4622</v>
@@ -54521,7 +54548,7 @@
         <v>6</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4624</v>
@@ -54538,7 +54565,7 @@
         <v>6</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4626</v>
@@ -54555,7 +54582,7 @@
         <v>6</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4628</v>
@@ -54572,7 +54599,7 @@
         <v>6</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4630</v>
@@ -54589,7 +54616,7 @@
         <v>6</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2334" t="s" s="3">
         <v>4632</v>
@@ -54606,7 +54633,7 @@
         <v>6</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2335" t="s" s="3">
         <v>4634</v>
@@ -54623,7 +54650,7 @@
         <v>6</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2336" t="s" s="3">
         <v>4636</v>
@@ -54640,7 +54667,7 @@
         <v>6</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2337" t="s" s="3">
         <v>4638</v>
@@ -54657,7 +54684,7 @@
         <v>6</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4640</v>
@@ -54674,7 +54701,7 @@
         <v>6</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4642</v>
@@ -54691,7 +54718,7 @@
         <v>6</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4644</v>
@@ -54708,7 +54735,7 @@
         <v>6</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4646</v>
@@ -54725,7 +54752,7 @@
         <v>6</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4648</v>
@@ -54742,7 +54769,7 @@
         <v>6</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4650</v>
@@ -54759,7 +54786,7 @@
         <v>6</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4652</v>
@@ -54776,7 +54803,7 @@
         <v>6</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4654</v>
@@ -54793,7 +54820,7 @@
         <v>6</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4656</v>
@@ -54810,7 +54837,7 @@
         <v>6</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4658</v>
@@ -54827,7 +54854,7 @@
         <v>6</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4660</v>
@@ -54844,7 +54871,7 @@
         <v>6</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2349" t="s" s="3">
         <v>4662</v>
@@ -54861,7 +54888,7 @@
         <v>6</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2350" t="s" s="3">
         <v>4664</v>
@@ -54878,7 +54905,7 @@
         <v>6</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2351" t="s" s="3">
         <v>4666</v>
@@ -54895,7 +54922,7 @@
         <v>6</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2352" t="s" s="3">
         <v>4668</v>
@@ -54912,7 +54939,7 @@
         <v>6</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4670</v>
@@ -54929,7 +54956,7 @@
         <v>6</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4672</v>
@@ -54946,7 +54973,7 @@
         <v>6</v>
       </c>
       <c r="D2355" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2355" t="s" s="3">
         <v>4674</v>
@@ -54963,7 +54990,7 @@
         <v>6</v>
       </c>
       <c r="D2356" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4676</v>
@@ -54980,7 +55007,7 @@
         <v>6</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4678</v>
@@ -54997,7 +55024,7 @@
         <v>6</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4680</v>
@@ -55014,7 +55041,7 @@
         <v>6</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2359" t="s" s="3">
         <v>4682</v>
@@ -55031,7 +55058,7 @@
         <v>6</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4684</v>
@@ -55048,7 +55075,7 @@
         <v>6</v>
       </c>
       <c r="D2361" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2361" t="s" s="3">
         <v>4686</v>
@@ -55065,7 +55092,7 @@
         <v>6</v>
       </c>
       <c r="D2362" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4688</v>
@@ -55082,7 +55109,7 @@
         <v>6</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4690</v>
@@ -55099,7 +55126,7 @@
         <v>6</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2364" t="s" s="3">
         <v>4692</v>
@@ -55116,7 +55143,7 @@
         <v>6</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2365" t="s" s="3">
         <v>4694</v>
@@ -55133,7 +55160,7 @@
         <v>6</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2366" t="s" s="3">
         <v>4696</v>
@@ -55150,7 +55177,7 @@
         <v>6</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4698</v>
@@ -55161,16 +55188,16 @@
         <v>2367.0</v>
       </c>
       <c r="B2368" t="s" s="3">
-        <v>3010</v>
+        <v>4699</v>
       </c>
       <c r="C2368" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2368" t="s" s="3">
-        <v>4699</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="2369" ht="36.0" customHeight="true">
@@ -55178,16 +55205,16 @@
         <v>2368.0</v>
       </c>
       <c r="B2369" t="s" s="3">
-        <v>4700</v>
+        <v>4701</v>
       </c>
       <c r="C2369" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2369" t="s" s="3">
-        <v>4701</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="2370" ht="36.0" customHeight="true">
@@ -55195,16 +55222,16 @@
         <v>2369.0</v>
       </c>
       <c r="B2370" t="s" s="3">
-        <v>4702</v>
+        <v>4703</v>
       </c>
       <c r="C2370" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2370" t="s" s="3">
-        <v>4703</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="2371" ht="36.0" customHeight="true">
@@ -55212,16 +55239,16 @@
         <v>2370.0</v>
       </c>
       <c r="B2371" t="s" s="3">
-        <v>4704</v>
+        <v>4705</v>
       </c>
       <c r="C2371" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2371" t="s" s="3">
-        <v>4570</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="2372" ht="36.0" customHeight="true">
@@ -55229,16 +55256,16 @@
         <v>2371.0</v>
       </c>
       <c r="B2372" t="s" s="3">
-        <v>4705</v>
+        <v>4707</v>
       </c>
       <c r="C2372" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2372" t="s" s="3">
-        <v>4706</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="2373" ht="36.0" customHeight="true">
@@ -55246,16 +55273,16 @@
         <v>2372.0</v>
       </c>
       <c r="B2373" t="s" s="3">
-        <v>4707</v>
+        <v>4709</v>
       </c>
       <c r="C2373" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2373" t="s" s="3">
-        <v>4708</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="2374" ht="36.0" customHeight="true">
@@ -55263,16 +55290,16 @@
         <v>2373.0</v>
       </c>
       <c r="B2374" t="s" s="3">
-        <v>4709</v>
+        <v>3010</v>
       </c>
       <c r="C2374" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2374" t="s" s="3">
-        <v>4710</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="2375" ht="36.0" customHeight="true">
@@ -55280,16 +55307,16 @@
         <v>2374.0</v>
       </c>
       <c r="B2375" t="s" s="3">
-        <v>4711</v>
+        <v>4712</v>
       </c>
       <c r="C2375" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2375" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2375" t="s" s="3">
-        <v>4712</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="2376" ht="36.0" customHeight="true">
@@ -55297,16 +55324,16 @@
         <v>2375.0</v>
       </c>
       <c r="B2376" t="s" s="3">
-        <v>4713</v>
+        <v>4714</v>
       </c>
       <c r="C2376" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2376" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2376" t="s" s="3">
-        <v>4714</v>
+        <v>4715</v>
       </c>
     </row>
     <row r="2377" ht="36.0" customHeight="true">
@@ -55314,16 +55341,16 @@
         <v>2376.0</v>
       </c>
       <c r="B2377" t="s" s="3">
-        <v>4715</v>
+        <v>4716</v>
       </c>
       <c r="C2377" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2377" t="s" s="3">
-        <v>4716</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="2378" ht="36.0" customHeight="true">
@@ -55334,10 +55361,10 @@
         <v>4717</v>
       </c>
       <c r="C2378" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4718</v>
@@ -55351,10 +55378,10 @@
         <v>4719</v>
       </c>
       <c r="C2379" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4720</v>
@@ -55368,10 +55395,10 @@
         <v>4721</v>
       </c>
       <c r="C2380" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4722</v>
@@ -55385,10 +55412,10 @@
         <v>4723</v>
       </c>
       <c r="C2381" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4724</v>
@@ -55402,10 +55429,10 @@
         <v>4725</v>
       </c>
       <c r="C2382" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4726</v>
@@ -55419,10 +55446,10 @@
         <v>4727</v>
       </c>
       <c r="C2383" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4728</v>
@@ -55439,7 +55466,7 @@
         <v>719</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4730</v>
@@ -55456,7 +55483,7 @@
         <v>719</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4732</v>
@@ -55473,7 +55500,7 @@
         <v>719</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4734</v>
@@ -55490,7 +55517,7 @@
         <v>719</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4736</v>
@@ -55507,7 +55534,7 @@
         <v>719</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4738</v>
@@ -55524,7 +55551,7 @@
         <v>719</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4740</v>
@@ -55541,7 +55568,7 @@
         <v>719</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4742</v>
@@ -55558,7 +55585,7 @@
         <v>719</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4744</v>
@@ -55575,7 +55602,7 @@
         <v>719</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4746</v>
@@ -55592,7 +55619,7 @@
         <v>719</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2393" t="s" s="3">
         <v>4748</v>
@@ -55609,7 +55636,7 @@
         <v>719</v>
       </c>
       <c r="D2394" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2394" t="s" s="3">
         <v>4750</v>
@@ -55626,7 +55653,7 @@
         <v>719</v>
       </c>
       <c r="D2395" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2395" t="s" s="3">
         <v>4752</v>
@@ -55643,7 +55670,7 @@
         <v>719</v>
       </c>
       <c r="D2396" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2396" t="s" s="3">
         <v>4754</v>
@@ -55660,7 +55687,7 @@
         <v>719</v>
       </c>
       <c r="D2397" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4756</v>
@@ -55677,7 +55704,7 @@
         <v>719</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4758</v>
@@ -55694,7 +55721,7 @@
         <v>719</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2399" t="s" s="3">
         <v>4760</v>
@@ -55711,7 +55738,7 @@
         <v>719</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2400" t="s" s="3">
         <v>4762</v>
@@ -55728,7 +55755,7 @@
         <v>719</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4764</v>
@@ -55745,7 +55772,7 @@
         <v>719</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4766</v>
@@ -55762,7 +55789,7 @@
         <v>719</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4768</v>
@@ -55779,7 +55806,7 @@
         <v>719</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4770</v>
@@ -55796,7 +55823,7 @@
         <v>719</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4772</v>
@@ -55813,7 +55840,7 @@
         <v>719</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4774</v>
@@ -55830,7 +55857,7 @@
         <v>719</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4776</v>
@@ -55847,7 +55874,7 @@
         <v>719</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4778</v>
@@ -55864,7 +55891,7 @@
         <v>719</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4780</v>
@@ -55881,7 +55908,7 @@
         <v>719</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4782</v>
@@ -55898,7 +55925,7 @@
         <v>719</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4784</v>
@@ -55915,7 +55942,7 @@
         <v>719</v>
       </c>
       <c r="D2412" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2412" t="s" s="3">
         <v>4786</v>
@@ -55932,7 +55959,7 @@
         <v>719</v>
       </c>
       <c r="D2413" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2413" t="s" s="3">
         <v>4788</v>
@@ -55949,7 +55976,7 @@
         <v>719</v>
       </c>
       <c r="D2414" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2414" t="s" s="3">
         <v>4790</v>
@@ -55966,7 +55993,7 @@
         <v>719</v>
       </c>
       <c r="D2415" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2415" t="s" s="3">
         <v>4792</v>
@@ -55983,7 +56010,7 @@
         <v>719</v>
       </c>
       <c r="D2416" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2416" t="s" s="3">
         <v>4794</v>
@@ -56000,7 +56027,7 @@
         <v>719</v>
       </c>
       <c r="D2417" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2417" t="s" s="3">
         <v>4796</v>
@@ -56017,7 +56044,7 @@
         <v>719</v>
       </c>
       <c r="D2418" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2418" t="s" s="3">
         <v>4798</v>
@@ -56034,10 +56061,10 @@
         <v>719</v>
       </c>
       <c r="D2419" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2419" t="s" s="3">
-        <v>4508</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="2420" ht="36.0" customHeight="true">
@@ -56045,16 +56072,16 @@
         <v>2419.0</v>
       </c>
       <c r="B2420" t="s" s="3">
-        <v>4800</v>
+        <v>4801</v>
       </c>
       <c r="C2420" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2420" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2420" t="s" s="3">
-        <v>4801</v>
+        <v>4802</v>
       </c>
     </row>
     <row r="2421" ht="36.0" customHeight="true">
@@ -56062,16 +56089,16 @@
         <v>2420.0</v>
       </c>
       <c r="B2421" t="s" s="3">
-        <v>4802</v>
+        <v>4803</v>
       </c>
       <c r="C2421" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2421" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2421" t="s" s="3">
-        <v>4803</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="2422" ht="36.0" customHeight="true">
@@ -56079,16 +56106,16 @@
         <v>2421.0</v>
       </c>
       <c r="B2422" t="s" s="3">
-        <v>4804</v>
+        <v>4805</v>
       </c>
       <c r="C2422" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2422" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2422" t="s" s="3">
-        <v>4805</v>
+        <v>4806</v>
       </c>
     </row>
     <row r="2423" ht="36.0" customHeight="true">
@@ -56096,16 +56123,16 @@
         <v>2422.0</v>
       </c>
       <c r="B2423" t="s" s="3">
-        <v>4806</v>
+        <v>4807</v>
       </c>
       <c r="C2423" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2423" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2423" t="s" s="3">
-        <v>4807</v>
+        <v>4808</v>
       </c>
     </row>
     <row r="2424" ht="36.0" customHeight="true">
@@ -56113,16 +56140,16 @@
         <v>2423.0</v>
       </c>
       <c r="B2424" t="s" s="3">
-        <v>4808</v>
+        <v>4809</v>
       </c>
       <c r="C2424" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2424" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2424" t="s" s="3">
-        <v>4809</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="2425" ht="36.0" customHeight="true">
@@ -56130,16 +56157,16 @@
         <v>2424.0</v>
       </c>
       <c r="B2425" t="s" s="3">
-        <v>4810</v>
+        <v>4811</v>
       </c>
       <c r="C2425" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2425" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2425" t="s" s="3">
-        <v>4811</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="2426" ht="36.0" customHeight="true">
@@ -56153,7 +56180,7 @@
         <v>719</v>
       </c>
       <c r="D2426" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2426" t="s" s="3">
         <v>4813</v>
@@ -56167,10 +56194,10 @@
         <v>4814</v>
       </c>
       <c r="C2427" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2427" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2427" t="s" s="3">
         <v>4815</v>
@@ -56184,10 +56211,10 @@
         <v>4816</v>
       </c>
       <c r="C2428" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2428" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2428" t="s" s="3">
         <v>4817</v>
@@ -56198,16 +56225,16 @@
         <v>2428.0</v>
       </c>
       <c r="B2429" t="s" s="3">
-        <v>4795</v>
+        <v>4818</v>
       </c>
       <c r="C2429" t="s" s="2">
-        <v>920</v>
+        <v>719</v>
       </c>
       <c r="D2429" t="s" s="2">
-        <v>4459</v>
+        <v>4471</v>
       </c>
       <c r="E2429" t="s" s="3">
-        <v>4818</v>
+        <v>4819</v>
       </c>
     </row>
     <row r="2430" ht="36.0" customHeight="true">
@@ -56215,13 +56242,13 @@
         <v>2429.0</v>
       </c>
       <c r="B2430" t="s" s="3">
-        <v>4819</v>
+        <v>4820</v>
       </c>
       <c r="C2430" t="s" s="2">
-        <v>6</v>
+        <v>719</v>
       </c>
       <c r="D2430" t="s" s="2">
-        <v>4820</v>
+        <v>4471</v>
       </c>
       <c r="E2430" t="s" s="3">
         <v>4821</v>
@@ -56235,10 +56262,10 @@
         <v>4822</v>
       </c>
       <c r="C2431" t="s" s="2">
-        <v>6</v>
+        <v>719</v>
       </c>
       <c r="D2431" t="s" s="2">
-        <v>4820</v>
+        <v>4471</v>
       </c>
       <c r="E2431" t="s" s="3">
         <v>4823</v>
@@ -56252,10 +56279,10 @@
         <v>4824</v>
       </c>
       <c r="C2432" t="s" s="2">
-        <v>6</v>
+        <v>719</v>
       </c>
       <c r="D2432" t="s" s="2">
-        <v>4820</v>
+        <v>4471</v>
       </c>
       <c r="E2432" t="s" s="3">
         <v>4825</v>
@@ -56269,10 +56296,10 @@
         <v>4826</v>
       </c>
       <c r="C2433" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D2433" t="s" s="2">
-        <v>4820</v>
+        <v>4471</v>
       </c>
       <c r="E2433" t="s" s="3">
         <v>4827</v>
@@ -56286,10 +56313,10 @@
         <v>4828</v>
       </c>
       <c r="C2434" t="s" s="2">
-        <v>6</v>
+        <v>920</v>
       </c>
       <c r="D2434" t="s" s="2">
-        <v>4820</v>
+        <v>4471</v>
       </c>
       <c r="E2434" t="s" s="3">
         <v>4829</v>
@@ -56300,16 +56327,16 @@
         <v>2434.0</v>
       </c>
       <c r="B2435" t="s" s="3">
+        <v>4807</v>
+      </c>
+      <c r="C2435" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D2435" t="s" s="2">
+        <v>4471</v>
+      </c>
+      <c r="E2435" t="s" s="3">
         <v>4830</v>
-      </c>
-      <c r="C2435" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2435" t="s" s="2">
-        <v>4820</v>
-      </c>
-      <c r="E2435" t="s" s="3">
-        <v>4831</v>
       </c>
     </row>
     <row r="2436" ht="36.0" customHeight="true">
@@ -56317,13 +56344,13 @@
         <v>2435.0</v>
       </c>
       <c r="B2436" t="s" s="3">
+        <v>4831</v>
+      </c>
+      <c r="C2436" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2436" t="s" s="2">
         <v>4832</v>
-      </c>
-      <c r="C2436" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2436" t="s" s="2">
-        <v>4820</v>
       </c>
       <c r="E2436" t="s" s="3">
         <v>4833</v>
@@ -56340,7 +56367,7 @@
         <v>6</v>
       </c>
       <c r="D2437" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2437" t="s" s="3">
         <v>4835</v>
@@ -56357,7 +56384,7 @@
         <v>6</v>
       </c>
       <c r="D2438" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2438" t="s" s="3">
         <v>4837</v>
@@ -56374,7 +56401,7 @@
         <v>6</v>
       </c>
       <c r="D2439" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2439" t="s" s="3">
         <v>4839</v>
@@ -56391,7 +56418,7 @@
         <v>6</v>
       </c>
       <c r="D2440" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2440" t="s" s="3">
         <v>4841</v>
@@ -56408,7 +56435,7 @@
         <v>6</v>
       </c>
       <c r="D2441" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2441" t="s" s="3">
         <v>4843</v>
@@ -56425,7 +56452,7 @@
         <v>6</v>
       </c>
       <c r="D2442" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2442" t="s" s="3">
         <v>4845</v>
@@ -56442,7 +56469,7 @@
         <v>6</v>
       </c>
       <c r="D2443" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2443" t="s" s="3">
         <v>4847</v>
@@ -56459,7 +56486,7 @@
         <v>6</v>
       </c>
       <c r="D2444" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2444" t="s" s="3">
         <v>4849</v>
@@ -56476,7 +56503,7 @@
         <v>6</v>
       </c>
       <c r="D2445" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2445" t="s" s="3">
         <v>4851</v>
@@ -56493,7 +56520,7 @@
         <v>6</v>
       </c>
       <c r="D2446" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2446" t="s" s="3">
         <v>4853</v>
@@ -56510,7 +56537,7 @@
         <v>6</v>
       </c>
       <c r="D2447" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2447" t="s" s="3">
         <v>4855</v>
@@ -56527,7 +56554,7 @@
         <v>6</v>
       </c>
       <c r="D2448" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2448" t="s" s="3">
         <v>4857</v>
@@ -56544,7 +56571,7 @@
         <v>6</v>
       </c>
       <c r="D2449" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2449" t="s" s="3">
         <v>4859</v>
@@ -56561,7 +56588,7 @@
         <v>6</v>
       </c>
       <c r="D2450" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2450" t="s" s="3">
         <v>4861</v>
@@ -56578,7 +56605,7 @@
         <v>6</v>
       </c>
       <c r="D2451" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2451" t="s" s="3">
         <v>4863</v>
@@ -56595,7 +56622,7 @@
         <v>6</v>
       </c>
       <c r="D2452" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2452" t="s" s="3">
         <v>4865</v>
@@ -56612,7 +56639,7 @@
         <v>6</v>
       </c>
       <c r="D2453" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2453" t="s" s="3">
         <v>4867</v>
@@ -56629,7 +56656,7 @@
         <v>6</v>
       </c>
       <c r="D2454" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2454" t="s" s="3">
         <v>4869</v>
@@ -56646,7 +56673,7 @@
         <v>6</v>
       </c>
       <c r="D2455" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2455" t="s" s="3">
         <v>4871</v>
@@ -56663,7 +56690,7 @@
         <v>6</v>
       </c>
       <c r="D2456" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2456" t="s" s="3">
         <v>4873</v>
@@ -56680,7 +56707,7 @@
         <v>6</v>
       </c>
       <c r="D2457" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2457" t="s" s="3">
         <v>4875</v>
@@ -56697,7 +56724,7 @@
         <v>6</v>
       </c>
       <c r="D2458" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2458" t="s" s="3">
         <v>4877</v>
@@ -56714,7 +56741,7 @@
         <v>6</v>
       </c>
       <c r="D2459" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2459" t="s" s="3">
         <v>4879</v>
@@ -56731,7 +56758,7 @@
         <v>6</v>
       </c>
       <c r="D2460" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2460" t="s" s="3">
         <v>4881</v>
@@ -56748,7 +56775,7 @@
         <v>6</v>
       </c>
       <c r="D2461" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2461" t="s" s="3">
         <v>4883</v>
@@ -56765,7 +56792,7 @@
         <v>6</v>
       </c>
       <c r="D2462" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2462" t="s" s="3">
         <v>4885</v>
@@ -56782,7 +56809,7 @@
         <v>6</v>
       </c>
       <c r="D2463" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2463" t="s" s="3">
         <v>4887</v>
@@ -56799,7 +56826,7 @@
         <v>6</v>
       </c>
       <c r="D2464" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2464" t="s" s="3">
         <v>4889</v>
@@ -56813,13 +56840,13 @@
         <v>4890</v>
       </c>
       <c r="C2465" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2465" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2465" t="s" s="3">
-        <v>4865</v>
+        <v>4891</v>
       </c>
     </row>
     <row r="2466" ht="36.0" customHeight="true">
@@ -56827,16 +56854,16 @@
         <v>2465.0</v>
       </c>
       <c r="B2466" t="s" s="3">
-        <v>4891</v>
+        <v>4892</v>
       </c>
       <c r="C2466" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2466" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2466" t="s" s="3">
-        <v>4892</v>
+        <v>4893</v>
       </c>
     </row>
     <row r="2467" ht="36.0" customHeight="true">
@@ -56844,16 +56871,16 @@
         <v>2466.0</v>
       </c>
       <c r="B2467" t="s" s="3">
-        <v>4893</v>
+        <v>4894</v>
       </c>
       <c r="C2467" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2467" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2467" t="s" s="3">
-        <v>4894</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="2468" ht="36.0" customHeight="true">
@@ -56861,16 +56888,16 @@
         <v>2467.0</v>
       </c>
       <c r="B2468" t="s" s="3">
-        <v>4895</v>
+        <v>4896</v>
       </c>
       <c r="C2468" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2468" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2468" t="s" s="3">
-        <v>4896</v>
+        <v>4897</v>
       </c>
     </row>
     <row r="2469" ht="36.0" customHeight="true">
@@ -56878,16 +56905,16 @@
         <v>2468.0</v>
       </c>
       <c r="B2469" t="s" s="3">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="C2469" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2469" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2469" t="s" s="3">
-        <v>4898</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="2470" ht="36.0" customHeight="true">
@@ -56895,16 +56922,16 @@
         <v>2469.0</v>
       </c>
       <c r="B2470" t="s" s="3">
-        <v>4899</v>
+        <v>4900</v>
       </c>
       <c r="C2470" t="s" s="2">
-        <v>719</v>
+        <v>6</v>
       </c>
       <c r="D2470" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2470" t="s" s="3">
-        <v>4900</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="2471" ht="36.0" customHeight="true">
@@ -56912,16 +56939,16 @@
         <v>2470.0</v>
       </c>
       <c r="B2471" t="s" s="3">
-        <v>4826</v>
+        <v>4902</v>
       </c>
       <c r="C2471" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2471" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2471" t="s" s="3">
-        <v>4901</v>
+        <v>4877</v>
       </c>
     </row>
     <row r="2472" ht="36.0" customHeight="true">
@@ -56929,16 +56956,16 @@
         <v>2471.0</v>
       </c>
       <c r="B2472" t="s" s="3">
-        <v>4902</v>
+        <v>4903</v>
       </c>
       <c r="C2472" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2472" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2472" t="s" s="3">
-        <v>4903</v>
+        <v>4904</v>
       </c>
     </row>
     <row r="2473" ht="36.0" customHeight="true">
@@ -56946,16 +56973,16 @@
         <v>2472.0</v>
       </c>
       <c r="B2473" t="s" s="3">
-        <v>4904</v>
+        <v>4905</v>
       </c>
       <c r="C2473" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2473" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2473" t="s" s="3">
-        <v>4905</v>
+        <v>4906</v>
       </c>
     </row>
     <row r="2474" ht="36.0" customHeight="true">
@@ -56963,16 +56990,16 @@
         <v>2473.0</v>
       </c>
       <c r="B2474" t="s" s="3">
-        <v>4906</v>
+        <v>4907</v>
       </c>
       <c r="C2474" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2474" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2474" t="s" s="3">
-        <v>4907</v>
+        <v>4908</v>
       </c>
     </row>
     <row r="2475" ht="36.0" customHeight="true">
@@ -56980,16 +57007,16 @@
         <v>2474.0</v>
       </c>
       <c r="B2475" t="s" s="3">
-        <v>4908</v>
+        <v>4909</v>
       </c>
       <c r="C2475" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2475" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2475" t="s" s="3">
-        <v>4909</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="2476" ht="36.0" customHeight="true">
@@ -56997,16 +57024,16 @@
         <v>2475.0</v>
       </c>
       <c r="B2476" t="s" s="3">
-        <v>4910</v>
+        <v>4911</v>
       </c>
       <c r="C2476" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2476" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2476" t="s" s="3">
-        <v>4911</v>
+        <v>4912</v>
       </c>
     </row>
     <row r="2477" ht="36.0" customHeight="true">
@@ -57014,13 +57041,13 @@
         <v>2476.0</v>
       </c>
       <c r="B2477" t="s" s="3">
-        <v>4912</v>
+        <v>4838</v>
       </c>
       <c r="C2477" t="s" s="2">
         <v>719</v>
       </c>
       <c r="D2477" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2477" t="s" s="3">
         <v>4913</v>
@@ -57037,7 +57064,7 @@
         <v>719</v>
       </c>
       <c r="D2478" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2478" t="s" s="3">
         <v>4915</v>
@@ -57054,7 +57081,7 @@
         <v>719</v>
       </c>
       <c r="D2479" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2479" t="s" s="3">
         <v>4917</v>
@@ -57071,7 +57098,7 @@
         <v>719</v>
       </c>
       <c r="D2480" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2480" t="s" s="3">
         <v>4919</v>
@@ -57088,7 +57115,7 @@
         <v>719</v>
       </c>
       <c r="D2481" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2481" t="s" s="3">
         <v>4921</v>
@@ -57105,7 +57132,7 @@
         <v>719</v>
       </c>
       <c r="D2482" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2482" t="s" s="3">
         <v>4923</v>
@@ -57122,7 +57149,7 @@
         <v>719</v>
       </c>
       <c r="D2483" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2483" t="s" s="3">
         <v>4925</v>
@@ -57139,7 +57166,7 @@
         <v>719</v>
       </c>
       <c r="D2484" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2484" t="s" s="3">
         <v>4927</v>
@@ -57156,7 +57183,7 @@
         <v>719</v>
       </c>
       <c r="D2485" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2485" t="s" s="3">
         <v>4929</v>
@@ -57173,7 +57200,7 @@
         <v>719</v>
       </c>
       <c r="D2486" t="s" s="2">
-        <v>4820</v>
+        <v>4832</v>
       </c>
       <c r="E2486" t="s" s="3">
         <v>4931</v>
@@ -57187,13 +57214,98 @@
         <v>4932</v>
       </c>
       <c r="C2487" t="s" s="2">
-        <v>6</v>
+        <v>719</v>
       </c>
       <c r="D2487" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2487" t="s" s="3">
         <v>4933</v>
       </c>
-      <c r="E2487" t="s" s="3">
+    </row>
+    <row r="2488" ht="36.0" customHeight="true">
+      <c r="A2488" t="n" s="2">
+        <v>2487.0</v>
+      </c>
+      <c r="B2488" t="s" s="3">
         <v>4934</v>
+      </c>
+      <c r="C2488" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D2488" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2488" t="s" s="3">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="2489" ht="36.0" customHeight="true">
+      <c r="A2489" t="n" s="2">
+        <v>2488.0</v>
+      </c>
+      <c r="B2489" t="s" s="3">
+        <v>4936</v>
+      </c>
+      <c r="C2489" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D2489" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2489" t="s" s="3">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="2490" ht="36.0" customHeight="true">
+      <c r="A2490" t="n" s="2">
+        <v>2489.0</v>
+      </c>
+      <c r="B2490" t="s" s="3">
+        <v>4938</v>
+      </c>
+      <c r="C2490" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D2490" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2490" t="s" s="3">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="2491" ht="36.0" customHeight="true">
+      <c r="A2491" t="n" s="2">
+        <v>2490.0</v>
+      </c>
+      <c r="B2491" t="s" s="3">
+        <v>4940</v>
+      </c>
+      <c r="C2491" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D2491" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2491" t="s" s="3">
+        <v>4941</v>
+      </c>
+    </row>
+    <row r="2492" ht="36.0" customHeight="true">
+      <c r="A2492" t="n" s="2">
+        <v>2491.0</v>
+      </c>
+      <c r="B2492" t="s" s="3">
+        <v>4942</v>
+      </c>
+      <c r="C2492" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D2492" t="s" s="2">
+        <v>4832</v>
+      </c>
+      <c r="E2492" t="s" s="3">
+        <v>4943</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10393" uniqueCount="5156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10397" uniqueCount="5158">
   <si>
     <t>연번</t>
   </si>
@@ -3917,12 +3917,12 @@
     <t>스트럿</t>
   </si>
   <si>
+    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
+  </si>
+  <si>
     <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
   </si>
   <si>
-    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
-  </si>
-  <si>
     <t>시랑</t>
   </si>
   <si>
@@ -5687,12 +5687,12 @@
     <t>그리너리 바스켓</t>
   </si>
   <si>
+    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
+  </si>
+  <si>
     <t>인천광역시 영종구 백운로 510(2동 1,2층 운북동)</t>
   </si>
   <si>
-    <t>인천광역시 영종구 백운로 510(1동 지1층 운북동)</t>
-  </si>
-  <si>
     <t>까페마인</t>
   </si>
   <si>
@@ -8648,12 +8648,12 @@
     <t>위자네</t>
   </si>
   <si>
+    <t>경기도 안양시 만안구 석천로 181(1층 석수동)</t>
+  </si>
+  <si>
     <t>경기도 화성시 효행구 봉담읍 장등1길 3-10(1층)</t>
   </si>
   <si>
-    <t>경기도 안양시 만안구 석천로 181(1층 석수동)</t>
-  </si>
-  <si>
     <t>위클리베이글 평촌점</t>
   </si>
   <si>
@@ -11517,6 +11517,12 @@
   </si>
   <si>
     <t>충청남도 서산시 부석면 봉락노라포1길 62(2동)</t>
+  </si>
+  <si>
+    <t>그린브라우니</t>
+  </si>
+  <si>
+    <t>충청남도 보령시 주공로 118(명천동)</t>
   </si>
   <si>
     <t>노을커피</t>
@@ -48667,7 +48673,7 @@
         <v>1946.0</v>
       </c>
       <c r="B1947" t="s" s="3">
-        <v>3807</v>
+        <v>3865</v>
       </c>
       <c r="C1947" t="s" s="2">
         <v>733</v>
@@ -48676,7 +48682,7 @@
         <v>3721</v>
       </c>
       <c r="E1947" t="s" s="3">
-        <v>3808</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="1948" ht="36.0" customHeight="true">
@@ -48684,7 +48690,7 @@
         <v>1947.0</v>
       </c>
       <c r="B1948" t="s" s="3">
-        <v>3865</v>
+        <v>3807</v>
       </c>
       <c r="C1948" t="s" s="2">
         <v>733</v>
@@ -48693,7 +48699,7 @@
         <v>3721</v>
       </c>
       <c r="E1948" t="s" s="3">
-        <v>3866</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="1949" ht="36.0" customHeight="true">
@@ -48840,7 +48846,7 @@
         <v>3883</v>
       </c>
       <c r="C1957" t="s" s="2">
-        <v>938</v>
+        <v>733</v>
       </c>
       <c r="D1957" t="s" s="2">
         <v>3721</v>
@@ -48874,13 +48880,13 @@
         <v>3887</v>
       </c>
       <c r="C1959" t="s" s="2">
-        <v>6</v>
+        <v>938</v>
       </c>
       <c r="D1959" t="s" s="2">
+        <v>3721</v>
+      </c>
+      <c r="E1959" t="s" s="3">
         <v>3888</v>
-      </c>
-      <c r="E1959" t="s" s="3">
-        <v>3889</v>
       </c>
     </row>
     <row r="1960" ht="36.0" customHeight="true">
@@ -48888,13 +48894,13 @@
         <v>1959.0</v>
       </c>
       <c r="B1960" t="s" s="3">
+        <v>3889</v>
+      </c>
+      <c r="C1960" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1960" t="s" s="2">
         <v>3890</v>
-      </c>
-      <c r="C1960" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1960" t="s" s="2">
-        <v>3888</v>
       </c>
       <c r="E1960" t="s" s="3">
         <v>3891</v>
@@ -48911,7 +48917,7 @@
         <v>6</v>
       </c>
       <c r="D1961" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1961" t="s" s="3">
         <v>3893</v>
@@ -48928,7 +48934,7 @@
         <v>6</v>
       </c>
       <c r="D1962" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1962" t="s" s="3">
         <v>3895</v>
@@ -48945,7 +48951,7 @@
         <v>6</v>
       </c>
       <c r="D1963" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1963" t="s" s="3">
         <v>3897</v>
@@ -48962,7 +48968,7 @@
         <v>6</v>
       </c>
       <c r="D1964" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1964" t="s" s="3">
         <v>3899</v>
@@ -48979,7 +48985,7 @@
         <v>6</v>
       </c>
       <c r="D1965" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1965" t="s" s="3">
         <v>3901</v>
@@ -48996,7 +49002,7 @@
         <v>6</v>
       </c>
       <c r="D1966" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1966" t="s" s="3">
         <v>3903</v>
@@ -49013,7 +49019,7 @@
         <v>6</v>
       </c>
       <c r="D1967" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1967" t="s" s="3">
         <v>3905</v>
@@ -49030,7 +49036,7 @@
         <v>6</v>
       </c>
       <c r="D1968" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1968" t="s" s="3">
         <v>3907</v>
@@ -49047,7 +49053,7 @@
         <v>6</v>
       </c>
       <c r="D1969" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1969" t="s" s="3">
         <v>3909</v>
@@ -49064,7 +49070,7 @@
         <v>6</v>
       </c>
       <c r="D1970" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1970" t="s" s="3">
         <v>3911</v>
@@ -49081,7 +49087,7 @@
         <v>6</v>
       </c>
       <c r="D1971" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1971" t="s" s="3">
         <v>3913</v>
@@ -49098,7 +49104,7 @@
         <v>6</v>
       </c>
       <c r="D1972" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1972" t="s" s="3">
         <v>3915</v>
@@ -49115,7 +49121,7 @@
         <v>6</v>
       </c>
       <c r="D1973" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1973" t="s" s="3">
         <v>3917</v>
@@ -49132,7 +49138,7 @@
         <v>6</v>
       </c>
       <c r="D1974" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1974" t="s" s="3">
         <v>3919</v>
@@ -49149,7 +49155,7 @@
         <v>6</v>
       </c>
       <c r="D1975" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1975" t="s" s="3">
         <v>3921</v>
@@ -49166,7 +49172,7 @@
         <v>6</v>
       </c>
       <c r="D1976" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1976" t="s" s="3">
         <v>3923</v>
@@ -49183,7 +49189,7 @@
         <v>6</v>
       </c>
       <c r="D1977" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1977" t="s" s="3">
         <v>3925</v>
@@ -49200,7 +49206,7 @@
         <v>6</v>
       </c>
       <c r="D1978" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1978" t="s" s="3">
         <v>3927</v>
@@ -49217,7 +49223,7 @@
         <v>6</v>
       </c>
       <c r="D1979" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1979" t="s" s="3">
         <v>3929</v>
@@ -49234,7 +49240,7 @@
         <v>6</v>
       </c>
       <c r="D1980" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1980" t="s" s="3">
         <v>3931</v>
@@ -49251,7 +49257,7 @@
         <v>6</v>
       </c>
       <c r="D1981" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1981" t="s" s="3">
         <v>3933</v>
@@ -49268,7 +49274,7 @@
         <v>6</v>
       </c>
       <c r="D1982" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1982" t="s" s="3">
         <v>3935</v>
@@ -49285,7 +49291,7 @@
         <v>6</v>
       </c>
       <c r="D1983" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1983" t="s" s="3">
         <v>3937</v>
@@ -49302,7 +49308,7 @@
         <v>6</v>
       </c>
       <c r="D1984" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1984" t="s" s="3">
         <v>3939</v>
@@ -49319,7 +49325,7 @@
         <v>6</v>
       </c>
       <c r="D1985" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1985" t="s" s="3">
         <v>3941</v>
@@ -49336,7 +49342,7 @@
         <v>6</v>
       </c>
       <c r="D1986" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1986" t="s" s="3">
         <v>3943</v>
@@ -49353,7 +49359,7 @@
         <v>6</v>
       </c>
       <c r="D1987" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1987" t="s" s="3">
         <v>3945</v>
@@ -49370,7 +49376,7 @@
         <v>6</v>
       </c>
       <c r="D1988" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1988" t="s" s="3">
         <v>3947</v>
@@ -49387,7 +49393,7 @@
         <v>6</v>
       </c>
       <c r="D1989" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1989" t="s" s="3">
         <v>3949</v>
@@ -49404,7 +49410,7 @@
         <v>6</v>
       </c>
       <c r="D1990" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1990" t="s" s="3">
         <v>3951</v>
@@ -49421,7 +49427,7 @@
         <v>6</v>
       </c>
       <c r="D1991" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1991" t="s" s="3">
         <v>3953</v>
@@ -49438,7 +49444,7 @@
         <v>6</v>
       </c>
       <c r="D1992" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1992" t="s" s="3">
         <v>3955</v>
@@ -49455,7 +49461,7 @@
         <v>6</v>
       </c>
       <c r="D1993" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1993" t="s" s="3">
         <v>3957</v>
@@ -49472,7 +49478,7 @@
         <v>6</v>
       </c>
       <c r="D1994" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1994" t="s" s="3">
         <v>3959</v>
@@ -49489,7 +49495,7 @@
         <v>6</v>
       </c>
       <c r="D1995" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1995" t="s" s="3">
         <v>3961</v>
@@ -49506,10 +49512,10 @@
         <v>6</v>
       </c>
       <c r="D1996" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1996" t="s" s="3">
-        <v>3937</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="1997" ht="36.0" customHeight="true">
@@ -49517,16 +49523,16 @@
         <v>1996.0</v>
       </c>
       <c r="B1997" t="s" s="3">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C1997" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1997" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1997" t="s" s="3">
-        <v>3964</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="1998" ht="36.0" customHeight="true">
@@ -49534,16 +49540,16 @@
         <v>1997.0</v>
       </c>
       <c r="B1998" t="s" s="3">
-        <v>3510</v>
+        <v>3965</v>
       </c>
       <c r="C1998" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1998" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1998" t="s" s="3">
-        <v>3965</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="1999" ht="36.0" customHeight="true">
@@ -49551,13 +49557,13 @@
         <v>1998.0</v>
       </c>
       <c r="B1999" t="s" s="3">
-        <v>3966</v>
+        <v>3510</v>
       </c>
       <c r="C1999" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1999" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E1999" t="s" s="3">
         <v>3967</v>
@@ -49574,7 +49580,7 @@
         <v>6</v>
       </c>
       <c r="D2000" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2000" t="s" s="3">
         <v>3969</v>
@@ -49591,7 +49597,7 @@
         <v>6</v>
       </c>
       <c r="D2001" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2001" t="s" s="3">
         <v>3971</v>
@@ -49608,7 +49614,7 @@
         <v>6</v>
       </c>
       <c r="D2002" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2002" t="s" s="3">
         <v>3973</v>
@@ -49625,7 +49631,7 @@
         <v>6</v>
       </c>
       <c r="D2003" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2003" t="s" s="3">
         <v>3975</v>
@@ -49642,7 +49648,7 @@
         <v>6</v>
       </c>
       <c r="D2004" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2004" t="s" s="3">
         <v>3977</v>
@@ -49656,10 +49662,10 @@
         <v>3978</v>
       </c>
       <c r="C2005" t="s" s="2">
-        <v>733</v>
+        <v>6</v>
       </c>
       <c r="D2005" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2005" t="s" s="3">
         <v>3979</v>
@@ -49676,7 +49682,7 @@
         <v>733</v>
       </c>
       <c r="D2006" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2006" t="s" s="3">
         <v>3981</v>
@@ -49693,7 +49699,7 @@
         <v>733</v>
       </c>
       <c r="D2007" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2007" t="s" s="3">
         <v>3983</v>
@@ -49710,7 +49716,7 @@
         <v>733</v>
       </c>
       <c r="D2008" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2008" t="s" s="3">
         <v>3985</v>
@@ -49727,7 +49733,7 @@
         <v>733</v>
       </c>
       <c r="D2009" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2009" t="s" s="3">
         <v>3987</v>
@@ -49744,7 +49750,7 @@
         <v>733</v>
       </c>
       <c r="D2010" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2010" t="s" s="3">
         <v>3989</v>
@@ -49761,7 +49767,7 @@
         <v>733</v>
       </c>
       <c r="D2011" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2011" t="s" s="3">
         <v>3991</v>
@@ -49778,7 +49784,7 @@
         <v>733</v>
       </c>
       <c r="D2012" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2012" t="s" s="3">
         <v>3993</v>
@@ -49795,7 +49801,7 @@
         <v>733</v>
       </c>
       <c r="D2013" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2013" t="s" s="3">
         <v>3995</v>
@@ -49812,7 +49818,7 @@
         <v>733</v>
       </c>
       <c r="D2014" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2014" t="s" s="3">
         <v>3997</v>
@@ -49829,7 +49835,7 @@
         <v>733</v>
       </c>
       <c r="D2015" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2015" t="s" s="3">
         <v>3999</v>
@@ -49846,7 +49852,7 @@
         <v>733</v>
       </c>
       <c r="D2016" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2016" t="s" s="3">
         <v>4001</v>
@@ -49863,7 +49869,7 @@
         <v>733</v>
       </c>
       <c r="D2017" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2017" t="s" s="3">
         <v>4003</v>
@@ -49880,7 +49886,7 @@
         <v>733</v>
       </c>
       <c r="D2018" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2018" t="s" s="3">
         <v>4005</v>
@@ -49897,7 +49903,7 @@
         <v>733</v>
       </c>
       <c r="D2019" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2019" t="s" s="3">
         <v>4007</v>
@@ -49914,7 +49920,7 @@
         <v>733</v>
       </c>
       <c r="D2020" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2020" t="s" s="3">
         <v>4009</v>
@@ -49931,7 +49937,7 @@
         <v>733</v>
       </c>
       <c r="D2021" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2021" t="s" s="3">
         <v>4011</v>
@@ -49948,7 +49954,7 @@
         <v>733</v>
       </c>
       <c r="D2022" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2022" t="s" s="3">
         <v>4013</v>
@@ -49965,7 +49971,7 @@
         <v>733</v>
       </c>
       <c r="D2023" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2023" t="s" s="3">
         <v>4015</v>
@@ -49982,7 +49988,7 @@
         <v>733</v>
       </c>
       <c r="D2024" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2024" t="s" s="3">
         <v>4017</v>
@@ -49999,7 +50005,7 @@
         <v>733</v>
       </c>
       <c r="D2025" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2025" t="s" s="3">
         <v>4019</v>
@@ -50016,7 +50022,7 @@
         <v>733</v>
       </c>
       <c r="D2026" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2026" t="s" s="3">
         <v>4021</v>
@@ -50033,7 +50039,7 @@
         <v>733</v>
       </c>
       <c r="D2027" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2027" t="s" s="3">
         <v>4023</v>
@@ -50050,7 +50056,7 @@
         <v>733</v>
       </c>
       <c r="D2028" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2028" t="s" s="3">
         <v>4025</v>
@@ -50067,7 +50073,7 @@
         <v>733</v>
       </c>
       <c r="D2029" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2029" t="s" s="3">
         <v>4027</v>
@@ -50084,7 +50090,7 @@
         <v>733</v>
       </c>
       <c r="D2030" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2030" t="s" s="3">
         <v>4029</v>
@@ -50101,7 +50107,7 @@
         <v>733</v>
       </c>
       <c r="D2031" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2031" t="s" s="3">
         <v>4031</v>
@@ -50115,10 +50121,10 @@
         <v>4032</v>
       </c>
       <c r="C2032" t="s" s="2">
-        <v>938</v>
+        <v>733</v>
       </c>
       <c r="D2032" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2032" t="s" s="3">
         <v>4033</v>
@@ -50135,7 +50141,7 @@
         <v>938</v>
       </c>
       <c r="D2033" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2033" t="s" s="3">
         <v>4035</v>
@@ -50146,16 +50152,16 @@
         <v>2033.0</v>
       </c>
       <c r="B2034" t="s" s="3">
-        <v>3963</v>
+        <v>4036</v>
       </c>
       <c r="C2034" t="s" s="2">
         <v>938</v>
       </c>
       <c r="D2034" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2034" t="s" s="3">
-        <v>3964</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="2035" ht="36.0" customHeight="true">
@@ -50163,16 +50169,16 @@
         <v>2034.0</v>
       </c>
       <c r="B2035" t="s" s="3">
-        <v>4036</v>
+        <v>3965</v>
       </c>
       <c r="C2035" t="s" s="2">
         <v>938</v>
       </c>
       <c r="D2035" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2035" t="s" s="3">
-        <v>4037</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="2036" ht="36.0" customHeight="true">
@@ -50186,7 +50192,7 @@
         <v>938</v>
       </c>
       <c r="D2036" t="s" s="2">
-        <v>3888</v>
+        <v>3890</v>
       </c>
       <c r="E2036" t="s" s="3">
         <v>4039</v>
@@ -50200,13 +50206,13 @@
         <v>4040</v>
       </c>
       <c r="C2037" t="s" s="2">
-        <v>6</v>
+        <v>938</v>
       </c>
       <c r="D2037" t="s" s="2">
+        <v>3890</v>
+      </c>
+      <c r="E2037" t="s" s="3">
         <v>4041</v>
-      </c>
-      <c r="E2037" t="s" s="3">
-        <v>4042</v>
       </c>
     </row>
     <row r="2038" ht="36.0" customHeight="true">
@@ -50214,13 +50220,13 @@
         <v>2037.0</v>
       </c>
       <c r="B2038" t="s" s="3">
+        <v>4042</v>
+      </c>
+      <c r="C2038" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2038" t="s" s="2">
         <v>4043</v>
-      </c>
-      <c r="C2038" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2038" t="s" s="2">
-        <v>4041</v>
       </c>
       <c r="E2038" t="s" s="3">
         <v>4044</v>
@@ -50237,7 +50243,7 @@
         <v>6</v>
       </c>
       <c r="D2039" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2039" t="s" s="3">
         <v>4046</v>
@@ -50254,7 +50260,7 @@
         <v>6</v>
       </c>
       <c r="D2040" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2040" t="s" s="3">
         <v>4048</v>
@@ -50271,7 +50277,7 @@
         <v>6</v>
       </c>
       <c r="D2041" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2041" t="s" s="3">
         <v>4050</v>
@@ -50288,7 +50294,7 @@
         <v>6</v>
       </c>
       <c r="D2042" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2042" t="s" s="3">
         <v>4052</v>
@@ -50305,7 +50311,7 @@
         <v>6</v>
       </c>
       <c r="D2043" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2043" t="s" s="3">
         <v>4054</v>
@@ -50322,7 +50328,7 @@
         <v>6</v>
       </c>
       <c r="D2044" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2044" t="s" s="3">
         <v>4056</v>
@@ -50339,7 +50345,7 @@
         <v>6</v>
       </c>
       <c r="D2045" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2045" t="s" s="3">
         <v>4058</v>
@@ -50356,7 +50362,7 @@
         <v>6</v>
       </c>
       <c r="D2046" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2046" t="s" s="3">
         <v>4060</v>
@@ -50373,7 +50379,7 @@
         <v>6</v>
       </c>
       <c r="D2047" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2047" t="s" s="3">
         <v>4062</v>
@@ -50390,7 +50396,7 @@
         <v>6</v>
       </c>
       <c r="D2048" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2048" t="s" s="3">
         <v>4064</v>
@@ -50407,7 +50413,7 @@
         <v>6</v>
       </c>
       <c r="D2049" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2049" t="s" s="3">
         <v>4066</v>
@@ -50424,7 +50430,7 @@
         <v>6</v>
       </c>
       <c r="D2050" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2050" t="s" s="3">
         <v>4068</v>
@@ -50441,7 +50447,7 @@
         <v>6</v>
       </c>
       <c r="D2051" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2051" t="s" s="3">
         <v>4070</v>
@@ -50458,7 +50464,7 @@
         <v>6</v>
       </c>
       <c r="D2052" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2052" t="s" s="3">
         <v>4072</v>
@@ -50475,7 +50481,7 @@
         <v>6</v>
       </c>
       <c r="D2053" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2053" t="s" s="3">
         <v>4074</v>
@@ -50492,7 +50498,7 @@
         <v>6</v>
       </c>
       <c r="D2054" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2054" t="s" s="3">
         <v>4076</v>
@@ -50509,7 +50515,7 @@
         <v>6</v>
       </c>
       <c r="D2055" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2055" t="s" s="3">
         <v>4078</v>
@@ -50526,7 +50532,7 @@
         <v>6</v>
       </c>
       <c r="D2056" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2056" t="s" s="3">
         <v>4080</v>
@@ -50543,7 +50549,7 @@
         <v>6</v>
       </c>
       <c r="D2057" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2057" t="s" s="3">
         <v>4082</v>
@@ -50560,7 +50566,7 @@
         <v>6</v>
       </c>
       <c r="D2058" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2058" t="s" s="3">
         <v>4084</v>
@@ -50577,7 +50583,7 @@
         <v>6</v>
       </c>
       <c r="D2059" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2059" t="s" s="3">
         <v>4086</v>
@@ -50594,7 +50600,7 @@
         <v>6</v>
       </c>
       <c r="D2060" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2060" t="s" s="3">
         <v>4088</v>
@@ -50611,7 +50617,7 @@
         <v>6</v>
       </c>
       <c r="D2061" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2061" t="s" s="3">
         <v>4090</v>
@@ -50628,7 +50634,7 @@
         <v>6</v>
       </c>
       <c r="D2062" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2062" t="s" s="3">
         <v>4092</v>
@@ -50645,7 +50651,7 @@
         <v>6</v>
       </c>
       <c r="D2063" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2063" t="s" s="3">
         <v>4094</v>
@@ -50662,7 +50668,7 @@
         <v>6</v>
       </c>
       <c r="D2064" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2064" t="s" s="3">
         <v>4096</v>
@@ -50679,7 +50685,7 @@
         <v>6</v>
       </c>
       <c r="D2065" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2065" t="s" s="3">
         <v>4098</v>
@@ -50696,7 +50702,7 @@
         <v>6</v>
       </c>
       <c r="D2066" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2066" t="s" s="3">
         <v>4100</v>
@@ -50713,7 +50719,7 @@
         <v>6</v>
       </c>
       <c r="D2067" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2067" t="s" s="3">
         <v>4102</v>
@@ -50730,7 +50736,7 @@
         <v>6</v>
       </c>
       <c r="D2068" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2068" t="s" s="3">
         <v>4104</v>
@@ -50747,7 +50753,7 @@
         <v>6</v>
       </c>
       <c r="D2069" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2069" t="s" s="3">
         <v>4106</v>
@@ -50764,7 +50770,7 @@
         <v>6</v>
       </c>
       <c r="D2070" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2070" t="s" s="3">
         <v>4108</v>
@@ -50781,7 +50787,7 @@
         <v>6</v>
       </c>
       <c r="D2071" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2071" t="s" s="3">
         <v>4110</v>
@@ -50798,7 +50804,7 @@
         <v>6</v>
       </c>
       <c r="D2072" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2072" t="s" s="3">
         <v>4112</v>
@@ -50815,7 +50821,7 @@
         <v>6</v>
       </c>
       <c r="D2073" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2073" t="s" s="3">
         <v>4114</v>
@@ -50832,7 +50838,7 @@
         <v>6</v>
       </c>
       <c r="D2074" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2074" t="s" s="3">
         <v>4116</v>
@@ -50849,7 +50855,7 @@
         <v>6</v>
       </c>
       <c r="D2075" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2075" t="s" s="3">
         <v>4118</v>
@@ -50866,7 +50872,7 @@
         <v>6</v>
       </c>
       <c r="D2076" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2076" t="s" s="3">
         <v>4120</v>
@@ -50883,7 +50889,7 @@
         <v>6</v>
       </c>
       <c r="D2077" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2077" t="s" s="3">
         <v>4122</v>
@@ -50900,7 +50906,7 @@
         <v>6</v>
       </c>
       <c r="D2078" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2078" t="s" s="3">
         <v>4124</v>
@@ -50917,7 +50923,7 @@
         <v>6</v>
       </c>
       <c r="D2079" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2079" t="s" s="3">
         <v>4126</v>
@@ -50934,7 +50940,7 @@
         <v>6</v>
       </c>
       <c r="D2080" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2080" t="s" s="3">
         <v>4128</v>
@@ -50951,7 +50957,7 @@
         <v>6</v>
       </c>
       <c r="D2081" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2081" t="s" s="3">
         <v>4130</v>
@@ -50968,7 +50974,7 @@
         <v>6</v>
       </c>
       <c r="D2082" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2082" t="s" s="3">
         <v>4132</v>
@@ -50985,7 +50991,7 @@
         <v>6</v>
       </c>
       <c r="D2083" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2083" t="s" s="3">
         <v>4134</v>
@@ -51002,7 +51008,7 @@
         <v>6</v>
       </c>
       <c r="D2084" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2084" t="s" s="3">
         <v>4136</v>
@@ -51019,7 +51025,7 @@
         <v>6</v>
       </c>
       <c r="D2085" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2085" t="s" s="3">
         <v>4138</v>
@@ -51036,7 +51042,7 @@
         <v>6</v>
       </c>
       <c r="D2086" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2086" t="s" s="3">
         <v>4140</v>
@@ -51053,7 +51059,7 @@
         <v>6</v>
       </c>
       <c r="D2087" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2087" t="s" s="3">
         <v>4142</v>
@@ -51070,7 +51076,7 @@
         <v>6</v>
       </c>
       <c r="D2088" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2088" t="s" s="3">
         <v>4144</v>
@@ -51087,7 +51093,7 @@
         <v>6</v>
       </c>
       <c r="D2089" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2089" t="s" s="3">
         <v>4146</v>
@@ -51104,7 +51110,7 @@
         <v>6</v>
       </c>
       <c r="D2090" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2090" t="s" s="3">
         <v>4148</v>
@@ -51121,7 +51127,7 @@
         <v>6</v>
       </c>
       <c r="D2091" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2091" t="s" s="3">
         <v>4150</v>
@@ -51138,7 +51144,7 @@
         <v>6</v>
       </c>
       <c r="D2092" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2092" t="s" s="3">
         <v>4152</v>
@@ -51155,7 +51161,7 @@
         <v>6</v>
       </c>
       <c r="D2093" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2093" t="s" s="3">
         <v>4154</v>
@@ -51172,7 +51178,7 @@
         <v>6</v>
       </c>
       <c r="D2094" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2094" t="s" s="3">
         <v>4156</v>
@@ -51189,7 +51195,7 @@
         <v>6</v>
       </c>
       <c r="D2095" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2095" t="s" s="3">
         <v>4158</v>
@@ -51206,7 +51212,7 @@
         <v>6</v>
       </c>
       <c r="D2096" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2096" t="s" s="3">
         <v>4160</v>
@@ -51223,7 +51229,7 @@
         <v>6</v>
       </c>
       <c r="D2097" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2097" t="s" s="3">
         <v>4162</v>
@@ -51240,7 +51246,7 @@
         <v>6</v>
       </c>
       <c r="D2098" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2098" t="s" s="3">
         <v>4164</v>
@@ -51257,7 +51263,7 @@
         <v>6</v>
       </c>
       <c r="D2099" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2099" t="s" s="3">
         <v>4166</v>
@@ -51274,7 +51280,7 @@
         <v>6</v>
       </c>
       <c r="D2100" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2100" t="s" s="3">
         <v>4168</v>
@@ -51291,7 +51297,7 @@
         <v>6</v>
       </c>
       <c r="D2101" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2101" t="s" s="3">
         <v>4170</v>
@@ -51308,7 +51314,7 @@
         <v>6</v>
       </c>
       <c r="D2102" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2102" t="s" s="3">
         <v>4172</v>
@@ -51325,7 +51331,7 @@
         <v>6</v>
       </c>
       <c r="D2103" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2103" t="s" s="3">
         <v>4174</v>
@@ -51342,7 +51348,7 @@
         <v>6</v>
       </c>
       <c r="D2104" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2104" t="s" s="3">
         <v>4176</v>
@@ -51359,7 +51365,7 @@
         <v>6</v>
       </c>
       <c r="D2105" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2105" t="s" s="3">
         <v>4178</v>
@@ -51376,7 +51382,7 @@
         <v>6</v>
       </c>
       <c r="D2106" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2106" t="s" s="3">
         <v>4180</v>
@@ -51393,7 +51399,7 @@
         <v>6</v>
       </c>
       <c r="D2107" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2107" t="s" s="3">
         <v>4182</v>
@@ -51410,7 +51416,7 @@
         <v>6</v>
       </c>
       <c r="D2108" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2108" t="s" s="3">
         <v>4184</v>
@@ -51427,7 +51433,7 @@
         <v>6</v>
       </c>
       <c r="D2109" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2109" t="s" s="3">
         <v>4186</v>
@@ -51444,7 +51450,7 @@
         <v>6</v>
       </c>
       <c r="D2110" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2110" t="s" s="3">
         <v>4188</v>
@@ -51461,7 +51467,7 @@
         <v>6</v>
       </c>
       <c r="D2111" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2111" t="s" s="3">
         <v>4190</v>
@@ -51478,7 +51484,7 @@
         <v>6</v>
       </c>
       <c r="D2112" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2112" t="s" s="3">
         <v>4192</v>
@@ -51495,7 +51501,7 @@
         <v>6</v>
       </c>
       <c r="D2113" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2113" t="s" s="3">
         <v>4194</v>
@@ -51512,7 +51518,7 @@
         <v>6</v>
       </c>
       <c r="D2114" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2114" t="s" s="3">
         <v>4196</v>
@@ -51529,7 +51535,7 @@
         <v>6</v>
       </c>
       <c r="D2115" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2115" t="s" s="3">
         <v>4198</v>
@@ -51546,7 +51552,7 @@
         <v>6</v>
       </c>
       <c r="D2116" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2116" t="s" s="3">
         <v>4200</v>
@@ -51563,7 +51569,7 @@
         <v>6</v>
       </c>
       <c r="D2117" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2117" t="s" s="3">
         <v>4202</v>
@@ -51580,7 +51586,7 @@
         <v>6</v>
       </c>
       <c r="D2118" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2118" t="s" s="3">
         <v>4204</v>
@@ -51597,7 +51603,7 @@
         <v>6</v>
       </c>
       <c r="D2119" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2119" t="s" s="3">
         <v>4206</v>
@@ -51614,7 +51620,7 @@
         <v>6</v>
       </c>
       <c r="D2120" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2120" t="s" s="3">
         <v>4208</v>
@@ -51631,7 +51637,7 @@
         <v>6</v>
       </c>
       <c r="D2121" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2121" t="s" s="3">
         <v>4210</v>
@@ -51648,7 +51654,7 @@
         <v>6</v>
       </c>
       <c r="D2122" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2122" t="s" s="3">
         <v>4212</v>
@@ -51665,7 +51671,7 @@
         <v>6</v>
       </c>
       <c r="D2123" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2123" t="s" s="3">
         <v>4214</v>
@@ -51682,7 +51688,7 @@
         <v>6</v>
       </c>
       <c r="D2124" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2124" t="s" s="3">
         <v>4216</v>
@@ -51699,7 +51705,7 @@
         <v>6</v>
       </c>
       <c r="D2125" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2125" t="s" s="3">
         <v>4218</v>
@@ -51716,7 +51722,7 @@
         <v>6</v>
       </c>
       <c r="D2126" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2126" t="s" s="3">
         <v>4220</v>
@@ -51733,7 +51739,7 @@
         <v>6</v>
       </c>
       <c r="D2127" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2127" t="s" s="3">
         <v>4222</v>
@@ -51750,7 +51756,7 @@
         <v>6</v>
       </c>
       <c r="D2128" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2128" t="s" s="3">
         <v>4224</v>
@@ -51767,7 +51773,7 @@
         <v>6</v>
       </c>
       <c r="D2129" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2129" t="s" s="3">
         <v>4226</v>
@@ -51784,7 +51790,7 @@
         <v>6</v>
       </c>
       <c r="D2130" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2130" t="s" s="3">
         <v>4228</v>
@@ -51801,7 +51807,7 @@
         <v>6</v>
       </c>
       <c r="D2131" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2131" t="s" s="3">
         <v>4230</v>
@@ -51818,7 +51824,7 @@
         <v>6</v>
       </c>
       <c r="D2132" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2132" t="s" s="3">
         <v>4232</v>
@@ -51835,7 +51841,7 @@
         <v>6</v>
       </c>
       <c r="D2133" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2133" t="s" s="3">
         <v>4234</v>
@@ -51852,7 +51858,7 @@
         <v>6</v>
       </c>
       <c r="D2134" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2134" t="s" s="3">
         <v>4236</v>
@@ -51869,7 +51875,7 @@
         <v>6</v>
       </c>
       <c r="D2135" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2135" t="s" s="3">
         <v>4238</v>
@@ -51880,16 +51886,16 @@
         <v>2135.0</v>
       </c>
       <c r="B2136" t="s" s="3">
-        <v>1346</v>
+        <v>4239</v>
       </c>
       <c r="C2136" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2136" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2136" t="s" s="3">
-        <v>4239</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="2137" ht="36.0" customHeight="true">
@@ -51897,13 +51903,13 @@
         <v>2136.0</v>
       </c>
       <c r="B2137" t="s" s="3">
-        <v>4240</v>
+        <v>1346</v>
       </c>
       <c r="C2137" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2137" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2137" t="s" s="3">
         <v>4241</v>
@@ -51920,7 +51926,7 @@
         <v>6</v>
       </c>
       <c r="D2138" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2138" t="s" s="3">
         <v>4243</v>
@@ -51937,7 +51943,7 @@
         <v>6</v>
       </c>
       <c r="D2139" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2139" t="s" s="3">
         <v>4245</v>
@@ -51954,7 +51960,7 @@
         <v>6</v>
       </c>
       <c r="D2140" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2140" t="s" s="3">
         <v>4247</v>
@@ -51971,7 +51977,7 @@
         <v>6</v>
       </c>
       <c r="D2141" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2141" t="s" s="3">
         <v>4249</v>
@@ -51988,7 +51994,7 @@
         <v>6</v>
       </c>
       <c r="D2142" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2142" t="s" s="3">
         <v>4251</v>
@@ -52005,7 +52011,7 @@
         <v>6</v>
       </c>
       <c r="D2143" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2143" t="s" s="3">
         <v>4253</v>
@@ -52022,7 +52028,7 @@
         <v>6</v>
       </c>
       <c r="D2144" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2144" t="s" s="3">
         <v>4255</v>
@@ -52039,7 +52045,7 @@
         <v>6</v>
       </c>
       <c r="D2145" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2145" t="s" s="3">
         <v>4257</v>
@@ -52056,7 +52062,7 @@
         <v>6</v>
       </c>
       <c r="D2146" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2146" t="s" s="3">
         <v>4259</v>
@@ -52073,7 +52079,7 @@
         <v>6</v>
       </c>
       <c r="D2147" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2147" t="s" s="3">
         <v>4261</v>
@@ -52090,7 +52096,7 @@
         <v>6</v>
       </c>
       <c r="D2148" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2148" t="s" s="3">
         <v>4263</v>
@@ -52107,7 +52113,7 @@
         <v>6</v>
       </c>
       <c r="D2149" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2149" t="s" s="3">
         <v>4265</v>
@@ -52124,7 +52130,7 @@
         <v>6</v>
       </c>
       <c r="D2150" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2150" t="s" s="3">
         <v>4267</v>
@@ -52141,7 +52147,7 @@
         <v>6</v>
       </c>
       <c r="D2151" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2151" t="s" s="3">
         <v>4269</v>
@@ -52158,7 +52164,7 @@
         <v>6</v>
       </c>
       <c r="D2152" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2152" t="s" s="3">
         <v>4271</v>
@@ -52175,7 +52181,7 @@
         <v>6</v>
       </c>
       <c r="D2153" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2153" t="s" s="3">
         <v>4273</v>
@@ -52192,7 +52198,7 @@
         <v>6</v>
       </c>
       <c r="D2154" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2154" t="s" s="3">
         <v>4275</v>
@@ -52209,7 +52215,7 @@
         <v>6</v>
       </c>
       <c r="D2155" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2155" t="s" s="3">
         <v>4277</v>
@@ -52226,7 +52232,7 @@
         <v>6</v>
       </c>
       <c r="D2156" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2156" t="s" s="3">
         <v>4279</v>
@@ -52243,7 +52249,7 @@
         <v>6</v>
       </c>
       <c r="D2157" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2157" t="s" s="3">
         <v>4281</v>
@@ -52260,7 +52266,7 @@
         <v>6</v>
       </c>
       <c r="D2158" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2158" t="s" s="3">
         <v>4283</v>
@@ -52277,7 +52283,7 @@
         <v>6</v>
       </c>
       <c r="D2159" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2159" t="s" s="3">
         <v>4285</v>
@@ -52294,7 +52300,7 @@
         <v>6</v>
       </c>
       <c r="D2160" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2160" t="s" s="3">
         <v>4287</v>
@@ -52311,7 +52317,7 @@
         <v>6</v>
       </c>
       <c r="D2161" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2161" t="s" s="3">
         <v>4289</v>
@@ -52328,7 +52334,7 @@
         <v>6</v>
       </c>
       <c r="D2162" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2162" t="s" s="3">
         <v>4291</v>
@@ -52345,7 +52351,7 @@
         <v>6</v>
       </c>
       <c r="D2163" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2163" t="s" s="3">
         <v>4293</v>
@@ -52362,7 +52368,7 @@
         <v>6</v>
       </c>
       <c r="D2164" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2164" t="s" s="3">
         <v>4295</v>
@@ -52379,7 +52385,7 @@
         <v>6</v>
       </c>
       <c r="D2165" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2165" t="s" s="3">
         <v>4297</v>
@@ -52396,7 +52402,7 @@
         <v>6</v>
       </c>
       <c r="D2166" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2166" t="s" s="3">
         <v>4299</v>
@@ -52413,7 +52419,7 @@
         <v>6</v>
       </c>
       <c r="D2167" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2167" t="s" s="3">
         <v>4301</v>
@@ -52430,7 +52436,7 @@
         <v>6</v>
       </c>
       <c r="D2168" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2168" t="s" s="3">
         <v>4303</v>
@@ -52447,7 +52453,7 @@
         <v>6</v>
       </c>
       <c r="D2169" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2169" t="s" s="3">
         <v>4305</v>
@@ -52464,7 +52470,7 @@
         <v>6</v>
       </c>
       <c r="D2170" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2170" t="s" s="3">
         <v>4307</v>
@@ -52481,7 +52487,7 @@
         <v>6</v>
       </c>
       <c r="D2171" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2171" t="s" s="3">
         <v>4309</v>
@@ -52498,7 +52504,7 @@
         <v>6</v>
       </c>
       <c r="D2172" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2172" t="s" s="3">
         <v>4311</v>
@@ -52515,7 +52521,7 @@
         <v>6</v>
       </c>
       <c r="D2173" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2173" t="s" s="3">
         <v>4313</v>
@@ -52532,7 +52538,7 @@
         <v>6</v>
       </c>
       <c r="D2174" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2174" t="s" s="3">
         <v>4315</v>
@@ -52549,7 +52555,7 @@
         <v>6</v>
       </c>
       <c r="D2175" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2175" t="s" s="3">
         <v>4317</v>
@@ -52566,7 +52572,7 @@
         <v>6</v>
       </c>
       <c r="D2176" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2176" t="s" s="3">
         <v>4319</v>
@@ -52580,10 +52586,10 @@
         <v>4320</v>
       </c>
       <c r="C2177" t="s" s="2">
-        <v>733</v>
+        <v>6</v>
       </c>
       <c r="D2177" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2177" t="s" s="3">
         <v>4321</v>
@@ -52600,7 +52606,7 @@
         <v>733</v>
       </c>
       <c r="D2178" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2178" t="s" s="3">
         <v>4323</v>
@@ -52617,7 +52623,7 @@
         <v>733</v>
       </c>
       <c r="D2179" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2179" t="s" s="3">
         <v>4325</v>
@@ -52634,7 +52640,7 @@
         <v>733</v>
       </c>
       <c r="D2180" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2180" t="s" s="3">
         <v>4327</v>
@@ -52651,7 +52657,7 @@
         <v>733</v>
       </c>
       <c r="D2181" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2181" t="s" s="3">
         <v>4329</v>
@@ -52668,7 +52674,7 @@
         <v>733</v>
       </c>
       <c r="D2182" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2182" t="s" s="3">
         <v>4331</v>
@@ -52685,7 +52691,7 @@
         <v>733</v>
       </c>
       <c r="D2183" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2183" t="s" s="3">
         <v>4333</v>
@@ -52702,7 +52708,7 @@
         <v>733</v>
       </c>
       <c r="D2184" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2184" t="s" s="3">
         <v>4335</v>
@@ -52719,7 +52725,7 @@
         <v>733</v>
       </c>
       <c r="D2185" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2185" t="s" s="3">
         <v>4337</v>
@@ -52736,7 +52742,7 @@
         <v>733</v>
       </c>
       <c r="D2186" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2186" t="s" s="3">
         <v>4339</v>
@@ -52753,7 +52759,7 @@
         <v>733</v>
       </c>
       <c r="D2187" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2187" t="s" s="3">
         <v>4341</v>
@@ -52770,7 +52776,7 @@
         <v>733</v>
       </c>
       <c r="D2188" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2188" t="s" s="3">
         <v>4343</v>
@@ -52787,7 +52793,7 @@
         <v>733</v>
       </c>
       <c r="D2189" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2189" t="s" s="3">
         <v>4345</v>
@@ -52804,7 +52810,7 @@
         <v>733</v>
       </c>
       <c r="D2190" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2190" t="s" s="3">
         <v>4347</v>
@@ -52821,7 +52827,7 @@
         <v>733</v>
       </c>
       <c r="D2191" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2191" t="s" s="3">
         <v>4349</v>
@@ -52838,7 +52844,7 @@
         <v>733</v>
       </c>
       <c r="D2192" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2192" t="s" s="3">
         <v>4351</v>
@@ -52855,7 +52861,7 @@
         <v>733</v>
       </c>
       <c r="D2193" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2193" t="s" s="3">
         <v>4353</v>
@@ -52872,7 +52878,7 @@
         <v>733</v>
       </c>
       <c r="D2194" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2194" t="s" s="3">
         <v>4355</v>
@@ -52889,10 +52895,10 @@
         <v>733</v>
       </c>
       <c r="D2195" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2195" t="s" s="3">
-        <v>4255</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="2196" ht="36.0" customHeight="true">
@@ -52900,16 +52906,16 @@
         <v>2195.0</v>
       </c>
       <c r="B2196" t="s" s="3">
-        <v>4357</v>
+        <v>4358</v>
       </c>
       <c r="C2196" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D2196" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2196" t="s" s="3">
-        <v>4358</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="2197" ht="36.0" customHeight="true">
@@ -52923,7 +52929,7 @@
         <v>733</v>
       </c>
       <c r="D2197" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2197" t="s" s="3">
         <v>4360</v>
@@ -52940,7 +52946,7 @@
         <v>733</v>
       </c>
       <c r="D2198" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2198" t="s" s="3">
         <v>4362</v>
@@ -52957,7 +52963,7 @@
         <v>733</v>
       </c>
       <c r="D2199" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2199" t="s" s="3">
         <v>4364</v>
@@ -52974,7 +52980,7 @@
         <v>733</v>
       </c>
       <c r="D2200" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2200" t="s" s="3">
         <v>4366</v>
@@ -52991,7 +52997,7 @@
         <v>733</v>
       </c>
       <c r="D2201" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2201" t="s" s="3">
         <v>4368</v>
@@ -53008,7 +53014,7 @@
         <v>733</v>
       </c>
       <c r="D2202" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2202" t="s" s="3">
         <v>4370</v>
@@ -53025,7 +53031,7 @@
         <v>733</v>
       </c>
       <c r="D2203" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2203" t="s" s="3">
         <v>4372</v>
@@ -53042,7 +53048,7 @@
         <v>733</v>
       </c>
       <c r="D2204" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2204" t="s" s="3">
         <v>4374</v>
@@ -53059,7 +53065,7 @@
         <v>733</v>
       </c>
       <c r="D2205" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2205" t="s" s="3">
         <v>4376</v>
@@ -53076,7 +53082,7 @@
         <v>733</v>
       </c>
       <c r="D2206" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2206" t="s" s="3">
         <v>4378</v>
@@ -53093,7 +53099,7 @@
         <v>733</v>
       </c>
       <c r="D2207" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2207" t="s" s="3">
         <v>4380</v>
@@ -53110,7 +53116,7 @@
         <v>733</v>
       </c>
       <c r="D2208" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2208" t="s" s="3">
         <v>4382</v>
@@ -53127,7 +53133,7 @@
         <v>733</v>
       </c>
       <c r="D2209" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2209" t="s" s="3">
         <v>4384</v>
@@ -53144,7 +53150,7 @@
         <v>733</v>
       </c>
       <c r="D2210" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2210" t="s" s="3">
         <v>4386</v>
@@ -53161,7 +53167,7 @@
         <v>733</v>
       </c>
       <c r="D2211" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2211" t="s" s="3">
         <v>4388</v>
@@ -53178,7 +53184,7 @@
         <v>733</v>
       </c>
       <c r="D2212" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2212" t="s" s="3">
         <v>4390</v>
@@ -53195,7 +53201,7 @@
         <v>733</v>
       </c>
       <c r="D2213" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2213" t="s" s="3">
         <v>4392</v>
@@ -53212,7 +53218,7 @@
         <v>733</v>
       </c>
       <c r="D2214" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2214" t="s" s="3">
         <v>4394</v>
@@ -53229,7 +53235,7 @@
         <v>733</v>
       </c>
       <c r="D2215" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2215" t="s" s="3">
         <v>4396</v>
@@ -53246,7 +53252,7 @@
         <v>733</v>
       </c>
       <c r="D2216" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2216" t="s" s="3">
         <v>4398</v>
@@ -53263,7 +53269,7 @@
         <v>733</v>
       </c>
       <c r="D2217" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2217" t="s" s="3">
         <v>4400</v>
@@ -53280,7 +53286,7 @@
         <v>733</v>
       </c>
       <c r="D2218" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2218" t="s" s="3">
         <v>4402</v>
@@ -53297,7 +53303,7 @@
         <v>733</v>
       </c>
       <c r="D2219" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2219" t="s" s="3">
         <v>4404</v>
@@ -53314,7 +53320,7 @@
         <v>733</v>
       </c>
       <c r="D2220" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2220" t="s" s="3">
         <v>4406</v>
@@ -53331,7 +53337,7 @@
         <v>733</v>
       </c>
       <c r="D2221" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2221" t="s" s="3">
         <v>4408</v>
@@ -53348,7 +53354,7 @@
         <v>733</v>
       </c>
       <c r="D2222" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2222" t="s" s="3">
         <v>4410</v>
@@ -53365,7 +53371,7 @@
         <v>733</v>
       </c>
       <c r="D2223" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2223" t="s" s="3">
         <v>4412</v>
@@ -53382,7 +53388,7 @@
         <v>733</v>
       </c>
       <c r="D2224" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2224" t="s" s="3">
         <v>4414</v>
@@ -53399,7 +53405,7 @@
         <v>733</v>
       </c>
       <c r="D2225" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2225" t="s" s="3">
         <v>4416</v>
@@ -53416,7 +53422,7 @@
         <v>733</v>
       </c>
       <c r="D2226" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2226" t="s" s="3">
         <v>4418</v>
@@ -53433,7 +53439,7 @@
         <v>733</v>
       </c>
       <c r="D2227" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2227" t="s" s="3">
         <v>4420</v>
@@ -53450,7 +53456,7 @@
         <v>733</v>
       </c>
       <c r="D2228" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2228" t="s" s="3">
         <v>4422</v>
@@ -53467,7 +53473,7 @@
         <v>733</v>
       </c>
       <c r="D2229" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2229" t="s" s="3">
         <v>4424</v>
@@ -53484,7 +53490,7 @@
         <v>733</v>
       </c>
       <c r="D2230" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2230" t="s" s="3">
         <v>4426</v>
@@ -53501,7 +53507,7 @@
         <v>733</v>
       </c>
       <c r="D2231" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2231" t="s" s="3">
         <v>4428</v>
@@ -53518,7 +53524,7 @@
         <v>733</v>
       </c>
       <c r="D2232" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2232" t="s" s="3">
         <v>4430</v>
@@ -53535,7 +53541,7 @@
         <v>733</v>
       </c>
       <c r="D2233" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2233" t="s" s="3">
         <v>4432</v>
@@ -53552,7 +53558,7 @@
         <v>733</v>
       </c>
       <c r="D2234" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2234" t="s" s="3">
         <v>4434</v>
@@ -53569,7 +53575,7 @@
         <v>733</v>
       </c>
       <c r="D2235" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2235" t="s" s="3">
         <v>4436</v>
@@ -53586,7 +53592,7 @@
         <v>733</v>
       </c>
       <c r="D2236" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2236" t="s" s="3">
         <v>4438</v>
@@ -53603,7 +53609,7 @@
         <v>733</v>
       </c>
       <c r="D2237" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2237" t="s" s="3">
         <v>4440</v>
@@ -53620,7 +53626,7 @@
         <v>733</v>
       </c>
       <c r="D2238" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2238" t="s" s="3">
         <v>4442</v>
@@ -53637,7 +53643,7 @@
         <v>733</v>
       </c>
       <c r="D2239" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2239" t="s" s="3">
         <v>4444</v>
@@ -53654,7 +53660,7 @@
         <v>733</v>
       </c>
       <c r="D2240" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2240" t="s" s="3">
         <v>4446</v>
@@ -53671,7 +53677,7 @@
         <v>733</v>
       </c>
       <c r="D2241" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2241" t="s" s="3">
         <v>4448</v>
@@ -53688,7 +53694,7 @@
         <v>733</v>
       </c>
       <c r="D2242" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2242" t="s" s="3">
         <v>4450</v>
@@ -53705,7 +53711,7 @@
         <v>733</v>
       </c>
       <c r="D2243" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2243" t="s" s="3">
         <v>4452</v>
@@ -53722,7 +53728,7 @@
         <v>733</v>
       </c>
       <c r="D2244" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2244" t="s" s="3">
         <v>4454</v>
@@ -53739,7 +53745,7 @@
         <v>733</v>
       </c>
       <c r="D2245" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2245" t="s" s="3">
         <v>4456</v>
@@ -53756,7 +53762,7 @@
         <v>733</v>
       </c>
       <c r="D2246" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2246" t="s" s="3">
         <v>4458</v>
@@ -53770,10 +53776,10 @@
         <v>4459</v>
       </c>
       <c r="C2247" t="s" s="2">
-        <v>938</v>
+        <v>733</v>
       </c>
       <c r="D2247" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2247" t="s" s="3">
         <v>4460</v>
@@ -53790,7 +53796,7 @@
         <v>938</v>
       </c>
       <c r="D2248" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2248" t="s" s="3">
         <v>4462</v>
@@ -53807,7 +53813,7 @@
         <v>938</v>
       </c>
       <c r="D2249" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2249" t="s" s="3">
         <v>4464</v>
@@ -53824,7 +53830,7 @@
         <v>938</v>
       </c>
       <c r="D2250" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2250" t="s" s="3">
         <v>4466</v>
@@ -53841,7 +53847,7 @@
         <v>938</v>
       </c>
       <c r="D2251" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2251" t="s" s="3">
         <v>4468</v>
@@ -53858,7 +53864,7 @@
         <v>938</v>
       </c>
       <c r="D2252" t="s" s="2">
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="E2252" t="s" s="3">
         <v>4470</v>
@@ -53872,13 +53878,13 @@
         <v>4471</v>
       </c>
       <c r="C2253" t="s" s="2">
-        <v>6</v>
+        <v>938</v>
       </c>
       <c r="D2253" t="s" s="2">
+        <v>4043</v>
+      </c>
+      <c r="E2253" t="s" s="3">
         <v>4472</v>
-      </c>
-      <c r="E2253" t="s" s="3">
-        <v>4473</v>
       </c>
     </row>
     <row r="2254" ht="36.0" customHeight="true">
@@ -53886,13 +53892,13 @@
         <v>2253.0</v>
       </c>
       <c r="B2254" t="s" s="3">
+        <v>4473</v>
+      </c>
+      <c r="C2254" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2254" t="s" s="2">
         <v>4474</v>
-      </c>
-      <c r="C2254" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2254" t="s" s="2">
-        <v>4472</v>
       </c>
       <c r="E2254" t="s" s="3">
         <v>4475</v>
@@ -53909,7 +53915,7 @@
         <v>6</v>
       </c>
       <c r="D2255" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2255" t="s" s="3">
         <v>4477</v>
@@ -53926,7 +53932,7 @@
         <v>6</v>
       </c>
       <c r="D2256" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2256" t="s" s="3">
         <v>4479</v>
@@ -53943,7 +53949,7 @@
         <v>6</v>
       </c>
       <c r="D2257" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2257" t="s" s="3">
         <v>4481</v>
@@ -53960,7 +53966,7 @@
         <v>6</v>
       </c>
       <c r="D2258" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2258" t="s" s="3">
         <v>4483</v>
@@ -53977,7 +53983,7 @@
         <v>6</v>
       </c>
       <c r="D2259" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2259" t="s" s="3">
         <v>4485</v>
@@ -53994,7 +54000,7 @@
         <v>6</v>
       </c>
       <c r="D2260" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2260" t="s" s="3">
         <v>4487</v>
@@ -54011,7 +54017,7 @@
         <v>6</v>
       </c>
       <c r="D2261" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2261" t="s" s="3">
         <v>4489</v>
@@ -54028,7 +54034,7 @@
         <v>6</v>
       </c>
       <c r="D2262" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2262" t="s" s="3">
         <v>4491</v>
@@ -54045,7 +54051,7 @@
         <v>6</v>
       </c>
       <c r="D2263" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2263" t="s" s="3">
         <v>4493</v>
@@ -54062,7 +54068,7 @@
         <v>6</v>
       </c>
       <c r="D2264" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2264" t="s" s="3">
         <v>4495</v>
@@ -54079,7 +54085,7 @@
         <v>6</v>
       </c>
       <c r="D2265" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2265" t="s" s="3">
         <v>4497</v>
@@ -54096,7 +54102,7 @@
         <v>6</v>
       </c>
       <c r="D2266" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2266" t="s" s="3">
         <v>4499</v>
@@ -54113,7 +54119,7 @@
         <v>6</v>
       </c>
       <c r="D2267" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2267" t="s" s="3">
         <v>4501</v>
@@ -54130,7 +54136,7 @@
         <v>6</v>
       </c>
       <c r="D2268" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2268" t="s" s="3">
         <v>4503</v>
@@ -54147,7 +54153,7 @@
         <v>6</v>
       </c>
       <c r="D2269" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2269" t="s" s="3">
         <v>4505</v>
@@ -54164,7 +54170,7 @@
         <v>6</v>
       </c>
       <c r="D2270" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2270" t="s" s="3">
         <v>4507</v>
@@ -54181,7 +54187,7 @@
         <v>6</v>
       </c>
       <c r="D2271" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2271" t="s" s="3">
         <v>4509</v>
@@ -54198,7 +54204,7 @@
         <v>6</v>
       </c>
       <c r="D2272" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2272" t="s" s="3">
         <v>4511</v>
@@ -54215,7 +54221,7 @@
         <v>6</v>
       </c>
       <c r="D2273" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2273" t="s" s="3">
         <v>4513</v>
@@ -54232,7 +54238,7 @@
         <v>6</v>
       </c>
       <c r="D2274" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2274" t="s" s="3">
         <v>4515</v>
@@ -54249,7 +54255,7 @@
         <v>6</v>
       </c>
       <c r="D2275" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2275" t="s" s="3">
         <v>4517</v>
@@ -54266,7 +54272,7 @@
         <v>6</v>
       </c>
       <c r="D2276" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2276" t="s" s="3">
         <v>4519</v>
@@ -54283,7 +54289,7 @@
         <v>6</v>
       </c>
       <c r="D2277" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2277" t="s" s="3">
         <v>4521</v>
@@ -54300,7 +54306,7 @@
         <v>6</v>
       </c>
       <c r="D2278" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2278" t="s" s="3">
         <v>4523</v>
@@ -54317,7 +54323,7 @@
         <v>6</v>
       </c>
       <c r="D2279" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2279" t="s" s="3">
         <v>4525</v>
@@ -54334,7 +54340,7 @@
         <v>6</v>
       </c>
       <c r="D2280" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2280" t="s" s="3">
         <v>4527</v>
@@ -54351,7 +54357,7 @@
         <v>6</v>
       </c>
       <c r="D2281" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2281" t="s" s="3">
         <v>4529</v>
@@ -54368,7 +54374,7 @@
         <v>6</v>
       </c>
       <c r="D2282" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2282" t="s" s="3">
         <v>4531</v>
@@ -54385,7 +54391,7 @@
         <v>6</v>
       </c>
       <c r="D2283" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2283" t="s" s="3">
         <v>4533</v>
@@ -54402,7 +54408,7 @@
         <v>6</v>
       </c>
       <c r="D2284" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2284" t="s" s="3">
         <v>4535</v>
@@ -54419,7 +54425,7 @@
         <v>6</v>
       </c>
       <c r="D2285" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2285" t="s" s="3">
         <v>4537</v>
@@ -54436,7 +54442,7 @@
         <v>6</v>
       </c>
       <c r="D2286" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2286" t="s" s="3">
         <v>4539</v>
@@ -54453,7 +54459,7 @@
         <v>6</v>
       </c>
       <c r="D2287" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2287" t="s" s="3">
         <v>4541</v>
@@ -54470,7 +54476,7 @@
         <v>6</v>
       </c>
       <c r="D2288" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2288" t="s" s="3">
         <v>4543</v>
@@ -54487,7 +54493,7 @@
         <v>6</v>
       </c>
       <c r="D2289" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2289" t="s" s="3">
         <v>4545</v>
@@ -54504,7 +54510,7 @@
         <v>6</v>
       </c>
       <c r="D2290" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2290" t="s" s="3">
         <v>4547</v>
@@ -54521,7 +54527,7 @@
         <v>6</v>
       </c>
       <c r="D2291" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2291" t="s" s="3">
         <v>4549</v>
@@ -54538,7 +54544,7 @@
         <v>6</v>
       </c>
       <c r="D2292" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2292" t="s" s="3">
         <v>4551</v>
@@ -54555,7 +54561,7 @@
         <v>6</v>
       </c>
       <c r="D2293" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2293" t="s" s="3">
         <v>4553</v>
@@ -54572,7 +54578,7 @@
         <v>6</v>
       </c>
       <c r="D2294" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2294" t="s" s="3">
         <v>4555</v>
@@ -54589,7 +54595,7 @@
         <v>6</v>
       </c>
       <c r="D2295" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2295" t="s" s="3">
         <v>4557</v>
@@ -54606,7 +54612,7 @@
         <v>6</v>
       </c>
       <c r="D2296" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2296" t="s" s="3">
         <v>4559</v>
@@ -54623,7 +54629,7 @@
         <v>6</v>
       </c>
       <c r="D2297" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2297" t="s" s="3">
         <v>4561</v>
@@ -54640,7 +54646,7 @@
         <v>6</v>
       </c>
       <c r="D2298" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2298" t="s" s="3">
         <v>4563</v>
@@ -54657,7 +54663,7 @@
         <v>6</v>
       </c>
       <c r="D2299" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2299" t="s" s="3">
         <v>4565</v>
@@ -54674,7 +54680,7 @@
         <v>6</v>
       </c>
       <c r="D2300" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2300" t="s" s="3">
         <v>4567</v>
@@ -54691,7 +54697,7 @@
         <v>6</v>
       </c>
       <c r="D2301" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2301" t="s" s="3">
         <v>4569</v>
@@ -54708,7 +54714,7 @@
         <v>6</v>
       </c>
       <c r="D2302" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2302" t="s" s="3">
         <v>4571</v>
@@ -54725,7 +54731,7 @@
         <v>6</v>
       </c>
       <c r="D2303" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2303" t="s" s="3">
         <v>4573</v>
@@ -54742,7 +54748,7 @@
         <v>6</v>
       </c>
       <c r="D2304" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2304" t="s" s="3">
         <v>4575</v>
@@ -54759,7 +54765,7 @@
         <v>6</v>
       </c>
       <c r="D2305" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2305" t="s" s="3">
         <v>4577</v>
@@ -54776,7 +54782,7 @@
         <v>6</v>
       </c>
       <c r="D2306" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2306" t="s" s="3">
         <v>4579</v>
@@ -54793,7 +54799,7 @@
         <v>6</v>
       </c>
       <c r="D2307" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2307" t="s" s="3">
         <v>4581</v>
@@ -54810,7 +54816,7 @@
         <v>6</v>
       </c>
       <c r="D2308" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2308" t="s" s="3">
         <v>4583</v>
@@ -54824,10 +54830,10 @@
         <v>4584</v>
       </c>
       <c r="C2309" t="s" s="2">
-        <v>733</v>
+        <v>6</v>
       </c>
       <c r="D2309" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2309" t="s" s="3">
         <v>4585</v>
@@ -54844,7 +54850,7 @@
         <v>733</v>
       </c>
       <c r="D2310" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2310" t="s" s="3">
         <v>4587</v>
@@ -54861,7 +54867,7 @@
         <v>733</v>
       </c>
       <c r="D2311" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2311" t="s" s="3">
         <v>4589</v>
@@ -54878,7 +54884,7 @@
         <v>733</v>
       </c>
       <c r="D2312" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2312" t="s" s="3">
         <v>4591</v>
@@ -54895,7 +54901,7 @@
         <v>733</v>
       </c>
       <c r="D2313" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2313" t="s" s="3">
         <v>4593</v>
@@ -54912,7 +54918,7 @@
         <v>733</v>
       </c>
       <c r="D2314" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2314" t="s" s="3">
         <v>4595</v>
@@ -54929,7 +54935,7 @@
         <v>733</v>
       </c>
       <c r="D2315" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2315" t="s" s="3">
         <v>4597</v>
@@ -54946,7 +54952,7 @@
         <v>733</v>
       </c>
       <c r="D2316" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2316" t="s" s="3">
         <v>4599</v>
@@ -54963,7 +54969,7 @@
         <v>733</v>
       </c>
       <c r="D2317" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2317" t="s" s="3">
         <v>4601</v>
@@ -54980,7 +54986,7 @@
         <v>733</v>
       </c>
       <c r="D2318" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2318" t="s" s="3">
         <v>4603</v>
@@ -54997,7 +55003,7 @@
         <v>733</v>
       </c>
       <c r="D2319" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2319" t="s" s="3">
         <v>4605</v>
@@ -55014,7 +55020,7 @@
         <v>733</v>
       </c>
       <c r="D2320" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2320" t="s" s="3">
         <v>4607</v>
@@ -55031,7 +55037,7 @@
         <v>733</v>
       </c>
       <c r="D2321" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2321" t="s" s="3">
         <v>4609</v>
@@ -55048,7 +55054,7 @@
         <v>733</v>
       </c>
       <c r="D2322" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2322" t="s" s="3">
         <v>4611</v>
@@ -55065,7 +55071,7 @@
         <v>733</v>
       </c>
       <c r="D2323" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2323" t="s" s="3">
         <v>4613</v>
@@ -55082,7 +55088,7 @@
         <v>733</v>
       </c>
       <c r="D2324" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2324" t="s" s="3">
         <v>4615</v>
@@ -55099,7 +55105,7 @@
         <v>733</v>
       </c>
       <c r="D2325" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2325" t="s" s="3">
         <v>4617</v>
@@ -55116,7 +55122,7 @@
         <v>733</v>
       </c>
       <c r="D2326" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2326" t="s" s="3">
         <v>4619</v>
@@ -55133,7 +55139,7 @@
         <v>733</v>
       </c>
       <c r="D2327" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2327" t="s" s="3">
         <v>4621</v>
@@ -55150,7 +55156,7 @@
         <v>733</v>
       </c>
       <c r="D2328" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2328" t="s" s="3">
         <v>4623</v>
@@ -55167,7 +55173,7 @@
         <v>733</v>
       </c>
       <c r="D2329" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2329" t="s" s="3">
         <v>4625</v>
@@ -55184,7 +55190,7 @@
         <v>733</v>
       </c>
       <c r="D2330" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2330" t="s" s="3">
         <v>4627</v>
@@ -55201,7 +55207,7 @@
         <v>733</v>
       </c>
       <c r="D2331" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2331" t="s" s="3">
         <v>4629</v>
@@ -55218,7 +55224,7 @@
         <v>733</v>
       </c>
       <c r="D2332" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2332" t="s" s="3">
         <v>4631</v>
@@ -55235,7 +55241,7 @@
         <v>733</v>
       </c>
       <c r="D2333" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2333" t="s" s="3">
         <v>4633</v>
@@ -55252,7 +55258,7 @@
         <v>733</v>
       </c>
       <c r="D2334" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2334" t="s" s="3">
         <v>4635</v>
@@ -55269,7 +55275,7 @@
         <v>733</v>
       </c>
       <c r="D2335" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2335" t="s" s="3">
         <v>4637</v>
@@ -55286,7 +55292,7 @@
         <v>733</v>
       </c>
       <c r="D2336" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2336" t="s" s="3">
         <v>4639</v>
@@ -55303,7 +55309,7 @@
         <v>733</v>
       </c>
       <c r="D2337" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2337" t="s" s="3">
         <v>4641</v>
@@ -55320,7 +55326,7 @@
         <v>733</v>
       </c>
       <c r="D2338" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2338" t="s" s="3">
         <v>4643</v>
@@ -55337,7 +55343,7 @@
         <v>733</v>
       </c>
       <c r="D2339" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2339" t="s" s="3">
         <v>4645</v>
@@ -55354,7 +55360,7 @@
         <v>733</v>
       </c>
       <c r="D2340" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2340" t="s" s="3">
         <v>4647</v>
@@ -55371,7 +55377,7 @@
         <v>733</v>
       </c>
       <c r="D2341" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2341" t="s" s="3">
         <v>4649</v>
@@ -55388,7 +55394,7 @@
         <v>733</v>
       </c>
       <c r="D2342" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2342" t="s" s="3">
         <v>4651</v>
@@ -55405,7 +55411,7 @@
         <v>733</v>
       </c>
       <c r="D2343" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2343" t="s" s="3">
         <v>4653</v>
@@ -55422,7 +55428,7 @@
         <v>733</v>
       </c>
       <c r="D2344" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2344" t="s" s="3">
         <v>4655</v>
@@ -55439,7 +55445,7 @@
         <v>733</v>
       </c>
       <c r="D2345" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2345" t="s" s="3">
         <v>4657</v>
@@ -55456,7 +55462,7 @@
         <v>733</v>
       </c>
       <c r="D2346" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2346" t="s" s="3">
         <v>4659</v>
@@ -55470,10 +55476,10 @@
         <v>4660</v>
       </c>
       <c r="C2347" t="s" s="2">
-        <v>938</v>
+        <v>733</v>
       </c>
       <c r="D2347" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2347" t="s" s="3">
         <v>4661</v>
@@ -55490,7 +55496,7 @@
         <v>938</v>
       </c>
       <c r="D2348" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2348" t="s" s="3">
         <v>4663</v>
@@ -55507,7 +55513,7 @@
         <v>938</v>
       </c>
       <c r="D2349" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2349" t="s" s="3">
         <v>4665</v>
@@ -55524,7 +55530,7 @@
         <v>938</v>
       </c>
       <c r="D2350" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2350" t="s" s="3">
         <v>4667</v>
@@ -55541,7 +55547,7 @@
         <v>938</v>
       </c>
       <c r="D2351" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2351" t="s" s="3">
         <v>4669</v>
@@ -55558,7 +55564,7 @@
         <v>938</v>
       </c>
       <c r="D2352" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2352" t="s" s="3">
         <v>4671</v>
@@ -55575,7 +55581,7 @@
         <v>938</v>
       </c>
       <c r="D2353" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2353" t="s" s="3">
         <v>4673</v>
@@ -55592,7 +55598,7 @@
         <v>938</v>
       </c>
       <c r="D2354" t="s" s="2">
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="E2354" t="s" s="3">
         <v>4675</v>
@@ -55606,13 +55612,13 @@
         <v>4676</v>
       </c>
       <c r="C2355" t="s" s="2">
-        <v>6</v>
+        <v>938</v>
       </c>
       <c r="D2355" t="s" s="2">
+        <v>4474</v>
+      </c>
+      <c r="E2355" t="s" s="3">
         <v>4677</v>
-      </c>
-      <c r="E2355" t="s" s="3">
-        <v>4678</v>
       </c>
     </row>
     <row r="2356" ht="36.0" customHeight="true">
@@ -55620,13 +55626,13 @@
         <v>2355.0</v>
       </c>
       <c r="B2356" t="s" s="3">
+        <v>4678</v>
+      </c>
+      <c r="C2356" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2356" t="s" s="2">
         <v>4679</v>
-      </c>
-      <c r="C2356" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2356" t="s" s="2">
-        <v>4677</v>
       </c>
       <c r="E2356" t="s" s="3">
         <v>4680</v>
@@ -55643,7 +55649,7 @@
         <v>6</v>
       </c>
       <c r="D2357" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2357" t="s" s="3">
         <v>4682</v>
@@ -55660,7 +55666,7 @@
         <v>6</v>
       </c>
       <c r="D2358" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2358" t="s" s="3">
         <v>4684</v>
@@ -55677,7 +55683,7 @@
         <v>6</v>
       </c>
       <c r="D2359" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2359" t="s" s="3">
         <v>4686</v>
@@ -55694,7 +55700,7 @@
         <v>6</v>
       </c>
       <c r="D2360" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2360" t="s" s="3">
         <v>4688</v>
@@ -55711,7 +55717,7 @@
         <v>6</v>
       </c>
       <c r="D2361" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2361" t="s" s="3">
         <v>4690</v>
@@ -55728,7 +55734,7 @@
         <v>6</v>
       </c>
       <c r="D2362" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2362" t="s" s="3">
         <v>4692</v>
@@ -55745,7 +55751,7 @@
         <v>6</v>
       </c>
       <c r="D2363" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2363" t="s" s="3">
         <v>4694</v>
@@ -55762,7 +55768,7 @@
         <v>6</v>
       </c>
       <c r="D2364" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2364" t="s" s="3">
         <v>4696</v>
@@ -55779,7 +55785,7 @@
         <v>6</v>
       </c>
       <c r="D2365" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2365" t="s" s="3">
         <v>4698</v>
@@ -55796,7 +55802,7 @@
         <v>6</v>
       </c>
       <c r="D2366" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2366" t="s" s="3">
         <v>4700</v>
@@ -55813,7 +55819,7 @@
         <v>6</v>
       </c>
       <c r="D2367" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2367" t="s" s="3">
         <v>4702</v>
@@ -55830,7 +55836,7 @@
         <v>6</v>
       </c>
       <c r="D2368" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2368" t="s" s="3">
         <v>4704</v>
@@ -55847,7 +55853,7 @@
         <v>6</v>
       </c>
       <c r="D2369" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2369" t="s" s="3">
         <v>4706</v>
@@ -55864,7 +55870,7 @@
         <v>6</v>
       </c>
       <c r="D2370" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2370" t="s" s="3">
         <v>4708</v>
@@ -55881,7 +55887,7 @@
         <v>6</v>
       </c>
       <c r="D2371" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2371" t="s" s="3">
         <v>4710</v>
@@ -55898,7 +55904,7 @@
         <v>6</v>
       </c>
       <c r="D2372" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2372" t="s" s="3">
         <v>4712</v>
@@ -55915,7 +55921,7 @@
         <v>6</v>
       </c>
       <c r="D2373" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2373" t="s" s="3">
         <v>4714</v>
@@ -55932,7 +55938,7 @@
         <v>6</v>
       </c>
       <c r="D2374" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2374" t="s" s="3">
         <v>4716</v>
@@ -55949,7 +55955,7 @@
         <v>6</v>
       </c>
       <c r="D2375" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2375" t="s" s="3">
         <v>4718</v>
@@ -55966,7 +55972,7 @@
         <v>6</v>
       </c>
       <c r="D2376" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2376" t="s" s="3">
         <v>4720</v>
@@ -55983,7 +55989,7 @@
         <v>6</v>
       </c>
       <c r="D2377" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2377" t="s" s="3">
         <v>4722</v>
@@ -56000,7 +56006,7 @@
         <v>6</v>
       </c>
       <c r="D2378" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2378" t="s" s="3">
         <v>4724</v>
@@ -56017,7 +56023,7 @@
         <v>6</v>
       </c>
       <c r="D2379" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2379" t="s" s="3">
         <v>4726</v>
@@ -56034,7 +56040,7 @@
         <v>6</v>
       </c>
       <c r="D2380" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2380" t="s" s="3">
         <v>4728</v>
@@ -56051,7 +56057,7 @@
         <v>6</v>
       </c>
       <c r="D2381" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2381" t="s" s="3">
         <v>4730</v>
@@ -56068,7 +56074,7 @@
         <v>6</v>
       </c>
       <c r="D2382" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2382" t="s" s="3">
         <v>4732</v>
@@ -56085,7 +56091,7 @@
         <v>6</v>
       </c>
       <c r="D2383" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2383" t="s" s="3">
         <v>4734</v>
@@ -56102,7 +56108,7 @@
         <v>6</v>
       </c>
       <c r="D2384" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2384" t="s" s="3">
         <v>4736</v>
@@ -56119,7 +56125,7 @@
         <v>6</v>
       </c>
       <c r="D2385" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2385" t="s" s="3">
         <v>4738</v>
@@ -56136,7 +56142,7 @@
         <v>6</v>
       </c>
       <c r="D2386" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2386" t="s" s="3">
         <v>4740</v>
@@ -56153,7 +56159,7 @@
         <v>6</v>
       </c>
       <c r="D2387" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2387" t="s" s="3">
         <v>4742</v>
@@ -56170,7 +56176,7 @@
         <v>6</v>
       </c>
       <c r="D2388" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2388" t="s" s="3">
         <v>4744</v>
@@ -56187,7 +56193,7 @@
         <v>6</v>
       </c>
       <c r="D2389" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2389" t="s" s="3">
         <v>4746</v>
@@ -56204,7 +56210,7 @@
         <v>6</v>
       </c>
       <c r="D2390" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2390" t="s" s="3">
         <v>4748</v>
@@ -56221,7 +56227,7 @@
         <v>6</v>
       </c>
       <c r="D2391" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2391" t="s" s="3">
         <v>4750</v>
@@ -56238,7 +56244,7 @@
         <v>6</v>
       </c>
       <c r="D2392" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2392" t="s" s="3">
         <v>4752</v>
@@ -56255,7 +56261,7 @@
         <v>6</v>
       </c>
       <c r="D2393" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2393" t="s" s="3">
         <v>4754</v>
@@ -56272,7 +56278,7 @@
         <v>6</v>
       </c>
       <c r="D2394" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2394" t="s" s="3">
         <v>4756</v>
@@ -56289,7 +56295,7 @@
         <v>6</v>
       </c>
       <c r="D2395" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2395" t="s" s="3">
         <v>4758</v>
@@ -56306,7 +56312,7 @@
         <v>6</v>
       </c>
       <c r="D2396" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2396" t="s" s="3">
         <v>4760</v>
@@ -56323,7 +56329,7 @@
         <v>6</v>
       </c>
       <c r="D2397" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2397" t="s" s="3">
         <v>4762</v>
@@ -56340,7 +56346,7 @@
         <v>6</v>
       </c>
       <c r="D2398" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2398" t="s" s="3">
         <v>4764</v>
@@ -56357,7 +56363,7 @@
         <v>6</v>
       </c>
       <c r="D2399" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2399" t="s" s="3">
         <v>4766</v>
@@ -56374,7 +56380,7 @@
         <v>6</v>
       </c>
       <c r="D2400" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2400" t="s" s="3">
         <v>4768</v>
@@ -56391,7 +56397,7 @@
         <v>6</v>
       </c>
       <c r="D2401" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2401" t="s" s="3">
         <v>4770</v>
@@ -56408,7 +56414,7 @@
         <v>6</v>
       </c>
       <c r="D2402" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2402" t="s" s="3">
         <v>4772</v>
@@ -56425,7 +56431,7 @@
         <v>6</v>
       </c>
       <c r="D2403" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2403" t="s" s="3">
         <v>4774</v>
@@ -56442,7 +56448,7 @@
         <v>6</v>
       </c>
       <c r="D2404" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2404" t="s" s="3">
         <v>4776</v>
@@ -56459,7 +56465,7 @@
         <v>6</v>
       </c>
       <c r="D2405" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2405" t="s" s="3">
         <v>4778</v>
@@ -56476,7 +56482,7 @@
         <v>6</v>
       </c>
       <c r="D2406" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2406" t="s" s="3">
         <v>4780</v>
@@ -56493,7 +56499,7 @@
         <v>6</v>
       </c>
       <c r="D2407" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2407" t="s" s="3">
         <v>4782</v>
@@ -56510,7 +56516,7 @@
         <v>6</v>
       </c>
       <c r="D2408" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2408" t="s" s="3">
         <v>4784</v>
@@ -56527,7 +56533,7 @@
         <v>6</v>
       </c>
       <c r="D2409" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2409" t="s" s="3">
         <v>4786</v>
@@ -56544,7 +56550,7 @@
         <v>6</v>
       </c>
       <c r="D2410" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2410" t="s" s="3">
         <v>4788</v>
@@ -56561,7 +56567,7 @@
         <v>6</v>
       </c>
       <c r="D2411" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2411" t="s" s="3">
         <v>4790</v>
@@ -56578,7 +56584,7 @@
         <v>6</v>
       </c>
       <c r="D2412" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2412" t="s" s="3">
         <v>4792</v>
@@ -56595,7 +56601,7 @@
         <v>6</v>
       </c>
       <c r="D2413" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2413" t="s" s="3">
         <v>4794</v>
@@ -56612,7 +56618,7 @@
         <v>6</v>
       </c>
       <c r="D2414" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2414" t="s" s="3">
         <v>4796</v>
@@ -56629,7 +56635,7 @@
         <v>6</v>
       </c>
       <c r="D2415" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2415" t="s" s="3">
         <v>4798</v>
@@ -56646,7 +56652,7 @@
         <v>6</v>
       </c>
       <c r="D2416" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2416" t="s" s="3">
         <v>4800</v>
@@ -56663,7 +56669,7 @@
         <v>6</v>
       </c>
       <c r="D2417" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2417" t="s" s="3">
         <v>4802</v>
@@ -56680,7 +56686,7 @@
         <v>6</v>
       </c>
       <c r="D2418" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2418" t="s" s="3">
         <v>4804</v>
@@ -56697,7 +56703,7 @@
         <v>6</v>
       </c>
       <c r="D2419" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2419" t="s" s="3">
         <v>4806</v>
@@ -56714,7 +56720,7 @@
         <v>6</v>
       </c>
       <c r="D2420" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2420" t="s" s="3">
         <v>4808</v>
@@ -56731,7 +56737,7 @@
         <v>6</v>
       </c>
       <c r="D2421" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2421" t="s" s="3">
         <v>4810</v>
@@ -56748,10 +56754,10 @@
         <v>6</v>
       </c>
       <c r="D2422" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2422" t="s" s="3">
-        <v>4784</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="2423" ht="36.0" customHeight="true">
@@ -56759,16 +56765,16 @@
         <v>2422.0</v>
       </c>
       <c r="B2423" t="s" s="3">
-        <v>4812</v>
+        <v>4813</v>
       </c>
       <c r="C2423" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2423" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2423" t="s" s="3">
-        <v>4813</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="2424" ht="36.0" customHeight="true">
@@ -56782,7 +56788,7 @@
         <v>6</v>
       </c>
       <c r="D2424" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2424" t="s" s="3">
         <v>4815</v>
@@ -56799,7 +56805,7 @@
         <v>6</v>
       </c>
       <c r="D2425" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2425" t="s" s="3">
         <v>4817</v>
@@ -56816,7 +56822,7 @@
         <v>6</v>
       </c>
       <c r="D2426" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2426" t="s" s="3">
         <v>4819</v>
@@ -56833,7 +56839,7 @@
         <v>6</v>
       </c>
       <c r="D2427" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2427" t="s" s="3">
         <v>4821</v>
@@ -56850,7 +56856,7 @@
         <v>6</v>
       </c>
       <c r="D2428" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2428" t="s" s="3">
         <v>4823</v>
@@ -56867,10 +56873,10 @@
         <v>6</v>
       </c>
       <c r="D2429" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2429" t="s" s="3">
-        <v>4746</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="2430" ht="36.0" customHeight="true">
@@ -56878,16 +56884,16 @@
         <v>2429.0</v>
       </c>
       <c r="B2430" t="s" s="3">
-        <v>3853</v>
+        <v>4826</v>
       </c>
       <c r="C2430" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2430" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2430" t="s" s="3">
-        <v>4825</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="2431" ht="36.0" customHeight="true">
@@ -56895,16 +56901,16 @@
         <v>2430.0</v>
       </c>
       <c r="B2431" t="s" s="3">
-        <v>4826</v>
+        <v>3855</v>
       </c>
       <c r="C2431" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2431" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2431" t="s" s="3">
-        <v>4784</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="2432" ht="36.0" customHeight="true">
@@ -56912,16 +56918,16 @@
         <v>2431.0</v>
       </c>
       <c r="B2432" t="s" s="3">
-        <v>4827</v>
+        <v>4828</v>
       </c>
       <c r="C2432" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2432" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2432" t="s" s="3">
-        <v>4828</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="2433" ht="36.0" customHeight="true">
@@ -56935,7 +56941,7 @@
         <v>6</v>
       </c>
       <c r="D2433" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2433" t="s" s="3">
         <v>4830</v>
@@ -56952,7 +56958,7 @@
         <v>6</v>
       </c>
       <c r="D2434" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2434" t="s" s="3">
         <v>4832</v>
@@ -56969,7 +56975,7 @@
         <v>6</v>
       </c>
       <c r="D2435" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2435" t="s" s="3">
         <v>4834</v>
@@ -56986,7 +56992,7 @@
         <v>6</v>
       </c>
       <c r="D2436" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2436" t="s" s="3">
         <v>4836</v>
@@ -57003,7 +57009,7 @@
         <v>6</v>
       </c>
       <c r="D2437" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2437" t="s" s="3">
         <v>4838</v>
@@ -57020,7 +57026,7 @@
         <v>6</v>
       </c>
       <c r="D2438" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2438" t="s" s="3">
         <v>4840</v>
@@ -57037,7 +57043,7 @@
         <v>6</v>
       </c>
       <c r="D2439" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2439" t="s" s="3">
         <v>4842</v>
@@ -57054,7 +57060,7 @@
         <v>6</v>
       </c>
       <c r="D2440" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2440" t="s" s="3">
         <v>4844</v>
@@ -57071,7 +57077,7 @@
         <v>6</v>
       </c>
       <c r="D2441" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2441" t="s" s="3">
         <v>4846</v>
@@ -57088,7 +57094,7 @@
         <v>6</v>
       </c>
       <c r="D2442" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2442" t="s" s="3">
         <v>4848</v>
@@ -57105,7 +57111,7 @@
         <v>6</v>
       </c>
       <c r="D2443" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2443" t="s" s="3">
         <v>4850</v>
@@ -57122,7 +57128,7 @@
         <v>6</v>
       </c>
       <c r="D2444" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2444" t="s" s="3">
         <v>4852</v>
@@ -57139,7 +57145,7 @@
         <v>6</v>
       </c>
       <c r="D2445" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2445" t="s" s="3">
         <v>4854</v>
@@ -57156,7 +57162,7 @@
         <v>6</v>
       </c>
       <c r="D2446" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2446" t="s" s="3">
         <v>4856</v>
@@ -57173,7 +57179,7 @@
         <v>6</v>
       </c>
       <c r="D2447" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2447" t="s" s="3">
         <v>4858</v>
@@ -57190,7 +57196,7 @@
         <v>6</v>
       </c>
       <c r="D2448" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2448" t="s" s="3">
         <v>4860</v>
@@ -57207,7 +57213,7 @@
         <v>6</v>
       </c>
       <c r="D2449" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2449" t="s" s="3">
         <v>4862</v>
@@ -57224,7 +57230,7 @@
         <v>6</v>
       </c>
       <c r="D2450" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2450" t="s" s="3">
         <v>4864</v>
@@ -57241,7 +57247,7 @@
         <v>6</v>
       </c>
       <c r="D2451" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2451" t="s" s="3">
         <v>4866</v>
@@ -57258,7 +57264,7 @@
         <v>6</v>
       </c>
       <c r="D2452" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2452" t="s" s="3">
         <v>4868</v>
@@ -57275,7 +57281,7 @@
         <v>6</v>
       </c>
       <c r="D2453" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2453" t="s" s="3">
         <v>4870</v>
@@ -57292,7 +57298,7 @@
         <v>6</v>
       </c>
       <c r="D2454" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2454" t="s" s="3">
         <v>4872</v>
@@ -57309,7 +57315,7 @@
         <v>6</v>
       </c>
       <c r="D2455" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2455" t="s" s="3">
         <v>4874</v>
@@ -57326,7 +57332,7 @@
         <v>6</v>
       </c>
       <c r="D2456" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2456" t="s" s="3">
         <v>4876</v>
@@ -57343,7 +57349,7 @@
         <v>6</v>
       </c>
       <c r="D2457" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2457" t="s" s="3">
         <v>4878</v>
@@ -57360,7 +57366,7 @@
         <v>6</v>
       </c>
       <c r="D2458" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2458" t="s" s="3">
         <v>4880</v>
@@ -57377,7 +57383,7 @@
         <v>6</v>
       </c>
       <c r="D2459" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2459" t="s" s="3">
         <v>4882</v>
@@ -57394,7 +57400,7 @@
         <v>6</v>
       </c>
       <c r="D2460" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2460" t="s" s="3">
         <v>4884</v>
@@ -57411,7 +57417,7 @@
         <v>6</v>
       </c>
       <c r="D2461" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2461" t="s" s="3">
         <v>4886</v>
@@ -57428,7 +57434,7 @@
         <v>6</v>
       </c>
       <c r="D2462" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2462" t="s" s="3">
         <v>4888</v>
@@ -57445,7 +57451,7 @@
         <v>6</v>
       </c>
       <c r="D2463" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2463" t="s" s="3">
         <v>4890</v>
@@ -57462,7 +57468,7 @@
         <v>6</v>
       </c>
       <c r="D2464" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2464" t="s" s="3">
         <v>4892</v>
@@ -57479,7 +57485,7 @@
         <v>6</v>
       </c>
       <c r="D2465" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2465" t="s" s="3">
         <v>4894</v>
@@ -57496,7 +57502,7 @@
         <v>6</v>
       </c>
       <c r="D2466" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2466" t="s" s="3">
         <v>4896</v>
@@ -57513,7 +57519,7 @@
         <v>6</v>
       </c>
       <c r="D2467" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2467" t="s" s="3">
         <v>4898</v>
@@ -57530,7 +57536,7 @@
         <v>6</v>
       </c>
       <c r="D2468" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2468" t="s" s="3">
         <v>4900</v>
@@ -57547,7 +57553,7 @@
         <v>6</v>
       </c>
       <c r="D2469" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2469" t="s" s="3">
         <v>4902</v>
@@ -57564,7 +57570,7 @@
         <v>6</v>
       </c>
       <c r="D2470" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2470" t="s" s="3">
         <v>4904</v>
@@ -57581,7 +57587,7 @@
         <v>6</v>
       </c>
       <c r="D2471" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2471" t="s" s="3">
         <v>4906</v>
@@ -57598,7 +57604,7 @@
         <v>6</v>
       </c>
       <c r="D2472" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2472" t="s" s="3">
         <v>4908</v>
@@ -57615,7 +57621,7 @@
         <v>6</v>
       </c>
       <c r="D2473" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2473" t="s" s="3">
         <v>4910</v>
@@ -57632,7 +57638,7 @@
         <v>6</v>
       </c>
       <c r="D2474" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2474" t="s" s="3">
         <v>4912</v>
@@ -57649,7 +57655,7 @@
         <v>6</v>
       </c>
       <c r="D2475" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2475" t="s" s="3">
         <v>4914</v>
@@ -57666,7 +57672,7 @@
         <v>6</v>
       </c>
       <c r="D2476" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2476" t="s" s="3">
         <v>4916</v>
@@ -57683,7 +57689,7 @@
         <v>6</v>
       </c>
       <c r="D2477" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2477" t="s" s="3">
         <v>4918</v>
@@ -57700,7 +57706,7 @@
         <v>6</v>
       </c>
       <c r="D2478" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2478" t="s" s="3">
         <v>4920</v>
@@ -57711,16 +57717,16 @@
         <v>2478.0</v>
       </c>
       <c r="B2479" t="s" s="3">
-        <v>3170</v>
+        <v>4921</v>
       </c>
       <c r="C2479" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2479" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2479" t="s" s="3">
-        <v>4921</v>
+        <v>4922</v>
       </c>
     </row>
     <row r="2480" ht="36.0" customHeight="true">
@@ -57728,13 +57734,13 @@
         <v>2479.0</v>
       </c>
       <c r="B2480" t="s" s="3">
-        <v>4922</v>
+        <v>3170</v>
       </c>
       <c r="C2480" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2480" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2480" t="s" s="3">
         <v>4923</v>
@@ -57751,7 +57757,7 @@
         <v>6</v>
       </c>
       <c r="D2481" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2481" t="s" s="3">
         <v>4925</v>
@@ -57768,10 +57774,10 @@
         <v>6</v>
       </c>
       <c r="D2482" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2482" t="s" s="3">
-        <v>4788</v>
+        <v>4927</v>
       </c>
     </row>
     <row r="2483" ht="36.0" customHeight="true">
@@ -57779,16 +57785,16 @@
         <v>2482.0</v>
       </c>
       <c r="B2483" t="s" s="3">
-        <v>4927</v>
+        <v>4928</v>
       </c>
       <c r="C2483" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D2483" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2483" t="s" s="3">
-        <v>4928</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="2484" ht="36.0" customHeight="true">
@@ -57802,7 +57808,7 @@
         <v>6</v>
       </c>
       <c r="D2484" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2484" t="s" s="3">
         <v>4930</v>
@@ -57819,7 +57825,7 @@
         <v>6</v>
       </c>
       <c r="D2485" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2485" t="s" s="3">
         <v>4932</v>
@@ -57836,7 +57842,7 @@
         <v>6</v>
       </c>
       <c r="D2486" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2486" t="s" s="3">
         <v>4934</v>
@@ -57853,7 +57859,7 @@
         <v>6</v>
       </c>
       <c r="D2487" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2487" t="s" s="3">
         <v>4936</v>
@@ -57870,7 +57876,7 @@
         <v>6</v>
       </c>
       <c r="D2488" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2488" t="s" s="3">
         <v>4938</v>
@@ -57884,10 +57890,10 @@
         <v>4939</v>
       </c>
       <c r="C2489" t="s" s="2">
-        <v>733</v>
+        <v>6</v>
       </c>
       <c r="D2489" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2489" t="s" s="3">
         <v>4940</v>
@@ -57904,7 +57910,7 @@
         <v>733</v>
       </c>
       <c r="D2490" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2490" t="s" s="3">
         <v>4942</v>
@@ -57921,7 +57927,7 @@
         <v>733</v>
       </c>
       <c r="D2491" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2491" t="s" s="3">
         <v>4944</v>
@@ -57938,7 +57944,7 @@
         <v>733</v>
       </c>
       <c r="D2492" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2492" t="s" s="3">
         <v>4946</v>
@@ -57955,7 +57961,7 @@
         <v>733</v>
       </c>
       <c r="D2493" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2493" t="s" s="3">
         <v>4948</v>
@@ -57972,7 +57978,7 @@
         <v>733</v>
       </c>
       <c r="D2494" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2494" t="s" s="3">
         <v>4950</v>
@@ -57989,7 +57995,7 @@
         <v>733</v>
       </c>
       <c r="D2495" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2495" t="s" s="3">
         <v>4952</v>
@@ -58006,7 +58012,7 @@
         <v>733</v>
       </c>
       <c r="D2496" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2496" t="s" s="3">
         <v>4954</v>
@@ -58023,7 +58029,7 @@
         <v>733</v>
       </c>
       <c r="D2497" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2497" t="s" s="3">
         <v>4956</v>
@@ -58040,7 +58046,7 @@
         <v>733</v>
       </c>
       <c r="D2498" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2498" t="s" s="3">
         <v>4958</v>
@@ -58057,7 +58063,7 @@
         <v>733</v>
       </c>
       <c r="D2499" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2499" t="s" s="3">
         <v>4960</v>
@@ -58074,7 +58080,7 @@
         <v>733</v>
       </c>
       <c r="D2500" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2500" t="s" s="3">
         <v>4962</v>
@@ -58091,7 +58097,7 @@
         <v>733</v>
       </c>
       <c r="D2501" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2501" t="s" s="3">
         <v>4964</v>
@@ -58108,7 +58114,7 @@
         <v>733</v>
       </c>
       <c r="D2502" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2502" t="s" s="3">
         <v>4966</v>
@@ -58125,7 +58131,7 @@
         <v>733</v>
       </c>
       <c r="D2503" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2503" t="s" s="3">
         <v>4968</v>
@@ -58142,7 +58148,7 @@
         <v>733</v>
       </c>
       <c r="D2504" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2504" t="s" s="3">
         <v>4970</v>
@@ -58159,7 +58165,7 @@
         <v>733</v>
       </c>
       <c r="D2505" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2505" t="s" s="3">
         <v>4972</v>
@@ -58176,7 +58182,7 @@
         <v>733</v>
       </c>
       <c r="D2506" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2506" t="s" s="3">
         <v>4974</v>
@@ -58193,7 +58199,7 @@
         <v>733</v>
       </c>
       <c r="D2507" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2507" t="s" s="3">
         <v>4976</v>
@@ -58210,7 +58216,7 @@
         <v>733</v>
       </c>
       <c r="D2508" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2508" t="s" s="3">
         <v>4978</v>
@@ -58227,7 +58233,7 @@
         <v>733</v>
       </c>
       <c r="D2509" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2509" t="s" s="3">
         <v>4980</v>
@@ -58244,7 +58250,7 @@
         <v>733</v>
       </c>
       <c r="D2510" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2510" t="s" s="3">
         <v>4982</v>
@@ -58261,7 +58267,7 @@
         <v>733</v>
       </c>
       <c r="D2511" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2511" t="s" s="3">
         <v>4984</v>
@@ -58278,7 +58284,7 @@
         <v>733</v>
       </c>
       <c r="D2512" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2512" t="s" s="3">
         <v>4986</v>
@@ -58295,7 +58301,7 @@
         <v>733</v>
       </c>
       <c r="D2513" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2513" t="s" s="3">
         <v>4988</v>
@@ -58312,7 +58318,7 @@
         <v>733</v>
       </c>
       <c r="D2514" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2514" t="s" s="3">
         <v>4990</v>
@@ -58329,7 +58335,7 @@
         <v>733</v>
       </c>
       <c r="D2515" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2515" t="s" s="3">
         <v>4992</v>
@@ -58346,7 +58352,7 @@
         <v>733</v>
       </c>
       <c r="D2516" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2516" t="s" s="3">
         <v>4994</v>
@@ -58363,7 +58369,7 @@
         <v>733</v>
       </c>
       <c r="D2517" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2517" t="s" s="3">
         <v>4996</v>
@@ -58380,7 +58386,7 @@
         <v>733</v>
       </c>
       <c r="D2518" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2518" t="s" s="3">
         <v>4998</v>
@@ -58397,7 +58403,7 @@
         <v>733</v>
       </c>
       <c r="D2519" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2519" t="s" s="3">
         <v>5000</v>
@@ -58414,7 +58420,7 @@
         <v>733</v>
       </c>
       <c r="D2520" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2520" t="s" s="3">
         <v>5002</v>
@@ -58431,7 +58437,7 @@
         <v>733</v>
       </c>
       <c r="D2521" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2521" t="s" s="3">
         <v>5004</v>
@@ -58448,7 +58454,7 @@
         <v>733</v>
       </c>
       <c r="D2522" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2522" t="s" s="3">
         <v>5006</v>
@@ -58465,7 +58471,7 @@
         <v>733</v>
       </c>
       <c r="D2523" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2523" t="s" s="3">
         <v>5008</v>
@@ -58482,7 +58488,7 @@
         <v>733</v>
       </c>
       <c r="D2524" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2524" t="s" s="3">
         <v>5010</v>
@@ -58499,7 +58505,7 @@
         <v>733</v>
       </c>
       <c r="D2525" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2525" t="s" s="3">
         <v>5012</v>
@@ -58516,7 +58522,7 @@
         <v>733</v>
       </c>
       <c r="D2526" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2526" t="s" s="3">
         <v>5014</v>
@@ -58533,7 +58539,7 @@
         <v>733</v>
       </c>
       <c r="D2527" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2527" t="s" s="3">
         <v>5016</v>
@@ -58550,7 +58556,7 @@
         <v>733</v>
       </c>
       <c r="D2528" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2528" t="s" s="3">
         <v>5018</v>
@@ -58567,7 +58573,7 @@
         <v>733</v>
       </c>
       <c r="D2529" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2529" t="s" s="3">
         <v>5020</v>
@@ -58584,7 +58590,7 @@
         <v>733</v>
       </c>
       <c r="D2530" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2530" t="s" s="3">
         <v>5022</v>
@@ -58601,10 +58607,10 @@
         <v>733</v>
       </c>
       <c r="D2531" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2531" t="s" s="3">
-        <v>4726</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="2532" ht="36.0" customHeight="true">
@@ -58612,16 +58618,16 @@
         <v>2531.0</v>
       </c>
       <c r="B2532" t="s" s="3">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="C2532" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D2532" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2532" t="s" s="3">
-        <v>5025</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="2533" ht="36.0" customHeight="true">
@@ -58635,7 +58641,7 @@
         <v>733</v>
       </c>
       <c r="D2533" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2533" t="s" s="3">
         <v>5027</v>
@@ -58652,7 +58658,7 @@
         <v>733</v>
       </c>
       <c r="D2534" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2534" t="s" s="3">
         <v>5029</v>
@@ -58669,7 +58675,7 @@
         <v>733</v>
       </c>
       <c r="D2535" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2535" t="s" s="3">
         <v>5031</v>
@@ -58686,7 +58692,7 @@
         <v>733</v>
       </c>
       <c r="D2536" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2536" t="s" s="3">
         <v>5033</v>
@@ -58703,7 +58709,7 @@
         <v>733</v>
       </c>
       <c r="D2537" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2537" t="s" s="3">
         <v>5035</v>
@@ -58720,7 +58726,7 @@
         <v>733</v>
       </c>
       <c r="D2538" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2538" t="s" s="3">
         <v>5037</v>
@@ -58734,10 +58740,10 @@
         <v>5038</v>
       </c>
       <c r="C2539" t="s" s="2">
-        <v>938</v>
+        <v>733</v>
       </c>
       <c r="D2539" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2539" t="s" s="3">
         <v>5039</v>
@@ -58754,7 +58760,7 @@
         <v>938</v>
       </c>
       <c r="D2540" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2540" t="s" s="3">
         <v>5041</v>
@@ -58765,16 +58771,16 @@
         <v>2540.0</v>
       </c>
       <c r="B2541" t="s" s="3">
-        <v>5019</v>
+        <v>5042</v>
       </c>
       <c r="C2541" t="s" s="2">
         <v>938</v>
       </c>
       <c r="D2541" t="s" s="2">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="E2541" t="s" s="3">
-        <v>5042</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="2542" ht="36.0" customHeight="true">
@@ -58782,16 +58788,16 @@
         <v>2541.0</v>
       </c>
       <c r="B2542" t="s" s="3">
-        <v>5043</v>
+        <v>5021</v>
       </c>
       <c r="C2542" t="s" s="2">
-        <v>6</v>
+        <v>938</v>
       </c>
       <c r="D2542" t="s" s="2">
+        <v>4679</v>
+      </c>
+      <c r="E2542" t="s" s="3">
         <v>5044</v>
-      </c>
-      <c r="E2542" t="s" s="3">
-        <v>5045</v>
       </c>
     </row>
     <row r="2543" ht="36.0" customHeight="true">
@@ -58799,13 +58805,13 @@
         <v>2542.0</v>
       </c>
       <c r="B2543" t="s" s="3">
+        <v>5045</v>
+      </c>
+      <c r="C2543" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D2543" t="s" s="2">
         <v>5046</v>
-      </c>
-      <c r="C2543" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2543" t="s" s="2">
-        <v>5044</v>
       </c>
       <c r="E2543" t="s" s="3">
         <v>5047</v>
@@ -58822,7 +58828,7 @@
         <v>6</v>
       </c>
       <c r="D2544" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2544" t="s" s="3">
         <v>5049</v>
@@ -58839,7 +58845,7 @@
         <v>6</v>
       </c>
       <c r="D2545" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2545" t="s" s="3">
         <v>5051</v>
@@ -58856,7 +58862,7 @@
         <v>6</v>
       </c>
       <c r="D2546" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2546" t="s" s="3">
         <v>5053</v>
@@ -58873,7 +58879,7 @@
         <v>6</v>
       </c>
       <c r="D2547" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2547" t="s" s="3">
         <v>5055</v>
@@ -58890,7 +58896,7 @@
         <v>6</v>
       </c>
       <c r="D2548" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2548" t="s" s="3">
         <v>5057</v>
@@ -58907,7 +58913,7 @@
         <v>6</v>
       </c>
       <c r="D2549" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2549" t="s" s="3">
         <v>5059</v>
@@ -58924,7 +58930,7 @@
         <v>6</v>
       </c>
       <c r="D2550" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2550" t="s" s="3">
         <v>5061</v>
@@ -58941,7 +58947,7 @@
         <v>6</v>
       </c>
       <c r="D2551" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2551" t="s" s="3">
         <v>5063</v>
@@ -58958,7 +58964,7 @@
         <v>6</v>
       </c>
       <c r="D2552" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2552" t="s" s="3">
         <v>5065</v>
@@ -58975,7 +58981,7 @@
         <v>6</v>
       </c>
       <c r="D2553" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2553" t="s" s="3">
         <v>5067</v>
@@ -58992,7 +58998,7 @@
         <v>6</v>
       </c>
       <c r="D2554" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2554" t="s" s="3">
         <v>5069</v>
@@ -59009,7 +59015,7 @@
         <v>6</v>
       </c>
       <c r="D2555" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2555" t="s" s="3">
         <v>5071</v>
@@ -59026,7 +59032,7 @@
         <v>6</v>
       </c>
       <c r="D2556" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2556" t="s" s="3">
         <v>5073</v>
@@ -59043,7 +59049,7 @@
         <v>6</v>
       </c>
       <c r="D2557" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2557" t="s" s="3">
         <v>5075</v>
@@ -59060,7 +59066,7 @@
         <v>6</v>
       </c>
       <c r="D2558" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2558" t="s" s="3">
         <v>5077</v>
@@ -59077,7 +59083,7 @@
         <v>6</v>
       </c>
       <c r="D2559" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2559" t="s" s="3">
         <v>5079</v>
@@ -59094,7 +59100,7 @@
         <v>6</v>
       </c>
       <c r="D2560" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2560" t="s" s="3">
         <v>5081</v>
@@ -59111,7 +59117,7 @@
         <v>6</v>
       </c>
       <c r="D2561" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2561" t="s" s="3">
         <v>5083</v>
@@ -59128,7 +59134,7 @@
         <v>6</v>
       </c>
       <c r="D2562" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2562" t="s" s="3">
         <v>5085</v>
@@ -59145,7 +59151,7 @@
         <v>6</v>
       </c>
       <c r="D2563" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2563" t="s" s="3">
         <v>5087</v>
@@ -59162,7 +59168,7 @@
         <v>6</v>
       </c>
       <c r="D2564" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2564" t="s" s="3">
         <v>5089</v>
@@ -59179,7 +59185,7 @@
         <v>6</v>
       </c>
       <c r="D2565" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2565" t="s" s="3">
         <v>5091</v>
@@ -59196,7 +59202,7 @@
         <v>6</v>
       </c>
       <c r="D2566" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2566" t="s" s="3">
         <v>5093</v>
@@ -59213,7 +59219,7 @@
         <v>6</v>
       </c>
       <c r="D2567" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2567" t="s" s="3">
         <v>5095</v>
@@ -59230,7 +59236,7 @@
         <v>6</v>
       </c>
       <c r="D2568" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2568" t="s" s="3">
         <v>5097</v>
@@ -59247,7 +59253,7 @@
         <v>6</v>
       </c>
       <c r="D2569" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2569" t="s" s="3">
         <v>5099</v>
@@ -59264,7 +59270,7 @@
         <v>6</v>
       </c>
       <c r="D2570" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2570" t="s" s="3">
         <v>5101</v>
@@ -59281,7 +59287,7 @@
         <v>6</v>
       </c>
       <c r="D2571" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2571" t="s" s="3">
         <v>5103</v>
@@ -59298,7 +59304,7 @@
         <v>6</v>
       </c>
       <c r="D2572" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2572" t="s" s="3">
         <v>5105</v>
@@ -59315,7 +59321,7 @@
         <v>6</v>
       </c>
       <c r="D2573" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2573" t="s" s="3">
         <v>5107</v>
@@ -59332,7 +59338,7 @@
         <v>6</v>
       </c>
       <c r="D2574" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2574" t="s" s="3">
         <v>5109</v>
@@ -59349,7 +59355,7 @@
         <v>6</v>
       </c>
       <c r="D2575" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2575" t="s" s="3">
         <v>5111</v>
@@ -59366,7 +59372,7 @@
         <v>6</v>
       </c>
       <c r="D2576" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2576" t="s" s="3">
         <v>5113</v>
@@ -59380,13 +59386,13 @@
         <v>5114</v>
       </c>
       <c r="C2577" t="s" s="2">
-        <v>733</v>
+        <v>6</v>
       </c>
       <c r="D2577" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2577" t="s" s="3">
-        <v>5089</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="2578" ht="36.0" customHeight="true">
@@ -59394,16 +59400,16 @@
         <v>2577.0</v>
       </c>
       <c r="B2578" t="s" s="3">
-        <v>5115</v>
+        <v>5116</v>
       </c>
       <c r="C2578" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D2578" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2578" t="s" s="3">
-        <v>5116</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="2579" ht="36.0" customHeight="true">
@@ -59417,7 +59423,7 @@
         <v>733</v>
       </c>
       <c r="D2579" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2579" t="s" s="3">
         <v>5118</v>
@@ -59434,7 +59440,7 @@
         <v>733</v>
       </c>
       <c r="D2580" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2580" t="s" s="3">
         <v>5120</v>
@@ -59451,7 +59457,7 @@
         <v>733</v>
       </c>
       <c r="D2581" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2581" t="s" s="3">
         <v>5122</v>
@@ -59468,7 +59474,7 @@
         <v>733</v>
       </c>
       <c r="D2582" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2582" t="s" s="3">
         <v>5124</v>
@@ -59479,16 +59485,16 @@
         <v>2582.0</v>
       </c>
       <c r="B2583" t="s" s="3">
-        <v>5050</v>
+        <v>5125</v>
       </c>
       <c r="C2583" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D2583" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2583" t="s" s="3">
-        <v>5125</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="2584" ht="36.0" customHeight="true">
@@ -59496,13 +59502,13 @@
         <v>2583.0</v>
       </c>
       <c r="B2584" t="s" s="3">
-        <v>5126</v>
+        <v>5052</v>
       </c>
       <c r="C2584" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D2584" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2584" t="s" s="3">
         <v>5127</v>
@@ -59519,7 +59525,7 @@
         <v>733</v>
       </c>
       <c r="D2585" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2585" t="s" s="3">
         <v>5129</v>
@@ -59536,7 +59542,7 @@
         <v>733</v>
       </c>
       <c r="D2586" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2586" t="s" s="3">
         <v>5131</v>
@@ -59553,7 +59559,7 @@
         <v>733</v>
       </c>
       <c r="D2587" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2587" t="s" s="3">
         <v>5133</v>
@@ -59570,7 +59576,7 @@
         <v>733</v>
       </c>
       <c r="D2588" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2588" t="s" s="3">
         <v>5135</v>
@@ -59587,7 +59593,7 @@
         <v>733</v>
       </c>
       <c r="D2589" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2589" t="s" s="3">
         <v>5137</v>
@@ -59604,7 +59610,7 @@
         <v>733</v>
       </c>
       <c r="D2590" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2590" t="s" s="3">
         <v>5139</v>
@@ -59621,7 +59627,7 @@
         <v>733</v>
       </c>
       <c r="D2591" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2591" t="s" s="3">
         <v>5141</v>
@@ -59638,7 +59644,7 @@
         <v>733</v>
       </c>
       <c r="D2592" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2592" t="s" s="3">
         <v>5143</v>
@@ -59655,7 +59661,7 @@
         <v>733</v>
       </c>
       <c r="D2593" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2593" t="s" s="3">
         <v>5145</v>
@@ -59672,7 +59678,7 @@
         <v>733</v>
       </c>
       <c r="D2594" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2594" t="s" s="3">
         <v>5147</v>
@@ -59689,7 +59695,7 @@
         <v>733</v>
       </c>
       <c r="D2595" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2595" t="s" s="3">
         <v>5149</v>
@@ -59706,7 +59712,7 @@
         <v>733</v>
       </c>
       <c r="D2596" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2596" t="s" s="3">
         <v>5151</v>
@@ -59723,7 +59729,7 @@
         <v>733</v>
       </c>
       <c r="D2597" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2597" t="s" s="3">
         <v>5153</v>
@@ -59740,10 +59746,27 @@
         <v>733</v>
       </c>
       <c r="D2598" t="s" s="2">
-        <v>5044</v>
+        <v>5046</v>
       </c>
       <c r="E2598" t="s" s="3">
         <v>5155</v>
+      </c>
+    </row>
+    <row r="2599" ht="36.0" customHeight="true">
+      <c r="A2599" t="n" s="2">
+        <v>2598.0</v>
+      </c>
+      <c r="B2599" t="s" s="3">
+        <v>5156</v>
+      </c>
+      <c r="C2599" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="D2599" t="s" s="2">
+        <v>5046</v>
+      </c>
+      <c r="E2599" t="s" s="3">
+        <v>5157</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10453" uniqueCount="5186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10457" uniqueCount="5189">
   <si>
     <t>연번</t>
   </si>
@@ -3164,12 +3164,12 @@
     <t>전남광주통합특별시 화순군 도곡면 덕리길 10-5(1층)</t>
   </si>
   <si>
+    <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
+  </si>
+  <si>
     <t>전남광주통합특별시 서구 상무시민로 136(수성빌딩 1층 치평동)</t>
   </si>
   <si>
-    <t>전남광주통합특별시 동구 동명로14번길 19-8(2층 동명동)</t>
-  </si>
-  <si>
     <t>쉘터커피로스터스</t>
   </si>
   <si>
@@ -3917,12 +3917,12 @@
     <t>스트럿</t>
   </si>
   <si>
+    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
+  </si>
+  <si>
     <t>부산광역시 부산진구 동성로39번길 28(1층 전포동)</t>
   </si>
   <si>
-    <t>부산광역시 해운대구 달맞이길62번길 6-8(1층 중동)</t>
-  </si>
-  <si>
     <t>시랑</t>
   </si>
   <si>
@@ -4697,12 +4697,6 @@
     <t>대구광역시 수성구 무학로21길 78(1층 두산동)</t>
   </si>
   <si>
-    <t>정가네 생고기</t>
-  </si>
-  <si>
-    <t>대구광역시 동구 안심로90길 12(1층 괴전동)</t>
-  </si>
-  <si>
     <t>정제(미식가의부엌)</t>
   </si>
   <si>
@@ -10544,6 +10538,12 @@
     <t>경기도 이천시 가좌로1번길 266(1,2층 장록동)</t>
   </si>
   <si>
+    <t>카페동네</t>
+  </si>
+  <si>
+    <t>경기도 부천시 원미구 부천로66번길 67(심곡동, 1층, 2층)</t>
+  </si>
+  <si>
     <t>카페로아1</t>
   </si>
   <si>
@@ -11237,12 +11237,6 @@
     <t>충청남도 태안군 태안읍 그절미길 2-99(1동 1층)</t>
   </si>
   <si>
-    <t>8하치</t>
-  </si>
-  <si>
-    <t>충청남도 아산시 온화로83번길 16-5(1동 101호 온천동)</t>
-  </si>
-  <si>
     <t>Inshore(인쇼어)</t>
   </si>
   <si>
@@ -11639,6 +11633,12 @@
     <t>충청남도 당진시 송악읍 송악로 660-1(1층 우측호)</t>
   </si>
   <si>
+    <t>어뮤즈퍼피</t>
+  </si>
+  <si>
+    <t>충청남도 천안시 서북구 1공단2길 5(1동 1층 성정동)</t>
+  </si>
+  <si>
     <t>에브리댕</t>
   </si>
   <si>
@@ -14699,12 +14699,6 @@
     <t>강원특별자치도 춘천시 금강로62번길 12(조양동)</t>
   </si>
   <si>
-    <t>윤옥관원주시청본점</t>
-  </si>
-  <si>
-    <t>강원특별자치도 원주시 만대공원길 50(109호 무실동)</t>
-  </si>
-  <si>
     <t>이그제큐티브라운지(Executive Lounge)</t>
   </si>
   <si>
@@ -14759,6 +14753,12 @@
     <t>강원특별자치도 춘천시 신북읍 금광길 1(1층)</t>
   </si>
   <si>
+    <t>진보경조개듬뿍칼국수</t>
+  </si>
+  <si>
+    <t>강원특별자치도 강릉시 난설헌로 91(1~2층 포남동)</t>
+  </si>
+  <si>
     <t>집사들의 수다</t>
   </si>
   <si>
@@ -15570,6 +15570,15 @@
   </si>
   <si>
     <t>전북특별자치도 남원시 시청북로 17(주1동 2층 도통동)</t>
+  </si>
+  <si>
+    <t>씨유시흥대야파크점</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>경기도 시흥시 비둘기공원7길 53(동호프라자 103호 일부호 대야동)</t>
   </si>
 </sst>
 </file>
@@ -29193,7 +29202,7 @@
         <v>1585</v>
       </c>
       <c r="C796" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D796" t="s" s="2">
         <v>1483</v>
@@ -29649,7 +29658,7 @@
         <v>822.0</v>
       </c>
       <c r="B823" t="s" s="3">
-        <v>1639</v>
+        <v>1551</v>
       </c>
       <c r="C823" t="s" s="2">
         <v>733</v>
@@ -29658,7 +29667,7 @@
         <v>1483</v>
       </c>
       <c r="E823" t="s" s="3">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="824" ht="36.0" customHeight="true">
@@ -29666,7 +29675,7 @@
         <v>823.0</v>
       </c>
       <c r="B824" t="s" s="3">
-        <v>1551</v>
+        <v>1640</v>
       </c>
       <c r="C824" t="s" s="2">
         <v>733</v>
@@ -29873,7 +29882,7 @@
         <v>1664</v>
       </c>
       <c r="C836" t="s" s="2">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D836" t="s" s="2">
         <v>1483</v>
@@ -29904,7 +29913,7 @@
         <v>837.0</v>
       </c>
       <c r="B838" t="s" s="3">
-        <v>1668</v>
+        <v>1545</v>
       </c>
       <c r="C838" t="s" s="2">
         <v>938</v>
@@ -29913,7 +29922,7 @@
         <v>1483</v>
       </c>
       <c r="E838" t="s" s="3">
-        <v>1669</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="839" ht="36.0" customHeight="true">
@@ -29921,7 +29930,7 @@
         <v>838.0</v>
       </c>
       <c r="B839" t="s" s="3">
-        <v>1545</v>
+        <v>1668</v>
       </c>
       <c r="C839" t="s" s="2">
         <v>938</v>
@@ -29930,7 +29939,7 @@
         <v>1483</v>
       </c>
       <c r="E839" t="s" s="3">
-        <v>1546</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="840" ht="36.0" customHeight="true">
@@ -29941,13 +29950,13 @@
         <v>1670</v>
       </c>
       <c r="C840" t="s" s="2">
-        <v>938</v>
+        <v>6</v>
       </c>
       <c r="D840" t="s" s="2">
-        <v>1483</v>
+        <v>1671</v>
       </c>
       <c r="E840" t="s" s="3">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="841" ht="36.0" customHeight="true">
@@ -29955,13 +29964,13 @@
         <v>840.0</v>
       </c>
       <c r="B841" t="s" s="3">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="C841" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D841" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E841" t="s" s="3">
         <v>1674</v>
@@ -29978,7 +29987,7 @@
         <v>6</v>
       </c>
       <c r="D842" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E842" t="s" s="3">
         <v>1676</v>
@@ -29995,7 +30004,7 @@
         <v>6</v>
       </c>
       <c r="D843" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E843" t="s" s="3">
         <v>1678</v>
@@ -30012,7 +30021,7 @@
         <v>6</v>
       </c>
       <c r="D844" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E844" t="s" s="3">
         <v>1680</v>
@@ -30029,7 +30038,7 @@
         <v>6</v>
       </c>
       <c r="D845" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E845" t="s" s="3">
         <v>1682</v>
@@ -30046,7 +30055,7 @@
         <v>6</v>
       </c>
       <c r="D846" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E846" t="s" s="3">
         <v>1684</v>
@@ -30063,7 +30072,7 @@
         <v>6</v>
       </c>
       <c r="D847" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E847" t="s" s="3">
         <v>1686</v>
@@ -30080,7 +30089,7 @@
         <v>6</v>
       </c>
       <c r="D848" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E848" t="s" s="3">
         <v>1688</v>
@@ -30097,7 +30106,7 @@
         <v>6</v>
       </c>
       <c r="D849" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E849" t="s" s="3">
         <v>1690</v>
@@ -30114,7 +30123,7 @@
         <v>6</v>
       </c>
       <c r="D850" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E850" t="s" s="3">
         <v>1692</v>
@@ -30131,7 +30140,7 @@
         <v>6</v>
       </c>
       <c r="D851" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E851" t="s" s="3">
         <v>1694</v>
@@ -30148,7 +30157,7 @@
         <v>6</v>
       </c>
       <c r="D852" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E852" t="s" s="3">
         <v>1696</v>
@@ -30165,7 +30174,7 @@
         <v>6</v>
       </c>
       <c r="D853" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E853" t="s" s="3">
         <v>1698</v>
@@ -30182,7 +30191,7 @@
         <v>6</v>
       </c>
       <c r="D854" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E854" t="s" s="3">
         <v>1700</v>
@@ -30199,7 +30208,7 @@
         <v>6</v>
       </c>
       <c r="D855" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E855" t="s" s="3">
         <v>1702</v>
@@ -30216,7 +30225,7 @@
         <v>6</v>
       </c>
       <c r="D856" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E856" t="s" s="3">
         <v>1704</v>
@@ -30233,7 +30242,7 @@
         <v>6</v>
       </c>
       <c r="D857" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E857" t="s" s="3">
         <v>1706</v>
@@ -30250,7 +30259,7 @@
         <v>6</v>
       </c>
       <c r="D858" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E858" t="s" s="3">
         <v>1708</v>
@@ -30267,7 +30276,7 @@
         <v>6</v>
       </c>
       <c r="D859" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E859" t="s" s="3">
         <v>1710</v>
@@ -30284,7 +30293,7 @@
         <v>6</v>
       </c>
       <c r="D860" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E860" t="s" s="3">
         <v>1712</v>
@@ -30301,7 +30310,7 @@
         <v>6</v>
       </c>
       <c r="D861" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E861" t="s" s="3">
         <v>1714</v>
@@ -30318,7 +30327,7 @@
         <v>6</v>
       </c>
       <c r="D862" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E862" t="s" s="3">
         <v>1716</v>
@@ -30335,7 +30344,7 @@
         <v>6</v>
       </c>
       <c r="D863" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E863" t="s" s="3">
         <v>1718</v>
@@ -30352,7 +30361,7 @@
         <v>6</v>
       </c>
       <c r="D864" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E864" t="s" s="3">
         <v>1720</v>
@@ -30369,7 +30378,7 @@
         <v>6</v>
       </c>
       <c r="D865" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E865" t="s" s="3">
         <v>1722</v>
@@ -30386,7 +30395,7 @@
         <v>6</v>
       </c>
       <c r="D866" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E866" t="s" s="3">
         <v>1724</v>
@@ -30403,7 +30412,7 @@
         <v>6</v>
       </c>
       <c r="D867" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E867" t="s" s="3">
         <v>1726</v>
@@ -30420,7 +30429,7 @@
         <v>6</v>
       </c>
       <c r="D868" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E868" t="s" s="3">
         <v>1728</v>
@@ -30437,7 +30446,7 @@
         <v>6</v>
       </c>
       <c r="D869" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E869" t="s" s="3">
         <v>1730</v>
@@ -30454,7 +30463,7 @@
         <v>6</v>
       </c>
       <c r="D870" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E870" t="s" s="3">
         <v>1732</v>
@@ -30471,7 +30480,7 @@
         <v>6</v>
       </c>
       <c r="D871" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E871" t="s" s="3">
         <v>1734</v>
@@ -30488,7 +30497,7 @@
         <v>6</v>
       </c>
       <c r="D872" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E872" t="s" s="3">
         <v>1736</v>
@@ -30505,7 +30514,7 @@
         <v>6</v>
       </c>
       <c r="D873" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E873" t="s" s="3">
         <v>1738</v>
@@ -30522,7 +30531,7 @@
         <v>6</v>
       </c>
       <c r="D874" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E874" t="s" s="3">
         <v>1740</v>
@@ -30539,7 +30548,7 @@
         <v>6</v>
       </c>
       <c r="D875" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E875" t="s" s="3">
         <v>1742</v>
@@ -30556,7 +30565,7 @@
         <v>6</v>
       </c>
       <c r="D876" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E876" t="s" s="3">
         <v>1744</v>
@@ -30573,7 +30582,7 @@
         <v>6</v>
       </c>
       <c r="D877" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E877" t="s" s="3">
         <v>1746</v>
@@ -30590,7 +30599,7 @@
         <v>6</v>
       </c>
       <c r="D878" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E878" t="s" s="3">
         <v>1748</v>
@@ -30607,7 +30616,7 @@
         <v>6</v>
       </c>
       <c r="D879" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E879" t="s" s="3">
         <v>1750</v>
@@ -30624,7 +30633,7 @@
         <v>6</v>
       </c>
       <c r="D880" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E880" t="s" s="3">
         <v>1752</v>
@@ -30641,7 +30650,7 @@
         <v>6</v>
       </c>
       <c r="D881" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E881" t="s" s="3">
         <v>1754</v>
@@ -30658,7 +30667,7 @@
         <v>6</v>
       </c>
       <c r="D882" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E882" t="s" s="3">
         <v>1756</v>
@@ -30675,7 +30684,7 @@
         <v>6</v>
       </c>
       <c r="D883" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E883" t="s" s="3">
         <v>1758</v>
@@ -30692,7 +30701,7 @@
         <v>6</v>
       </c>
       <c r="D884" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E884" t="s" s="3">
         <v>1760</v>
@@ -30709,7 +30718,7 @@
         <v>6</v>
       </c>
       <c r="D885" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E885" t="s" s="3">
         <v>1762</v>
@@ -30726,7 +30735,7 @@
         <v>6</v>
       </c>
       <c r="D886" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E886" t="s" s="3">
         <v>1764</v>
@@ -30743,7 +30752,7 @@
         <v>6</v>
       </c>
       <c r="D887" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E887" t="s" s="3">
         <v>1766</v>
@@ -30760,7 +30769,7 @@
         <v>6</v>
       </c>
       <c r="D888" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E888" t="s" s="3">
         <v>1768</v>
@@ -30777,7 +30786,7 @@
         <v>6</v>
       </c>
       <c r="D889" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E889" t="s" s="3">
         <v>1770</v>
@@ -30794,7 +30803,7 @@
         <v>6</v>
       </c>
       <c r="D890" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E890" t="s" s="3">
         <v>1772</v>
@@ -30811,7 +30820,7 @@
         <v>6</v>
       </c>
       <c r="D891" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E891" t="s" s="3">
         <v>1774</v>
@@ -30828,7 +30837,7 @@
         <v>6</v>
       </c>
       <c r="D892" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E892" t="s" s="3">
         <v>1776</v>
@@ -30845,7 +30854,7 @@
         <v>6</v>
       </c>
       <c r="D893" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E893" t="s" s="3">
         <v>1778</v>
@@ -30862,7 +30871,7 @@
         <v>6</v>
       </c>
       <c r="D894" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E894" t="s" s="3">
         <v>1780</v>
@@ -30879,7 +30888,7 @@
         <v>6</v>
       </c>
       <c r="D895" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E895" t="s" s="3">
         <v>1782</v>
@@ -30896,7 +30905,7 @@
         <v>6</v>
       </c>
       <c r="D896" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E896" t="s" s="3">
         <v>1784</v>
@@ -30913,7 +30922,7 @@
         <v>6</v>
       </c>
       <c r="D897" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E897" t="s" s="3">
         <v>1786</v>
@@ -30930,7 +30939,7 @@
         <v>6</v>
       </c>
       <c r="D898" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E898" t="s" s="3">
         <v>1788</v>
@@ -30947,7 +30956,7 @@
         <v>6</v>
       </c>
       <c r="D899" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E899" t="s" s="3">
         <v>1790</v>
@@ -30964,7 +30973,7 @@
         <v>6</v>
       </c>
       <c r="D900" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E900" t="s" s="3">
         <v>1792</v>
@@ -30981,7 +30990,7 @@
         <v>6</v>
       </c>
       <c r="D901" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E901" t="s" s="3">
         <v>1794</v>
@@ -30998,7 +31007,7 @@
         <v>6</v>
       </c>
       <c r="D902" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E902" t="s" s="3">
         <v>1796</v>
@@ -31015,7 +31024,7 @@
         <v>6</v>
       </c>
       <c r="D903" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E903" t="s" s="3">
         <v>1798</v>
@@ -31032,7 +31041,7 @@
         <v>6</v>
       </c>
       <c r="D904" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E904" t="s" s="3">
         <v>1800</v>
@@ -31049,7 +31058,7 @@
         <v>6</v>
       </c>
       <c r="D905" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E905" t="s" s="3">
         <v>1802</v>
@@ -31066,7 +31075,7 @@
         <v>6</v>
       </c>
       <c r="D906" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E906" t="s" s="3">
         <v>1804</v>
@@ -31083,7 +31092,7 @@
         <v>6</v>
       </c>
       <c r="D907" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E907" t="s" s="3">
         <v>1806</v>
@@ -31100,7 +31109,7 @@
         <v>6</v>
       </c>
       <c r="D908" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E908" t="s" s="3">
         <v>1808</v>
@@ -31117,7 +31126,7 @@
         <v>6</v>
       </c>
       <c r="D909" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E909" t="s" s="3">
         <v>1810</v>
@@ -31134,7 +31143,7 @@
         <v>6</v>
       </c>
       <c r="D910" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E910" t="s" s="3">
         <v>1812</v>
@@ -31151,7 +31160,7 @@
         <v>6</v>
       </c>
       <c r="D911" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E911" t="s" s="3">
         <v>1814</v>
@@ -31168,7 +31177,7 @@
         <v>6</v>
       </c>
       <c r="D912" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E912" t="s" s="3">
         <v>1816</v>
@@ -31185,7 +31194,7 @@
         <v>6</v>
       </c>
       <c r="D913" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E913" t="s" s="3">
         <v>1818</v>
@@ -31202,7 +31211,7 @@
         <v>6</v>
       </c>
       <c r="D914" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E914" t="s" s="3">
         <v>1820</v>
@@ -31219,7 +31228,7 @@
         <v>6</v>
       </c>
       <c r="D915" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E915" t="s" s="3">
         <v>1822</v>
@@ -31230,16 +31239,16 @@
         <v>915.0</v>
       </c>
       <c r="B916" t="s" s="3">
+        <v>1821</v>
+      </c>
+      <c r="C916" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D916" t="s" s="2">
+        <v>1671</v>
+      </c>
+      <c r="E916" t="s" s="3">
         <v>1823</v>
-      </c>
-      <c r="C916" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D916" t="s" s="2">
-        <v>1673</v>
-      </c>
-      <c r="E916" t="s" s="3">
-        <v>1824</v>
       </c>
     </row>
     <row r="917" ht="36.0" customHeight="true">
@@ -31247,13 +31256,13 @@
         <v>916.0</v>
       </c>
       <c r="B917" t="s" s="3">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="C917" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D917" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E917" t="s" s="3">
         <v>1825</v>
@@ -31270,7 +31279,7 @@
         <v>6</v>
       </c>
       <c r="D918" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E918" t="s" s="3">
         <v>1827</v>
@@ -31287,7 +31296,7 @@
         <v>6</v>
       </c>
       <c r="D919" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E919" t="s" s="3">
         <v>1829</v>
@@ -31304,7 +31313,7 @@
         <v>6</v>
       </c>
       <c r="D920" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E920" t="s" s="3">
         <v>1831</v>
@@ -31321,7 +31330,7 @@
         <v>6</v>
       </c>
       <c r="D921" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E921" t="s" s="3">
         <v>1833</v>
@@ -31338,7 +31347,7 @@
         <v>6</v>
       </c>
       <c r="D922" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E922" t="s" s="3">
         <v>1835</v>
@@ -31355,7 +31364,7 @@
         <v>6</v>
       </c>
       <c r="D923" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E923" t="s" s="3">
         <v>1837</v>
@@ -31372,7 +31381,7 @@
         <v>6</v>
       </c>
       <c r="D924" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E924" t="s" s="3">
         <v>1839</v>
@@ -31389,7 +31398,7 @@
         <v>6</v>
       </c>
       <c r="D925" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E925" t="s" s="3">
         <v>1841</v>
@@ -31406,7 +31415,7 @@
         <v>6</v>
       </c>
       <c r="D926" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E926" t="s" s="3">
         <v>1843</v>
@@ -31423,7 +31432,7 @@
         <v>6</v>
       </c>
       <c r="D927" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E927" t="s" s="3">
         <v>1845</v>
@@ -31440,7 +31449,7 @@
         <v>6</v>
       </c>
       <c r="D928" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E928" t="s" s="3">
         <v>1847</v>
@@ -31457,7 +31466,7 @@
         <v>6</v>
       </c>
       <c r="D929" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E929" t="s" s="3">
         <v>1849</v>
@@ -31474,7 +31483,7 @@
         <v>6</v>
       </c>
       <c r="D930" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E930" t="s" s="3">
         <v>1851</v>
@@ -31491,7 +31500,7 @@
         <v>6</v>
       </c>
       <c r="D931" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E931" t="s" s="3">
         <v>1853</v>
@@ -31508,7 +31517,7 @@
         <v>6</v>
       </c>
       <c r="D932" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E932" t="s" s="3">
         <v>1855</v>
@@ -31525,7 +31534,7 @@
         <v>6</v>
       </c>
       <c r="D933" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E933" t="s" s="3">
         <v>1857</v>
@@ -31542,7 +31551,7 @@
         <v>6</v>
       </c>
       <c r="D934" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E934" t="s" s="3">
         <v>1859</v>
@@ -31559,7 +31568,7 @@
         <v>6</v>
       </c>
       <c r="D935" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E935" t="s" s="3">
         <v>1861</v>
@@ -31576,7 +31585,7 @@
         <v>6</v>
       </c>
       <c r="D936" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E936" t="s" s="3">
         <v>1863</v>
@@ -31593,7 +31602,7 @@
         <v>6</v>
       </c>
       <c r="D937" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E937" t="s" s="3">
         <v>1865</v>
@@ -31610,7 +31619,7 @@
         <v>6</v>
       </c>
       <c r="D938" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E938" t="s" s="3">
         <v>1867</v>
@@ -31627,7 +31636,7 @@
         <v>6</v>
       </c>
       <c r="D939" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E939" t="s" s="3">
         <v>1869</v>
@@ -31644,7 +31653,7 @@
         <v>6</v>
       </c>
       <c r="D940" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E940" t="s" s="3">
         <v>1871</v>
@@ -31658,10 +31667,10 @@
         <v>1872</v>
       </c>
       <c r="C941" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D941" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E941" t="s" s="3">
         <v>1873</v>
@@ -31678,7 +31687,7 @@
         <v>733</v>
       </c>
       <c r="D942" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E942" t="s" s="3">
         <v>1875</v>
@@ -31695,7 +31704,7 @@
         <v>733</v>
       </c>
       <c r="D943" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E943" t="s" s="3">
         <v>1877</v>
@@ -31712,7 +31721,7 @@
         <v>733</v>
       </c>
       <c r="D944" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E944" t="s" s="3">
         <v>1879</v>
@@ -31729,7 +31738,7 @@
         <v>733</v>
       </c>
       <c r="D945" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E945" t="s" s="3">
         <v>1881</v>
@@ -31746,7 +31755,7 @@
         <v>733</v>
       </c>
       <c r="D946" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E946" t="s" s="3">
         <v>1883</v>
@@ -31763,7 +31772,7 @@
         <v>733</v>
       </c>
       <c r="D947" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E947" t="s" s="3">
         <v>1885</v>
@@ -31780,7 +31789,7 @@
         <v>733</v>
       </c>
       <c r="D948" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E948" t="s" s="3">
         <v>1887</v>
@@ -31797,7 +31806,7 @@
         <v>733</v>
       </c>
       <c r="D949" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E949" t="s" s="3">
         <v>1889</v>
@@ -31814,7 +31823,7 @@
         <v>733</v>
       </c>
       <c r="D950" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E950" t="s" s="3">
         <v>1891</v>
@@ -31831,7 +31840,7 @@
         <v>733</v>
       </c>
       <c r="D951" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E951" t="s" s="3">
         <v>1893</v>
@@ -31842,16 +31851,16 @@
         <v>951.0</v>
       </c>
       <c r="B952" t="s" s="3">
+        <v>1892</v>
+      </c>
+      <c r="C952" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="D952" t="s" s="2">
+        <v>1671</v>
+      </c>
+      <c r="E952" t="s" s="3">
         <v>1894</v>
-      </c>
-      <c r="C952" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="D952" t="s" s="2">
-        <v>1673</v>
-      </c>
-      <c r="E952" t="s" s="3">
-        <v>1895</v>
       </c>
     </row>
     <row r="953" ht="36.0" customHeight="true">
@@ -31859,13 +31868,13 @@
         <v>952.0</v>
       </c>
       <c r="B953" t="s" s="3">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="C953" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D953" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E953" t="s" s="3">
         <v>1896</v>
@@ -31882,7 +31891,7 @@
         <v>733</v>
       </c>
       <c r="D954" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E954" t="s" s="3">
         <v>1898</v>
@@ -31899,7 +31908,7 @@
         <v>733</v>
       </c>
       <c r="D955" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E955" t="s" s="3">
         <v>1900</v>
@@ -31916,7 +31925,7 @@
         <v>733</v>
       </c>
       <c r="D956" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E956" t="s" s="3">
         <v>1902</v>
@@ -31933,7 +31942,7 @@
         <v>733</v>
       </c>
       <c r="D957" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E957" t="s" s="3">
         <v>1904</v>
@@ -31950,7 +31959,7 @@
         <v>733</v>
       </c>
       <c r="D958" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E958" t="s" s="3">
         <v>1906</v>
@@ -31967,7 +31976,7 @@
         <v>733</v>
       </c>
       <c r="D959" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E959" t="s" s="3">
         <v>1908</v>
@@ -31984,7 +31993,7 @@
         <v>733</v>
       </c>
       <c r="D960" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E960" t="s" s="3">
         <v>1910</v>
@@ -32001,7 +32010,7 @@
         <v>733</v>
       </c>
       <c r="D961" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E961" t="s" s="3">
         <v>1912</v>
@@ -32018,7 +32027,7 @@
         <v>733</v>
       </c>
       <c r="D962" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E962" t="s" s="3">
         <v>1914</v>
@@ -32035,7 +32044,7 @@
         <v>733</v>
       </c>
       <c r="D963" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E963" t="s" s="3">
         <v>1916</v>
@@ -32052,7 +32061,7 @@
         <v>733</v>
       </c>
       <c r="D964" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E964" t="s" s="3">
         <v>1918</v>
@@ -32069,7 +32078,7 @@
         <v>733</v>
       </c>
       <c r="D965" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E965" t="s" s="3">
         <v>1920</v>
@@ -32086,7 +32095,7 @@
         <v>733</v>
       </c>
       <c r="D966" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E966" t="s" s="3">
         <v>1922</v>
@@ -32103,7 +32112,7 @@
         <v>733</v>
       </c>
       <c r="D967" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E967" t="s" s="3">
         <v>1924</v>
@@ -32120,7 +32129,7 @@
         <v>733</v>
       </c>
       <c r="D968" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E968" t="s" s="3">
         <v>1926</v>
@@ -32137,7 +32146,7 @@
         <v>733</v>
       </c>
       <c r="D969" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E969" t="s" s="3">
         <v>1928</v>
@@ -32154,7 +32163,7 @@
         <v>733</v>
       </c>
       <c r="D970" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E970" t="s" s="3">
         <v>1930</v>
@@ -32171,7 +32180,7 @@
         <v>733</v>
       </c>
       <c r="D971" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E971" t="s" s="3">
         <v>1932</v>
@@ -32188,7 +32197,7 @@
         <v>733</v>
       </c>
       <c r="D972" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E972" t="s" s="3">
         <v>1934</v>
@@ -32205,7 +32214,7 @@
         <v>733</v>
       </c>
       <c r="D973" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E973" t="s" s="3">
         <v>1936</v>
@@ -32222,7 +32231,7 @@
         <v>733</v>
       </c>
       <c r="D974" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E974" t="s" s="3">
         <v>1938</v>
@@ -32239,7 +32248,7 @@
         <v>733</v>
       </c>
       <c r="D975" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E975" t="s" s="3">
         <v>1940</v>
@@ -32256,7 +32265,7 @@
         <v>733</v>
       </c>
       <c r="D976" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E976" t="s" s="3">
         <v>1942</v>
@@ -32273,7 +32282,7 @@
         <v>733</v>
       </c>
       <c r="D977" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E977" t="s" s="3">
         <v>1944</v>
@@ -32290,7 +32299,7 @@
         <v>733</v>
       </c>
       <c r="D978" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E978" t="s" s="3">
         <v>1946</v>
@@ -32307,7 +32316,7 @@
         <v>733</v>
       </c>
       <c r="D979" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E979" t="s" s="3">
         <v>1948</v>
@@ -32324,7 +32333,7 @@
         <v>733</v>
       </c>
       <c r="D980" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E980" t="s" s="3">
         <v>1950</v>
@@ -32341,7 +32350,7 @@
         <v>733</v>
       </c>
       <c r="D981" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E981" t="s" s="3">
         <v>1952</v>
@@ -32358,7 +32367,7 @@
         <v>733</v>
       </c>
       <c r="D982" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E982" t="s" s="3">
         <v>1954</v>
@@ -32375,7 +32384,7 @@
         <v>733</v>
       </c>
       <c r="D983" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E983" t="s" s="3">
         <v>1956</v>
@@ -32392,7 +32401,7 @@
         <v>733</v>
       </c>
       <c r="D984" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E984" t="s" s="3">
         <v>1958</v>
@@ -32409,7 +32418,7 @@
         <v>733</v>
       </c>
       <c r="D985" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E985" t="s" s="3">
         <v>1960</v>
@@ -32426,7 +32435,7 @@
         <v>733</v>
       </c>
       <c r="D986" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E986" t="s" s="3">
         <v>1962</v>
@@ -32443,7 +32452,7 @@
         <v>733</v>
       </c>
       <c r="D987" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E987" t="s" s="3">
         <v>1964</v>
@@ -32460,7 +32469,7 @@
         <v>733</v>
       </c>
       <c r="D988" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E988" t="s" s="3">
         <v>1966</v>
@@ -32477,7 +32486,7 @@
         <v>733</v>
       </c>
       <c r="D989" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E989" t="s" s="3">
         <v>1968</v>
@@ -32494,7 +32503,7 @@
         <v>733</v>
       </c>
       <c r="D990" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E990" t="s" s="3">
         <v>1970</v>
@@ -32511,7 +32520,7 @@
         <v>733</v>
       </c>
       <c r="D991" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E991" t="s" s="3">
         <v>1972</v>
@@ -32528,7 +32537,7 @@
         <v>733</v>
       </c>
       <c r="D992" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E992" t="s" s="3">
         <v>1974</v>
@@ -32545,7 +32554,7 @@
         <v>733</v>
       </c>
       <c r="D993" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E993" t="s" s="3">
         <v>1976</v>
@@ -32562,7 +32571,7 @@
         <v>733</v>
       </c>
       <c r="D994" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E994" t="s" s="3">
         <v>1978</v>
@@ -32579,7 +32588,7 @@
         <v>733</v>
       </c>
       <c r="D995" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E995" t="s" s="3">
         <v>1980</v>
@@ -32596,7 +32605,7 @@
         <v>733</v>
       </c>
       <c r="D996" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E996" t="s" s="3">
         <v>1982</v>
@@ -32613,7 +32622,7 @@
         <v>733</v>
       </c>
       <c r="D997" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E997" t="s" s="3">
         <v>1984</v>
@@ -32630,7 +32639,7 @@
         <v>733</v>
       </c>
       <c r="D998" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E998" t="s" s="3">
         <v>1986</v>
@@ -32647,7 +32656,7 @@
         <v>733</v>
       </c>
       <c r="D999" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E999" t="s" s="3">
         <v>1988</v>
@@ -32664,7 +32673,7 @@
         <v>733</v>
       </c>
       <c r="D1000" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1000" t="s" s="3">
         <v>1990</v>
@@ -32681,7 +32690,7 @@
         <v>733</v>
       </c>
       <c r="D1001" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1001" t="s" s="3">
         <v>1992</v>
@@ -32698,7 +32707,7 @@
         <v>733</v>
       </c>
       <c r="D1002" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1002" t="s" s="3">
         <v>1994</v>
@@ -32715,7 +32724,7 @@
         <v>733</v>
       </c>
       <c r="D1003" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1003" t="s" s="3">
         <v>1996</v>
@@ -32732,7 +32741,7 @@
         <v>733</v>
       </c>
       <c r="D1004" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1004" t="s" s="3">
         <v>1998</v>
@@ -32749,7 +32758,7 @@
         <v>733</v>
       </c>
       <c r="D1005" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1005" t="s" s="3">
         <v>2000</v>
@@ -32766,7 +32775,7 @@
         <v>733</v>
       </c>
       <c r="D1006" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1006" t="s" s="3">
         <v>2002</v>
@@ -32783,7 +32792,7 @@
         <v>733</v>
       </c>
       <c r="D1007" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1007" t="s" s="3">
         <v>2004</v>
@@ -32800,7 +32809,7 @@
         <v>733</v>
       </c>
       <c r="D1008" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1008" t="s" s="3">
         <v>2006</v>
@@ -32814,10 +32823,10 @@
         <v>2007</v>
       </c>
       <c r="C1009" t="s" s="2">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D1009" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E1009" t="s" s="3">
         <v>2008</v>
@@ -32831,13 +32840,13 @@
         <v>2009</v>
       </c>
       <c r="C1010" t="s" s="2">
-        <v>938</v>
+        <v>6</v>
       </c>
       <c r="D1010" t="s" s="2">
-        <v>1673</v>
+        <v>2010</v>
       </c>
       <c r="E1010" t="s" s="3">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1011" ht="36.0" customHeight="true">
@@ -32845,13 +32854,13 @@
         <v>1010.0</v>
       </c>
       <c r="B1011" t="s" s="3">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C1011" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1011" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1011" t="s" s="3">
         <v>2013</v>
@@ -32868,7 +32877,7 @@
         <v>6</v>
       </c>
       <c r="D1012" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1012" t="s" s="3">
         <v>2015</v>
@@ -32885,7 +32894,7 @@
         <v>6</v>
       </c>
       <c r="D1013" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1013" t="s" s="3">
         <v>2017</v>
@@ -32902,7 +32911,7 @@
         <v>6</v>
       </c>
       <c r="D1014" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1014" t="s" s="3">
         <v>2019</v>
@@ -32919,7 +32928,7 @@
         <v>6</v>
       </c>
       <c r="D1015" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1015" t="s" s="3">
         <v>2021</v>
@@ -32936,7 +32945,7 @@
         <v>6</v>
       </c>
       <c r="D1016" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1016" t="s" s="3">
         <v>2023</v>
@@ -32953,7 +32962,7 @@
         <v>6</v>
       </c>
       <c r="D1017" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1017" t="s" s="3">
         <v>2025</v>
@@ -32970,7 +32979,7 @@
         <v>6</v>
       </c>
       <c r="D1018" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1018" t="s" s="3">
         <v>2027</v>
@@ -32987,7 +32996,7 @@
         <v>6</v>
       </c>
       <c r="D1019" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1019" t="s" s="3">
         <v>2029</v>
@@ -33004,7 +33013,7 @@
         <v>6</v>
       </c>
       <c r="D1020" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1020" t="s" s="3">
         <v>2031</v>
@@ -33021,7 +33030,7 @@
         <v>6</v>
       </c>
       <c r="D1021" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1021" t="s" s="3">
         <v>2033</v>
@@ -33038,7 +33047,7 @@
         <v>6</v>
       </c>
       <c r="D1022" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1022" t="s" s="3">
         <v>2035</v>
@@ -33055,7 +33064,7 @@
         <v>6</v>
       </c>
       <c r="D1023" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1023" t="s" s="3">
         <v>2037</v>
@@ -33072,7 +33081,7 @@
         <v>6</v>
       </c>
       <c r="D1024" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1024" t="s" s="3">
         <v>2039</v>
@@ -33089,7 +33098,7 @@
         <v>6</v>
       </c>
       <c r="D1025" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1025" t="s" s="3">
         <v>2041</v>
@@ -33106,7 +33115,7 @@
         <v>6</v>
       </c>
       <c r="D1026" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1026" t="s" s="3">
         <v>2043</v>
@@ -33123,7 +33132,7 @@
         <v>6</v>
       </c>
       <c r="D1027" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1027" t="s" s="3">
         <v>2045</v>
@@ -33140,7 +33149,7 @@
         <v>6</v>
       </c>
       <c r="D1028" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1028" t="s" s="3">
         <v>2047</v>
@@ -33157,7 +33166,7 @@
         <v>6</v>
       </c>
       <c r="D1029" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1029" t="s" s="3">
         <v>2049</v>
@@ -33174,7 +33183,7 @@
         <v>6</v>
       </c>
       <c r="D1030" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1030" t="s" s="3">
         <v>2051</v>
@@ -33191,7 +33200,7 @@
         <v>6</v>
       </c>
       <c r="D1031" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1031" t="s" s="3">
         <v>2053</v>
@@ -33208,7 +33217,7 @@
         <v>6</v>
       </c>
       <c r="D1032" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1032" t="s" s="3">
         <v>2055</v>
@@ -33225,7 +33234,7 @@
         <v>6</v>
       </c>
       <c r="D1033" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1033" t="s" s="3">
         <v>2057</v>
@@ -33242,7 +33251,7 @@
         <v>6</v>
       </c>
       <c r="D1034" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1034" t="s" s="3">
         <v>2059</v>
@@ -33259,7 +33268,7 @@
         <v>6</v>
       </c>
       <c r="D1035" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1035" t="s" s="3">
         <v>2061</v>
@@ -33276,7 +33285,7 @@
         <v>6</v>
       </c>
       <c r="D1036" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1036" t="s" s="3">
         <v>2063</v>
@@ -33293,7 +33302,7 @@
         <v>6</v>
       </c>
       <c r="D1037" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1037" t="s" s="3">
         <v>2065</v>
@@ -33310,7 +33319,7 @@
         <v>6</v>
       </c>
       <c r="D1038" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1038" t="s" s="3">
         <v>2067</v>
@@ -33327,7 +33336,7 @@
         <v>6</v>
       </c>
       <c r="D1039" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1039" t="s" s="3">
         <v>2069</v>
@@ -33344,7 +33353,7 @@
         <v>6</v>
       </c>
       <c r="D1040" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1040" t="s" s="3">
         <v>2071</v>
@@ -33361,7 +33370,7 @@
         <v>6</v>
       </c>
       <c r="D1041" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1041" t="s" s="3">
         <v>2073</v>
@@ -33378,7 +33387,7 @@
         <v>6</v>
       </c>
       <c r="D1042" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1042" t="s" s="3">
         <v>2075</v>
@@ -33395,7 +33404,7 @@
         <v>6</v>
       </c>
       <c r="D1043" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1043" t="s" s="3">
         <v>2077</v>
@@ -33412,7 +33421,7 @@
         <v>6</v>
       </c>
       <c r="D1044" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1044" t="s" s="3">
         <v>2079</v>
@@ -33429,7 +33438,7 @@
         <v>6</v>
       </c>
       <c r="D1045" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1045" t="s" s="3">
         <v>2081</v>
@@ -33446,7 +33455,7 @@
         <v>6</v>
       </c>
       <c r="D1046" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1046" t="s" s="3">
         <v>2083</v>
@@ -33463,7 +33472,7 @@
         <v>6</v>
       </c>
       <c r="D1047" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1047" t="s" s="3">
         <v>2085</v>
@@ -33480,7 +33489,7 @@
         <v>6</v>
       </c>
       <c r="D1048" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1048" t="s" s="3">
         <v>2087</v>
@@ -33497,7 +33506,7 @@
         <v>6</v>
       </c>
       <c r="D1049" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1049" t="s" s="3">
         <v>2089</v>
@@ -33514,7 +33523,7 @@
         <v>6</v>
       </c>
       <c r="D1050" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1050" t="s" s="3">
         <v>2091</v>
@@ -33531,7 +33540,7 @@
         <v>6</v>
       </c>
       <c r="D1051" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1051" t="s" s="3">
         <v>2093</v>
@@ -33548,7 +33557,7 @@
         <v>6</v>
       </c>
       <c r="D1052" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1052" t="s" s="3">
         <v>2095</v>
@@ -33565,7 +33574,7 @@
         <v>6</v>
       </c>
       <c r="D1053" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1053" t="s" s="3">
         <v>2097</v>
@@ -33582,7 +33591,7 @@
         <v>6</v>
       </c>
       <c r="D1054" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1054" t="s" s="3">
         <v>2099</v>
@@ -33599,7 +33608,7 @@
         <v>6</v>
       </c>
       <c r="D1055" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1055" t="s" s="3">
         <v>2101</v>
@@ -33616,7 +33625,7 @@
         <v>6</v>
       </c>
       <c r="D1056" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1056" t="s" s="3">
         <v>2103</v>
@@ -33633,7 +33642,7 @@
         <v>6</v>
       </c>
       <c r="D1057" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1057" t="s" s="3">
         <v>2105</v>
@@ -33647,10 +33656,10 @@
         <v>2106</v>
       </c>
       <c r="C1058" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D1058" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1058" t="s" s="3">
         <v>2107</v>
@@ -33667,7 +33676,7 @@
         <v>733</v>
       </c>
       <c r="D1059" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1059" t="s" s="3">
         <v>2109</v>
@@ -33684,7 +33693,7 @@
         <v>733</v>
       </c>
       <c r="D1060" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1060" t="s" s="3">
         <v>2111</v>
@@ -33701,7 +33710,7 @@
         <v>733</v>
       </c>
       <c r="D1061" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1061" t="s" s="3">
         <v>2113</v>
@@ -33718,7 +33727,7 @@
         <v>733</v>
       </c>
       <c r="D1062" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1062" t="s" s="3">
         <v>2115</v>
@@ -33735,7 +33744,7 @@
         <v>733</v>
       </c>
       <c r="D1063" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1063" t="s" s="3">
         <v>2117</v>
@@ -33752,7 +33761,7 @@
         <v>733</v>
       </c>
       <c r="D1064" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1064" t="s" s="3">
         <v>2119</v>
@@ -33769,7 +33778,7 @@
         <v>733</v>
       </c>
       <c r="D1065" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1065" t="s" s="3">
         <v>2121</v>
@@ -33786,7 +33795,7 @@
         <v>733</v>
       </c>
       <c r="D1066" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1066" t="s" s="3">
         <v>2123</v>
@@ -33803,7 +33812,7 @@
         <v>733</v>
       </c>
       <c r="D1067" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1067" t="s" s="3">
         <v>2125</v>
@@ -33820,7 +33829,7 @@
         <v>733</v>
       </c>
       <c r="D1068" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1068" t="s" s="3">
         <v>2127</v>
@@ -33837,7 +33846,7 @@
         <v>733</v>
       </c>
       <c r="D1069" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1069" t="s" s="3">
         <v>2129</v>
@@ -33854,7 +33863,7 @@
         <v>733</v>
       </c>
       <c r="D1070" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1070" t="s" s="3">
         <v>2131</v>
@@ -33871,7 +33880,7 @@
         <v>733</v>
       </c>
       <c r="D1071" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1071" t="s" s="3">
         <v>2133</v>
@@ -33888,7 +33897,7 @@
         <v>733</v>
       </c>
       <c r="D1072" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1072" t="s" s="3">
         <v>2135</v>
@@ -33905,7 +33914,7 @@
         <v>733</v>
       </c>
       <c r="D1073" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1073" t="s" s="3">
         <v>2137</v>
@@ -33916,16 +33925,16 @@
         <v>1073.0</v>
       </c>
       <c r="B1074" t="s" s="3">
-        <v>2138</v>
+        <v>2090</v>
       </c>
       <c r="C1074" t="s" s="2">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D1074" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1074" t="s" s="3">
-        <v>2139</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1075" ht="36.0" customHeight="true">
@@ -33933,16 +33942,16 @@
         <v>1074.0</v>
       </c>
       <c r="B1075" t="s" s="3">
-        <v>2092</v>
+        <v>2138</v>
       </c>
       <c r="C1075" t="s" s="2">
         <v>938</v>
       </c>
       <c r="D1075" t="s" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E1075" t="s" s="3">
-        <v>2093</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1076" ht="36.0" customHeight="true">
@@ -33953,13 +33962,13 @@
         <v>2140</v>
       </c>
       <c r="C1076" t="s" s="2">
-        <v>938</v>
+        <v>6</v>
       </c>
       <c r="D1076" t="s" s="2">
-        <v>2012</v>
+        <v>2141</v>
       </c>
       <c r="E1076" t="s" s="3">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1077" ht="36.0" customHeight="true">
@@ -33967,13 +33976,13 @@
         <v>1076.0</v>
       </c>
       <c r="B1077" t="s" s="3">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="C1077" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1077" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1077" t="s" s="3">
         <v>2144</v>
@@ -33990,7 +33999,7 @@
         <v>6</v>
       </c>
       <c r="D1078" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1078" t="s" s="3">
         <v>2146</v>
@@ -34007,7 +34016,7 @@
         <v>6</v>
       </c>
       <c r="D1079" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1079" t="s" s="3">
         <v>2148</v>
@@ -34024,7 +34033,7 @@
         <v>6</v>
       </c>
       <c r="D1080" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1080" t="s" s="3">
         <v>2150</v>
@@ -34041,7 +34050,7 @@
         <v>6</v>
       </c>
       <c r="D1081" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1081" t="s" s="3">
         <v>2152</v>
@@ -34058,7 +34067,7 @@
         <v>6</v>
       </c>
       <c r="D1082" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1082" t="s" s="3">
         <v>2154</v>
@@ -34075,7 +34084,7 @@
         <v>6</v>
       </c>
       <c r="D1083" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1083" t="s" s="3">
         <v>2156</v>
@@ -34092,7 +34101,7 @@
         <v>6</v>
       </c>
       <c r="D1084" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1084" t="s" s="3">
         <v>2158</v>
@@ -34109,7 +34118,7 @@
         <v>6</v>
       </c>
       <c r="D1085" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1085" t="s" s="3">
         <v>2160</v>
@@ -34126,7 +34135,7 @@
         <v>6</v>
       </c>
       <c r="D1086" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1086" t="s" s="3">
         <v>2162</v>
@@ -34143,7 +34152,7 @@
         <v>6</v>
       </c>
       <c r="D1087" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1087" t="s" s="3">
         <v>2164</v>
@@ -34160,7 +34169,7 @@
         <v>6</v>
       </c>
       <c r="D1088" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1088" t="s" s="3">
         <v>2166</v>
@@ -34177,7 +34186,7 @@
         <v>6</v>
       </c>
       <c r="D1089" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1089" t="s" s="3">
         <v>2168</v>
@@ -34194,7 +34203,7 @@
         <v>6</v>
       </c>
       <c r="D1090" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1090" t="s" s="3">
         <v>2170</v>
@@ -34211,7 +34220,7 @@
         <v>6</v>
       </c>
       <c r="D1091" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1091" t="s" s="3">
         <v>2172</v>
@@ -34228,7 +34237,7 @@
         <v>6</v>
       </c>
       <c r="D1092" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1092" t="s" s="3">
         <v>2174</v>
@@ -34245,7 +34254,7 @@
         <v>6</v>
       </c>
       <c r="D1093" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1093" t="s" s="3">
         <v>2176</v>
@@ -34262,7 +34271,7 @@
         <v>6</v>
       </c>
       <c r="D1094" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1094" t="s" s="3">
         <v>2178</v>
@@ -34279,7 +34288,7 @@
         <v>6</v>
       </c>
       <c r="D1095" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1095" t="s" s="3">
         <v>2180</v>
@@ -34296,7 +34305,7 @@
         <v>6</v>
       </c>
       <c r="D1096" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1096" t="s" s="3">
         <v>2182</v>
@@ -34313,7 +34322,7 @@
         <v>6</v>
       </c>
       <c r="D1097" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1097" t="s" s="3">
         <v>2184</v>
@@ -34330,7 +34339,7 @@
         <v>6</v>
       </c>
       <c r="D1098" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1098" t="s" s="3">
         <v>2186</v>
@@ -34344,10 +34353,10 @@
         <v>2187</v>
       </c>
       <c r="C1099" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D1099" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1099" t="s" s="3">
         <v>2188</v>
@@ -34364,7 +34373,7 @@
         <v>733</v>
       </c>
       <c r="D1100" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1100" t="s" s="3">
         <v>2190</v>
@@ -34381,7 +34390,7 @@
         <v>733</v>
       </c>
       <c r="D1101" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1101" t="s" s="3">
         <v>2192</v>
@@ -34398,7 +34407,7 @@
         <v>733</v>
       </c>
       <c r="D1102" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1102" t="s" s="3">
         <v>2194</v>
@@ -34415,7 +34424,7 @@
         <v>733</v>
       </c>
       <c r="D1103" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1103" t="s" s="3">
         <v>2196</v>
@@ -34432,7 +34441,7 @@
         <v>733</v>
       </c>
       <c r="D1104" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1104" t="s" s="3">
         <v>2198</v>
@@ -34449,7 +34458,7 @@
         <v>733</v>
       </c>
       <c r="D1105" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1105" t="s" s="3">
         <v>2200</v>
@@ -34466,7 +34475,7 @@
         <v>733</v>
       </c>
       <c r="D1106" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1106" t="s" s="3">
         <v>2202</v>
@@ -34483,7 +34492,7 @@
         <v>733</v>
       </c>
       <c r="D1107" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1107" t="s" s="3">
         <v>2204</v>
@@ -34500,7 +34509,7 @@
         <v>733</v>
       </c>
       <c r="D1108" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1108" t="s" s="3">
         <v>2206</v>
@@ -34517,7 +34526,7 @@
         <v>733</v>
       </c>
       <c r="D1109" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1109" t="s" s="3">
         <v>2208</v>
@@ -34534,7 +34543,7 @@
         <v>733</v>
       </c>
       <c r="D1110" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1110" t="s" s="3">
         <v>2210</v>
@@ -34548,10 +34557,10 @@
         <v>2211</v>
       </c>
       <c r="C1111" t="s" s="2">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D1111" t="s" s="2">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="E1111" t="s" s="3">
         <v>2212</v>
@@ -34565,13 +34574,13 @@
         <v>2213</v>
       </c>
       <c r="C1112" t="s" s="2">
-        <v>938</v>
+        <v>6</v>
       </c>
       <c r="D1112" t="s" s="2">
-        <v>2143</v>
+        <v>2214</v>
       </c>
       <c r="E1112" t="s" s="3">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1113" ht="36.0" customHeight="true">
@@ -34579,13 +34588,13 @@
         <v>1112.0</v>
       </c>
       <c r="B1113" t="s" s="3">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C1113" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1113" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1113" t="s" s="3">
         <v>2217</v>
@@ -34602,7 +34611,7 @@
         <v>6</v>
       </c>
       <c r="D1114" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1114" t="s" s="3">
         <v>2219</v>
@@ -34619,7 +34628,7 @@
         <v>6</v>
       </c>
       <c r="D1115" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1115" t="s" s="3">
         <v>2221</v>
@@ -34636,7 +34645,7 @@
         <v>6</v>
       </c>
       <c r="D1116" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1116" t="s" s="3">
         <v>2223</v>
@@ -34653,7 +34662,7 @@
         <v>6</v>
       </c>
       <c r="D1117" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1117" t="s" s="3">
         <v>2225</v>
@@ -34670,7 +34679,7 @@
         <v>6</v>
       </c>
       <c r="D1118" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1118" t="s" s="3">
         <v>2227</v>
@@ -34687,7 +34696,7 @@
         <v>6</v>
       </c>
       <c r="D1119" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1119" t="s" s="3">
         <v>2229</v>
@@ -34701,10 +34710,10 @@
         <v>2230</v>
       </c>
       <c r="C1120" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D1120" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1120" t="s" s="3">
         <v>2231</v>
@@ -34718,10 +34727,10 @@
         <v>2232</v>
       </c>
       <c r="C1121" t="s" s="2">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D1121" t="s" s="2">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E1121" t="s" s="3">
         <v>2233</v>
@@ -34735,13 +34744,13 @@
         <v>2234</v>
       </c>
       <c r="C1122" t="s" s="2">
-        <v>938</v>
+        <v>6</v>
       </c>
       <c r="D1122" t="s" s="2">
-        <v>2216</v>
+        <v>2235</v>
       </c>
       <c r="E1122" t="s" s="3">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="1123" ht="36.0" customHeight="true">
@@ -34749,13 +34758,13 @@
         <v>1122.0</v>
       </c>
       <c r="B1123" t="s" s="3">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="C1123" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1123" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1123" t="s" s="3">
         <v>2238</v>
@@ -34772,7 +34781,7 @@
         <v>6</v>
       </c>
       <c r="D1124" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1124" t="s" s="3">
         <v>2240</v>
@@ -34789,7 +34798,7 @@
         <v>6</v>
       </c>
       <c r="D1125" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1125" t="s" s="3">
         <v>2242</v>
@@ -34806,7 +34815,7 @@
         <v>6</v>
       </c>
       <c r="D1126" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1126" t="s" s="3">
         <v>2244</v>
@@ -34823,7 +34832,7 @@
         <v>6</v>
       </c>
       <c r="D1127" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1127" t="s" s="3">
         <v>2246</v>
@@ -34840,7 +34849,7 @@
         <v>6</v>
       </c>
       <c r="D1128" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1128" t="s" s="3">
         <v>2248</v>
@@ -34857,7 +34866,7 @@
         <v>6</v>
       </c>
       <c r="D1129" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1129" t="s" s="3">
         <v>2250</v>
@@ -34874,7 +34883,7 @@
         <v>6</v>
       </c>
       <c r="D1130" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1130" t="s" s="3">
         <v>2252</v>
@@ -34891,7 +34900,7 @@
         <v>6</v>
       </c>
       <c r="D1131" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1131" t="s" s="3">
         <v>2254</v>
@@ -34908,7 +34917,7 @@
         <v>6</v>
       </c>
       <c r="D1132" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1132" t="s" s="3">
         <v>2256</v>
@@ -34925,7 +34934,7 @@
         <v>6</v>
       </c>
       <c r="D1133" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1133" t="s" s="3">
         <v>2258</v>
@@ -34942,7 +34951,7 @@
         <v>6</v>
       </c>
       <c r="D1134" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1134" t="s" s="3">
         <v>2260</v>
@@ -34959,7 +34968,7 @@
         <v>6</v>
       </c>
       <c r="D1135" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1135" t="s" s="3">
         <v>2262</v>
@@ -34976,7 +34985,7 @@
         <v>6</v>
       </c>
       <c r="D1136" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1136" t="s" s="3">
         <v>2264</v>
@@ -34993,7 +35002,7 @@
         <v>6</v>
       </c>
       <c r="D1137" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1137" t="s" s="3">
         <v>2266</v>
@@ -35010,7 +35019,7 @@
         <v>6</v>
       </c>
       <c r="D1138" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1138" t="s" s="3">
         <v>2268</v>
@@ -35027,7 +35036,7 @@
         <v>6</v>
       </c>
       <c r="D1139" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1139" t="s" s="3">
         <v>2270</v>
@@ -35044,7 +35053,7 @@
         <v>6</v>
       </c>
       <c r="D1140" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1140" t="s" s="3">
         <v>2272</v>
@@ -35061,7 +35070,7 @@
         <v>6</v>
       </c>
       <c r="D1141" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1141" t="s" s="3">
         <v>2274</v>
@@ -35078,7 +35087,7 @@
         <v>6</v>
       </c>
       <c r="D1142" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1142" t="s" s="3">
         <v>2276</v>
@@ -35095,7 +35104,7 @@
         <v>6</v>
       </c>
       <c r="D1143" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1143" t="s" s="3">
         <v>2278</v>
@@ -35112,7 +35121,7 @@
         <v>6</v>
       </c>
       <c r="D1144" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1144" t="s" s="3">
         <v>2280</v>
@@ -35129,7 +35138,7 @@
         <v>6</v>
       </c>
       <c r="D1145" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1145" t="s" s="3">
         <v>2282</v>
@@ -35146,7 +35155,7 @@
         <v>6</v>
       </c>
       <c r="D1146" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1146" t="s" s="3">
         <v>2284</v>
@@ -35163,7 +35172,7 @@
         <v>6</v>
       </c>
       <c r="D1147" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1147" t="s" s="3">
         <v>2286</v>
@@ -35180,7 +35189,7 @@
         <v>6</v>
       </c>
       <c r="D1148" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1148" t="s" s="3">
         <v>2288</v>
@@ -35197,7 +35206,7 @@
         <v>6</v>
       </c>
       <c r="D1149" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1149" t="s" s="3">
         <v>2290</v>
@@ -35214,7 +35223,7 @@
         <v>6</v>
       </c>
       <c r="D1150" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1150" t="s" s="3">
         <v>2292</v>
@@ -35231,7 +35240,7 @@
         <v>6</v>
       </c>
       <c r="D1151" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1151" t="s" s="3">
         <v>2294</v>
@@ -35248,7 +35257,7 @@
         <v>6</v>
       </c>
       <c r="D1152" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1152" t="s" s="3">
         <v>2296</v>
@@ -35265,7 +35274,7 @@
         <v>6</v>
       </c>
       <c r="D1153" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1153" t="s" s="3">
         <v>2298</v>
@@ -35282,7 +35291,7 @@
         <v>6</v>
       </c>
       <c r="D1154" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1154" t="s" s="3">
         <v>2300</v>
@@ -35299,7 +35308,7 @@
         <v>6</v>
       </c>
       <c r="D1155" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1155" t="s" s="3">
         <v>2302</v>
@@ -35316,7 +35325,7 @@
         <v>6</v>
       </c>
       <c r="D1156" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1156" t="s" s="3">
         <v>2304</v>
@@ -35333,7 +35342,7 @@
         <v>6</v>
       </c>
       <c r="D1157" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1157" t="s" s="3">
         <v>2306</v>
@@ -35350,7 +35359,7 @@
         <v>6</v>
       </c>
       <c r="D1158" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1158" t="s" s="3">
         <v>2308</v>
@@ -35367,7 +35376,7 @@
         <v>6</v>
       </c>
       <c r="D1159" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1159" t="s" s="3">
         <v>2310</v>
@@ -35384,7 +35393,7 @@
         <v>6</v>
       </c>
       <c r="D1160" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1160" t="s" s="3">
         <v>2312</v>
@@ -35401,7 +35410,7 @@
         <v>6</v>
       </c>
       <c r="D1161" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1161" t="s" s="3">
         <v>2314</v>
@@ -35418,7 +35427,7 @@
         <v>6</v>
       </c>
       <c r="D1162" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1162" t="s" s="3">
         <v>2316</v>
@@ -35435,7 +35444,7 @@
         <v>6</v>
       </c>
       <c r="D1163" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1163" t="s" s="3">
         <v>2318</v>
@@ -35452,7 +35461,7 @@
         <v>6</v>
       </c>
       <c r="D1164" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1164" t="s" s="3">
         <v>2320</v>
@@ -35469,7 +35478,7 @@
         <v>6</v>
       </c>
       <c r="D1165" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1165" t="s" s="3">
         <v>2322</v>
@@ -35486,7 +35495,7 @@
         <v>6</v>
       </c>
       <c r="D1166" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1166" t="s" s="3">
         <v>2324</v>
@@ -35503,7 +35512,7 @@
         <v>6</v>
       </c>
       <c r="D1167" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1167" t="s" s="3">
         <v>2326</v>
@@ -35520,7 +35529,7 @@
         <v>6</v>
       </c>
       <c r="D1168" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1168" t="s" s="3">
         <v>2328</v>
@@ -35537,7 +35546,7 @@
         <v>6</v>
       </c>
       <c r="D1169" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1169" t="s" s="3">
         <v>2330</v>
@@ -35554,7 +35563,7 @@
         <v>6</v>
       </c>
       <c r="D1170" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1170" t="s" s="3">
         <v>2332</v>
@@ -35571,7 +35580,7 @@
         <v>6</v>
       </c>
       <c r="D1171" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1171" t="s" s="3">
         <v>2334</v>
@@ -35588,7 +35597,7 @@
         <v>6</v>
       </c>
       <c r="D1172" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1172" t="s" s="3">
         <v>2336</v>
@@ -35605,7 +35614,7 @@
         <v>6</v>
       </c>
       <c r="D1173" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1173" t="s" s="3">
         <v>2338</v>
@@ -35622,7 +35631,7 @@
         <v>6</v>
       </c>
       <c r="D1174" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1174" t="s" s="3">
         <v>2340</v>
@@ -35639,7 +35648,7 @@
         <v>6</v>
       </c>
       <c r="D1175" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1175" t="s" s="3">
         <v>2342</v>
@@ -35656,7 +35665,7 @@
         <v>6</v>
       </c>
       <c r="D1176" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1176" t="s" s="3">
         <v>2344</v>
@@ -35673,7 +35682,7 @@
         <v>6</v>
       </c>
       <c r="D1177" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1177" t="s" s="3">
         <v>2346</v>
@@ -35690,7 +35699,7 @@
         <v>6</v>
       </c>
       <c r="D1178" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1178" t="s" s="3">
         <v>2348</v>
@@ -35707,7 +35716,7 @@
         <v>6</v>
       </c>
       <c r="D1179" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1179" t="s" s="3">
         <v>2350</v>
@@ -35724,7 +35733,7 @@
         <v>6</v>
       </c>
       <c r="D1180" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1180" t="s" s="3">
         <v>2352</v>
@@ -35741,7 +35750,7 @@
         <v>6</v>
       </c>
       <c r="D1181" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1181" t="s" s="3">
         <v>2354</v>
@@ -35758,7 +35767,7 @@
         <v>6</v>
       </c>
       <c r="D1182" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1182" t="s" s="3">
         <v>2356</v>
@@ -35775,7 +35784,7 @@
         <v>6</v>
       </c>
       <c r="D1183" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1183" t="s" s="3">
         <v>2358</v>
@@ -35792,7 +35801,7 @@
         <v>6</v>
       </c>
       <c r="D1184" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1184" t="s" s="3">
         <v>2360</v>
@@ -35809,7 +35818,7 @@
         <v>6</v>
       </c>
       <c r="D1185" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1185" t="s" s="3">
         <v>2362</v>
@@ -35826,7 +35835,7 @@
         <v>6</v>
       </c>
       <c r="D1186" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1186" t="s" s="3">
         <v>2364</v>
@@ -35843,7 +35852,7 @@
         <v>6</v>
       </c>
       <c r="D1187" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1187" t="s" s="3">
         <v>2366</v>
@@ -35860,7 +35869,7 @@
         <v>6</v>
       </c>
       <c r="D1188" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1188" t="s" s="3">
         <v>2368</v>
@@ -35877,7 +35886,7 @@
         <v>6</v>
       </c>
       <c r="D1189" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1189" t="s" s="3">
         <v>2370</v>
@@ -35894,7 +35903,7 @@
         <v>6</v>
       </c>
       <c r="D1190" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1190" t="s" s="3">
         <v>2372</v>
@@ -35911,7 +35920,7 @@
         <v>6</v>
       </c>
       <c r="D1191" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1191" t="s" s="3">
         <v>2374</v>
@@ -35928,7 +35937,7 @@
         <v>6</v>
       </c>
       <c r="D1192" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1192" t="s" s="3">
         <v>2376</v>
@@ -35945,7 +35954,7 @@
         <v>6</v>
       </c>
       <c r="D1193" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1193" t="s" s="3">
         <v>2378</v>
@@ -35956,16 +35965,16 @@
         <v>1193.0</v>
       </c>
       <c r="B1194" t="s" s="3">
+        <v>1697</v>
+      </c>
+      <c r="C1194" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1194" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1194" t="s" s="3">
         <v>2379</v>
-      </c>
-      <c r="C1194" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1194" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1194" t="s" s="3">
-        <v>2380</v>
       </c>
     </row>
     <row r="1195" ht="36.0" customHeight="true">
@@ -35973,13 +35982,13 @@
         <v>1194.0</v>
       </c>
       <c r="B1195" t="s" s="3">
-        <v>1699</v>
+        <v>2380</v>
       </c>
       <c r="C1195" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1195" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1195" t="s" s="3">
         <v>2381</v>
@@ -35996,7 +36005,7 @@
         <v>6</v>
       </c>
       <c r="D1196" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1196" t="s" s="3">
         <v>2383</v>
@@ -36013,7 +36022,7 @@
         <v>6</v>
       </c>
       <c r="D1197" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1197" t="s" s="3">
         <v>2385</v>
@@ -36030,7 +36039,7 @@
         <v>6</v>
       </c>
       <c r="D1198" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1198" t="s" s="3">
         <v>2387</v>
@@ -36047,7 +36056,7 @@
         <v>6</v>
       </c>
       <c r="D1199" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1199" t="s" s="3">
         <v>2389</v>
@@ -36064,7 +36073,7 @@
         <v>6</v>
       </c>
       <c r="D1200" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1200" t="s" s="3">
         <v>2391</v>
@@ -36081,7 +36090,7 @@
         <v>6</v>
       </c>
       <c r="D1201" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1201" t="s" s="3">
         <v>2393</v>
@@ -36098,7 +36107,7 @@
         <v>6</v>
       </c>
       <c r="D1202" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1202" t="s" s="3">
         <v>2395</v>
@@ -36115,7 +36124,7 @@
         <v>6</v>
       </c>
       <c r="D1203" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1203" t="s" s="3">
         <v>2397</v>
@@ -36132,7 +36141,7 @@
         <v>6</v>
       </c>
       <c r="D1204" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1204" t="s" s="3">
         <v>2399</v>
@@ -36149,7 +36158,7 @@
         <v>6</v>
       </c>
       <c r="D1205" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1205" t="s" s="3">
         <v>2401</v>
@@ -36166,7 +36175,7 @@
         <v>6</v>
       </c>
       <c r="D1206" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1206" t="s" s="3">
         <v>2403</v>
@@ -36183,7 +36192,7 @@
         <v>6</v>
       </c>
       <c r="D1207" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1207" t="s" s="3">
         <v>2405</v>
@@ -36200,7 +36209,7 @@
         <v>6</v>
       </c>
       <c r="D1208" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1208" t="s" s="3">
         <v>2407</v>
@@ -36217,7 +36226,7 @@
         <v>6</v>
       </c>
       <c r="D1209" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1209" t="s" s="3">
         <v>2409</v>
@@ -36234,7 +36243,7 @@
         <v>6</v>
       </c>
       <c r="D1210" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1210" t="s" s="3">
         <v>2411</v>
@@ -36251,7 +36260,7 @@
         <v>6</v>
       </c>
       <c r="D1211" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1211" t="s" s="3">
         <v>2413</v>
@@ -36268,7 +36277,7 @@
         <v>6</v>
       </c>
       <c r="D1212" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1212" t="s" s="3">
         <v>2415</v>
@@ -36285,7 +36294,7 @@
         <v>6</v>
       </c>
       <c r="D1213" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1213" t="s" s="3">
         <v>2417</v>
@@ -36302,7 +36311,7 @@
         <v>6</v>
       </c>
       <c r="D1214" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1214" t="s" s="3">
         <v>2419</v>
@@ -36319,7 +36328,7 @@
         <v>6</v>
       </c>
       <c r="D1215" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1215" t="s" s="3">
         <v>2421</v>
@@ -36336,7 +36345,7 @@
         <v>6</v>
       </c>
       <c r="D1216" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1216" t="s" s="3">
         <v>2423</v>
@@ -36353,7 +36362,7 @@
         <v>6</v>
       </c>
       <c r="D1217" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1217" t="s" s="3">
         <v>2425</v>
@@ -36370,7 +36379,7 @@
         <v>6</v>
       </c>
       <c r="D1218" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1218" t="s" s="3">
         <v>2427</v>
@@ -36387,7 +36396,7 @@
         <v>6</v>
       </c>
       <c r="D1219" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1219" t="s" s="3">
         <v>2429</v>
@@ -36404,7 +36413,7 @@
         <v>6</v>
       </c>
       <c r="D1220" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1220" t="s" s="3">
         <v>2431</v>
@@ -36421,7 +36430,7 @@
         <v>6</v>
       </c>
       <c r="D1221" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1221" t="s" s="3">
         <v>2433</v>
@@ -36438,7 +36447,7 @@
         <v>6</v>
       </c>
       <c r="D1222" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1222" t="s" s="3">
         <v>2435</v>
@@ -36455,7 +36464,7 @@
         <v>6</v>
       </c>
       <c r="D1223" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1223" t="s" s="3">
         <v>2437</v>
@@ -36472,7 +36481,7 @@
         <v>6</v>
       </c>
       <c r="D1224" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1224" t="s" s="3">
         <v>2439</v>
@@ -36489,7 +36498,7 @@
         <v>6</v>
       </c>
       <c r="D1225" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1225" t="s" s="3">
         <v>2441</v>
@@ -36506,7 +36515,7 @@
         <v>6</v>
       </c>
       <c r="D1226" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1226" t="s" s="3">
         <v>2443</v>
@@ -36523,7 +36532,7 @@
         <v>6</v>
       </c>
       <c r="D1227" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1227" t="s" s="3">
         <v>2445</v>
@@ -36540,7 +36549,7 @@
         <v>6</v>
       </c>
       <c r="D1228" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1228" t="s" s="3">
         <v>2447</v>
@@ -36557,7 +36566,7 @@
         <v>6</v>
       </c>
       <c r="D1229" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1229" t="s" s="3">
         <v>2449</v>
@@ -36574,7 +36583,7 @@
         <v>6</v>
       </c>
       <c r="D1230" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1230" t="s" s="3">
         <v>2451</v>
@@ -36591,7 +36600,7 @@
         <v>6</v>
       </c>
       <c r="D1231" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1231" t="s" s="3">
         <v>2453</v>
@@ -36608,7 +36617,7 @@
         <v>6</v>
       </c>
       <c r="D1232" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1232" t="s" s="3">
         <v>2455</v>
@@ -36625,7 +36634,7 @@
         <v>6</v>
       </c>
       <c r="D1233" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1233" t="s" s="3">
         <v>2457</v>
@@ -36642,7 +36651,7 @@
         <v>6</v>
       </c>
       <c r="D1234" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1234" t="s" s="3">
         <v>2459</v>
@@ -36659,7 +36668,7 @@
         <v>6</v>
       </c>
       <c r="D1235" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1235" t="s" s="3">
         <v>2461</v>
@@ -36676,7 +36685,7 @@
         <v>6</v>
       </c>
       <c r="D1236" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1236" t="s" s="3">
         <v>2463</v>
@@ -36693,7 +36702,7 @@
         <v>6</v>
       </c>
       <c r="D1237" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1237" t="s" s="3">
         <v>2465</v>
@@ -36710,7 +36719,7 @@
         <v>6</v>
       </c>
       <c r="D1238" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1238" t="s" s="3">
         <v>2467</v>
@@ -36727,7 +36736,7 @@
         <v>6</v>
       </c>
       <c r="D1239" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1239" t="s" s="3">
         <v>2469</v>
@@ -36744,7 +36753,7 @@
         <v>6</v>
       </c>
       <c r="D1240" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1240" t="s" s="3">
         <v>2471</v>
@@ -36761,7 +36770,7 @@
         <v>6</v>
       </c>
       <c r="D1241" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1241" t="s" s="3">
         <v>2473</v>
@@ -36778,7 +36787,7 @@
         <v>6</v>
       </c>
       <c r="D1242" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1242" t="s" s="3">
         <v>2475</v>
@@ -36795,7 +36804,7 @@
         <v>6</v>
       </c>
       <c r="D1243" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1243" t="s" s="3">
         <v>2477</v>
@@ -36812,7 +36821,7 @@
         <v>6</v>
       </c>
       <c r="D1244" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1244" t="s" s="3">
         <v>2479</v>
@@ -36829,7 +36838,7 @@
         <v>6</v>
       </c>
       <c r="D1245" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1245" t="s" s="3">
         <v>2481</v>
@@ -36846,7 +36855,7 @@
         <v>6</v>
       </c>
       <c r="D1246" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1246" t="s" s="3">
         <v>2483</v>
@@ -36863,7 +36872,7 @@
         <v>6</v>
       </c>
       <c r="D1247" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1247" t="s" s="3">
         <v>2485</v>
@@ -36880,7 +36889,7 @@
         <v>6</v>
       </c>
       <c r="D1248" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1248" t="s" s="3">
         <v>2487</v>
@@ -36897,7 +36906,7 @@
         <v>6</v>
       </c>
       <c r="D1249" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1249" t="s" s="3">
         <v>2489</v>
@@ -36914,7 +36923,7 @@
         <v>6</v>
       </c>
       <c r="D1250" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1250" t="s" s="3">
         <v>2491</v>
@@ -36931,7 +36940,7 @@
         <v>6</v>
       </c>
       <c r="D1251" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1251" t="s" s="3">
         <v>2493</v>
@@ -36948,7 +36957,7 @@
         <v>6</v>
       </c>
       <c r="D1252" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1252" t="s" s="3">
         <v>2495</v>
@@ -36965,7 +36974,7 @@
         <v>6</v>
       </c>
       <c r="D1253" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1253" t="s" s="3">
         <v>2497</v>
@@ -36982,7 +36991,7 @@
         <v>6</v>
       </c>
       <c r="D1254" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1254" t="s" s="3">
         <v>2499</v>
@@ -36999,7 +37008,7 @@
         <v>6</v>
       </c>
       <c r="D1255" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1255" t="s" s="3">
         <v>2501</v>
@@ -37016,7 +37025,7 @@
         <v>6</v>
       </c>
       <c r="D1256" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1256" t="s" s="3">
         <v>2503</v>
@@ -37033,7 +37042,7 @@
         <v>6</v>
       </c>
       <c r="D1257" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1257" t="s" s="3">
         <v>2505</v>
@@ -37050,7 +37059,7 @@
         <v>6</v>
       </c>
       <c r="D1258" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1258" t="s" s="3">
         <v>2507</v>
@@ -37067,7 +37076,7 @@
         <v>6</v>
       </c>
       <c r="D1259" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1259" t="s" s="3">
         <v>2509</v>
@@ -37084,7 +37093,7 @@
         <v>6</v>
       </c>
       <c r="D1260" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1260" t="s" s="3">
         <v>2511</v>
@@ -37101,7 +37110,7 @@
         <v>6</v>
       </c>
       <c r="D1261" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1261" t="s" s="3">
         <v>2513</v>
@@ -37118,7 +37127,7 @@
         <v>6</v>
       </c>
       <c r="D1262" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1262" t="s" s="3">
         <v>2515</v>
@@ -37135,7 +37144,7 @@
         <v>6</v>
       </c>
       <c r="D1263" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1263" t="s" s="3">
         <v>2517</v>
@@ -37152,7 +37161,7 @@
         <v>6</v>
       </c>
       <c r="D1264" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1264" t="s" s="3">
         <v>2519</v>
@@ -37169,7 +37178,7 @@
         <v>6</v>
       </c>
       <c r="D1265" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1265" t="s" s="3">
         <v>2521</v>
@@ -37186,7 +37195,7 @@
         <v>6</v>
       </c>
       <c r="D1266" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1266" t="s" s="3">
         <v>2523</v>
@@ -37203,7 +37212,7 @@
         <v>6</v>
       </c>
       <c r="D1267" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1267" t="s" s="3">
         <v>2525</v>
@@ -37220,7 +37229,7 @@
         <v>6</v>
       </c>
       <c r="D1268" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1268" t="s" s="3">
         <v>2527</v>
@@ -37237,7 +37246,7 @@
         <v>6</v>
       </c>
       <c r="D1269" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1269" t="s" s="3">
         <v>2529</v>
@@ -37254,7 +37263,7 @@
         <v>6</v>
       </c>
       <c r="D1270" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1270" t="s" s="3">
         <v>2531</v>
@@ -37271,7 +37280,7 @@
         <v>6</v>
       </c>
       <c r="D1271" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1271" t="s" s="3">
         <v>2533</v>
@@ -37288,7 +37297,7 @@
         <v>6</v>
       </c>
       <c r="D1272" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1272" t="s" s="3">
         <v>2535</v>
@@ -37305,7 +37314,7 @@
         <v>6</v>
       </c>
       <c r="D1273" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1273" t="s" s="3">
         <v>2537</v>
@@ -37322,7 +37331,7 @@
         <v>6</v>
       </c>
       <c r="D1274" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1274" t="s" s="3">
         <v>2539</v>
@@ -37339,7 +37348,7 @@
         <v>6</v>
       </c>
       <c r="D1275" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1275" t="s" s="3">
         <v>2541</v>
@@ -37356,7 +37365,7 @@
         <v>6</v>
       </c>
       <c r="D1276" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1276" t="s" s="3">
         <v>2543</v>
@@ -37373,7 +37382,7 @@
         <v>6</v>
       </c>
       <c r="D1277" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1277" t="s" s="3">
         <v>2545</v>
@@ -37390,7 +37399,7 @@
         <v>6</v>
       </c>
       <c r="D1278" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1278" t="s" s="3">
         <v>2547</v>
@@ -37407,7 +37416,7 @@
         <v>6</v>
       </c>
       <c r="D1279" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1279" t="s" s="3">
         <v>2549</v>
@@ -37424,7 +37433,7 @@
         <v>6</v>
       </c>
       <c r="D1280" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1280" t="s" s="3">
         <v>2551</v>
@@ -37441,7 +37450,7 @@
         <v>6</v>
       </c>
       <c r="D1281" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1281" t="s" s="3">
         <v>2553</v>
@@ -37458,7 +37467,7 @@
         <v>6</v>
       </c>
       <c r="D1282" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1282" t="s" s="3">
         <v>2555</v>
@@ -37475,7 +37484,7 @@
         <v>6</v>
       </c>
       <c r="D1283" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1283" t="s" s="3">
         <v>2557</v>
@@ -37492,7 +37501,7 @@
         <v>6</v>
       </c>
       <c r="D1284" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1284" t="s" s="3">
         <v>2559</v>
@@ -37509,7 +37518,7 @@
         <v>6</v>
       </c>
       <c r="D1285" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1285" t="s" s="3">
         <v>2561</v>
@@ -37526,7 +37535,7 @@
         <v>6</v>
       </c>
       <c r="D1286" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1286" t="s" s="3">
         <v>2563</v>
@@ -37543,7 +37552,7 @@
         <v>6</v>
       </c>
       <c r="D1287" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1287" t="s" s="3">
         <v>2565</v>
@@ -37560,7 +37569,7 @@
         <v>6</v>
       </c>
       <c r="D1288" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1288" t="s" s="3">
         <v>2567</v>
@@ -37577,7 +37586,7 @@
         <v>6</v>
       </c>
       <c r="D1289" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1289" t="s" s="3">
         <v>2569</v>
@@ -37594,7 +37603,7 @@
         <v>6</v>
       </c>
       <c r="D1290" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1290" t="s" s="3">
         <v>2571</v>
@@ -37611,7 +37620,7 @@
         <v>6</v>
       </c>
       <c r="D1291" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1291" t="s" s="3">
         <v>2573</v>
@@ -37628,7 +37637,7 @@
         <v>6</v>
       </c>
       <c r="D1292" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1292" t="s" s="3">
         <v>2575</v>
@@ -37645,7 +37654,7 @@
         <v>6</v>
       </c>
       <c r="D1293" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1293" t="s" s="3">
         <v>2577</v>
@@ -37662,7 +37671,7 @@
         <v>6</v>
       </c>
       <c r="D1294" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1294" t="s" s="3">
         <v>2579</v>
@@ -37679,7 +37688,7 @@
         <v>6</v>
       </c>
       <c r="D1295" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1295" t="s" s="3">
         <v>2581</v>
@@ -37696,7 +37705,7 @@
         <v>6</v>
       </c>
       <c r="D1296" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1296" t="s" s="3">
         <v>2583</v>
@@ -37713,7 +37722,7 @@
         <v>6</v>
       </c>
       <c r="D1297" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1297" t="s" s="3">
         <v>2585</v>
@@ -37730,7 +37739,7 @@
         <v>6</v>
       </c>
       <c r="D1298" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1298" t="s" s="3">
         <v>2587</v>
@@ -37747,7 +37756,7 @@
         <v>6</v>
       </c>
       <c r="D1299" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1299" t="s" s="3">
         <v>2589</v>
@@ -37764,7 +37773,7 @@
         <v>6</v>
       </c>
       <c r="D1300" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1300" t="s" s="3">
         <v>2591</v>
@@ -37781,7 +37790,7 @@
         <v>6</v>
       </c>
       <c r="D1301" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1301" t="s" s="3">
         <v>2593</v>
@@ -37798,7 +37807,7 @@
         <v>6</v>
       </c>
       <c r="D1302" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1302" t="s" s="3">
         <v>2595</v>
@@ -37815,7 +37824,7 @@
         <v>6</v>
       </c>
       <c r="D1303" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1303" t="s" s="3">
         <v>2597</v>
@@ -37832,7 +37841,7 @@
         <v>6</v>
       </c>
       <c r="D1304" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1304" t="s" s="3">
         <v>2599</v>
@@ -37849,7 +37858,7 @@
         <v>6</v>
       </c>
       <c r="D1305" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1305" t="s" s="3">
         <v>2601</v>
@@ -37866,7 +37875,7 @@
         <v>6</v>
       </c>
       <c r="D1306" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1306" t="s" s="3">
         <v>2603</v>
@@ -37877,16 +37886,16 @@
         <v>1306.0</v>
       </c>
       <c r="B1307" t="s" s="3">
+        <v>289</v>
+      </c>
+      <c r="C1307" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1307" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1307" t="s" s="3">
         <v>2604</v>
-      </c>
-      <c r="C1307" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1307" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1307" t="s" s="3">
-        <v>2605</v>
       </c>
     </row>
     <row r="1308" ht="36.0" customHeight="true">
@@ -37894,13 +37903,13 @@
         <v>1307.0</v>
       </c>
       <c r="B1308" t="s" s="3">
-        <v>289</v>
+        <v>2605</v>
       </c>
       <c r="C1308" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1308" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1308" t="s" s="3">
         <v>2606</v>
@@ -37917,7 +37926,7 @@
         <v>6</v>
       </c>
       <c r="D1309" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1309" t="s" s="3">
         <v>2608</v>
@@ -37934,7 +37943,7 @@
         <v>6</v>
       </c>
       <c r="D1310" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1310" t="s" s="3">
         <v>2610</v>
@@ -37951,7 +37960,7 @@
         <v>6</v>
       </c>
       <c r="D1311" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1311" t="s" s="3">
         <v>2612</v>
@@ -37968,7 +37977,7 @@
         <v>6</v>
       </c>
       <c r="D1312" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1312" t="s" s="3">
         <v>2614</v>
@@ -37985,7 +37994,7 @@
         <v>6</v>
       </c>
       <c r="D1313" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1313" t="s" s="3">
         <v>2616</v>
@@ -38002,7 +38011,7 @@
         <v>6</v>
       </c>
       <c r="D1314" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1314" t="s" s="3">
         <v>2618</v>
@@ -38019,7 +38028,7 @@
         <v>6</v>
       </c>
       <c r="D1315" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1315" t="s" s="3">
         <v>2620</v>
@@ -38036,7 +38045,7 @@
         <v>6</v>
       </c>
       <c r="D1316" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1316" t="s" s="3">
         <v>2622</v>
@@ -38053,7 +38062,7 @@
         <v>6</v>
       </c>
       <c r="D1317" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1317" t="s" s="3">
         <v>2624</v>
@@ -38070,7 +38079,7 @@
         <v>6</v>
       </c>
       <c r="D1318" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1318" t="s" s="3">
         <v>2626</v>
@@ -38087,7 +38096,7 @@
         <v>6</v>
       </c>
       <c r="D1319" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1319" t="s" s="3">
         <v>2628</v>
@@ -38104,7 +38113,7 @@
         <v>6</v>
       </c>
       <c r="D1320" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1320" t="s" s="3">
         <v>2630</v>
@@ -38121,7 +38130,7 @@
         <v>6</v>
       </c>
       <c r="D1321" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1321" t="s" s="3">
         <v>2632</v>
@@ -38138,7 +38147,7 @@
         <v>6</v>
       </c>
       <c r="D1322" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1322" t="s" s="3">
         <v>2634</v>
@@ -38155,7 +38164,7 @@
         <v>6</v>
       </c>
       <c r="D1323" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1323" t="s" s="3">
         <v>2636</v>
@@ -38172,7 +38181,7 @@
         <v>6</v>
       </c>
       <c r="D1324" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1324" t="s" s="3">
         <v>2638</v>
@@ -38189,7 +38198,7 @@
         <v>6</v>
       </c>
       <c r="D1325" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1325" t="s" s="3">
         <v>2640</v>
@@ -38206,7 +38215,7 @@
         <v>6</v>
       </c>
       <c r="D1326" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1326" t="s" s="3">
         <v>2642</v>
@@ -38223,7 +38232,7 @@
         <v>6</v>
       </c>
       <c r="D1327" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1327" t="s" s="3">
         <v>2644</v>
@@ -38240,7 +38249,7 @@
         <v>6</v>
       </c>
       <c r="D1328" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1328" t="s" s="3">
         <v>2646</v>
@@ -38257,7 +38266,7 @@
         <v>6</v>
       </c>
       <c r="D1329" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1329" t="s" s="3">
         <v>2648</v>
@@ -38274,7 +38283,7 @@
         <v>6</v>
       </c>
       <c r="D1330" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1330" t="s" s="3">
         <v>2650</v>
@@ -38291,7 +38300,7 @@
         <v>6</v>
       </c>
       <c r="D1331" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1331" t="s" s="3">
         <v>2652</v>
@@ -38308,7 +38317,7 @@
         <v>6</v>
       </c>
       <c r="D1332" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1332" t="s" s="3">
         <v>2654</v>
@@ -38325,7 +38334,7 @@
         <v>6</v>
       </c>
       <c r="D1333" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1333" t="s" s="3">
         <v>2656</v>
@@ -38342,7 +38351,7 @@
         <v>6</v>
       </c>
       <c r="D1334" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1334" t="s" s="3">
         <v>2658</v>
@@ -38359,7 +38368,7 @@
         <v>6</v>
       </c>
       <c r="D1335" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1335" t="s" s="3">
         <v>2660</v>
@@ -38376,7 +38385,7 @@
         <v>6</v>
       </c>
       <c r="D1336" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1336" t="s" s="3">
         <v>2662</v>
@@ -38393,7 +38402,7 @@
         <v>6</v>
       </c>
       <c r="D1337" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1337" t="s" s="3">
         <v>2664</v>
@@ -38410,7 +38419,7 @@
         <v>6</v>
       </c>
       <c r="D1338" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1338" t="s" s="3">
         <v>2666</v>
@@ -38427,7 +38436,7 @@
         <v>6</v>
       </c>
       <c r="D1339" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1339" t="s" s="3">
         <v>2668</v>
@@ -38444,7 +38453,7 @@
         <v>6</v>
       </c>
       <c r="D1340" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1340" t="s" s="3">
         <v>2670</v>
@@ -38461,7 +38470,7 @@
         <v>6</v>
       </c>
       <c r="D1341" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1341" t="s" s="3">
         <v>2672</v>
@@ -38478,7 +38487,7 @@
         <v>6</v>
       </c>
       <c r="D1342" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1342" t="s" s="3">
         <v>2674</v>
@@ -38495,7 +38504,7 @@
         <v>6</v>
       </c>
       <c r="D1343" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1343" t="s" s="3">
         <v>2676</v>
@@ -38512,7 +38521,7 @@
         <v>6</v>
       </c>
       <c r="D1344" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1344" t="s" s="3">
         <v>2678</v>
@@ -38529,7 +38538,7 @@
         <v>6</v>
       </c>
       <c r="D1345" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1345" t="s" s="3">
         <v>2680</v>
@@ -38546,7 +38555,7 @@
         <v>6</v>
       </c>
       <c r="D1346" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1346" t="s" s="3">
         <v>2682</v>
@@ -38563,7 +38572,7 @@
         <v>6</v>
       </c>
       <c r="D1347" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1347" t="s" s="3">
         <v>2684</v>
@@ -38580,7 +38589,7 @@
         <v>6</v>
       </c>
       <c r="D1348" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1348" t="s" s="3">
         <v>2686</v>
@@ -38597,7 +38606,7 @@
         <v>6</v>
       </c>
       <c r="D1349" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1349" t="s" s="3">
         <v>2688</v>
@@ -38614,7 +38623,7 @@
         <v>6</v>
       </c>
       <c r="D1350" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1350" t="s" s="3">
         <v>2690</v>
@@ -38631,7 +38640,7 @@
         <v>6</v>
       </c>
       <c r="D1351" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1351" t="s" s="3">
         <v>2692</v>
@@ -38648,7 +38657,7 @@
         <v>6</v>
       </c>
       <c r="D1352" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1352" t="s" s="3">
         <v>2694</v>
@@ -38665,7 +38674,7 @@
         <v>6</v>
       </c>
       <c r="D1353" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1353" t="s" s="3">
         <v>2696</v>
@@ -38682,7 +38691,7 @@
         <v>6</v>
       </c>
       <c r="D1354" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1354" t="s" s="3">
         <v>2698</v>
@@ -38699,7 +38708,7 @@
         <v>6</v>
       </c>
       <c r="D1355" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1355" t="s" s="3">
         <v>2700</v>
@@ -38716,7 +38725,7 @@
         <v>6</v>
       </c>
       <c r="D1356" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1356" t="s" s="3">
         <v>2702</v>
@@ -38733,7 +38742,7 @@
         <v>6</v>
       </c>
       <c r="D1357" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1357" t="s" s="3">
         <v>2704</v>
@@ -38750,10 +38759,10 @@
         <v>6</v>
       </c>
       <c r="D1358" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1358" t="s" s="3">
-        <v>2706</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1359" ht="36.0" customHeight="true">
@@ -38761,16 +38770,16 @@
         <v>1358.0</v>
       </c>
       <c r="B1359" t="s" s="3">
+        <v>2706</v>
+      </c>
+      <c r="C1359" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1359" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1359" t="s" s="3">
         <v>2707</v>
-      </c>
-      <c r="C1359" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1359" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1359" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1360" ht="36.0" customHeight="true">
@@ -38784,7 +38793,7 @@
         <v>6</v>
       </c>
       <c r="D1360" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1360" t="s" s="3">
         <v>2709</v>
@@ -38801,7 +38810,7 @@
         <v>6</v>
       </c>
       <c r="D1361" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1361" t="s" s="3">
         <v>2711</v>
@@ -38818,7 +38827,7 @@
         <v>6</v>
       </c>
       <c r="D1362" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1362" t="s" s="3">
         <v>2713</v>
@@ -38835,7 +38844,7 @@
         <v>6</v>
       </c>
       <c r="D1363" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1363" t="s" s="3">
         <v>2715</v>
@@ -38852,7 +38861,7 @@
         <v>6</v>
       </c>
       <c r="D1364" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1364" t="s" s="3">
         <v>2717</v>
@@ -38869,7 +38878,7 @@
         <v>6</v>
       </c>
       <c r="D1365" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1365" t="s" s="3">
         <v>2719</v>
@@ -38886,7 +38895,7 @@
         <v>6</v>
       </c>
       <c r="D1366" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1366" t="s" s="3">
         <v>2721</v>
@@ -38903,7 +38912,7 @@
         <v>6</v>
       </c>
       <c r="D1367" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1367" t="s" s="3">
         <v>2723</v>
@@ -38920,7 +38929,7 @@
         <v>6</v>
       </c>
       <c r="D1368" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1368" t="s" s="3">
         <v>2725</v>
@@ -38937,7 +38946,7 @@
         <v>6</v>
       </c>
       <c r="D1369" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1369" t="s" s="3">
         <v>2727</v>
@@ -38954,7 +38963,7 @@
         <v>6</v>
       </c>
       <c r="D1370" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1370" t="s" s="3">
         <v>2729</v>
@@ -38971,7 +38980,7 @@
         <v>6</v>
       </c>
       <c r="D1371" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1371" t="s" s="3">
         <v>2731</v>
@@ -38988,7 +38997,7 @@
         <v>6</v>
       </c>
       <c r="D1372" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1372" t="s" s="3">
         <v>2733</v>
@@ -39005,7 +39014,7 @@
         <v>6</v>
       </c>
       <c r="D1373" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1373" t="s" s="3">
         <v>2735</v>
@@ -39022,7 +39031,7 @@
         <v>6</v>
       </c>
       <c r="D1374" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1374" t="s" s="3">
         <v>2737</v>
@@ -39039,7 +39048,7 @@
         <v>6</v>
       </c>
       <c r="D1375" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1375" t="s" s="3">
         <v>2739</v>
@@ -39056,7 +39065,7 @@
         <v>6</v>
       </c>
       <c r="D1376" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1376" t="s" s="3">
         <v>2741</v>
@@ -39073,7 +39082,7 @@
         <v>6</v>
       </c>
       <c r="D1377" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1377" t="s" s="3">
         <v>2743</v>
@@ -39090,7 +39099,7 @@
         <v>6</v>
       </c>
       <c r="D1378" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1378" t="s" s="3">
         <v>2745</v>
@@ -39107,7 +39116,7 @@
         <v>6</v>
       </c>
       <c r="D1379" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1379" t="s" s="3">
         <v>2747</v>
@@ -39124,7 +39133,7 @@
         <v>6</v>
       </c>
       <c r="D1380" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1380" t="s" s="3">
         <v>2749</v>
@@ -39141,7 +39150,7 @@
         <v>6</v>
       </c>
       <c r="D1381" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1381" t="s" s="3">
         <v>2751</v>
@@ -39158,7 +39167,7 @@
         <v>6</v>
       </c>
       <c r="D1382" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1382" t="s" s="3">
         <v>2753</v>
@@ -39175,7 +39184,7 @@
         <v>6</v>
       </c>
       <c r="D1383" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1383" t="s" s="3">
         <v>2755</v>
@@ -39192,7 +39201,7 @@
         <v>6</v>
       </c>
       <c r="D1384" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1384" t="s" s="3">
         <v>2757</v>
@@ -39209,7 +39218,7 @@
         <v>6</v>
       </c>
       <c r="D1385" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1385" t="s" s="3">
         <v>2759</v>
@@ -39226,7 +39235,7 @@
         <v>6</v>
       </c>
       <c r="D1386" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1386" t="s" s="3">
         <v>2761</v>
@@ -39243,7 +39252,7 @@
         <v>6</v>
       </c>
       <c r="D1387" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1387" t="s" s="3">
         <v>2763</v>
@@ -39260,10 +39269,10 @@
         <v>6</v>
       </c>
       <c r="D1388" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1388" t="s" s="3">
-        <v>2765</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1389" ht="36.0" customHeight="true">
@@ -39271,16 +39280,16 @@
         <v>1388.0</v>
       </c>
       <c r="B1389" t="s" s="3">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="C1389" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1389" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1389" t="s" s="3">
-        <v>2308</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1390" ht="36.0" customHeight="true">
@@ -39288,16 +39297,16 @@
         <v>1389.0</v>
       </c>
       <c r="B1390" t="s" s="3">
+        <v>2766</v>
+      </c>
+      <c r="C1390" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1390" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1390" t="s" s="3">
         <v>2767</v>
-      </c>
-      <c r="C1390" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1390" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1390" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1391" ht="36.0" customHeight="true">
@@ -39311,7 +39320,7 @@
         <v>6</v>
       </c>
       <c r="D1391" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1391" t="s" s="3">
         <v>2769</v>
@@ -39328,7 +39337,7 @@
         <v>6</v>
       </c>
       <c r="D1392" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1392" t="s" s="3">
         <v>2771</v>
@@ -39345,7 +39354,7 @@
         <v>6</v>
       </c>
       <c r="D1393" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1393" t="s" s="3">
         <v>2773</v>
@@ -39362,7 +39371,7 @@
         <v>6</v>
       </c>
       <c r="D1394" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1394" t="s" s="3">
         <v>2775</v>
@@ -39379,7 +39388,7 @@
         <v>6</v>
       </c>
       <c r="D1395" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1395" t="s" s="3">
         <v>2777</v>
@@ -39396,7 +39405,7 @@
         <v>6</v>
       </c>
       <c r="D1396" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1396" t="s" s="3">
         <v>2779</v>
@@ -39413,7 +39422,7 @@
         <v>6</v>
       </c>
       <c r="D1397" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1397" t="s" s="3">
         <v>2781</v>
@@ -39430,7 +39439,7 @@
         <v>6</v>
       </c>
       <c r="D1398" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1398" t="s" s="3">
         <v>2783</v>
@@ -39447,7 +39456,7 @@
         <v>6</v>
       </c>
       <c r="D1399" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1399" t="s" s="3">
         <v>2785</v>
@@ -39464,7 +39473,7 @@
         <v>6</v>
       </c>
       <c r="D1400" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1400" t="s" s="3">
         <v>2787</v>
@@ -39481,10 +39490,10 @@
         <v>6</v>
       </c>
       <c r="D1401" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1401" t="s" s="3">
-        <v>2789</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1402" ht="36.0" customHeight="true">
@@ -39492,16 +39501,16 @@
         <v>1401.0</v>
       </c>
       <c r="B1402" t="s" s="3">
+        <v>2789</v>
+      </c>
+      <c r="C1402" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1402" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1402" t="s" s="3">
         <v>2790</v>
-      </c>
-      <c r="C1402" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1402" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1402" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1403" ht="36.0" customHeight="true">
@@ -39515,7 +39524,7 @@
         <v>6</v>
       </c>
       <c r="D1403" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1403" t="s" s="3">
         <v>2792</v>
@@ -39532,7 +39541,7 @@
         <v>6</v>
       </c>
       <c r="D1404" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1404" t="s" s="3">
         <v>2794</v>
@@ -39549,7 +39558,7 @@
         <v>6</v>
       </c>
       <c r="D1405" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1405" t="s" s="3">
         <v>2796</v>
@@ -39566,7 +39575,7 @@
         <v>6</v>
       </c>
       <c r="D1406" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1406" t="s" s="3">
         <v>2798</v>
@@ -39583,7 +39592,7 @@
         <v>6</v>
       </c>
       <c r="D1407" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1407" t="s" s="3">
         <v>2800</v>
@@ -39600,7 +39609,7 @@
         <v>6</v>
       </c>
       <c r="D1408" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1408" t="s" s="3">
         <v>2802</v>
@@ -39617,7 +39626,7 @@
         <v>6</v>
       </c>
       <c r="D1409" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1409" t="s" s="3">
         <v>2804</v>
@@ -39634,7 +39643,7 @@
         <v>6</v>
       </c>
       <c r="D1410" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1410" t="s" s="3">
         <v>2806</v>
@@ -39651,7 +39660,7 @@
         <v>6</v>
       </c>
       <c r="D1411" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1411" t="s" s="3">
         <v>2808</v>
@@ -39668,7 +39677,7 @@
         <v>6</v>
       </c>
       <c r="D1412" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1412" t="s" s="3">
         <v>2810</v>
@@ -39685,7 +39694,7 @@
         <v>6</v>
       </c>
       <c r="D1413" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1413" t="s" s="3">
         <v>2812</v>
@@ -39702,7 +39711,7 @@
         <v>6</v>
       </c>
       <c r="D1414" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1414" t="s" s="3">
         <v>2814</v>
@@ -39719,7 +39728,7 @@
         <v>6</v>
       </c>
       <c r="D1415" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1415" t="s" s="3">
         <v>2816</v>
@@ -39736,7 +39745,7 @@
         <v>6</v>
       </c>
       <c r="D1416" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1416" t="s" s="3">
         <v>2818</v>
@@ -39753,7 +39762,7 @@
         <v>6</v>
       </c>
       <c r="D1417" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1417" t="s" s="3">
         <v>2820</v>
@@ -39770,7 +39779,7 @@
         <v>6</v>
       </c>
       <c r="D1418" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1418" t="s" s="3">
         <v>2822</v>
@@ -39787,7 +39796,7 @@
         <v>6</v>
       </c>
       <c r="D1419" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1419" t="s" s="3">
         <v>2824</v>
@@ -39804,10 +39813,10 @@
         <v>6</v>
       </c>
       <c r="D1420" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1420" t="s" s="3">
-        <v>2826</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="1421" ht="36.0" customHeight="true">
@@ -39815,16 +39824,16 @@
         <v>1420.0</v>
       </c>
       <c r="B1421" t="s" s="3">
+        <v>2826</v>
+      </c>
+      <c r="C1421" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1421" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1421" t="s" s="3">
         <v>2827</v>
-      </c>
-      <c r="C1421" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1421" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1421" t="s" s="3">
-        <v>2820</v>
       </c>
     </row>
     <row r="1422" ht="36.0" customHeight="true">
@@ -39838,7 +39847,7 @@
         <v>6</v>
       </c>
       <c r="D1422" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1422" t="s" s="3">
         <v>2829</v>
@@ -39855,7 +39864,7 @@
         <v>6</v>
       </c>
       <c r="D1423" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1423" t="s" s="3">
         <v>2831</v>
@@ -39872,7 +39881,7 @@
         <v>6</v>
       </c>
       <c r="D1424" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1424" t="s" s="3">
         <v>2833</v>
@@ -39889,7 +39898,7 @@
         <v>6</v>
       </c>
       <c r="D1425" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1425" t="s" s="3">
         <v>2835</v>
@@ -39906,7 +39915,7 @@
         <v>6</v>
       </c>
       <c r="D1426" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1426" t="s" s="3">
         <v>2837</v>
@@ -39923,7 +39932,7 @@
         <v>6</v>
       </c>
       <c r="D1427" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1427" t="s" s="3">
         <v>2839</v>
@@ -39940,7 +39949,7 @@
         <v>6</v>
       </c>
       <c r="D1428" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1428" t="s" s="3">
         <v>2841</v>
@@ -39957,7 +39966,7 @@
         <v>6</v>
       </c>
       <c r="D1429" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1429" t="s" s="3">
         <v>2843</v>
@@ -39974,7 +39983,7 @@
         <v>6</v>
       </c>
       <c r="D1430" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1430" t="s" s="3">
         <v>2845</v>
@@ -39991,7 +40000,7 @@
         <v>6</v>
       </c>
       <c r="D1431" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1431" t="s" s="3">
         <v>2847</v>
@@ -40008,7 +40017,7 @@
         <v>6</v>
       </c>
       <c r="D1432" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1432" t="s" s="3">
         <v>2849</v>
@@ -40025,7 +40034,7 @@
         <v>6</v>
       </c>
       <c r="D1433" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1433" t="s" s="3">
         <v>2851</v>
@@ -40042,7 +40051,7 @@
         <v>6</v>
       </c>
       <c r="D1434" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1434" t="s" s="3">
         <v>2853</v>
@@ -40059,7 +40068,7 @@
         <v>6</v>
       </c>
       <c r="D1435" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1435" t="s" s="3">
         <v>2855</v>
@@ -40076,10 +40085,10 @@
         <v>6</v>
       </c>
       <c r="D1436" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1436" t="s" s="3">
-        <v>2857</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1437" ht="36.0" customHeight="true">
@@ -40087,16 +40096,16 @@
         <v>1436.0</v>
       </c>
       <c r="B1437" t="s" s="3">
+        <v>2857</v>
+      </c>
+      <c r="C1437" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1437" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1437" t="s" s="3">
         <v>2858</v>
-      </c>
-      <c r="C1437" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1437" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1437" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1438" ht="36.0" customHeight="true">
@@ -40110,10 +40119,10 @@
         <v>6</v>
       </c>
       <c r="D1438" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1438" t="s" s="3">
-        <v>2860</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="1439" ht="36.0" customHeight="true">
@@ -40121,16 +40130,16 @@
         <v>1438.0</v>
       </c>
       <c r="B1439" t="s" s="3">
+        <v>2860</v>
+      </c>
+      <c r="C1439" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1439" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1439" t="s" s="3">
         <v>2861</v>
-      </c>
-      <c r="C1439" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1439" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1439" t="s" s="3">
-        <v>2808</v>
       </c>
     </row>
     <row r="1440" ht="36.0" customHeight="true">
@@ -40144,7 +40153,7 @@
         <v>6</v>
       </c>
       <c r="D1440" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1440" t="s" s="3">
         <v>2863</v>
@@ -40161,7 +40170,7 @@
         <v>6</v>
       </c>
       <c r="D1441" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1441" t="s" s="3">
         <v>2865</v>
@@ -40178,7 +40187,7 @@
         <v>6</v>
       </c>
       <c r="D1442" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1442" t="s" s="3">
         <v>2867</v>
@@ -40195,10 +40204,10 @@
         <v>6</v>
       </c>
       <c r="D1443" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1443" t="s" s="3">
-        <v>2869</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1444" ht="36.0" customHeight="true">
@@ -40206,16 +40215,16 @@
         <v>1443.0</v>
       </c>
       <c r="B1444" t="s" s="3">
+        <v>2869</v>
+      </c>
+      <c r="C1444" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1444" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1444" t="s" s="3">
         <v>2870</v>
-      </c>
-      <c r="C1444" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1444" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1444" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1445" ht="36.0" customHeight="true">
@@ -40229,7 +40238,7 @@
         <v>6</v>
       </c>
       <c r="D1445" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1445" t="s" s="3">
         <v>2872</v>
@@ -40246,7 +40255,7 @@
         <v>6</v>
       </c>
       <c r="D1446" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1446" t="s" s="3">
         <v>2874</v>
@@ -40263,7 +40272,7 @@
         <v>6</v>
       </c>
       <c r="D1447" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1447" t="s" s="3">
         <v>2876</v>
@@ -40280,7 +40289,7 @@
         <v>6</v>
       </c>
       <c r="D1448" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1448" t="s" s="3">
         <v>2878</v>
@@ -40297,7 +40306,7 @@
         <v>6</v>
       </c>
       <c r="D1449" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1449" t="s" s="3">
         <v>2880</v>
@@ -40314,7 +40323,7 @@
         <v>6</v>
       </c>
       <c r="D1450" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1450" t="s" s="3">
         <v>2882</v>
@@ -40331,7 +40340,7 @@
         <v>6</v>
       </c>
       <c r="D1451" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1451" t="s" s="3">
         <v>2884</v>
@@ -40348,7 +40357,7 @@
         <v>6</v>
       </c>
       <c r="D1452" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1452" t="s" s="3">
         <v>2886</v>
@@ -40365,7 +40374,7 @@
         <v>6</v>
       </c>
       <c r="D1453" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1453" t="s" s="3">
         <v>2888</v>
@@ -40382,7 +40391,7 @@
         <v>6</v>
       </c>
       <c r="D1454" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1454" t="s" s="3">
         <v>2890</v>
@@ -40393,16 +40402,16 @@
         <v>1454.0</v>
       </c>
       <c r="B1455" t="s" s="3">
+        <v>2889</v>
+      </c>
+      <c r="C1455" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1455" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1455" t="s" s="3">
         <v>2891</v>
-      </c>
-      <c r="C1455" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1455" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1455" t="s" s="3">
-        <v>2892</v>
       </c>
     </row>
     <row r="1456" ht="36.0" customHeight="true">
@@ -40410,13 +40419,13 @@
         <v>1455.0</v>
       </c>
       <c r="B1456" t="s" s="3">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="C1456" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1456" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1456" t="s" s="3">
         <v>2893</v>
@@ -40433,7 +40442,7 @@
         <v>6</v>
       </c>
       <c r="D1457" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1457" t="s" s="3">
         <v>2895</v>
@@ -40450,7 +40459,7 @@
         <v>6</v>
       </c>
       <c r="D1458" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1458" t="s" s="3">
         <v>2897</v>
@@ -40467,7 +40476,7 @@
         <v>6</v>
       </c>
       <c r="D1459" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1459" t="s" s="3">
         <v>2899</v>
@@ -40484,7 +40493,7 @@
         <v>6</v>
       </c>
       <c r="D1460" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1460" t="s" s="3">
         <v>2901</v>
@@ -40501,7 +40510,7 @@
         <v>6</v>
       </c>
       <c r="D1461" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1461" t="s" s="3">
         <v>2903</v>
@@ -40518,7 +40527,7 @@
         <v>6</v>
       </c>
       <c r="D1462" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1462" t="s" s="3">
         <v>2905</v>
@@ -40535,7 +40544,7 @@
         <v>6</v>
       </c>
       <c r="D1463" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1463" t="s" s="3">
         <v>2907</v>
@@ -40552,7 +40561,7 @@
         <v>6</v>
       </c>
       <c r="D1464" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1464" t="s" s="3">
         <v>2909</v>
@@ -40569,7 +40578,7 @@
         <v>6</v>
       </c>
       <c r="D1465" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1465" t="s" s="3">
         <v>2911</v>
@@ -40586,7 +40595,7 @@
         <v>6</v>
       </c>
       <c r="D1466" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1466" t="s" s="3">
         <v>2913</v>
@@ -40603,7 +40612,7 @@
         <v>6</v>
       </c>
       <c r="D1467" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1467" t="s" s="3">
         <v>2915</v>
@@ -40620,7 +40629,7 @@
         <v>6</v>
       </c>
       <c r="D1468" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1468" t="s" s="3">
         <v>2917</v>
@@ -40637,7 +40646,7 @@
         <v>6</v>
       </c>
       <c r="D1469" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1469" t="s" s="3">
         <v>2919</v>
@@ -40654,7 +40663,7 @@
         <v>6</v>
       </c>
       <c r="D1470" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1470" t="s" s="3">
         <v>2921</v>
@@ -40671,7 +40680,7 @@
         <v>6</v>
       </c>
       <c r="D1471" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1471" t="s" s="3">
         <v>2923</v>
@@ -40688,7 +40697,7 @@
         <v>6</v>
       </c>
       <c r="D1472" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1472" t="s" s="3">
         <v>2925</v>
@@ -40705,7 +40714,7 @@
         <v>6</v>
       </c>
       <c r="D1473" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1473" t="s" s="3">
         <v>2927</v>
@@ -40722,7 +40731,7 @@
         <v>6</v>
       </c>
       <c r="D1474" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1474" t="s" s="3">
         <v>2929</v>
@@ -40739,7 +40748,7 @@
         <v>6</v>
       </c>
       <c r="D1475" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1475" t="s" s="3">
         <v>2931</v>
@@ -40756,7 +40765,7 @@
         <v>6</v>
       </c>
       <c r="D1476" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1476" t="s" s="3">
         <v>2933</v>
@@ -40773,7 +40782,7 @@
         <v>6</v>
       </c>
       <c r="D1477" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1477" t="s" s="3">
         <v>2935</v>
@@ -40790,7 +40799,7 @@
         <v>6</v>
       </c>
       <c r="D1478" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1478" t="s" s="3">
         <v>2937</v>
@@ -40807,7 +40816,7 @@
         <v>6</v>
       </c>
       <c r="D1479" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1479" t="s" s="3">
         <v>2939</v>
@@ -40824,7 +40833,7 @@
         <v>6</v>
       </c>
       <c r="D1480" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1480" t="s" s="3">
         <v>2941</v>
@@ -40841,7 +40850,7 @@
         <v>6</v>
       </c>
       <c r="D1481" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1481" t="s" s="3">
         <v>2943</v>
@@ -40858,7 +40867,7 @@
         <v>6</v>
       </c>
       <c r="D1482" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1482" t="s" s="3">
         <v>2945</v>
@@ -40875,7 +40884,7 @@
         <v>6</v>
       </c>
       <c r="D1483" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1483" t="s" s="3">
         <v>2947</v>
@@ -40892,7 +40901,7 @@
         <v>6</v>
       </c>
       <c r="D1484" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1484" t="s" s="3">
         <v>2949</v>
@@ -40909,7 +40918,7 @@
         <v>6</v>
       </c>
       <c r="D1485" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1485" t="s" s="3">
         <v>2951</v>
@@ -40926,7 +40935,7 @@
         <v>6</v>
       </c>
       <c r="D1486" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1486" t="s" s="3">
         <v>2953</v>
@@ -40943,7 +40952,7 @@
         <v>6</v>
       </c>
       <c r="D1487" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1487" t="s" s="3">
         <v>2955</v>
@@ -40960,7 +40969,7 @@
         <v>6</v>
       </c>
       <c r="D1488" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1488" t="s" s="3">
         <v>2957</v>
@@ -40977,7 +40986,7 @@
         <v>6</v>
       </c>
       <c r="D1489" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1489" t="s" s="3">
         <v>2959</v>
@@ -40994,7 +41003,7 @@
         <v>6</v>
       </c>
       <c r="D1490" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1490" t="s" s="3">
         <v>2961</v>
@@ -41011,7 +41020,7 @@
         <v>6</v>
       </c>
       <c r="D1491" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1491" t="s" s="3">
         <v>2963</v>
@@ -41028,7 +41037,7 @@
         <v>6</v>
       </c>
       <c r="D1492" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1492" t="s" s="3">
         <v>2965</v>
@@ -41045,7 +41054,7 @@
         <v>6</v>
       </c>
       <c r="D1493" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1493" t="s" s="3">
         <v>2967</v>
@@ -41062,7 +41071,7 @@
         <v>6</v>
       </c>
       <c r="D1494" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1494" t="s" s="3">
         <v>2969</v>
@@ -41079,7 +41088,7 @@
         <v>6</v>
       </c>
       <c r="D1495" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1495" t="s" s="3">
         <v>2971</v>
@@ -41096,7 +41105,7 @@
         <v>6</v>
       </c>
       <c r="D1496" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1496" t="s" s="3">
         <v>2973</v>
@@ -41113,7 +41122,7 @@
         <v>6</v>
       </c>
       <c r="D1497" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1497" t="s" s="3">
         <v>2975</v>
@@ -41130,7 +41139,7 @@
         <v>6</v>
       </c>
       <c r="D1498" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1498" t="s" s="3">
         <v>2977</v>
@@ -41147,7 +41156,7 @@
         <v>6</v>
       </c>
       <c r="D1499" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1499" t="s" s="3">
         <v>2979</v>
@@ -41164,10 +41173,10 @@
         <v>6</v>
       </c>
       <c r="D1500" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1500" t="s" s="3">
-        <v>2981</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1501" ht="36.0" customHeight="true">
@@ -41175,16 +41184,16 @@
         <v>1500.0</v>
       </c>
       <c r="B1501" t="s" s="3">
+        <v>2981</v>
+      </c>
+      <c r="C1501" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1501" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1501" t="s" s="3">
         <v>2982</v>
-      </c>
-      <c r="C1501" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1501" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1501" t="s" s="3">
-        <v>2308</v>
       </c>
     </row>
     <row r="1502" ht="36.0" customHeight="true">
@@ -41198,7 +41207,7 @@
         <v>6</v>
       </c>
       <c r="D1502" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1502" t="s" s="3">
         <v>2984</v>
@@ -41215,7 +41224,7 @@
         <v>6</v>
       </c>
       <c r="D1503" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1503" t="s" s="3">
         <v>2986</v>
@@ -41232,7 +41241,7 @@
         <v>6</v>
       </c>
       <c r="D1504" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1504" t="s" s="3">
         <v>2988</v>
@@ -41249,7 +41258,7 @@
         <v>6</v>
       </c>
       <c r="D1505" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1505" t="s" s="3">
         <v>2990</v>
@@ -41266,7 +41275,7 @@
         <v>6</v>
       </c>
       <c r="D1506" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1506" t="s" s="3">
         <v>2992</v>
@@ -41283,7 +41292,7 @@
         <v>6</v>
       </c>
       <c r="D1507" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1507" t="s" s="3">
         <v>2994</v>
@@ -41300,7 +41309,7 @@
         <v>6</v>
       </c>
       <c r="D1508" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1508" t="s" s="3">
         <v>2996</v>
@@ -41317,7 +41326,7 @@
         <v>6</v>
       </c>
       <c r="D1509" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1509" t="s" s="3">
         <v>2998</v>
@@ -41334,7 +41343,7 @@
         <v>6</v>
       </c>
       <c r="D1510" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1510" t="s" s="3">
         <v>3000</v>
@@ -41351,7 +41360,7 @@
         <v>6</v>
       </c>
       <c r="D1511" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1511" t="s" s="3">
         <v>3002</v>
@@ -41368,7 +41377,7 @@
         <v>6</v>
       </c>
       <c r="D1512" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1512" t="s" s="3">
         <v>3004</v>
@@ -41385,7 +41394,7 @@
         <v>6</v>
       </c>
       <c r="D1513" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1513" t="s" s="3">
         <v>3006</v>
@@ -41402,7 +41411,7 @@
         <v>6</v>
       </c>
       <c r="D1514" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1514" t="s" s="3">
         <v>3008</v>
@@ -41419,7 +41428,7 @@
         <v>6</v>
       </c>
       <c r="D1515" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1515" t="s" s="3">
         <v>3010</v>
@@ -41436,7 +41445,7 @@
         <v>6</v>
       </c>
       <c r="D1516" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1516" t="s" s="3">
         <v>3012</v>
@@ -41453,7 +41462,7 @@
         <v>6</v>
       </c>
       <c r="D1517" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1517" t="s" s="3">
         <v>3014</v>
@@ -41470,7 +41479,7 @@
         <v>6</v>
       </c>
       <c r="D1518" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1518" t="s" s="3">
         <v>3016</v>
@@ -41487,7 +41496,7 @@
         <v>6</v>
       </c>
       <c r="D1519" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1519" t="s" s="3">
         <v>3018</v>
@@ -41504,7 +41513,7 @@
         <v>6</v>
       </c>
       <c r="D1520" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1520" t="s" s="3">
         <v>3020</v>
@@ -41521,7 +41530,7 @@
         <v>6</v>
       </c>
       <c r="D1521" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1521" t="s" s="3">
         <v>3022</v>
@@ -41538,7 +41547,7 @@
         <v>6</v>
       </c>
       <c r="D1522" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1522" t="s" s="3">
         <v>3024</v>
@@ -41555,7 +41564,7 @@
         <v>6</v>
       </c>
       <c r="D1523" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1523" t="s" s="3">
         <v>3026</v>
@@ -41572,7 +41581,7 @@
         <v>6</v>
       </c>
       <c r="D1524" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1524" t="s" s="3">
         <v>3028</v>
@@ -41589,7 +41598,7 @@
         <v>6</v>
       </c>
       <c r="D1525" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1525" t="s" s="3">
         <v>3030</v>
@@ -41606,7 +41615,7 @@
         <v>6</v>
       </c>
       <c r="D1526" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1526" t="s" s="3">
         <v>3032</v>
@@ -41623,7 +41632,7 @@
         <v>6</v>
       </c>
       <c r="D1527" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1527" t="s" s="3">
         <v>3034</v>
@@ -41640,7 +41649,7 @@
         <v>6</v>
       </c>
       <c r="D1528" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1528" t="s" s="3">
         <v>3036</v>
@@ -41657,7 +41666,7 @@
         <v>6</v>
       </c>
       <c r="D1529" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1529" t="s" s="3">
         <v>3038</v>
@@ -41674,7 +41683,7 @@
         <v>6</v>
       </c>
       <c r="D1530" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1530" t="s" s="3">
         <v>3040</v>
@@ -41691,7 +41700,7 @@
         <v>6</v>
       </c>
       <c r="D1531" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1531" t="s" s="3">
         <v>3042</v>
@@ -41708,7 +41717,7 @@
         <v>6</v>
       </c>
       <c r="D1532" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1532" t="s" s="3">
         <v>3044</v>
@@ -41725,7 +41734,7 @@
         <v>6</v>
       </c>
       <c r="D1533" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1533" t="s" s="3">
         <v>3046</v>
@@ -41742,7 +41751,7 @@
         <v>6</v>
       </c>
       <c r="D1534" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1534" t="s" s="3">
         <v>3048</v>
@@ -41759,7 +41768,7 @@
         <v>6</v>
       </c>
       <c r="D1535" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1535" t="s" s="3">
         <v>3050</v>
@@ -41776,7 +41785,7 @@
         <v>6</v>
       </c>
       <c r="D1536" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1536" t="s" s="3">
         <v>3052</v>
@@ -41793,7 +41802,7 @@
         <v>6</v>
       </c>
       <c r="D1537" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1537" t="s" s="3">
         <v>3054</v>
@@ -41810,7 +41819,7 @@
         <v>6</v>
       </c>
       <c r="D1538" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1538" t="s" s="3">
         <v>3056</v>
@@ -41827,7 +41836,7 @@
         <v>6</v>
       </c>
       <c r="D1539" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1539" t="s" s="3">
         <v>3058</v>
@@ -41844,7 +41853,7 @@
         <v>6</v>
       </c>
       <c r="D1540" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1540" t="s" s="3">
         <v>3060</v>
@@ -41861,7 +41870,7 @@
         <v>6</v>
       </c>
       <c r="D1541" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1541" t="s" s="3">
         <v>3062</v>
@@ -41878,7 +41887,7 @@
         <v>6</v>
       </c>
       <c r="D1542" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1542" t="s" s="3">
         <v>3064</v>
@@ -41895,7 +41904,7 @@
         <v>6</v>
       </c>
       <c r="D1543" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1543" t="s" s="3">
         <v>3066</v>
@@ -41912,7 +41921,7 @@
         <v>6</v>
       </c>
       <c r="D1544" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1544" t="s" s="3">
         <v>3068</v>
@@ -41929,7 +41938,7 @@
         <v>6</v>
       </c>
       <c r="D1545" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1545" t="s" s="3">
         <v>3070</v>
@@ -41946,7 +41955,7 @@
         <v>6</v>
       </c>
       <c r="D1546" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1546" t="s" s="3">
         <v>3072</v>
@@ -41963,7 +41972,7 @@
         <v>6</v>
       </c>
       <c r="D1547" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1547" t="s" s="3">
         <v>3074</v>
@@ -41980,7 +41989,7 @@
         <v>6</v>
       </c>
       <c r="D1548" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1548" t="s" s="3">
         <v>3076</v>
@@ -41997,7 +42006,7 @@
         <v>6</v>
       </c>
       <c r="D1549" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1549" t="s" s="3">
         <v>3078</v>
@@ -42014,7 +42023,7 @@
         <v>6</v>
       </c>
       <c r="D1550" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1550" t="s" s="3">
         <v>3080</v>
@@ -42031,7 +42040,7 @@
         <v>6</v>
       </c>
       <c r="D1551" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1551" t="s" s="3">
         <v>3082</v>
@@ -42048,7 +42057,7 @@
         <v>6</v>
       </c>
       <c r="D1552" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1552" t="s" s="3">
         <v>3084</v>
@@ -42065,7 +42074,7 @@
         <v>6</v>
       </c>
       <c r="D1553" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1553" t="s" s="3">
         <v>3086</v>
@@ -42082,7 +42091,7 @@
         <v>6</v>
       </c>
       <c r="D1554" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1554" t="s" s="3">
         <v>3088</v>
@@ -42099,7 +42108,7 @@
         <v>6</v>
       </c>
       <c r="D1555" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1555" t="s" s="3">
         <v>3090</v>
@@ -42116,7 +42125,7 @@
         <v>6</v>
       </c>
       <c r="D1556" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1556" t="s" s="3">
         <v>3092</v>
@@ -42133,7 +42142,7 @@
         <v>6</v>
       </c>
       <c r="D1557" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1557" t="s" s="3">
         <v>3094</v>
@@ -42150,7 +42159,7 @@
         <v>6</v>
       </c>
       <c r="D1558" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1558" t="s" s="3">
         <v>3096</v>
@@ -42167,7 +42176,7 @@
         <v>6</v>
       </c>
       <c r="D1559" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1559" t="s" s="3">
         <v>3098</v>
@@ -42184,7 +42193,7 @@
         <v>6</v>
       </c>
       <c r="D1560" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1560" t="s" s="3">
         <v>3100</v>
@@ -42201,7 +42210,7 @@
         <v>6</v>
       </c>
       <c r="D1561" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1561" t="s" s="3">
         <v>3102</v>
@@ -42218,7 +42227,7 @@
         <v>6</v>
       </c>
       <c r="D1562" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1562" t="s" s="3">
         <v>3104</v>
@@ -42235,7 +42244,7 @@
         <v>6</v>
       </c>
       <c r="D1563" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1563" t="s" s="3">
         <v>3106</v>
@@ -42252,7 +42261,7 @@
         <v>6</v>
       </c>
       <c r="D1564" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1564" t="s" s="3">
         <v>3108</v>
@@ -42269,7 +42278,7 @@
         <v>6</v>
       </c>
       <c r="D1565" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1565" t="s" s="3">
         <v>3110</v>
@@ -42286,7 +42295,7 @@
         <v>6</v>
       </c>
       <c r="D1566" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1566" t="s" s="3">
         <v>3112</v>
@@ -42303,7 +42312,7 @@
         <v>6</v>
       </c>
       <c r="D1567" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1567" t="s" s="3">
         <v>3114</v>
@@ -42320,7 +42329,7 @@
         <v>6</v>
       </c>
       <c r="D1568" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1568" t="s" s="3">
         <v>3116</v>
@@ -42337,7 +42346,7 @@
         <v>6</v>
       </c>
       <c r="D1569" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1569" t="s" s="3">
         <v>3118</v>
@@ -42354,7 +42363,7 @@
         <v>6</v>
       </c>
       <c r="D1570" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1570" t="s" s="3">
         <v>3120</v>
@@ -42371,7 +42380,7 @@
         <v>6</v>
       </c>
       <c r="D1571" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1571" t="s" s="3">
         <v>3122</v>
@@ -42388,7 +42397,7 @@
         <v>6</v>
       </c>
       <c r="D1572" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1572" t="s" s="3">
         <v>3124</v>
@@ -42405,7 +42414,7 @@
         <v>6</v>
       </c>
       <c r="D1573" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1573" t="s" s="3">
         <v>3126</v>
@@ -42422,7 +42431,7 @@
         <v>6</v>
       </c>
       <c r="D1574" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1574" t="s" s="3">
         <v>3128</v>
@@ -42439,7 +42448,7 @@
         <v>6</v>
       </c>
       <c r="D1575" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1575" t="s" s="3">
         <v>3130</v>
@@ -42456,7 +42465,7 @@
         <v>6</v>
       </c>
       <c r="D1576" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1576" t="s" s="3">
         <v>3132</v>
@@ -42473,7 +42482,7 @@
         <v>6</v>
       </c>
       <c r="D1577" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1577" t="s" s="3">
         <v>3134</v>
@@ -42490,7 +42499,7 @@
         <v>6</v>
       </c>
       <c r="D1578" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1578" t="s" s="3">
         <v>3136</v>
@@ -42507,7 +42516,7 @@
         <v>6</v>
       </c>
       <c r="D1579" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1579" t="s" s="3">
         <v>3138</v>
@@ -42524,7 +42533,7 @@
         <v>6</v>
       </c>
       <c r="D1580" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1580" t="s" s="3">
         <v>3140</v>
@@ -42541,7 +42550,7 @@
         <v>6</v>
       </c>
       <c r="D1581" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1581" t="s" s="3">
         <v>3142</v>
@@ -42558,7 +42567,7 @@
         <v>6</v>
       </c>
       <c r="D1582" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1582" t="s" s="3">
         <v>3144</v>
@@ -42575,7 +42584,7 @@
         <v>6</v>
       </c>
       <c r="D1583" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1583" t="s" s="3">
         <v>3146</v>
@@ -42592,7 +42601,7 @@
         <v>6</v>
       </c>
       <c r="D1584" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1584" t="s" s="3">
         <v>3148</v>
@@ -42609,7 +42618,7 @@
         <v>6</v>
       </c>
       <c r="D1585" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1585" t="s" s="3">
         <v>3150</v>
@@ -42626,7 +42635,7 @@
         <v>6</v>
       </c>
       <c r="D1586" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1586" t="s" s="3">
         <v>3152</v>
@@ -42643,7 +42652,7 @@
         <v>6</v>
       </c>
       <c r="D1587" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1587" t="s" s="3">
         <v>3154</v>
@@ -42660,7 +42669,7 @@
         <v>6</v>
       </c>
       <c r="D1588" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1588" t="s" s="3">
         <v>3156</v>
@@ -42677,7 +42686,7 @@
         <v>6</v>
       </c>
       <c r="D1589" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1589" t="s" s="3">
         <v>3158</v>
@@ -42694,7 +42703,7 @@
         <v>6</v>
       </c>
       <c r="D1590" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1590" t="s" s="3">
         <v>3160</v>
@@ -42711,7 +42720,7 @@
         <v>6</v>
       </c>
       <c r="D1591" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1591" t="s" s="3">
         <v>3162</v>
@@ -42728,7 +42737,7 @@
         <v>6</v>
       </c>
       <c r="D1592" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1592" t="s" s="3">
         <v>3164</v>
@@ -42745,7 +42754,7 @@
         <v>6</v>
       </c>
       <c r="D1593" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1593" t="s" s="3">
         <v>3166</v>
@@ -42762,7 +42771,7 @@
         <v>6</v>
       </c>
       <c r="D1594" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1594" t="s" s="3">
         <v>3168</v>
@@ -42779,7 +42788,7 @@
         <v>6</v>
       </c>
       <c r="D1595" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1595" t="s" s="3">
         <v>3170</v>
@@ -42796,7 +42805,7 @@
         <v>6</v>
       </c>
       <c r="D1596" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1596" t="s" s="3">
         <v>3172</v>
@@ -42807,16 +42816,16 @@
         <v>1596.0</v>
       </c>
       <c r="B1597" t="s" s="3">
+        <v>664</v>
+      </c>
+      <c r="C1597" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1597" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1597" t="s" s="3">
         <v>3173</v>
-      </c>
-      <c r="C1597" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D1597" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1597" t="s" s="3">
-        <v>3174</v>
       </c>
     </row>
     <row r="1598" ht="36.0" customHeight="true">
@@ -42824,13 +42833,13 @@
         <v>1597.0</v>
       </c>
       <c r="B1598" t="s" s="3">
-        <v>664</v>
+        <v>3174</v>
       </c>
       <c r="C1598" t="s" s="2">
         <v>6</v>
       </c>
       <c r="D1598" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1598" t="s" s="3">
         <v>3175</v>
@@ -42847,7 +42856,7 @@
         <v>6</v>
       </c>
       <c r="D1599" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1599" t="s" s="3">
         <v>3177</v>
@@ -42864,7 +42873,7 @@
         <v>6</v>
       </c>
       <c r="D1600" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1600" t="s" s="3">
         <v>3179</v>
@@ -42881,7 +42890,7 @@
         <v>6</v>
       </c>
       <c r="D1601" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1601" t="s" s="3">
         <v>3181</v>
@@ -42898,7 +42907,7 @@
         <v>6</v>
       </c>
       <c r="D1602" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1602" t="s" s="3">
         <v>3183</v>
@@ -42915,7 +42924,7 @@
         <v>6</v>
       </c>
       <c r="D1603" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1603" t="s" s="3">
         <v>3185</v>
@@ -42932,7 +42941,7 @@
         <v>6</v>
       </c>
       <c r="D1604" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1604" t="s" s="3">
         <v>3187</v>
@@ -42949,7 +42958,7 @@
         <v>6</v>
       </c>
       <c r="D1605" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1605" t="s" s="3">
         <v>3189</v>
@@ -42966,7 +42975,7 @@
         <v>6</v>
       </c>
       <c r="D1606" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1606" t="s" s="3">
         <v>3191</v>
@@ -42983,7 +42992,7 @@
         <v>6</v>
       </c>
       <c r="D1607" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1607" t="s" s="3">
         <v>3193</v>
@@ -43000,7 +43009,7 @@
         <v>6</v>
       </c>
       <c r="D1608" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1608" t="s" s="3">
         <v>3195</v>
@@ -43017,7 +43026,7 @@
         <v>6</v>
       </c>
       <c r="D1609" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1609" t="s" s="3">
         <v>3197</v>
@@ -43034,7 +43043,7 @@
         <v>6</v>
       </c>
       <c r="D1610" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1610" t="s" s="3">
         <v>3199</v>
@@ -43051,7 +43060,7 @@
         <v>6</v>
       </c>
       <c r="D1611" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1611" t="s" s="3">
         <v>3201</v>
@@ -43068,7 +43077,7 @@
         <v>6</v>
       </c>
       <c r="D1612" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1612" t="s" s="3">
         <v>3203</v>
@@ -43085,7 +43094,7 @@
         <v>6</v>
       </c>
       <c r="D1613" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1613" t="s" s="3">
         <v>3205</v>
@@ -43102,7 +43111,7 @@
         <v>6</v>
       </c>
       <c r="D1614" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1614" t="s" s="3">
         <v>3207</v>
@@ -43119,7 +43128,7 @@
         <v>6</v>
       </c>
       <c r="D1615" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1615" t="s" s="3">
         <v>3209</v>
@@ -43136,7 +43145,7 @@
         <v>6</v>
       </c>
       <c r="D1616" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1616" t="s" s="3">
         <v>3211</v>
@@ -43153,7 +43162,7 @@
         <v>6</v>
       </c>
       <c r="D1617" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1617" t="s" s="3">
         <v>3213</v>
@@ -43170,7 +43179,7 @@
         <v>6</v>
       </c>
       <c r="D1618" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1618" t="s" s="3">
         <v>3215</v>
@@ -43187,7 +43196,7 @@
         <v>6</v>
       </c>
       <c r="D1619" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1619" t="s" s="3">
         <v>3217</v>
@@ -43204,7 +43213,7 @@
         <v>6</v>
       </c>
       <c r="D1620" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1620" t="s" s="3">
         <v>3219</v>
@@ -43221,7 +43230,7 @@
         <v>6</v>
       </c>
       <c r="D1621" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1621" t="s" s="3">
         <v>3221</v>
@@ -43238,7 +43247,7 @@
         <v>6</v>
       </c>
       <c r="D1622" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1622" t="s" s="3">
         <v>3223</v>
@@ -43255,7 +43264,7 @@
         <v>6</v>
       </c>
       <c r="D1623" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1623" t="s" s="3">
         <v>3225</v>
@@ -43272,7 +43281,7 @@
         <v>6</v>
       </c>
       <c r="D1624" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1624" t="s" s="3">
         <v>3227</v>
@@ -43289,7 +43298,7 @@
         <v>6</v>
       </c>
       <c r="D1625" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1625" t="s" s="3">
         <v>3229</v>
@@ -43306,7 +43315,7 @@
         <v>6</v>
       </c>
       <c r="D1626" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1626" t="s" s="3">
         <v>3231</v>
@@ -43323,7 +43332,7 @@
         <v>6</v>
       </c>
       <c r="D1627" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1627" t="s" s="3">
         <v>3233</v>
@@ -43340,7 +43349,7 @@
         <v>6</v>
       </c>
       <c r="D1628" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1628" t="s" s="3">
         <v>3235</v>
@@ -43357,7 +43366,7 @@
         <v>6</v>
       </c>
       <c r="D1629" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1629" t="s" s="3">
         <v>3237</v>
@@ -43371,10 +43380,10 @@
         <v>3238</v>
       </c>
       <c r="C1630" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D1630" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1630" t="s" s="3">
         <v>3239</v>
@@ -43391,7 +43400,7 @@
         <v>733</v>
       </c>
       <c r="D1631" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1631" t="s" s="3">
         <v>3241</v>
@@ -43408,7 +43417,7 @@
         <v>733</v>
       </c>
       <c r="D1632" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1632" t="s" s="3">
         <v>3243</v>
@@ -43425,7 +43434,7 @@
         <v>733</v>
       </c>
       <c r="D1633" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1633" t="s" s="3">
         <v>3245</v>
@@ -43442,7 +43451,7 @@
         <v>733</v>
       </c>
       <c r="D1634" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1634" t="s" s="3">
         <v>3247</v>
@@ -43459,7 +43468,7 @@
         <v>733</v>
       </c>
       <c r="D1635" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1635" t="s" s="3">
         <v>3249</v>
@@ -43476,7 +43485,7 @@
         <v>733</v>
       </c>
       <c r="D1636" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1636" t="s" s="3">
         <v>3251</v>
@@ -43493,7 +43502,7 @@
         <v>733</v>
       </c>
       <c r="D1637" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1637" t="s" s="3">
         <v>3253</v>
@@ -43510,7 +43519,7 @@
         <v>733</v>
       </c>
       <c r="D1638" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1638" t="s" s="3">
         <v>3255</v>
@@ -43527,7 +43536,7 @@
         <v>733</v>
       </c>
       <c r="D1639" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1639" t="s" s="3">
         <v>3257</v>
@@ -43544,7 +43553,7 @@
         <v>733</v>
       </c>
       <c r="D1640" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1640" t="s" s="3">
         <v>3259</v>
@@ -43561,7 +43570,7 @@
         <v>733</v>
       </c>
       <c r="D1641" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1641" t="s" s="3">
         <v>3261</v>
@@ -43578,7 +43587,7 @@
         <v>733</v>
       </c>
       <c r="D1642" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1642" t="s" s="3">
         <v>3263</v>
@@ -43595,7 +43604,7 @@
         <v>733</v>
       </c>
       <c r="D1643" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1643" t="s" s="3">
         <v>3265</v>
@@ -43612,7 +43621,7 @@
         <v>733</v>
       </c>
       <c r="D1644" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1644" t="s" s="3">
         <v>3267</v>
@@ -43629,7 +43638,7 @@
         <v>733</v>
       </c>
       <c r="D1645" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1645" t="s" s="3">
         <v>3269</v>
@@ -43646,7 +43655,7 @@
         <v>733</v>
       </c>
       <c r="D1646" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1646" t="s" s="3">
         <v>3271</v>
@@ -43663,7 +43672,7 @@
         <v>733</v>
       </c>
       <c r="D1647" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1647" t="s" s="3">
         <v>3273</v>
@@ -43680,7 +43689,7 @@
         <v>733</v>
       </c>
       <c r="D1648" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1648" t="s" s="3">
         <v>3275</v>
@@ -43697,7 +43706,7 @@
         <v>733</v>
       </c>
       <c r="D1649" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1649" t="s" s="3">
         <v>3277</v>
@@ -43714,7 +43723,7 @@
         <v>733</v>
       </c>
       <c r="D1650" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1650" t="s" s="3">
         <v>3279</v>
@@ -43731,7 +43740,7 @@
         <v>733</v>
       </c>
       <c r="D1651" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1651" t="s" s="3">
         <v>3281</v>
@@ -43748,7 +43757,7 @@
         <v>733</v>
       </c>
       <c r="D1652" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1652" t="s" s="3">
         <v>3283</v>
@@ -43765,7 +43774,7 @@
         <v>733</v>
       </c>
       <c r="D1653" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1653" t="s" s="3">
         <v>3285</v>
@@ -43782,7 +43791,7 @@
         <v>733</v>
       </c>
       <c r="D1654" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1654" t="s" s="3">
         <v>3287</v>
@@ -43793,16 +43802,16 @@
         <v>1654.0</v>
       </c>
       <c r="B1655" t="s" s="3">
+        <v>2377</v>
+      </c>
+      <c r="C1655" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="D1655" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1655" t="s" s="3">
         <v>3288</v>
-      </c>
-      <c r="C1655" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="D1655" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1655" t="s" s="3">
-        <v>3289</v>
       </c>
     </row>
     <row r="1656" ht="36.0" customHeight="true">
@@ -43810,13 +43819,13 @@
         <v>1655.0</v>
       </c>
       <c r="B1656" t="s" s="3">
-        <v>2379</v>
+        <v>3289</v>
       </c>
       <c r="C1656" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D1656" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1656" t="s" s="3">
         <v>3290</v>
@@ -43833,10 +43842,10 @@
         <v>733</v>
       </c>
       <c r="D1657" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1657" t="s" s="3">
-        <v>3292</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="1658" ht="36.0" customHeight="true">
@@ -43844,16 +43853,16 @@
         <v>1657.0</v>
       </c>
       <c r="B1658" t="s" s="3">
+        <v>3292</v>
+      </c>
+      <c r="C1658" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="D1658" t="s" s="2">
+        <v>2235</v>
+      </c>
+      <c r="E1658" t="s" s="3">
         <v>3293</v>
-      </c>
-      <c r="C1658" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="D1658" t="s" s="2">
-        <v>2237</v>
-      </c>
-      <c r="E1658" t="s" s="3">
-        <v>2495</v>
       </c>
     </row>
     <row r="1659" ht="36.0" customHeight="true">
@@ -43867,7 +43876,7 @@
         <v>733</v>
       </c>
       <c r="D1659" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1659" t="s" s="3">
         <v>3295</v>
@@ -43884,7 +43893,7 @@
         <v>733</v>
       </c>
       <c r="D1660" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1660" t="s" s="3">
         <v>3297</v>
@@ -43901,7 +43910,7 @@
         <v>733</v>
       </c>
       <c r="D1661" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1661" t="s" s="3">
         <v>3299</v>
@@ -43918,7 +43927,7 @@
         <v>733</v>
       </c>
       <c r="D1662" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1662" t="s" s="3">
         <v>3301</v>
@@ -43935,7 +43944,7 @@
         <v>733</v>
       </c>
       <c r="D1663" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1663" t="s" s="3">
         <v>3303</v>
@@ -43952,7 +43961,7 @@
         <v>733</v>
       </c>
       <c r="D1664" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1664" t="s" s="3">
         <v>3305</v>
@@ -43969,7 +43978,7 @@
         <v>733</v>
       </c>
       <c r="D1665" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1665" t="s" s="3">
         <v>3307</v>
@@ -43986,7 +43995,7 @@
         <v>733</v>
       </c>
       <c r="D1666" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1666" t="s" s="3">
         <v>3309</v>
@@ -44003,7 +44012,7 @@
         <v>733</v>
       </c>
       <c r="D1667" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1667" t="s" s="3">
         <v>3311</v>
@@ -44020,7 +44029,7 @@
         <v>733</v>
       </c>
       <c r="D1668" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1668" t="s" s="3">
         <v>3313</v>
@@ -44037,7 +44046,7 @@
         <v>733</v>
       </c>
       <c r="D1669" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1669" t="s" s="3">
         <v>3315</v>
@@ -44054,7 +44063,7 @@
         <v>733</v>
       </c>
       <c r="D1670" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1670" t="s" s="3">
         <v>3317</v>
@@ -44071,7 +44080,7 @@
         <v>733</v>
       </c>
       <c r="D1671" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1671" t="s" s="3">
         <v>3319</v>
@@ -44088,7 +44097,7 @@
         <v>733</v>
       </c>
       <c r="D1672" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1672" t="s" s="3">
         <v>3321</v>
@@ -44105,7 +44114,7 @@
         <v>733</v>
       </c>
       <c r="D1673" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1673" t="s" s="3">
         <v>3323</v>
@@ -44122,7 +44131,7 @@
         <v>733</v>
       </c>
       <c r="D1674" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1674" t="s" s="3">
         <v>3325</v>
@@ -44139,7 +44148,7 @@
         <v>733</v>
       </c>
       <c r="D1675" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1675" t="s" s="3">
         <v>3327</v>
@@ -44156,7 +44165,7 @@
         <v>733</v>
       </c>
       <c r="D1676" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1676" t="s" s="3">
         <v>3329</v>
@@ -44167,16 +44176,16 @@
         <v>1676.0</v>
       </c>
       <c r="B1677" t="s" s="3">
-        <v>3330</v>
+        <v>2480</v>
       </c>
       <c r="C1677" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D1677" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1677" t="s" s="3">
-        <v>3331</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="1678" ht="36.0" customHeight="true">
@@ -44184,16 +44193,16 @@
         <v>1677.0</v>
       </c>
       <c r="B1678" t="s" s="3">
-        <v>2482</v>
+        <v>3330</v>
       </c>
       <c r="C1678" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D1678" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1678" t="s" s="3">
-        <v>2483</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="1679" ht="36.0" customHeight="true">
@@ -44207,7 +44216,7 @@
         <v>733</v>
       </c>
       <c r="D1679" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1679" t="s" s="3">
         <v>3333</v>
@@ -44224,7 +44233,7 @@
         <v>733</v>
       </c>
       <c r="D1680" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1680" t="s" s="3">
         <v>3335</v>
@@ -44241,7 +44250,7 @@
         <v>733</v>
       </c>
       <c r="D1681" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1681" t="s" s="3">
         <v>3337</v>
@@ -44258,7 +44267,7 @@
         <v>733</v>
       </c>
       <c r="D1682" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1682" t="s" s="3">
         <v>3339</v>
@@ -44275,7 +44284,7 @@
         <v>733</v>
       </c>
       <c r="D1683" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1683" t="s" s="3">
         <v>3341</v>
@@ -44292,7 +44301,7 @@
         <v>733</v>
       </c>
       <c r="D1684" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1684" t="s" s="3">
         <v>3343</v>
@@ -44309,7 +44318,7 @@
         <v>733</v>
       </c>
       <c r="D1685" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1685" t="s" s="3">
         <v>3345</v>
@@ -44326,7 +44335,7 @@
         <v>733</v>
       </c>
       <c r="D1686" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1686" t="s" s="3">
         <v>3347</v>
@@ -44343,7 +44352,7 @@
         <v>733</v>
       </c>
       <c r="D1687" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1687" t="s" s="3">
         <v>3349</v>
@@ -44360,7 +44369,7 @@
         <v>733</v>
       </c>
       <c r="D1688" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1688" t="s" s="3">
         <v>3351</v>
@@ -44377,7 +44386,7 @@
         <v>733</v>
       </c>
       <c r="D1689" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1689" t="s" s="3">
         <v>3353</v>
@@ -44394,7 +44403,7 @@
         <v>733</v>
       </c>
       <c r="D1690" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1690" t="s" s="3">
         <v>3355</v>
@@ -44411,7 +44420,7 @@
         <v>733</v>
       </c>
       <c r="D1691" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1691" t="s" s="3">
         <v>3357</v>
@@ -44428,7 +44437,7 @@
         <v>733</v>
       </c>
       <c r="D1692" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1692" t="s" s="3">
         <v>3359</v>
@@ -44445,7 +44454,7 @@
         <v>733</v>
       </c>
       <c r="D1693" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1693" t="s" s="3">
         <v>3361</v>
@@ -44462,7 +44471,7 @@
         <v>733</v>
       </c>
       <c r="D1694" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1694" t="s" s="3">
         <v>3363</v>
@@ -44479,7 +44488,7 @@
         <v>733</v>
       </c>
       <c r="D1695" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1695" t="s" s="3">
         <v>3365</v>
@@ -44496,7 +44505,7 @@
         <v>733</v>
       </c>
       <c r="D1696" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1696" t="s" s="3">
         <v>3367</v>
@@ -44513,7 +44522,7 @@
         <v>733</v>
       </c>
       <c r="D1697" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1697" t="s" s="3">
         <v>3369</v>
@@ -44530,7 +44539,7 @@
         <v>733</v>
       </c>
       <c r="D1698" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1698" t="s" s="3">
         <v>3371</v>
@@ -44547,7 +44556,7 @@
         <v>733</v>
       </c>
       <c r="D1699" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1699" t="s" s="3">
         <v>3373</v>
@@ -44564,7 +44573,7 @@
         <v>733</v>
       </c>
       <c r="D1700" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1700" t="s" s="3">
         <v>3375</v>
@@ -44581,7 +44590,7 @@
         <v>733</v>
       </c>
       <c r="D1701" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1701" t="s" s="3">
         <v>3377</v>
@@ -44598,7 +44607,7 @@
         <v>733</v>
       </c>
       <c r="D1702" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1702" t="s" s="3">
         <v>3379</v>
@@ -44615,7 +44624,7 @@
         <v>733</v>
       </c>
       <c r="D1703" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1703" t="s" s="3">
         <v>3381</v>
@@ -44632,7 +44641,7 @@
         <v>733</v>
       </c>
       <c r="D1704" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1704" t="s" s="3">
         <v>3383</v>
@@ -44649,7 +44658,7 @@
         <v>733</v>
       </c>
       <c r="D1705" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1705" t="s" s="3">
         <v>3385</v>
@@ -44666,7 +44675,7 @@
         <v>733</v>
       </c>
       <c r="D1706" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1706" t="s" s="3">
         <v>3387</v>
@@ -44683,7 +44692,7 @@
         <v>733</v>
       </c>
       <c r="D1707" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1707" t="s" s="3">
         <v>3389</v>
@@ -44700,7 +44709,7 @@
         <v>733</v>
       </c>
       <c r="D1708" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1708" t="s" s="3">
         <v>3391</v>
@@ -44717,7 +44726,7 @@
         <v>733</v>
       </c>
       <c r="D1709" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1709" t="s" s="3">
         <v>3393</v>
@@ -44734,7 +44743,7 @@
         <v>733</v>
       </c>
       <c r="D1710" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1710" t="s" s="3">
         <v>3395</v>
@@ -44751,7 +44760,7 @@
         <v>733</v>
       </c>
       <c r="D1711" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1711" t="s" s="3">
         <v>3397</v>
@@ -44768,7 +44777,7 @@
         <v>733</v>
       </c>
       <c r="D1712" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1712" t="s" s="3">
         <v>3399</v>
@@ -44785,7 +44794,7 @@
         <v>733</v>
       </c>
       <c r="D1713" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1713" t="s" s="3">
         <v>3401</v>
@@ -44802,7 +44811,7 @@
         <v>733</v>
       </c>
       <c r="D1714" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1714" t="s" s="3">
         <v>3403</v>
@@ -44819,7 +44828,7 @@
         <v>733</v>
       </c>
       <c r="D1715" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1715" t="s" s="3">
         <v>3405</v>
@@ -44836,7 +44845,7 @@
         <v>733</v>
       </c>
       <c r="D1716" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1716" t="s" s="3">
         <v>3407</v>
@@ -44853,7 +44862,7 @@
         <v>733</v>
       </c>
       <c r="D1717" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1717" t="s" s="3">
         <v>3409</v>
@@ -44870,7 +44879,7 @@
         <v>733</v>
       </c>
       <c r="D1718" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1718" t="s" s="3">
         <v>3411</v>
@@ -44887,7 +44896,7 @@
         <v>733</v>
       </c>
       <c r="D1719" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1719" t="s" s="3">
         <v>3413</v>
@@ -44904,7 +44913,7 @@
         <v>733</v>
       </c>
       <c r="D1720" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1720" t="s" s="3">
         <v>3415</v>
@@ -44921,7 +44930,7 @@
         <v>733</v>
       </c>
       <c r="D1721" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1721" t="s" s="3">
         <v>3417</v>
@@ -44938,7 +44947,7 @@
         <v>733</v>
       </c>
       <c r="D1722" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1722" t="s" s="3">
         <v>3419</v>
@@ -44955,7 +44964,7 @@
         <v>733</v>
       </c>
       <c r="D1723" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1723" t="s" s="3">
         <v>3421</v>
@@ -44972,7 +44981,7 @@
         <v>733</v>
       </c>
       <c r="D1724" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1724" t="s" s="3">
         <v>3423</v>
@@ -44989,7 +44998,7 @@
         <v>733</v>
       </c>
       <c r="D1725" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1725" t="s" s="3">
         <v>3425</v>
@@ -45006,7 +45015,7 @@
         <v>733</v>
       </c>
       <c r="D1726" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1726" t="s" s="3">
         <v>3427</v>
@@ -45023,7 +45032,7 @@
         <v>733</v>
       </c>
       <c r="D1727" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1727" t="s" s="3">
         <v>3429</v>
@@ -45040,7 +45049,7 @@
         <v>733</v>
       </c>
       <c r="D1728" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1728" t="s" s="3">
         <v>3431</v>
@@ -45057,7 +45066,7 @@
         <v>733</v>
       </c>
       <c r="D1729" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1729" t="s" s="3">
         <v>3433</v>
@@ -45074,7 +45083,7 @@
         <v>733</v>
       </c>
       <c r="D1730" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1730" t="s" s="3">
         <v>3435</v>
@@ -45091,7 +45100,7 @@
         <v>733</v>
       </c>
       <c r="D1731" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1731" t="s" s="3">
         <v>3437</v>
@@ -45108,7 +45117,7 @@
         <v>733</v>
       </c>
       <c r="D1732" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1732" t="s" s="3">
         <v>3439</v>
@@ -45125,7 +45134,7 @@
         <v>733</v>
       </c>
       <c r="D1733" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1733" t="s" s="3">
         <v>3441</v>
@@ -45142,7 +45151,7 @@
         <v>733</v>
       </c>
       <c r="D1734" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1734" t="s" s="3">
         <v>3443</v>
@@ -45159,7 +45168,7 @@
         <v>733</v>
       </c>
       <c r="D1735" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1735" t="s" s="3">
         <v>3445</v>
@@ -45176,7 +45185,7 @@
         <v>733</v>
       </c>
       <c r="D1736" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1736" t="s" s="3">
         <v>3447</v>
@@ -45193,7 +45202,7 @@
         <v>733</v>
       </c>
       <c r="D1737" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1737" t="s" s="3">
         <v>3449</v>
@@ -45210,7 +45219,7 @@
         <v>733</v>
       </c>
       <c r="D1738" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1738" t="s" s="3">
         <v>3451</v>
@@ -45227,7 +45236,7 @@
         <v>733</v>
       </c>
       <c r="D1739" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1739" t="s" s="3">
         <v>3453</v>
@@ -45244,7 +45253,7 @@
         <v>733</v>
       </c>
       <c r="D1740" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1740" t="s" s="3">
         <v>3455</v>
@@ -45261,7 +45270,7 @@
         <v>733</v>
       </c>
       <c r="D1741" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1741" t="s" s="3">
         <v>3457</v>
@@ -45278,7 +45287,7 @@
         <v>733</v>
       </c>
       <c r="D1742" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1742" t="s" s="3">
         <v>3459</v>
@@ -45295,7 +45304,7 @@
         <v>733</v>
       </c>
       <c r="D1743" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1743" t="s" s="3">
         <v>3461</v>
@@ -45312,7 +45321,7 @@
         <v>733</v>
       </c>
       <c r="D1744" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1744" t="s" s="3">
         <v>3463</v>
@@ -45329,7 +45338,7 @@
         <v>733</v>
       </c>
       <c r="D1745" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1745" t="s" s="3">
         <v>3465</v>
@@ -45346,7 +45355,7 @@
         <v>733</v>
       </c>
       <c r="D1746" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1746" t="s" s="3">
         <v>3467</v>
@@ -45363,7 +45372,7 @@
         <v>733</v>
       </c>
       <c r="D1747" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1747" t="s" s="3">
         <v>3469</v>
@@ -45380,7 +45389,7 @@
         <v>733</v>
       </c>
       <c r="D1748" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1748" t="s" s="3">
         <v>3471</v>
@@ -45397,7 +45406,7 @@
         <v>733</v>
       </c>
       <c r="D1749" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1749" t="s" s="3">
         <v>3473</v>
@@ -45414,7 +45423,7 @@
         <v>733</v>
       </c>
       <c r="D1750" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1750" t="s" s="3">
         <v>3475</v>
@@ -45431,7 +45440,7 @@
         <v>733</v>
       </c>
       <c r="D1751" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1751" t="s" s="3">
         <v>3477</v>
@@ -45448,7 +45457,7 @@
         <v>733</v>
       </c>
       <c r="D1752" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1752" t="s" s="3">
         <v>3479</v>
@@ -45465,7 +45474,7 @@
         <v>733</v>
       </c>
       <c r="D1753" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1753" t="s" s="3">
         <v>3481</v>
@@ -45482,7 +45491,7 @@
         <v>733</v>
       </c>
       <c r="D1754" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1754" t="s" s="3">
         <v>3483</v>
@@ -45499,7 +45508,7 @@
         <v>733</v>
       </c>
       <c r="D1755" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1755" t="s" s="3">
         <v>3485</v>
@@ -45516,7 +45525,7 @@
         <v>733</v>
       </c>
       <c r="D1756" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1756" t="s" s="3">
         <v>3487</v>
@@ -45533,7 +45542,7 @@
         <v>733</v>
       </c>
       <c r="D1757" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1757" t="s" s="3">
         <v>3489</v>
@@ -45550,7 +45559,7 @@
         <v>733</v>
       </c>
       <c r="D1758" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1758" t="s" s="3">
         <v>3491</v>
@@ -45567,7 +45576,7 @@
         <v>733</v>
       </c>
       <c r="D1759" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1759" t="s" s="3">
         <v>3493</v>
@@ -45584,7 +45593,7 @@
         <v>733</v>
       </c>
       <c r="D1760" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1760" t="s" s="3">
         <v>3495</v>
@@ -45601,7 +45610,7 @@
         <v>733</v>
       </c>
       <c r="D1761" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1761" t="s" s="3">
         <v>3497</v>
@@ -45618,7 +45627,7 @@
         <v>733</v>
       </c>
       <c r="D1762" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1762" t="s" s="3">
         <v>3499</v>
@@ -45635,7 +45644,7 @@
         <v>733</v>
       </c>
       <c r="D1763" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1763" t="s" s="3">
         <v>3501</v>
@@ -45652,7 +45661,7 @@
         <v>733</v>
       </c>
       <c r="D1764" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1764" t="s" s="3">
         <v>3503</v>
@@ -45669,7 +45678,7 @@
         <v>733</v>
       </c>
       <c r="D1765" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1765" t="s" s="3">
         <v>3505</v>
@@ -45686,7 +45695,7 @@
         <v>733</v>
       </c>
       <c r="D1766" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1766" t="s" s="3">
         <v>3507</v>
@@ -45703,7 +45712,7 @@
         <v>733</v>
       </c>
       <c r="D1767" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1767" t="s" s="3">
         <v>3509</v>
@@ -45720,7 +45729,7 @@
         <v>733</v>
       </c>
       <c r="D1768" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1768" t="s" s="3">
         <v>3511</v>
@@ -45737,7 +45746,7 @@
         <v>733</v>
       </c>
       <c r="D1769" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1769" t="s" s="3">
         <v>3513</v>
@@ -45754,7 +45763,7 @@
         <v>733</v>
       </c>
       <c r="D1770" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1770" t="s" s="3">
         <v>3515</v>
@@ -45771,7 +45780,7 @@
         <v>733</v>
       </c>
       <c r="D1771" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1771" t="s" s="3">
         <v>3517</v>
@@ -45788,7 +45797,7 @@
         <v>733</v>
       </c>
       <c r="D1772" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1772" t="s" s="3">
         <v>3519</v>
@@ -45805,7 +45814,7 @@
         <v>733</v>
       </c>
       <c r="D1773" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1773" t="s" s="3">
         <v>3521</v>
@@ -45822,7 +45831,7 @@
         <v>733</v>
       </c>
       <c r="D1774" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1774" t="s" s="3">
         <v>3523</v>
@@ -45839,7 +45848,7 @@
         <v>733</v>
       </c>
       <c r="D1775" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1775" t="s" s="3">
         <v>3525</v>
@@ -45856,7 +45865,7 @@
         <v>733</v>
       </c>
       <c r="D1776" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1776" t="s" s="3">
         <v>3527</v>
@@ -45873,7 +45882,7 @@
         <v>733</v>
       </c>
       <c r="D1777" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1777" t="s" s="3">
         <v>3529</v>
@@ -45890,7 +45899,7 @@
         <v>733</v>
       </c>
       <c r="D1778" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1778" t="s" s="3">
         <v>3531</v>
@@ -45907,7 +45916,7 @@
         <v>733</v>
       </c>
       <c r="D1779" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1779" t="s" s="3">
         <v>3533</v>
@@ -45924,7 +45933,7 @@
         <v>733</v>
       </c>
       <c r="D1780" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1780" t="s" s="3">
         <v>3535</v>
@@ -45941,7 +45950,7 @@
         <v>733</v>
       </c>
       <c r="D1781" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1781" t="s" s="3">
         <v>3537</v>
@@ -45958,7 +45967,7 @@
         <v>733</v>
       </c>
       <c r="D1782" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1782" t="s" s="3">
         <v>3539</v>
@@ -45975,7 +45984,7 @@
         <v>733</v>
       </c>
       <c r="D1783" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1783" t="s" s="3">
         <v>3541</v>
@@ -45992,7 +46001,7 @@
         <v>733</v>
       </c>
       <c r="D1784" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1784" t="s" s="3">
         <v>3543</v>
@@ -46009,7 +46018,7 @@
         <v>733</v>
       </c>
       <c r="D1785" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1785" t="s" s="3">
         <v>3545</v>
@@ -46026,7 +46035,7 @@
         <v>733</v>
       </c>
       <c r="D1786" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1786" t="s" s="3">
         <v>3547</v>
@@ -46043,7 +46052,7 @@
         <v>733</v>
       </c>
       <c r="D1787" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1787" t="s" s="3">
         <v>3549</v>
@@ -46060,7 +46069,7 @@
         <v>733</v>
       </c>
       <c r="D1788" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1788" t="s" s="3">
         <v>3551</v>
@@ -46077,7 +46086,7 @@
         <v>733</v>
       </c>
       <c r="D1789" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1789" t="s" s="3">
         <v>3553</v>
@@ -46094,7 +46103,7 @@
         <v>733</v>
       </c>
       <c r="D1790" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1790" t="s" s="3">
         <v>3555</v>
@@ -46111,7 +46120,7 @@
         <v>733</v>
       </c>
       <c r="D1791" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1791" t="s" s="3">
         <v>3557</v>
@@ -46128,7 +46137,7 @@
         <v>733</v>
       </c>
       <c r="D1792" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1792" t="s" s="3">
         <v>3559</v>
@@ -46145,7 +46154,7 @@
         <v>733</v>
       </c>
       <c r="D1793" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1793" t="s" s="3">
         <v>3561</v>
@@ -46162,7 +46171,7 @@
         <v>733</v>
       </c>
       <c r="D1794" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1794" t="s" s="3">
         <v>3563</v>
@@ -46179,7 +46188,7 @@
         <v>733</v>
       </c>
       <c r="D1795" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1795" t="s" s="3">
         <v>3565</v>
@@ -46196,7 +46205,7 @@
         <v>733</v>
       </c>
       <c r="D1796" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1796" t="s" s="3">
         <v>3567</v>
@@ -46213,7 +46222,7 @@
         <v>733</v>
       </c>
       <c r="D1797" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1797" t="s" s="3">
         <v>3569</v>
@@ -46230,7 +46239,7 @@
         <v>733</v>
       </c>
       <c r="D1798" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1798" t="s" s="3">
         <v>3571</v>
@@ -46247,7 +46256,7 @@
         <v>733</v>
       </c>
       <c r="D1799" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1799" t="s" s="3">
         <v>3573</v>
@@ -46264,7 +46273,7 @@
         <v>733</v>
       </c>
       <c r="D1800" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1800" t="s" s="3">
         <v>3575</v>
@@ -46281,7 +46290,7 @@
         <v>733</v>
       </c>
       <c r="D1801" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1801" t="s" s="3">
         <v>3577</v>
@@ -46298,10 +46307,10 @@
         <v>733</v>
       </c>
       <c r="D1802" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1802" t="s" s="3">
-        <v>3405</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="1803" ht="36.0" customHeight="true">
@@ -46315,7 +46324,7 @@
         <v>733</v>
       </c>
       <c r="D1803" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1803" t="s" s="3">
         <v>3580</v>
@@ -46326,16 +46335,16 @@
         <v>1803.0</v>
       </c>
       <c r="B1804" t="s" s="3">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="C1804" t="s" s="2">
         <v>733</v>
       </c>
       <c r="D1804" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1804" t="s" s="3">
-        <v>3191</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="1805" ht="36.0" customHeight="true">
@@ -46349,7 +46358,7 @@
         <v>733</v>
       </c>
       <c r="D1805" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1805" t="s" s="3">
         <v>3582</v>
@@ -46366,7 +46375,7 @@
         <v>733</v>
       </c>
       <c r="D1806" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1806" t="s" s="3">
         <v>3584</v>
@@ -46383,7 +46392,7 @@
         <v>733</v>
       </c>
       <c r="D1807" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1807" t="s" s="3">
         <v>3586</v>
@@ -46400,7 +46409,7 @@
         <v>733</v>
       </c>
       <c r="D1808" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1808" t="s" s="3">
         <v>3588</v>
@@ -46417,7 +46426,7 @@
         <v>733</v>
       </c>
       <c r="D1809" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1809" t="s" s="3">
         <v>3590</v>
@@ -46434,7 +46443,7 @@
         <v>733</v>
       </c>
       <c r="D1810" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1810" t="s" s="3">
         <v>3592</v>
@@ -46451,7 +46460,7 @@
         <v>733</v>
       </c>
       <c r="D1811" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1811" t="s" s="3">
         <v>3594</v>
@@ -46468,7 +46477,7 @@
         <v>733</v>
       </c>
       <c r="D1812" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1812" t="s" s="3">
         <v>3596</v>
@@ -46485,7 +46494,7 @@
         <v>733</v>
       </c>
       <c r="D1813" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1813" t="s" s="3">
         <v>3598</v>
@@ -46502,7 +46511,7 @@
         <v>733</v>
       </c>
       <c r="D1814" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1814" t="s" s="3">
         <v>3600</v>
@@ -46519,7 +46528,7 @@
         <v>733</v>
       </c>
       <c r="D1815" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1815" t="s" s="3">
         <v>3602</v>
@@ -46536,7 +46545,7 @@
         <v>733</v>
       </c>
       <c r="D1816" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1816" t="s" s="3">
         <v>3604</v>
@@ -46553,7 +46562,7 @@
         <v>733</v>
       </c>
       <c r="D1817" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1817" t="s" s="3">
         <v>3606</v>
@@ -46570,7 +46579,7 @@
         <v>938</v>
       </c>
       <c r="D1818" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1818" t="s" s="3">
         <v>3608</v>
@@ -46587,7 +46596,7 @@
         <v>938</v>
       </c>
       <c r="D1819" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1819" t="s" s="3">
         <v>3610</v>
@@ -46604,7 +46613,7 @@
         <v>938</v>
       </c>
       <c r="D1820" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1820" t="s" s="3">
         <v>3612</v>
@@ -46621,7 +46630,7 @@
         <v>938</v>
       </c>
       <c r="D1821" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1821" t="s" s="3">
         <v>3614</v>
@@ -46638,7 +46647,7 @@
         <v>938</v>
       </c>
       <c r="D1822" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1822" t="s" s="3">
         <v>3616</v>
@@ -46655,7 +46664,7 @@
         <v>938</v>
       </c>
       <c r="D1823" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1823" t="s" s="3">
         <v>3618</v>
@@ -46672,7 +46681,7 @@
         <v>938</v>
       </c>
       <c r="D1824" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1824" t="s" s="3">
         <v>3620</v>
@@ -46689,7 +46698,7 @@
         <v>938</v>
       </c>
       <c r="D1825" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1825" t="s" s="3">
         <v>3622</v>
@@ -46700,16 +46709,16 @@
         <v>1825.0</v>
       </c>
       <c r="B1826" t="s" s="3">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="C1826" t="s" s="2">
         <v>938</v>
       </c>
       <c r="D1826" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1826" t="s" s="3">
-        <v>2888</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="1827" ht="36.0" customHeight="true">
@@ -46723,7 +46732,7 @@
         <v>938</v>
       </c>
       <c r="D1827" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1827" t="s" s="3">
         <v>3624</v>
@@ -46740,7 +46749,7 @@
         <v>938</v>
       </c>
       <c r="D1828" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1828" t="s" s="3">
         <v>3626</v>
@@ -46757,7 +46766,7 @@
         <v>938</v>
       </c>
       <c r="D1829" t="s" s="2">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E1829" t="s" s="3">
         <v>3628</v>
@@ -48607,7 +48616,7 @@
         <v>3847</v>
       </c>
       <c r="C1938" t="s" s="2">
-        <v>6</v>
+        <v>733</v>
       </c>
       <c r="D1938" t="s" s="2">
         <v>3739</v>
@@ -48927,7 +48936,7 @@
         <v>1956.0</v>
       </c>
       <c r="B1957" t="s" s="3">
-        <v>3825</v>
+        <v>3823</v>
       </c>
       <c r="C1957" t="s" s="2">
         <v>733</v>
@@ -48936,7 +48945,7 @@
         <v>3739</v>
       </c>
       <c r="E1957" t="s" s="3">
-        <v>3826</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="1958" ht="36.0" customHeight="true">
@@ -57223,7 +57232,7 @@
         <v>2444.0</v>
       </c>
       <c r="B2445" t="s" s="3">
-        <v>3873</v>
+        <v>3871</v>
       </c>
       <c r="C2445" t="s" s="2">
         <v>6</v>
@@ -58056,7 +58065,7 @@
         <v>2493.0</v>
       </c>
       <c r="B2494" t="s" s="3">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="C2494" t="s" s="2">
         <v>6</v>
@@ -60089,6 +60098,23 @@
       </c>
       <c r="E2613" t="s" s="3">
         <v>5185</v>
+      </c>
+    </row>
+    <row r="2614" ht="36.0" customHeight="true">
+      <c r="A2614" t="n" s="2">
+        <v>2613.0</v>
+      </c>
+      <c r="B2614" t="s" s="3">
+        <v>5186</v>
+      </c>
+      <c r="C2614" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="D2614" t="s" s="2">
+        <v>5187</v>
+      </c>
+      <c r="E2614" t="s" s="3">
+        <v>5188</v>
       </c>
     </row>
   </sheetData>
